--- a/26년도_2주간_식단.xlsx
+++ b/26년도_2주간_식단.xlsx
@@ -6,51 +6,53 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="500" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8월2주차_합산식단" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="장보기_8월2주차" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8월1주차_합산식단" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="장보기_8월1주차" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7월4주차_합산식단" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="장보기_7월4주차" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7월3주차_합산식단" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="장보기_7월3주차" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7월2주차_합산식단" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="장보기_7월2주차" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7월1주차_합산식단" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="장보기_7월1주차" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6월4주차_합산식단" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="장보기_6월4주차" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6월3주차_합산식단" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="장보기_6월3주차" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6월2주차_합산식단" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="장보기_6월2주차" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6월1주차_합산식단" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="장보기_6월1주차" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5월4주차_합산식단" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="장보기_5월4주차" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5월3주차_합산식단" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="장보기_5월3주차" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5월2주차_합산식단" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="장보기_5월2주차" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5월1주차_합산식단" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="장보기_5월1주차" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4월4주차_합산식단" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="장보기_4월4주차" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4월3주차_합산식단" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="장보기_4월3주차" sheetId="32" state="visible" r:id="rId32"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4월2주차_합산식단" sheetId="33" state="visible" r:id="rId33"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="장보기_4월2주차" sheetId="34" state="visible" r:id="rId34"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3월5주차_4월1주차_합산식단" sheetId="35" state="visible" r:id="rId35"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="장보기_3월5주차_4월1주차" sheetId="36" state="visible" r:id="rId36"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3월3주차_4주차_합산식단" sheetId="37" state="visible" r:id="rId37"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="장보기_3월3주차_4주차" sheetId="38" state="visible" r:id="rId38"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8월3주차_합산식단" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="장보기_8월3주차" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8월2주차_합산식단" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="장보기_8월2주차" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8월1주차_합산식단" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="장보기_8월1주차" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7월4주차_합산식단" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="장보기_7월4주차" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7월3주차_합산식단" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="장보기_7월3주차" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7월2주차_합산식단" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="장보기_7월2주차" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7월1주차_합산식단" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="장보기_7월1주차" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6월4주차_합산식단" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="장보기_6월4주차" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6월3주차_합산식단" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="장보기_6월3주차" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6월2주차_합산식단" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="장보기_6월2주차" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6월1주차_합산식단" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="장보기_6월1주차" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5월4주차_합산식단" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="장보기_5월4주차" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5월3주차_합산식단" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="장보기_5월3주차" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5월2주차_합산식단" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="장보기_5월2주차" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5월1주차_합산식단" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="장보기_5월1주차" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4월4주차_합산식단" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="장보기_4월4주차" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4월3주차_합산식단" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="장보기_4월3주차" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4월2주차_합산식단" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="장보기_4월2주차" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3월5주차_4월1주차_합산식단" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="장보기_3월5주차_4월1주차" sheetId="38" state="visible" r:id="rId38"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3월3주차_4주차_합산식단" sheetId="39" state="visible" r:id="rId39"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="장보기_3월3주차_4주차" sheetId="40" state="visible" r:id="rId40"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Titles" localSheetId="34">'3월5주차_4월1주차_합산식단'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="34">'3월5주차_4월1주차_합산식단'!$A$1:$E$9</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="35">'장보기_3월5주차_4월1주차'!$A$1:$E$21</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="36">'3월3주차_4주차_합산식단'!$A$1:$E$9</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="37">'장보기_3월3주차_4주차'!$A$1:$E$35</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="36">'3월5주차_4월1주차_합산식단'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="36">'3월5주차_4월1주차_합산식단'!$A$1:$E$9</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="37">'장보기_3월5주차_4월1주차'!$A$1:$E$21</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="38">'3월3주차_4주차_합산식단'!$A$1:$E$9</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="39">'장보기_3월3주차_4주차'!$A$1:$E$35</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
 </workbook>
@@ -1319,140 +1321,156 @@
     <row r="2" ht="276" customHeight="1" s="90">
       <c r="A2" s="119" t="inlineStr">
         <is>
-          <t>화 (8/4)</t>
+          <t>화 (8/11)</t>
         </is>
       </c>
       <c r="B2" s="120" t="inlineStr">
         <is>
-          <t>순살 가자미 데리야끼 구이
-+ 맑은 배추국
-+ 크래미 오이무침
-+ 제철과일 (간식)</t>
+          <t>소고기 찹스테이크
++ 콩나물국
++ 매쉬포테이토
++ 키즈김치
++ 수박 (간식)</t>
         </is>
       </c>
       <c r="C2" s="120" t="inlineStr">
         <is>
-          <t>[순살 가자미 데리야끼 구이]
-1. 순살 가자미 4~5쪽 → 냉장실에서
-   천천히 해동, 키친타월로 물기 완전 제거
-2. 소금 살짝 + 미림(청주) 발라 10분
-   → 다시 물기 제거 (비린내 제거)
-3. 데리야끼: 간장 3T + 미림 1.5T
-   + 설탕 1T + 물 2T → 섞어 냉장
-   (당일 밀가루/전분 얇게 입힘)
-[맑은 배추국]
-4. 알배추 3~4잎 채썰기 / 두부 약간 / 대파 → 냉장
-5. 물 1L + 멸치·다시마육수</t>
+          <t>[소고기 찹스테이크]
+1. 부채살 600g 사방 3cm 큐브
+   밑간: 올리브유 1T+다진마늘 1T+소금·후추 냉장
+2. 파프리카 1개+양송이 8개+양파 1개
+   한입크기 냉장
+3. 소스: 스테이크소스 4T+케첩 2T+굴소스 1T
+   +다진마늘 1t+물 1T 냉장
+[콩나물국 — 감칠맛 만능육수]
+4. 콩나물 1봉 씻어 냉장 / 대파 어슷
+5. 육수재료: 물 1.2L+국물용멸치 15마리
+   (머리·내장 제거 → 마른팬 30초 볶기)
+   +다시마 1장+건새우 1줌+무 한토막
+[매쉬포테이토]
+6. 감자 3개 껍질 벗겨 큼직하게 물에 담가 냉장
+[키즈김치] 어린이김치 통 준비</t>
         </is>
       </c>
       <c r="D2" s="120" t="inlineStr">
         <is>
-          <t>★ 식사 20분 전 시작
-[맑은 배추국 — 먼저]
-1. 육수+배추 8분
-2. 국간장 1T+소금, 대파 마무리 (시원 담백)
-[크래미 오이무침]
-3. 오이 반달 + 크래미 찢기
-   → 식초 1T + 설탕 1t + 소금 살짝 무치기
-[순살 가자미 데리야끼 — 마지막]
-4. 가자미 물기 제거 후 밀가루 얇게
-5. 팬 충분히 예열+기름 → 껍질면부터 3~4분
-   딱 한 번만 뒤집어 3분 (안 부서지게)
-6. 데리야끼 부어 조려 글레이즈 코팅(윤기)
-   ※ 아이용은 살 발라 접시에 + 소스 살짝
-[제철과일] 씻어서</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="216" customHeight="1" s="90">
+          <t>★ 식사 30분 전
+[콩나물국 — 먼저]
+1. 육수재료 찬물부터 → 끓으면 다시마 건지고
+   중불 10분 → 체에 거르기 (진한 육수)
+2. 콩나물 넣고 뚜껑 덮어 5분 (중간에 안 열기)
+3. 간: 국간장 1.5T+소금+다진마늘
+   +멸치액젓 1t (감칠맛), 대파 마무리
+   ※ 싱거우면 무조건 간 더! (맹맹 방지)
+[매쉬포테이토]
+4. 감자 삶아 으깨 우유 3T+소금 부드럽게
+[찹스테이크 — 마지막]
+5. 고기 센불 겉면만 → 채소 1분
+   → 소스 부어 2분 졸이기
+[키즈김치] 접시에 / [수박] 잘라서</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="276" customHeight="1" s="90">
       <c r="A3" s="119" t="inlineStr">
         <is>
-          <t>수 (8/5)</t>
+          <t>수 (8/12)</t>
         </is>
       </c>
       <c r="B3" s="120" t="inlineStr">
         <is>
-          <t>돼지안심 청경채 굴소스볶음
-+ 두부 맑은국
-+ 김구이
-+ 가래떡구이 (간식)</t>
+          <t>돼지 앞다리살 데리야끼
++ 양지 미역국
++ 계란말이
++ 키즈김치
++ 참외 (간식)</t>
         </is>
       </c>
       <c r="C3" s="120" t="inlineStr">
         <is>
-          <t>[돼지안심 청경채 굴소스볶음]
-1. 돼지안심 500g → 0.7cm 썰어
-   밑간: 청주·소금·후추 + 전분 1t → 냉장
-2. 청경채 4~5포기 밑동 손질 / 양파 / 대파
-   / 마늘 → 냉장
-3. 소스: 굴소스 2T + 간장 1T + 설탕 1t
-   + 물 3T + 전분 1t → 섞어 냉장
-[두부 맑은국]
-4. 두부 1/2모 깍둑 / 무 약간 / 대파 → 냉장
-5. 물 1L + 육수</t>
+          <t>[돼지 앞다리살 데리야끼]
+1. 돼지 앞다리살 600g → 0.5cm 얇게 썰기
+   (앞다리살=안 질기고 좋음) 밑간 청주·후추 냉장
+2. 데리야끼: 간장 3T+미림 1.5T+설탕 1T
+   +물 2T+다진마늘 1t 냉장
+3. 양파 1개 채썰기 냉장
+[양지 미역국 — 기름 안 지게]
+4. 양지 250g 한입크기 → 끓는물에 살짝 데쳐
+   핏물·기름 빼기 → 냉장
+5. 염장미역 물에 불려 짜서 냉장
+6. 육수재료: 물 1.2L+멸치 15마리(볶기)
+   +다시마+건새우 준비
+[계란말이]
+7. 달걀 4개+당근·대파 조금 다져 풀어 냉장
+[키즈김치] 통 준비</t>
         </is>
       </c>
       <c r="D3" s="120" t="inlineStr">
         <is>
-          <t>★ 식사 20분 전 시작
-[두부 맑은국 — 먼저]
-1. 육수 끓여 국간장 1T+소금
-2. 두부 넣고 5분, 대파 마무리
-[돼지안심 청경채 굴소스볶음 — 마지막]
-3. 팬에 기름, 마늘+돼지 센불 볶기
-4. 양파 1분, 청경채 줄기 먼저 30초
-5. 소스 붓고 센불, 청경채 잎+대파
-   → 숨 죽으면 완성 (밝은 윤기)
-[김구이] 참기름 약불 구이
-[가래떡구이] 노릇 구워 꿀</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="291" customHeight="1" s="90">
+          <t>★ 식사 25분 전
+[양지 미역국 — 먼저]
+1. 냄비에 데친 양지+불린 미역 넣고
+   국간장 1T로 1분 볶기 (참기름 생략/최소=기름 안 지게)
+2. 만능육수(멸치·다시마·건새우) 붓고 중불 15분
+   → 뜨는 기름 걷어내기 (담백하게)
+3. 간: 국간장 1.5T+소금+다진마늘+액젓 1t
+   ※ 싱거우면 간 더!
+[계란말이] 약불에서 도톰하게 말아 썰기
+[돼지 앞다리살 데리야끼 — 마지막]
+4. 팬에 고기+양파 볶다 데리야끼 부어
+   조려서 윤기 (검게 X, 밝게)
+[키즈김치] 접시에 / [참외] 깎아서</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="276" customHeight="1" s="90">
       <c r="A4" s="119" t="inlineStr">
         <is>
-          <t>금 (8/7)</t>
+          <t>금 (8/14)</t>
         </is>
       </c>
       <c r="B4" s="120" t="inlineStr">
         <is>
-          <t>감바스 (마늘새우)
-+ 옥수수 스프
-+ 미니 주먹밥
-+ 과일 (간식)</t>
+          <t>오야코동
++ 맑은 무국
++ 애호박전
++ 키즈김치
++ 옥수수 (간식)</t>
         </is>
       </c>
       <c r="C4" s="120" t="inlineStr">
         <is>
-          <t>[감바스]
-1. 새우살 400g → 소금·후추 밑간 → 냉장
-2. 마늘 10~15쪽 편썰기 → 냉장
-   (페페론치노는 아이용이라 생략/아주 조금)
-3. 올리브오일·방울토마토·파슬리 준비
-[옥수수 스프]
-4. 스위트콘 1캔 / 양파 1/4 / 우유
-   / 버터 조금 준비 (당일 갈기)
-[미니 주먹밥]
-5. 밥 + 참기름 + 소금 + 김가루 (당일 뭉치기)</t>
+          <t>[오야코동]
+1. 닭다리살 400g 한입크기 밑간 청주·소금 냉장
+2. 양파 1개 채썰기 / 대파 / 달걀 5개 풀어 냉장
+3. 덮밥소스: 간장 3T+미림 2T+설탕 1T
+   +물 200ml (당일 멸치육수 조금 섞으면 감칠맛↑)
+[맑은 무국 — 감칠맛 만능육수]
+4. 무 1/4개 나박 / 대파
+5. 육수재료: 멸치 15마리(볶기)+다시마
+   +건새우+무 한토막
+[애호박전]
+6. 애호박 1개 동그랗게 썰어 소금 살짝
+   → 부침가루·계란옷 준비(당일)
+[키즈김치] 통 준비</t>
         </is>
       </c>
       <c r="D4" s="120" t="inlineStr">
         <is>
-          <t>★ 식사 20분 전 시작
-[옥수수 스프 — 먼저]
-1. 양파 버터에 살짝 볶다 콘+물 조금 끓이기
-2. 믹서에 곱게 갈기 → 냄비에 우유 넣고
-   소금·후추로 데우기 (부드럽게)
-[미니 주먹밥]
-3. 밥에 참기름·소금·김가루 섞어
-   한입 크기로 동글동글
-[감바스 — 마지막]
-4. 작은 팬에 올리브오일 넉넉 + 편마늘
-   약불로 향 내기 (마늘 안 태우게!)
-5. 새우 넣고 잠기듯 약~중불 3~4분
-6. 방울토마토·파슬리 마무리
-   → 주먹밥/빵에 오일 찍어먹기
-[과일] 접시에</t>
+          <t>★ 식사 20분 전
+[맑은 무국 — 먼저]
+1. 만능육수 우려 거르기 → 무 넣고 중불 8분
+   (무 투명해질 때까지)
+2. 간: 국간장 1.5T+소금+다진마늘+액젓 1t
+   대파 마무리 ※ 싱거우면 간 더!
+[애호박전]
+3. 애호박 물기 닦고 부침가루→계란옷
+   → 팬에 노릇하게 부치기
+[오야코동 — 마지막]
+4. 팬에 덮밥소스+양파 끓이다 닭 넣어 익히기
+5. 달걀 풀어 붓고 반숙으로 익히기
+   → 밥 위에 올리고 대파
+[키즈김치] 접시에 / [옥수수] 삶기</t>
         </is>
       </c>
     </row>
@@ -1468,8 +1486,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="25" customWidth="1" style="90" min="1" max="1"/>
     <col width="14" customWidth="1" style="90" min="2" max="2"/>
@@ -1478,661 +1496,396 @@
     <col width="14" customWidth="1" style="90" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25" customHeight="1" s="90">
-      <c r="A1" s="91" t="inlineStr">
-        <is>
-          <t>7월 2주차 장보기 (7/7~7/10)</t>
-        </is>
-      </c>
-      <c r="B1" s="92" t="n"/>
-      <c r="C1" s="92" t="n"/>
-      <c r="D1" s="92" t="n"/>
-      <c r="E1" s="93" t="n"/>
-    </row>
-    <row r="2" ht="18.5" customHeight="1" s="90">
-      <c r="A2" s="1" t="inlineStr">
+    <row r="1" ht="30" customHeight="1" s="90">
+      <c r="A1" s="89" t="inlineStr">
+        <is>
+          <t>7월 3주차 장보기 (7/14~7/15)</t>
+        </is>
+      </c>
+      <c r="B1" s="137" t="n"/>
+      <c r="C1" s="137" t="n"/>
+      <c r="D1" s="137" t="n"/>
+      <c r="E1" s="138" t="n"/>
+    </row>
+    <row r="2" ht="25" customHeight="1" s="90">
+      <c r="A2" s="78" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" s="78" t="inlineStr">
         <is>
           <t>수량</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C2" s="78" t="inlineStr">
         <is>
           <t>사용 메뉴</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="D2" s="78" t="inlineStr">
         <is>
           <t>구매 시기</t>
         </is>
       </c>
-      <c r="E2" s="1" t="inlineStr">
+      <c r="E2" s="78" t="inlineStr">
         <is>
           <t>예상 금액</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="18.5" customHeight="1" s="90">
-      <c r="A3" s="104" t="inlineStr">
+    <row r="3" ht="22" customHeight="1" s="90">
+      <c r="A3" s="81" t="inlineStr">
         <is>
           <t>정육</t>
         </is>
       </c>
-      <c r="B3" s="6" t="n"/>
-      <c r="C3" s="6" t="n"/>
-      <c r="D3" s="6" t="n"/>
-      <c r="E3" s="6" t="n"/>
-    </row>
-    <row r="4" ht="33" customHeight="1" s="90">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>닭다리살 (재고 3쪽 + 추가)</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>200g</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>카레소스구이</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>재고+추가</t>
-        </is>
-      </c>
-      <c r="E4" s="139" t="n">
+      <c r="B3" s="81" t="n"/>
+      <c r="C3" s="81" t="n"/>
+      <c r="D3" s="81" t="n"/>
+      <c r="E3" s="81" t="n"/>
+    </row>
+    <row r="4" ht="22" customHeight="1" s="90">
+      <c r="A4" s="80" t="inlineStr">
+        <is>
+          <t>돼지목살</t>
+        </is>
+      </c>
+      <c r="B4" s="79" t="inlineStr">
+        <is>
+          <t>800g</t>
+        </is>
+      </c>
+      <c r="C4" s="80" t="inlineStr">
+        <is>
+          <t>간장구이</t>
+        </is>
+      </c>
+      <c r="D4" s="79" t="inlineStr">
+        <is>
+          <t>첫째주</t>
+        </is>
+      </c>
+      <c r="E4" s="82" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1" s="90">
+      <c r="A5" s="80" t="inlineStr">
+        <is>
+          <t>닭다리살</t>
+        </is>
+      </c>
+      <c r="B5" s="79" t="inlineStr">
+        <is>
+          <t>800g</t>
+        </is>
+      </c>
+      <c r="C5" s="80" t="inlineStr">
+        <is>
+          <t>간장조림</t>
+        </is>
+      </c>
+      <c r="D5" s="79" t="inlineStr">
+        <is>
+          <t>첫째주</t>
+        </is>
+      </c>
+      <c r="E5" s="82" t="n">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1" s="90">
+      <c r="A6" s="80" t="inlineStr">
+        <is>
+          <t>차돌박이</t>
+        </is>
+      </c>
+      <c r="B6" s="79" t="inlineStr">
+        <is>
+          <t>250g</t>
+        </is>
+      </c>
+      <c r="C6" s="80" t="inlineStr">
+        <is>
+          <t>차돌미역국</t>
+        </is>
+      </c>
+      <c r="D6" s="79" t="inlineStr">
+        <is>
+          <t>첫째주</t>
+        </is>
+      </c>
+      <c r="E6" s="82" t="n">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1" s="90">
+      <c r="A7" s="83" t="inlineStr">
+        <is>
+          <t>수산</t>
+        </is>
+      </c>
+      <c r="B7" s="83" t="n"/>
+      <c r="C7" s="83" t="n"/>
+      <c r="D7" s="83" t="n"/>
+      <c r="E7" s="83" t="n"/>
+    </row>
+    <row r="8" ht="22" customHeight="1" s="90">
+      <c r="A8" s="80" t="inlineStr">
+        <is>
+          <t>(이번 주차 해당 없음)</t>
+        </is>
+      </c>
+      <c r="B8" s="79" t="n"/>
+      <c r="C8" s="80" t="n"/>
+      <c r="D8" s="79" t="n"/>
+      <c r="E8" s="80" t="n"/>
+    </row>
+    <row r="9" ht="22" customHeight="1" s="90">
+      <c r="A9" s="84" t="inlineStr">
+        <is>
+          <t>채소</t>
+        </is>
+      </c>
+      <c r="B9" s="84" t="n"/>
+      <c r="C9" s="84" t="n"/>
+      <c r="D9" s="84" t="n"/>
+      <c r="E9" s="84" t="n"/>
+    </row>
+    <row r="10" ht="22" customHeight="1" s="90">
+      <c r="A10" s="80" t="inlineStr">
+        <is>
+          <t>양파</t>
+        </is>
+      </c>
+      <c r="B10" s="79" t="inlineStr">
+        <is>
+          <t>2개</t>
+        </is>
+      </c>
+      <c r="C10" s="80" t="inlineStr">
+        <is>
+          <t>간장구이/간장조림</t>
+        </is>
+      </c>
+      <c r="D10" s="79" t="inlineStr">
+        <is>
+          <t>첫째주</t>
+        </is>
+      </c>
+      <c r="E10" s="82" t="n">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1" s="90">
+      <c r="A11" s="80" t="inlineStr">
+        <is>
+          <t>대파</t>
+        </is>
+      </c>
+      <c r="B11" s="79" t="inlineStr">
+        <is>
+          <t>2대</t>
+        </is>
+      </c>
+      <c r="C11" s="80" t="inlineStr">
+        <is>
+          <t>콩나물국/간장조림</t>
+        </is>
+      </c>
+      <c r="D11" s="79" t="inlineStr">
+        <is>
+          <t>첫째주</t>
+        </is>
+      </c>
+      <c r="E11" s="82" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1" s="90">
+      <c r="A12" s="80" t="inlineStr">
+        <is>
+          <t>감자</t>
+        </is>
+      </c>
+      <c r="B12" s="79" t="inlineStr">
+        <is>
+          <t>2개</t>
+        </is>
+      </c>
+      <c r="C12" s="80" t="inlineStr">
+        <is>
+          <t>감자채볶음</t>
+        </is>
+      </c>
+      <c r="D12" s="79" t="inlineStr">
+        <is>
+          <t>첫째주</t>
+        </is>
+      </c>
+      <c r="E12" s="82" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1" s="90">
+      <c r="A13" s="80" t="inlineStr">
+        <is>
+          <t>당근</t>
+        </is>
+      </c>
+      <c r="B13" s="79" t="inlineStr">
+        <is>
+          <t>1/3개</t>
+        </is>
+      </c>
+      <c r="C13" s="80" t="inlineStr">
+        <is>
+          <t>간장조림</t>
+        </is>
+      </c>
+      <c r="D13" s="79" t="inlineStr">
+        <is>
+          <t>첫째주</t>
+        </is>
+      </c>
+      <c r="E13" s="82" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1" s="90">
+      <c r="A14" s="80" t="inlineStr">
+        <is>
+          <t>콩나물</t>
+        </is>
+      </c>
+      <c r="B14" s="79" t="inlineStr">
+        <is>
+          <t>1봉지</t>
+        </is>
+      </c>
+      <c r="C14" s="80" t="inlineStr">
+        <is>
+          <t>콩나물국</t>
+        </is>
+      </c>
+      <c r="D14" s="79" t="inlineStr">
+        <is>
+          <t>첫째주</t>
+        </is>
+      </c>
+      <c r="E14" s="82" t="n">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1" s="90">
+      <c r="A15" s="85" t="inlineStr">
+        <is>
+          <t>두부류</t>
+        </is>
+      </c>
+      <c r="B15" s="85" t="n"/>
+      <c r="C15" s="85" t="n"/>
+      <c r="D15" s="85" t="n"/>
+      <c r="E15" s="85" t="n"/>
+    </row>
+    <row r="16" ht="22" customHeight="1" s="90">
+      <c r="A16" s="80" t="inlineStr">
+        <is>
+          <t>염장미역</t>
+        </is>
+      </c>
+      <c r="B16" s="79" t="inlineStr">
+        <is>
+          <t>1팩</t>
+        </is>
+      </c>
+      <c r="C16" s="80" t="inlineStr">
+        <is>
+          <t>차돌미역국</t>
+        </is>
+      </c>
+      <c r="D16" s="79" t="inlineStr">
+        <is>
+          <t>첫째주</t>
+        </is>
+      </c>
+      <c r="E16" s="82" t="n">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1" s="90">
+      <c r="A17" s="86" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="B17" s="86" t="n"/>
+      <c r="C17" s="86" t="n"/>
+      <c r="D17" s="86" t="n"/>
+      <c r="E17" s="86" t="n"/>
+    </row>
+    <row r="18" ht="22" customHeight="1" s="90">
+      <c r="A18" s="80" t="inlineStr">
+        <is>
+          <t>달걀</t>
+        </is>
+      </c>
+      <c r="B18" s="79" t="inlineStr">
+        <is>
+          <t>10개입</t>
+        </is>
+      </c>
+      <c r="C18" s="80" t="inlineStr">
+        <is>
+          <t>계란말이/각종</t>
+        </is>
+      </c>
+      <c r="D18" s="79" t="inlineStr">
+        <is>
+          <t>첫째주</t>
+        </is>
+      </c>
+      <c r="E18" s="82" t="n">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1" s="90">
+      <c r="A19" s="80" t="inlineStr">
+        <is>
+          <t>옥수수</t>
+        </is>
+      </c>
+      <c r="B19" s="79" t="inlineStr">
+        <is>
+          <t>2개</t>
+        </is>
+      </c>
+      <c r="C19" s="80" t="inlineStr">
+        <is>
+          <t>간식</t>
+        </is>
+      </c>
+      <c r="D19" s="79" t="inlineStr">
+        <is>
+          <t>첫째주</t>
+        </is>
+      </c>
+      <c r="E19" s="82" t="n">
         <v>3000</v>
       </c>
     </row>
-    <row r="5" ht="18.5" customHeight="1" s="90">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>양지머리</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>250g</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>양지미역국</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>둘째주</t>
-        </is>
-      </c>
-      <c r="E5" s="139" t="n">
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="6" ht="18.5" customHeight="1" s="90">
-      <c r="A6" s="105" t="inlineStr">
-        <is>
-          <t>수산</t>
-        </is>
-      </c>
-      <c r="B6" s="11" t="n"/>
-      <c r="C6" s="11" t="n"/>
-      <c r="D6" s="11" t="n"/>
-      <c r="E6" s="11" t="n"/>
-    </row>
-    <row r="7" ht="18.5" customHeight="1" s="90">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>새우살 (냉장)</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>400g</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>에비마요</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>둘째주</t>
-        </is>
-      </c>
-      <c r="E7" s="139" t="n">
-        <v>9000</v>
-      </c>
-    </row>
-    <row r="8" ht="18.5" customHeight="1" s="90">
-      <c r="A8" s="96" t="inlineStr">
-        <is>
-          <t>채소</t>
-        </is>
-      </c>
-      <c r="B8" s="13" t="n"/>
-      <c r="C8" s="13" t="n"/>
-      <c r="D8" s="13" t="n"/>
-      <c r="E8" s="13" t="n"/>
-    </row>
-    <row r="9" ht="18.5" customHeight="1" s="90">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>양파</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>2개</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>카레구이/오리볶음</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>첫째주</t>
-        </is>
-      </c>
-      <c r="E9" s="139" t="n">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="10" ht="18.5" customHeight="1" s="90">
-      <c r="A10" s="14" t="inlineStr">
-        <is>
-          <t>대파</t>
-        </is>
-      </c>
-      <c r="B10" s="15" t="inlineStr">
-        <is>
-          <t>3대</t>
-        </is>
-      </c>
-      <c r="C10" s="14" t="inlineStr">
-        <is>
-          <t>오뎅탕/오리볶음/달걀국</t>
-        </is>
-      </c>
-      <c r="D10" s="14" t="inlineStr">
-        <is>
-          <t>첫째주</t>
-        </is>
-      </c>
-      <c r="E10" s="140" t="n">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="11" ht="18.5" customHeight="1" s="90">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>무</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>1/6개</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>오뎅탕</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>첫째주</t>
-        </is>
-      </c>
-      <c r="E11" s="139" t="n">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="12" ht="18.5" customHeight="1" s="90">
-      <c r="A12" s="17" t="inlineStr">
-        <is>
-          <t>청경채</t>
-        </is>
-      </c>
-      <c r="B12" s="13" t="inlineStr">
-        <is>
-          <t>2~3포기</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>오리 굴소스볶음</t>
-        </is>
-      </c>
-      <c r="D12" s="17" t="inlineStr">
-        <is>
-          <t>둘째주</t>
-        </is>
-      </c>
-      <c r="E12" s="141" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="13" ht="18.5" customHeight="1" s="90">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>당근</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>1/4개</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>소시지볶음</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>첫째주</t>
-        </is>
-      </c>
-      <c r="E13" s="139" t="n">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="14" ht="18.5" customHeight="1" s="90">
-      <c r="A14" s="101" t="inlineStr">
-        <is>
-          <t>두부류</t>
-        </is>
-      </c>
-      <c r="B14" s="20" t="n"/>
-      <c r="C14" s="20" t="n"/>
-      <c r="D14" s="20" t="n"/>
-      <c r="E14" s="142" t="n"/>
-    </row>
-    <row r="15" ht="18.5" customHeight="1" s="90">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>염장미역</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>1팩</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>양지미역국</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>둘째주</t>
-        </is>
-      </c>
-      <c r="E15" s="139" t="n">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="16" ht="18.5" customHeight="1" s="90">
-      <c r="A16" s="22" t="inlineStr">
-        <is>
-          <t>기타</t>
-        </is>
-      </c>
-      <c r="B16" s="23" t="n"/>
-      <c r="C16" s="23" t="n"/>
-      <c r="D16" s="23" t="n"/>
-      <c r="E16" s="143" t="n"/>
-    </row>
-    <row r="17" ht="18.5" customHeight="1" s="90">
-      <c r="A17" s="25" t="inlineStr">
-        <is>
-          <t>가래떡</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>1팩</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>가래떡구이</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>첫째주</t>
-        </is>
-      </c>
-      <c r="E17" s="139" t="n">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="18" ht="18.5" customHeight="1" s="90">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>소시지</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>6개입</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>소시지야채볶음</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>둘째주</t>
-        </is>
-      </c>
-      <c r="E18" s="139" t="n">
-        <v>3500</v>
-      </c>
-    </row>
-    <row r="19" ht="18.5" customHeight="1" s="90">
-      <c r="A19" s="26" t="inlineStr">
-        <is>
-          <t>스위트콘</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>1캔</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>간식</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>둘째주</t>
-        </is>
-      </c>
-      <c r="E19" s="139" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="20" ht="18.5" customHeight="1" s="90">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>감자전분</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>1봉</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>에비마요</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>둘째주</t>
-        </is>
-      </c>
-      <c r="E20" s="139" t="n">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="21" ht="18.5" customHeight="1" s="90">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>마요네즈</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>1개</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>에비마요</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>둘째주</t>
-        </is>
-      </c>
-      <c r="E21" s="139" t="n">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="22" ht="18.5" customHeight="1" s="90">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>카레가루</t>
-        </is>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>1봉</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>카레소스구이</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>첫째주</t>
-        </is>
-      </c>
-      <c r="E22" s="139" t="n">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="23" ht="18.5" customHeight="1" s="90">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>다시마</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>소량</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>오뎅탕</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>첫째주</t>
-        </is>
-      </c>
-      <c r="E23" s="139" t="n">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="24" ht="18.5" customHeight="1" s="90">
-      <c r="A24" s="27" t="n"/>
-      <c r="B24" s="7" t="n"/>
-      <c r="C24" s="7" t="n"/>
-      <c r="D24" s="7" t="n"/>
-      <c r="E24" s="7" t="n"/>
-    </row>
-    <row r="25" ht="33" customHeight="1" s="90">
-      <c r="A25" s="28" t="inlineStr">
-        <is>
-          <t>[재고 활용 — 구매 불필요]</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="n"/>
-      <c r="C25" s="7" t="n"/>
-      <c r="D25" s="7" t="n"/>
-      <c r="E25" s="7" t="n"/>
-    </row>
-    <row r="26" ht="18.5" customHeight="1" s="90">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>소고기 안심 200g</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>재고</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>안심 스테이크</t>
-        </is>
-      </c>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E26" s="144" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" ht="18.5" customHeight="1" s="90">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>오뎅 1/2팩</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>재고</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>오뎅탕</t>
-        </is>
-      </c>
-      <c r="D27" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E27" s="7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" ht="18.5" customHeight="1" s="90">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>오리 슬라이스</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>재고</t>
-        </is>
-      </c>
-      <c r="C28" s="7" t="inlineStr">
-        <is>
-          <t>오리 굴소스볶음</t>
-        </is>
-      </c>
-      <c r="D28" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E28" s="7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" ht="18.5" customHeight="1" s="90">
-      <c r="A29" s="30" t="inlineStr">
-        <is>
-          <t>콩나물 1팩</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>재고</t>
-        </is>
-      </c>
-      <c r="C29" s="7" t="inlineStr">
-        <is>
-          <t>콩나물무침</t>
-        </is>
-      </c>
-      <c r="D29" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E29" s="145" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" ht="18.5" customHeight="1" s="90">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>두부</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>재고</t>
-        </is>
-      </c>
-      <c r="C30" s="7" t="inlineStr">
-        <is>
-          <t>두부구이</t>
-        </is>
-      </c>
-      <c r="D30" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E30" s="7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" ht="18.5" customHeight="1" s="90">
-      <c r="A31" s="7" t="n"/>
-      <c r="B31" s="7" t="n"/>
-      <c r="C31" s="7" t="n"/>
-      <c r="D31" s="7" t="n"/>
-      <c r="E31" s="7" t="n"/>
-    </row>
-    <row r="32" ht="47.5" customHeight="1" s="90">
-      <c r="A32" s="32" t="inlineStr">
-        <is>
-          <t>합계 (신규 구매분)</t>
-        </is>
-      </c>
-      <c r="B32" s="7" t="n"/>
-      <c r="C32" s="7" t="n"/>
-      <c r="D32" s="7" t="n"/>
-      <c r="E32" s="146">
-        <f>SUM(E4:E5,E7,E9:E13,E15,E17:E23)</f>
-        <v/>
+    <row r="20" ht="25" customHeight="1" s="90">
+      <c r="A20" s="87" t="inlineStr">
+        <is>
+          <t>합계</t>
+        </is>
+      </c>
+      <c r="B20" s="87" t="n"/>
+      <c r="C20" s="87" t="n"/>
+      <c r="D20" s="87" t="n"/>
+      <c r="E20" s="88" t="n">
+        <v>50300</v>
       </c>
     </row>
   </sheetData>
@@ -2140,7 +1893,7 @@
     <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0"/>
 </worksheet>
 </file>
 
@@ -2181,6 +1934,921 @@
         </is>
       </c>
     </row>
+    <row r="2" ht="352" customHeight="1" s="90">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>화 (7/7)</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>닭다리살 카레소스구이
++ 오뎅탕
++ 콩나물무침
++ 제철 과일 (간식)</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>[닭다리살 카레소스구이]
+1. 닭다리살 600g(재고+추가) → 한입 크기
+2. 밑간: 소금 + 후추 → 30분
+3. 소스: 카레가루 2T + 간장 1T + 꿀(또는 설탕) 1T
+   + 다진마늘 1T + 올리브오일 1T → 섞어 냉장
+4. 양파 1개 → 굵게 채썰기
+[오뎅탕]
+5. 오뎅 1/2팩(재고) → 먹기 좋게 자르기
+6. 무 1/6개 → 나박썰기
+7. 대파 1대 → 어슷
+8. 냄비에 물 1L + 다시마 1조각 세팅
+[콩나물무침]
+9. 콩나물 1팩(재고) → 씻기
+10. 양념: 참기름 1T + 국간장 1T + 다진마늘 1/2t
+    + 깨소금 → 소스컵에</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>★ 식사 25분 전 시작
+[콩나물 — 먼저]
+1. 냄비에 물 넉넉히 끓이기
+2. 콩나물 넣고 뚜껑 닫고 중불 7분
+   ※ 중간에 뚜껑 열지 않기!
+3. 찬물에 헹궈 물기 빼기
+4. 양념 넣고 조물조물 무치기
+[오뎅탕]
+5. 냄비에 물+다시마 센불
+6. 끓기 직전 다시마 건지기
+7. 무 넣고 중불 5분
+8. 오뎅 넣고 3분
+9. 국간장 1T + 소금 → 대파 마무리
+[닭다리살 카레소스구이 — 마지막]
+10. 팬에 기름, 닭다리살 센불 겉면 2분
+11. 중불로 낮추고 양파 넣어 3분
+12. 카레소스 부어 중불 5분
+    (뒤적이며 소스 코팅)
+13. 완성 후 접시에 담기
+[제철 과일] 씻어서 접시에</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="409.6" customHeight="1" s="90">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>수 (7/8)</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>오리 굴소스 채소볶음
++ 안심 스테이크
++ 달걀국
++ 두부구이
++ 가래떡구이 (간식)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>[오리 굴소스 채소볶음] ★아이 부드럽게 핵심
+1. 오리 슬라이스(재고) → 한입보다 작게 자르기
+2. ★연육: 양파 1/2개 갈아서 즙 내기
+   → 오리에 양파즙 + 맛술 1T + 후추
+   → 버무려 냉장 (하룻밤 재우기 = 연육 핵심)
+3. 양파 1개 → 굵게 채썰기 → 냉장
+4. 대파 1대 → 어슷 → 냉장
+5. 청경채 2~3포기 → 반으로 자르기 → 냉장
+6. 소스: 굴소스 2T + 간장 1T + 설탕 1T
+   + 참기름 1T → 소스컵
+[안심 스테이크]
+7. 안심 200g(재고) → 키친타올로 핏물 제거
+8. 아이들용: 0.5cm 얇게 슬라이스
+   어른용: 두께 유지
+9. 소금 + 후추 양면 → 냉장
+[달걀국]
+10. 대파 1대 → 송송썰기
+11. 달걀 3개 풀어 냉장
+12. 냄비에 물 800ml 세팅
+[두부구이]
+13. 두부(재고) → 1cm 두께
+    → 키친타올 물기 제거
+[가래떡구이]
+14. 가래떡 적당량 → 한입 크기</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>★ 식사 25분 전 시작
+[달걀국 — 먼저]
+1. 물 센불로 끓이기
+2. 국간장 1T + 소금 → 대파 넣기
+3. 달걀 풀어 돌려 붓기, 10초 후 불 끄기
+[가래떡구이]
+4. 팬에 기름 살짝, 중불 앞뒤 노릇 구이
+[두부구이]
+5. 같은 팬에 기름, 두부 중불 앞뒤 각 2분
+6. 소금 살짝 뿌려 완성
+[안심 스테이크]
+7. 팬 센불로 달구기 (연기 날 정도)
+8. 기름 두르고 안심 올리기
+   - 아이용(얇은 슬라이스): 앞뒤 각 30초 (웰던)
+   - 어른용(두꺼운 덩어리): 앞뒤 각 2분 (미디엄)
+9. 종이호일 감싸 3분 레스팅
+[오리 굴소스 채소볶음 — 마지막]
+10. 팬에 기름 없이(오리 기름 나옴) 센불
+11. ★ 양파즙 양념째로 오리 올려 빠르게 볶기
+    ※ 센불 2분! 오래 볶으면 질겨짐!
+12. 고기 80% 익으면 양파+청경채 넣고 1분
+13. 소스(굴소스+간장+설탕) 부어 30초 볶기
+14. 대파+참기름 → 불 끄기
+15. 접시에 담고 참깨 뿌리기</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="352" customHeight="1" s="90">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>금 (7/10)</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>에비마요 (새우마요)
++ 양지미역국
++ 소시지야채볶음
++ 옥수수 (간식)</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>[에비마요]
+1. 새우살 400g → 껍질·내장 제거
+   → 흐르는 물에 씻어 물기 제거 → 냉장
+2. 밑간: 청주 1T + 후추 → 버무려 냉장
+3. 감자전분 3T 별도 준비
+4. 마요소스: 마요네즈 4T + 케첩 1T
+   + 설탕 1T + 레몬즙 1T → 섞어 냉장
+[양지미역국]
+5. 양지머리 250g → 한입 크기
+6. 염장 미역 → 물에 30분 불리기 → 짜서 냉장
+7. 냄비에 물 1.2L 세팅
+[소시지야채볶음]
+8. 소시지 6개 → 칼집 넣기
+9. 양파 1/2개 → 채썰기
+10. 당근 1/4개 → 채썰기
+[옥수수]
+11. 스위트콘 1캔 준비</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>★ 식사 30분 전 시작
+[양지미역국 — 먼저]
+1. 냄비에 참기름, 양지 중불 2분 볶기
+2. 미역 넣고 1분 볶기
+3. 물 1.2L 붓고 센불
+4. 끓으면 중불 15분
+5. 국간장 1T + 다진마늘 + 소금
+[소시지야채볶음]
+6. 팬에 기름, 소시지 중불 2분
+7. 양파+당근 넣고 1분
+8. 케첩 2T + 설탕 1t → 볶아 완성
+[에비마요 — 마지막]
+9. 새우에 감자전분 고루 묻히기
+10. 팬에 기름 넉넉히, 중불
+11. 하나씩 올려 앞뒤 각 2분 노릇하게
+    ※ 한번에 부으면 뭉치니 하나씩!
+12. 노릇해지면 마요소스 넣고 불 끄기
+13. 잔열로 소스 고루 버무리기
+14. 접시에 담기
+[옥수수] 스위트콘 데워서 접시에</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.4" right="0.4" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="65" horizontalDpi="4294967293" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E32"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
+  <cols>
+    <col width="25" customWidth="1" style="90" min="1" max="1"/>
+    <col width="14" customWidth="1" style="90" min="2" max="2"/>
+    <col width="28" customWidth="1" style="90" min="3" max="3"/>
+    <col width="16" customWidth="1" style="90" min="4" max="4"/>
+    <col width="14" customWidth="1" style="90" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="25" customHeight="1" s="90">
+      <c r="A1" s="91" t="inlineStr">
+        <is>
+          <t>7월 2주차 장보기 (7/7~7/10)</t>
+        </is>
+      </c>
+      <c r="B1" s="92" t="n"/>
+      <c r="C1" s="92" t="n"/>
+      <c r="D1" s="92" t="n"/>
+      <c r="E1" s="93" t="n"/>
+    </row>
+    <row r="2" ht="18.5" customHeight="1" s="90">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>재료</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>수량</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>사용 메뉴</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>구매 시기</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>예상 금액</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18.5" customHeight="1" s="90">
+      <c r="A3" s="104" t="inlineStr">
+        <is>
+          <t>정육</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="n"/>
+      <c r="C3" s="6" t="n"/>
+      <c r="D3" s="6" t="n"/>
+      <c r="E3" s="6" t="n"/>
+    </row>
+    <row r="4" ht="33" customHeight="1" s="90">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>닭다리살 (재고 3쪽 + 추가)</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>200g</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>카레소스구이</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>재고+추가</t>
+        </is>
+      </c>
+      <c r="E4" s="139" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="5" ht="18.5" customHeight="1" s="90">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>양지머리</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>250g</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>양지미역국</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>둘째주</t>
+        </is>
+      </c>
+      <c r="E5" s="139" t="n">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="6" ht="18.5" customHeight="1" s="90">
+      <c r="A6" s="105" t="inlineStr">
+        <is>
+          <t>수산</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="n"/>
+      <c r="C6" s="11" t="n"/>
+      <c r="D6" s="11" t="n"/>
+      <c r="E6" s="11" t="n"/>
+    </row>
+    <row r="7" ht="18.5" customHeight="1" s="90">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>새우살 (냉장)</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>400g</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>에비마요</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>둘째주</t>
+        </is>
+      </c>
+      <c r="E7" s="139" t="n">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="8" ht="18.5" customHeight="1" s="90">
+      <c r="A8" s="96" t="inlineStr">
+        <is>
+          <t>채소</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="n"/>
+      <c r="C8" s="13" t="n"/>
+      <c r="D8" s="13" t="n"/>
+      <c r="E8" s="13" t="n"/>
+    </row>
+    <row r="9" ht="18.5" customHeight="1" s="90">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>양파</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>2개</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>카레구이/오리볶음</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>첫째주</t>
+        </is>
+      </c>
+      <c r="E9" s="139" t="n">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="10" ht="18.5" customHeight="1" s="90">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>대파</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>3대</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>오뎅탕/오리볶음/달걀국</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>첫째주</t>
+        </is>
+      </c>
+      <c r="E10" s="140" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="11" ht="18.5" customHeight="1" s="90">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>1/6개</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>오뎅탕</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>첫째주</t>
+        </is>
+      </c>
+      <c r="E11" s="139" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="12" ht="18.5" customHeight="1" s="90">
+      <c r="A12" s="17" t="inlineStr">
+        <is>
+          <t>청경채</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>2~3포기</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="inlineStr">
+        <is>
+          <t>오리 굴소스볶음</t>
+        </is>
+      </c>
+      <c r="D12" s="17" t="inlineStr">
+        <is>
+          <t>둘째주</t>
+        </is>
+      </c>
+      <c r="E12" s="141" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="13" ht="18.5" customHeight="1" s="90">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>당근</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>1/4개</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>소시지볶음</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>첫째주</t>
+        </is>
+      </c>
+      <c r="E13" s="139" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="14" ht="18.5" customHeight="1" s="90">
+      <c r="A14" s="101" t="inlineStr">
+        <is>
+          <t>두부류</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="n"/>
+      <c r="C14" s="20" t="n"/>
+      <c r="D14" s="20" t="n"/>
+      <c r="E14" s="142" t="n"/>
+    </row>
+    <row r="15" ht="18.5" customHeight="1" s="90">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>염장미역</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>1팩</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>양지미역국</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>둘째주</t>
+        </is>
+      </c>
+      <c r="E15" s="139" t="n">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="16" ht="18.5" customHeight="1" s="90">
+      <c r="A16" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="B16" s="23" t="n"/>
+      <c r="C16" s="23" t="n"/>
+      <c r="D16" s="23" t="n"/>
+      <c r="E16" s="143" t="n"/>
+    </row>
+    <row r="17" ht="18.5" customHeight="1" s="90">
+      <c r="A17" s="25" t="inlineStr">
+        <is>
+          <t>가래떡</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>1팩</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>가래떡구이</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>첫째주</t>
+        </is>
+      </c>
+      <c r="E17" s="139" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="18" ht="18.5" customHeight="1" s="90">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>소시지</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>6개입</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>소시지야채볶음</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>둘째주</t>
+        </is>
+      </c>
+      <c r="E18" s="139" t="n">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="19" ht="18.5" customHeight="1" s="90">
+      <c r="A19" s="26" t="inlineStr">
+        <is>
+          <t>스위트콘</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>1캔</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>간식</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>둘째주</t>
+        </is>
+      </c>
+      <c r="E19" s="139" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="20" ht="18.5" customHeight="1" s="90">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>감자전분</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>1봉</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>에비마요</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>둘째주</t>
+        </is>
+      </c>
+      <c r="E20" s="139" t="n">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="21" ht="18.5" customHeight="1" s="90">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>마요네즈</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>1개</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>에비마요</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>둘째주</t>
+        </is>
+      </c>
+      <c r="E21" s="139" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="22" ht="18.5" customHeight="1" s="90">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>카레가루</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>1봉</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>카레소스구이</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>첫째주</t>
+        </is>
+      </c>
+      <c r="E22" s="139" t="n">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="23" ht="18.5" customHeight="1" s="90">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>다시마</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>소량</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>오뎅탕</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>첫째주</t>
+        </is>
+      </c>
+      <c r="E23" s="139" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="24" ht="18.5" customHeight="1" s="90">
+      <c r="A24" s="27" t="n"/>
+      <c r="B24" s="7" t="n"/>
+      <c r="C24" s="7" t="n"/>
+      <c r="D24" s="7" t="n"/>
+      <c r="E24" s="7" t="n"/>
+    </row>
+    <row r="25" ht="33" customHeight="1" s="90">
+      <c r="A25" s="28" t="inlineStr">
+        <is>
+          <t>[재고 활용 — 구매 불필요]</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="n"/>
+      <c r="C25" s="7" t="n"/>
+      <c r="D25" s="7" t="n"/>
+      <c r="E25" s="7" t="n"/>
+    </row>
+    <row r="26" ht="18.5" customHeight="1" s="90">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>소고기 안심 200g</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>재고</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>안심 스테이크</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E26" s="144" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" ht="18.5" customHeight="1" s="90">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>오뎅 1/2팩</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>재고</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>오뎅탕</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" ht="18.5" customHeight="1" s="90">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>오리 슬라이스</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>재고</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>오리 굴소스볶음</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" ht="18.5" customHeight="1" s="90">
+      <c r="A29" s="30" t="inlineStr">
+        <is>
+          <t>콩나물 1팩</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>재고</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>콩나물무침</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E29" s="145" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" ht="18.5" customHeight="1" s="90">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>두부</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>재고</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>두부구이</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" ht="18.5" customHeight="1" s="90">
+      <c r="A31" s="7" t="n"/>
+      <c r="B31" s="7" t="n"/>
+      <c r="C31" s="7" t="n"/>
+      <c r="D31" s="7" t="n"/>
+      <c r="E31" s="7" t="n"/>
+    </row>
+    <row r="32" ht="47.5" customHeight="1" s="90">
+      <c r="A32" s="32" t="inlineStr">
+        <is>
+          <t>합계 (신규 구매분)</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="n"/>
+      <c r="C32" s="7" t="n"/>
+      <c r="D32" s="7" t="n"/>
+      <c r="E32" s="146">
+        <f>SUM(E4:E5,E7,E9:E13,E15,E17:E23)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.4" right="0.4" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
+  <cols>
+    <col width="8" customWidth="1" style="90" min="1" max="1"/>
+    <col width="18" customWidth="1" style="90" min="2" max="2"/>
+    <col width="55" customWidth="1" style="90" min="3" max="3"/>
+    <col width="65" customWidth="1" style="90" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="25" customHeight="1" s="90">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>요일</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>메뉴</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>전날 밤 준비</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>당일 조리</t>
+        </is>
+      </c>
+    </row>
     <row r="2" ht="250.5" customHeight="1" s="90">
       <c r="A2" s="2" t="inlineStr">
         <is>
@@ -2346,7 +3014,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2921,867 +3589,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.4" right="0.4" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
-  <cols>
-    <col width="8" customWidth="1" style="90" min="1" max="1"/>
-    <col width="18" customWidth="1" style="90" min="2" max="2"/>
-    <col width="55" customWidth="1" style="90" min="3" max="3"/>
-    <col width="65" customWidth="1" style="90" min="4" max="4"/>
-    <col hidden="1" width="1" customWidth="1" style="90" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="25" customHeight="1" s="90">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>요일</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>메뉴</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>전날 밤 준비</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>당일 조리</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="308.5" customHeight="1" s="90">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>화 (6/23)</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>소불고기 잡채
-+ 맑은무국
-+ 계란말이
-+ 제철 과일 (간식)</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>[소불고기 잡채]
-1. 소불고기용 500g → 간장 3T + 설탕 1.5T
-   + 배즙 2T + 다진마늘 1T + 참기름 1T + 후추
-   → 버무려 냉장
-2. 당면 200g → 찬물 30분 불리기 → 체에 냉장
-3. 양파 1개, 당근 1/2개 채썰기
-4. 시금치 1줌 → 끓는물 30초 데쳐 참기름+소금
-5. 파프리카 1개(빨강) → 채썰기
-[맑은무국]
-6. 무 1/4개 → 나박썰기
-7. 대파 1대 → 어슷썰기
-8. 냄비에 물 1L 세팅
-[계란말이]
-9. 계란 5개 + 소금 + 당근 잘게 다진 것 → 섞어 냉장</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>★ 식사 25분 전 시작
-[맑은무국 — 먼저]
-1. 냄비에 물+무 센불
-2. 끓으면 중불 10분 (무 투명해질 때까지)
-3. 국간장 1T + 다진마늘 + 소금
-4. 대파 마무리
-[계란말이]
-5. 팬에 기름 얇게, 약불
-6. 계란물 1/3 → 반쯤 익으면 돌돌 말기
-7. 2회 반복 → 식혀 잘라 접시
-[소불고기 잡채 — 마지막]
-8. 팬에 기름, 소불고기 센불 2분 → 꺼내기
-9. 양파+당근+파프리카 중불 2분
-10. 당면 넣고 간장 2T + 설탕 1T + 참기름 1T
-11. 고기+시금치 넣고 섞기
-12. 참깨 뿌려 완성
-[제철 과일] 씻어서 접시에</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="294" customHeight="1" s="90">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>수 (6/24)</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>돼지안심 청경채 굴소스볶음
-+ 파계란국
-+ 감자볶음 + 콘샐러드
-+ 제철 과일 (간식)</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>[돼지안심 청경채 굴소스볶음]
-1. 돼지안심 500g → 어슷 썰기
-2. 밑간: 소금 2꼬집 + 올리브오일 1T → 30분 → 냉장
-3. 청경채 4포기 → 4등분
-4. 양파 1개 → 4등분
-5. 마늘 3톨 → 슬라이스
-6. 소스: 굴소스 2.5T + 매실액 1.5T
-   + 감자전분 1/2t + 물 2T → 냉장
-[파계란국]
-7. 대파 2대 → 송송썰기
-8. 계란 3개 풀어 냉장
-9. 냄비에 물 800ml 세팅
-[감자볶음]
-10. 감자 2개 → 한입 크기 → 물에 담가두기
-[콘샐러드]
-11. 옥수수캔 1개 + 마요 2T + 설탕 1t → 냉장</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>★ 식사 20분 전 시작
-[파계란국 — 먼저]
-1. 물 센불로 끓이기
-2. 대파 넣고 국간장 1T + 소금
-3. 계란 풀어 돌려 붓기, 10초 후 불 끄기
-[감자볶음]
-4. 팬에 기름, 감자 중불 5분 (뚜껑)
-5. 소금+후추 → 노릇하면 완성
-[돼지안심 청경채 굴소스볶음 — 마지막]
-6. 팬에 기름, 안심 센불 80% (2분)
-7. 양파+마늘 1분
-8. 청경채 30초 ※ 오래 볶으면 물 빠져!
-9. 소스 부어 센불 30초 마무리
-10. 참기름 한 바퀴
-[콘샐러드] 냉장고에서 꺼내 담기
-[제철 과일] 씻어서 접시에</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="294" customHeight="1" s="90">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>금 (6/25)</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>새우전
-+ 배추된장국
-+ 두부전 + 김구이
-+ 인절미 (간식)</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>[새우전]
-1. 신선 새우 400g → 껍질·내장 제거 → 물기 제거
-2. 반은 통째로, 반은 잘게 다지기
-3. 부침가루 2T 비닐봉투에 넣고 통새우 묻히기
-4. 계란 3개 + 소금 1/2t + 후추
-   + 다진 당근 1/4개 + 대파 1대 송송 → 냉장
-[배추된장국]
-5. 배추 3~4잎 → 한입 크기
-6. 두부 1/2모 → 깍둑썰기
-7. 냄비에 물 1L + 코인육수 1개 세팅
-[두부전]
-8. 두부 1모 → 1cm 두께, 키친타올로 물기
-9. 부침가루 3T, 계란 2개 별도 풀어 냉장
-[인절미]
-10. 시판 인절미 해동</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>★ 식사 25분 전 시작
-[배추된장국 — 먼저]
-1. 물+코인육수 센불로 끓이기
-2. 된장 2T 풀고 배추 중불 3분
-3. 두부+다진마늘 3분
-4. 대파 마무리
-[두부전]
-5. 부침가루 묻히기 → 계란물에 담가 부치기
-6. 중불 앞뒤 각 2분
-[새우전 — 마지막]
-7. 통새우를 계란물에 퐁당
-8. 다진새우+채소 계란물 한 숟가락씩 올려
-9. 팬에 기름 넉넉히, 중불 앞뒤 노릇
-   ※ 삶아서 부치면 물 안 나옴!
-[김구이] 참기름, 약불 구이
-[인절미] 접시에 담아 제공</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.4" right="0.4" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:E31"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
-  <cols>
-    <col width="25" customWidth="1" style="90" min="1" max="1"/>
-    <col width="14" customWidth="1" style="90" min="2" max="2"/>
-    <col width="28" customWidth="1" style="90" min="3" max="3"/>
-    <col width="16" customWidth="1" style="90" min="4" max="4"/>
-    <col width="14" customWidth="1" style="90" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="25" customHeight="1" s="90">
-      <c r="A1" s="94" t="inlineStr">
-        <is>
-          <t>6월 4주차 장보기 목록</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18.5" customHeight="1" s="90">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>재료</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>수량</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t>사용 메뉴</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t>구매 시기</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t>예상 금액</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18.5" customHeight="1" s="90">
-      <c r="A3" s="104" t="inlineStr">
-        <is>
-          <t>정육</t>
-        </is>
-      </c>
-      <c r="B3" s="104" t="n"/>
-      <c r="C3" s="104" t="n"/>
-      <c r="D3" s="104" t="n"/>
-      <c r="E3" s="104" t="n"/>
-    </row>
-    <row r="4" ht="18.5" customHeight="1" s="90">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>소불고기용 (냉장)</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>500g</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>화(잡채)</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>4주차 구매</t>
-        </is>
-      </c>
-      <c r="E4" s="139" t="n">
-        <v>14000</v>
-      </c>
-    </row>
-    <row r="5" ht="18.5" customHeight="1" s="90">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>돼지안심 (냉장)</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>500g</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>수(굴소스볶음)</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>4주차 구매</t>
-        </is>
-      </c>
-      <c r="E5" s="139" t="n">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="6" ht="18.5" customHeight="1" s="90">
-      <c r="A6" s="105" t="inlineStr">
-        <is>
-          <t>수산</t>
-        </is>
-      </c>
-      <c r="B6" s="105" t="n"/>
-      <c r="C6" s="105" t="n"/>
-      <c r="D6" s="105" t="n"/>
-      <c r="E6" s="105" t="n"/>
-    </row>
-    <row r="7" ht="18.5" customHeight="1" s="90">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>신선 새우 (중하)</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>400g</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>금(새우전)</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>4주차 구매</t>
-        </is>
-      </c>
-      <c r="E7" s="139" t="n">
-        <v>14000</v>
-      </c>
-    </row>
-    <row r="8" ht="18.5" customHeight="1" s="90">
-      <c r="A8" s="101" t="inlineStr">
-        <is>
-          <t>두부류</t>
-        </is>
-      </c>
-      <c r="B8" s="101" t="n"/>
-      <c r="C8" s="101" t="n"/>
-      <c r="D8" s="101" t="n"/>
-      <c r="E8" s="101" t="n"/>
-    </row>
-    <row r="9" ht="18.5" customHeight="1" s="90">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>두부</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>1.5모</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>금(된장국+두부전)</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>4주차 구매</t>
-        </is>
-      </c>
-      <c r="E9" s="139" t="n">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="10" ht="18.5" customHeight="1" s="90">
-      <c r="A10" s="96" t="inlineStr">
-        <is>
-          <t>채소</t>
-        </is>
-      </c>
-      <c r="B10" s="96" t="n"/>
-      <c r="C10" s="96" t="n"/>
-      <c r="D10" s="96" t="n"/>
-      <c r="E10" s="96" t="n"/>
-    </row>
-    <row r="11" ht="18.5" customHeight="1" s="90">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>청경채</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>4포기</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>수(굴소스볶음)</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>4주차 구매</t>
-        </is>
-      </c>
-      <c r="E11" s="139" t="n">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="12" ht="18.5" customHeight="1" s="90">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>시금치</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>1줌</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>화(잡채)</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>4주차 구매</t>
-        </is>
-      </c>
-      <c r="E12" s="139" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="13" ht="18.5" customHeight="1" s="90">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>파프리카 (빨강)</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>1개</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>화(잡채)</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>4주차 구매</t>
-        </is>
-      </c>
-      <c r="E13" s="139" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="14" ht="18.5" customHeight="1" s="90">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>배추</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>1/4포기</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>금(된장국)</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>4주차 구매</t>
-        </is>
-      </c>
-      <c r="E14" s="139" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="15" ht="18.5" customHeight="1" s="90">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>양파</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>2개</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>화(잡채)+수(굴소스볶음)</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>4주차 구매</t>
-        </is>
-      </c>
-      <c r="E15" s="139" t="n">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="16" ht="33" customHeight="1" s="90">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>당근</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>1개</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>화(잡채·계란말이)+금(새우전)</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>4주차 구매</t>
-        </is>
-      </c>
-      <c r="E16" s="139" t="n">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="17" ht="18.5" customHeight="1" s="90">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>감자</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>2개</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>수(감자볶음)</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>4주차 구매</t>
-        </is>
-      </c>
-      <c r="E17" s="139" t="n">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="18" ht="18.5" customHeight="1" s="90">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>대파</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>4대</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>화·수·금 전체</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>4주차 구매</t>
-        </is>
-      </c>
-      <c r="E18" s="139" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="19" ht="18.5" customHeight="1" s="90">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>무</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>1/4개</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>화(무국)</t>
-        </is>
-      </c>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>4주차 구매</t>
-        </is>
-      </c>
-      <c r="E19" s="139" t="n">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="20" ht="18.5" customHeight="1" s="90">
-      <c r="A20" s="25" t="inlineStr">
-        <is>
-          <t>달걀</t>
-        </is>
-      </c>
-      <c r="B20" s="38" t="n"/>
-      <c r="C20" s="38" t="n"/>
-      <c r="D20" s="38" t="n"/>
-      <c r="E20" s="38" t="n"/>
-    </row>
-    <row r="21" ht="33" customHeight="1" s="90">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>달걀</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>15개(1판+α)</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>화(계란말이5)+수(파계란국3)+금(새우전3·두부전2)</t>
-        </is>
-      </c>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>4주차 구매</t>
-        </is>
-      </c>
-      <c r="E21" s="139" t="n">
-        <v>4500</v>
-      </c>
-    </row>
-    <row r="22" ht="18.5" customHeight="1" s="90">
-      <c r="A22" s="26" t="inlineStr">
-        <is>
-          <t>가공식품</t>
-        </is>
-      </c>
-      <c r="B22" s="39" t="n"/>
-      <c r="C22" s="39" t="n"/>
-      <c r="D22" s="39" t="n"/>
-      <c r="E22" s="39" t="n"/>
-    </row>
-    <row r="23" ht="18.5" customHeight="1" s="90">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>당면</t>
-        </is>
-      </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>200g</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>화(잡채)</t>
-        </is>
-      </c>
-      <c r="D23" s="8" t="inlineStr">
-        <is>
-          <t>4주차 구매</t>
-        </is>
-      </c>
-      <c r="E23" s="139" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="24" ht="18.5" customHeight="1" s="90">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>옥수수캔</t>
-        </is>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>1개</t>
-        </is>
-      </c>
-      <c r="C24" s="7" t="inlineStr">
-        <is>
-          <t>수(콘샐러드)</t>
-        </is>
-      </c>
-      <c r="D24" s="8" t="inlineStr">
-        <is>
-          <t>4주차 구매</t>
-        </is>
-      </c>
-      <c r="E24" s="139" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="25" ht="18.5" customHeight="1" s="90">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>인절미 (시판)</t>
-        </is>
-      </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>1팩</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>금(간식)</t>
-        </is>
-      </c>
-      <c r="D25" s="8" t="inlineStr">
-        <is>
-          <t>4주차 구매</t>
-        </is>
-      </c>
-      <c r="E25" s="139" t="n">
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="26" ht="18.5" customHeight="1" s="90">
-      <c r="A26" s="35" t="inlineStr">
-        <is>
-          <t>양념/기타</t>
-        </is>
-      </c>
-      <c r="B26" s="40" t="n"/>
-      <c r="C26" s="40" t="n"/>
-      <c r="D26" s="40" t="n"/>
-      <c r="E26" s="40" t="n"/>
-    </row>
-    <row r="27" ht="18.5" customHeight="1" s="90">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>굴소스</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>재고 확인</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>수(굴소스볶음)</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>재고</t>
-        </is>
-      </c>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>재고</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="18.5" customHeight="1" s="90">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>매실액</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>재고 확인</t>
-        </is>
-      </c>
-      <c r="C28" s="7" t="inlineStr">
-        <is>
-          <t>수(굴소스볶음)</t>
-        </is>
-      </c>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>재고</t>
-        </is>
-      </c>
-      <c r="E28" s="7" t="inlineStr">
-        <is>
-          <t>재고</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="18.5" customHeight="1" s="90">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t>코인육수</t>
-        </is>
-      </c>
-      <c r="B29" s="8" t="inlineStr">
-        <is>
-          <t>1개</t>
-        </is>
-      </c>
-      <c r="C29" s="7" t="inlineStr">
-        <is>
-          <t>금(된장국)</t>
-        </is>
-      </c>
-      <c r="D29" s="8" t="inlineStr">
-        <is>
-          <t>4주차 구매</t>
-        </is>
-      </c>
-      <c r="E29" s="139" t="n">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="30" ht="18.5" customHeight="1" s="90"/>
-    <row r="31" ht="33" customHeight="1" s="90">
-      <c r="A31" s="36" t="inlineStr">
-        <is>
-          <t>예상 합계 (재고 제외 신규 구매분)</t>
-        </is>
-      </c>
-      <c r="B31" s="36" t="n"/>
-      <c r="C31" s="36" t="n"/>
-      <c r="D31" s="36" t="n"/>
-      <c r="E31" s="147" t="n">
-        <v>69600</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
@@ -3825,39 +3632,149 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="366.5" customHeight="1" s="90">
+    <row r="2" ht="308.5" customHeight="1" s="90">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>화 (6/16)</t>
+          <t>화 (6/23)</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>돼지안심 소금구이
+          <t>소불고기 잡채
++ 맑은무국
++ 계란말이
++ 제철 과일 (간식)</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>[소불고기 잡채]
+1. 소불고기용 500g → 간장 3T + 설탕 1.5T
+   + 배즙 2T + 다진마늘 1T + 참기름 1T + 후추
+   → 버무려 냉장
+2. 당면 200g → 찬물 30분 불리기 → 체에 냉장
+3. 양파 1개, 당근 1/2개 채썰기
+4. 시금치 1줌 → 끓는물 30초 데쳐 참기름+소금
+5. 파프리카 1개(빨강) → 채썰기
+[맑은무국]
+6. 무 1/4개 → 나박썰기
+7. 대파 1대 → 어슷썰기
+8. 냄비에 물 1L 세팅
+[계란말이]
+9. 계란 5개 + 소금 + 당근 잘게 다진 것 → 섞어 냉장</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>★ 식사 25분 전 시작
+[맑은무국 — 먼저]
+1. 냄비에 물+무 센불
+2. 끓으면 중불 10분 (무 투명해질 때까지)
+3. 국간장 1T + 다진마늘 + 소금
+4. 대파 마무리
+[계란말이]
+5. 팬에 기름 얇게, 약불
+6. 계란물 1/3 → 반쯤 익으면 돌돌 말기
+7. 2회 반복 → 식혀 잘라 접시
+[소불고기 잡채 — 마지막]
+8. 팬에 기름, 소불고기 센불 2분 → 꺼내기
+9. 양파+당근+파프리카 중불 2분
+10. 당면 넣고 간장 2T + 설탕 1T + 참기름 1T
+11. 고기+시금치 넣고 섞기
+12. 참깨 뿌려 완성
+[제철 과일] 씻어서 접시에</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="294" customHeight="1" s="90">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>수 (6/24)</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>돼지안심 청경채 굴소스볶음
++ 파계란국
++ 감자볶음 + 콘샐러드
++ 제철 과일 (간식)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>[돼지안심 청경채 굴소스볶음]
+1. 돼지안심 500g → 어슷 썰기
+2. 밑간: 소금 2꼬집 + 올리브오일 1T → 30분 → 냉장
+3. 청경채 4포기 → 4등분
+4. 양파 1개 → 4등분
+5. 마늘 3톨 → 슬라이스
+6. 소스: 굴소스 2.5T + 매실액 1.5T
+   + 감자전분 1/2t + 물 2T → 냉장
+[파계란국]
+7. 대파 2대 → 송송썰기
+8. 계란 3개 풀어 냉장
+9. 냄비에 물 800ml 세팅
+[감자볶음]
+10. 감자 2개 → 한입 크기 → 물에 담가두기
+[콘샐러드]
+11. 옥수수캔 1개 + 마요 2T + 설탕 1t → 냉장</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>★ 식사 20분 전 시작
+[파계란국 — 먼저]
+1. 물 센불로 끓이기
+2. 대파 넣고 국간장 1T + 소금
+3. 계란 풀어 돌려 붓기, 10초 후 불 끄기
+[감자볶음]
+4. 팬에 기름, 감자 중불 5분 (뚜껑)
+5. 소금+후추 → 노릇하면 완성
+[돼지안심 청경채 굴소스볶음 — 마지막]
+6. 팬에 기름, 안심 센불 80% (2분)
+7. 양파+마늘 1분
+8. 청경채 30초 ※ 오래 볶으면 물 빠져!
+9. 소스 부어 센불 30초 마무리
+10. 참기름 한 바퀴
+[콘샐러드] 냉장고에서 꺼내 담기
+[제철 과일] 씻어서 접시에</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="294" customHeight="1" s="90">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>금 (6/25)</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>새우전
 + 배추된장국
-+ 계란찜 + 감자채볶음
-+ 가래떡구이 (간식)</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>[돼지안심 소금구이]
-1. 돼지안심 600g → 1cm 두께로 썰기
-2. 소금 1t + 후추 → 양면에 고루 뿌려 냉장
++ 두부전 + 김구이
++ 인절미 (간식)</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>[새우전]
+1. 신선 새우 400g → 껍질·내장 제거 → 물기 제거
+2. 반은 통째로, 반은 잘게 다지기
+3. 부침가루 2T 비닐봉투에 넣고 통새우 묻히기
+4. 계란 3개 + 소금 1/2t + 후추
+   + 다진 당근 1/4개 + 대파 1대 송송 → 냉장
 [배추된장국]
-3. 배추 3~4잎 → 한입 크기로 썰기
-4. 두부 1/2모 → 깍둑썰기
-5. 대파 1대 → 어슷썰기
-6. 냄비에 물 1L + 코인육수 1개 세팅
-[계란찜]
-7. 계란 4개 + 물 200ml + 소금 1/2t 섞어 냉장
-   ※ 새우젓 1/2t 넣으면 감칠맛 UP
-[감자채볶음]
-8. 감자 2개 → 가늘게 채썰기 → 찬물 10분 전분 빼기
-※ 가래떡은 재고분 사용</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
+5. 배추 3~4잎 → 한입 크기
+6. 두부 1/2모 → 깍둑썰기
+7. 냄비에 물 1L + 코인육수 1개 세팅
+[두부전]
+8. 두부 1모 → 1cm 두께, 키친타올로 물기
+9. 부침가루 3T, 계란 2개 별도 풀어 냉장
+[인절미]
+10. 시판 인절미 해동</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>★ 식사 25분 전 시작
 [배추된장국 — 먼저]
@@ -3865,117 +3782,16 @@
 2. 된장 2T 풀고 배추 중불 3분
 3. 두부+다진마늘 3분
 4. 대파 마무리
-[계란찜]
-5. 뚝배기에 계란물 넣고 중불
-6. 가장자리 익으면 섞기 → 뚜껑 약불 5분
-7. 참기름+깨 마무리
-[감자채볶음]
-8. 팬에 기름, 감자채 중불 3~4분
-9. 소금+후추, 투명해지면 완성
-[돼지안심 소금구이 — 스텐팬]
-10. 예열 → 물방울 테스트 → 기름
-11. 안심 한쪽 2분 → 뒤집어 2분
-    ※ 핑크빛 남을 때 꺼내기!
-[가래떡구이]
-12. 팬에 기름, 중불 앞뒤 노릇
-13. 간장 1T + 설탕 1T 졸이기 → 깨</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="250.5" customHeight="1" s="90">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>수 (6/17)</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>삼치 데리야끼강정
-+ 두부전 + 김구이
-+ 옥수수 (간식)</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>[삼치 데리야끼강정]
-1. 냉동 삼치살 → 냉장 해동
-2. 키친타올로 물기 완전 제거
-3. 한입 크기로 자르기 (아이들 먹기 좋게)
-4. 소금 1/2t + 후추 → 밑간 후 냉장
-5. 데리야끼 소스: 간장 3T + 미림 2T + 설탕 1.5T + 물 2T → 섞어 냉장
-6. 감자전분 별도 준비
 [두부전]
-7. 두부 1모 → 1cm 두께, 물기 빼기
-8. 부침가루 3T
-9. 계란 2개 풀어 냉장
-[옥수수]
-10. 옥수수 3개 → 삶아서 냉장</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>★ 식사 20분 전 시작
-[삼치 데리야끼강정 — 먼저]
-1. 삼치에 감자전분 고루 묻히기 (여분 털기)
-2. 팬에 기름 넉넉히, 중불
-3. 앞뒤 각 3분씩 바삭하게 튀기기
-4. 키친타올에 기름 빼기
-5. 다른 팬에 데리야끼 소스 → 중불 졸이기
-6. 걸쭉해지면 삼치 넣고 소스 끼얹기 → 깨 뿌려 마무리
-[두부전]
-7. 부침가루 묻히기
-8. 계란물에 담가 중불 부치기
-9. 앞뒤 각 2분
-[김구이] 참기름 발라 약불 구이 (또는 시판 구운김)
-[옥수수] 전자레인지 2분 데우기</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="279.5" customHeight="1" s="90">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>금 (6/19)</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>닭다리살 카레소스구이
-+ 레토르트 미역국(소진)
-+ 소시지야채볶음
-+ 제철 과일 (간식)</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>[닭다리살 카레소스구이]
-1. 닭다리살 700g → 한입 크기
-2. 카레소스: 카레가루 2T + 간장 2T + 설탕 1T
-   + 다진마늘 1T + 맛술 1T → 섞기
-3. 닭에 버무려 냉장 (하룻밤)
-[레토르트 미역국]
-4. 냉동실 레토르트 미역국 꺼내 냉장 해동
-[소시지야채볶음]
-5. 비엔나소시지 1팩(200g) → 칼집
-6. 양파 1/2개 채썰기, 당근 1/4개 채썰기</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>★ 식사 25분 전 시작
-[레토르트 미역국 — 먼저]
-1. 냄비에 레토르트 미역국 붓고 중불 데우기
-2. 끓으면 약불 보온
-   ※ 재고 소진 목적 — 간 확인 후 필요시 국간장 추가
-[소시지야채볶음]
-3. 팬에 기름, 소시지 중불 2분 (칼집 벌어질 때까지)
-4. 양파+당근 넣고 2분 더 볶기
-5. 간장 1T + 설탕 1/2T → 깨
-[닭다리살 카레소스구이 — 마지막]
-6. 팬에 기름 넉넉히, 중불
-7. 닭 껍질면 아래로 3분 (바삭하게)
-8. 뒤집어 2분 → 남은 양념 끼얹으며 약불 2분
-   ※ 카레 양념이 탈 수 있으니 불 조절 주의
-[제철 과일] 씻어서 접시에 담기</t>
+5. 부침가루 묻히기 → 계란물에 담가 부치기
+6. 중불 앞뒤 각 2분
+[새우전 — 마지막]
+7. 통새우를 계란물에 퐁당
+8. 다진새우+채소 계란물 한 숟가락씩 올려
+9. 팬에 기름 넉넉히, 중불 앞뒤 노릇
+   ※ 삶아서 부치면 물 안 나옴!
+[김구이] 참기름, 약불 구이
+[인절미] 접시에 담아 제공</t>
         </is>
       </c>
     </row>
@@ -4004,7 +3820,7 @@
     <row r="1" ht="25" customHeight="1" s="90">
       <c r="A1" s="94" t="inlineStr">
         <is>
-          <t>6월 3주차 장보기 목록  (재고: 가래떡)</t>
+          <t>6월 4주차 장보기 목록</t>
         </is>
       </c>
     </row>
@@ -4049,180 +3865,180 @@
     <row r="4" ht="18.5" customHeight="1" s="90">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>돼지안심 (냉장)</t>
+          <t>소불고기용 (냉장)</t>
         </is>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>600g</t>
+          <t>500g</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>화(소금구이)</t>
+          <t>화(잡채)</t>
         </is>
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>3주차 구매</t>
+          <t>4주차 구매</t>
         </is>
       </c>
       <c r="E4" s="139" t="n">
-        <v>12000</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="5" ht="18.5" customHeight="1" s="90">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>닭다리살 (순살, 냉장)</t>
+          <t>돼지안심 (냉장)</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>700g</t>
+          <t>500g</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>금(카레소스구이)</t>
+          <t>수(굴소스볶음)</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>3주차 구매</t>
+          <t>4주차 구매</t>
         </is>
       </c>
       <c r="E5" s="139" t="n">
-        <v>9000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="6" ht="18.5" customHeight="1" s="90">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>양지머리</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>300g</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>금(미역국)</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>3주차 구매</t>
-        </is>
-      </c>
-      <c r="E6" s="139" t="n">
-        <v>12000</v>
-      </c>
+      <c r="A6" s="105" t="inlineStr">
+        <is>
+          <t>수산</t>
+        </is>
+      </c>
+      <c r="B6" s="105" t="n"/>
+      <c r="C6" s="105" t="n"/>
+      <c r="D6" s="105" t="n"/>
+      <c r="E6" s="105" t="n"/>
     </row>
     <row r="7" ht="18.5" customHeight="1" s="90">
-      <c r="A7" s="105" t="inlineStr">
-        <is>
-          <t>수산</t>
-        </is>
-      </c>
-      <c r="B7" s="105" t="n"/>
-      <c r="C7" s="105" t="n"/>
-      <c r="D7" s="105" t="n"/>
-      <c r="E7" s="105" t="n"/>
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>신선 새우 (중하)</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>400g</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>금(새우전)</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>4주차 구매</t>
+        </is>
+      </c>
+      <c r="E7" s="139" t="n">
+        <v>14000</v>
+      </c>
     </row>
     <row r="8" ht="18.5" customHeight="1" s="90">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>대구살 필렛 (냉장)</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>500g</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>수(간장무조림)</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>3주차 구매</t>
-        </is>
-      </c>
-      <c r="E8" s="139" t="n">
-        <v>12000</v>
-      </c>
+      <c r="A8" s="101" t="inlineStr">
+        <is>
+          <t>두부류</t>
+        </is>
+      </c>
+      <c r="B8" s="101" t="n"/>
+      <c r="C8" s="101" t="n"/>
+      <c r="D8" s="101" t="n"/>
+      <c r="E8" s="101" t="n"/>
     </row>
     <row r="9" ht="18.5" customHeight="1" s="90">
-      <c r="A9" s="101" t="inlineStr">
-        <is>
-          <t>두부류</t>
-        </is>
-      </c>
-      <c r="B9" s="101" t="n"/>
-      <c r="C9" s="101" t="n"/>
-      <c r="D9" s="101" t="n"/>
-      <c r="E9" s="101" t="n"/>
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>두부</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>1.5모</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>금(된장국+두부전)</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>4주차 구매</t>
+        </is>
+      </c>
+      <c r="E9" s="139" t="n">
+        <v>3000</v>
+      </c>
     </row>
     <row r="10" ht="18.5" customHeight="1" s="90">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>두부</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>1.5모</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>화(된장국)+수(두부전)</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>3주차 구매</t>
-        </is>
-      </c>
-      <c r="E10" s="139" t="n">
+      <c r="A10" s="96" t="inlineStr">
+        <is>
+          <t>채소</t>
+        </is>
+      </c>
+      <c r="B10" s="96" t="n"/>
+      <c r="C10" s="96" t="n"/>
+      <c r="D10" s="96" t="n"/>
+      <c r="E10" s="96" t="n"/>
+    </row>
+    <row r="11" ht="18.5" customHeight="1" s="90">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>청경채</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>4포기</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>수(굴소스볶음)</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>4주차 구매</t>
+        </is>
+      </c>
+      <c r="E11" s="139" t="n">
         <v>3000</v>
       </c>
-    </row>
-    <row r="11" ht="18.5" customHeight="1" s="90">
-      <c r="A11" s="98" t="inlineStr">
-        <is>
-          <t>해조류</t>
-        </is>
-      </c>
-      <c r="B11" s="98" t="n"/>
-      <c r="C11" s="98" t="n"/>
-      <c r="D11" s="98" t="n"/>
-      <c r="E11" s="98" t="n"/>
     </row>
     <row r="12" ht="18.5" customHeight="1" s="90">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>염장미역</t>
+          <t>시금치</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>50g</t>
+          <t>1줌</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>금(미역국)</t>
+          <t>화(잡채)</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>3주차 구매</t>
+          <t>4주차 구매</t>
         </is>
       </c>
       <c r="E12" s="139" t="n">
@@ -4230,15 +4046,29 @@
       </c>
     </row>
     <row r="13" ht="18.5" customHeight="1" s="90">
-      <c r="A13" s="96" t="inlineStr">
-        <is>
-          <t>채소</t>
-        </is>
-      </c>
-      <c r="B13" s="96" t="n"/>
-      <c r="C13" s="96" t="n"/>
-      <c r="D13" s="96" t="n"/>
-      <c r="E13" s="96" t="n"/>
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>파프리카 (빨강)</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>1개</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>화(잡채)</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>4주차 구매</t>
+        </is>
+      </c>
+      <c r="E13" s="139" t="n">
+        <v>2000</v>
+      </c>
     </row>
     <row r="14" ht="18.5" customHeight="1" s="90">
       <c r="A14" s="7" t="inlineStr">
@@ -4253,12 +4083,12 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>화(된장국)</t>
+          <t>금(된장국)</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>3주차 구매</t>
+          <t>4주차 구매</t>
         </is>
       </c>
       <c r="E14" s="139" t="n">
@@ -4268,126 +4098,126 @@
     <row r="15" ht="18.5" customHeight="1" s="90">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>양파</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>1/2개</t>
+          <t>2개</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>수(대구조림)</t>
+          <t>화(잡채)+수(굴소스볶음)</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>3주차 구매</t>
+          <t>4주차 구매</t>
         </is>
       </c>
       <c r="E15" s="139" t="n">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="16" ht="18.5" customHeight="1" s="90">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="16" ht="33" customHeight="1" s="90">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>감자</t>
+          <t>당근</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>2개</t>
+          <t>1개</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>화(감자채볶음)</t>
+          <t>화(잡채·계란말이)+금(새우전)</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>3주차 구매</t>
+          <t>4주차 구매</t>
         </is>
       </c>
       <c r="E16" s="139" t="n">
-        <v>1500</v>
+        <v>800</v>
       </c>
     </row>
     <row r="17" ht="18.5" customHeight="1" s="90">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>양파</t>
+          <t>감자</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>1개</t>
+          <t>2개</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>금(소시지볶음)</t>
+          <t>수(감자볶음)</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>3주차 구매</t>
+          <t>4주차 구매</t>
         </is>
       </c>
       <c r="E17" s="139" t="n">
-        <v>500</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="18" ht="18.5" customHeight="1" s="90">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>당근</t>
+          <t>대파</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>1개</t>
+          <t>4대</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>금(소시지볶음)</t>
+          <t>화·수·금 전체</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>3주차 구매</t>
+          <t>4주차 구매</t>
         </is>
       </c>
       <c r="E18" s="139" t="n">
-        <v>800</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="19" ht="18.5" customHeight="1" s="90">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>대파</t>
+          <t>무</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>3대</t>
+          <t>1/4개</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>화·수·금 전체</t>
+          <t>화(무국)</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>3주차 구매</t>
+          <t>4주차 구매</t>
         </is>
       </c>
       <c r="E19" s="139" t="n">
-        <v>1500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="20" ht="18.5" customHeight="1" s="90">
@@ -4401,7 +4231,7 @@
       <c r="D20" s="38" t="n"/>
       <c r="E20" s="38" t="n"/>
     </row>
-    <row r="21" ht="18.5" customHeight="1" s="90">
+    <row r="21" ht="33" customHeight="1" s="90">
       <c r="A21" s="7" t="inlineStr">
         <is>
           <t>달걀</t>
@@ -4409,21 +4239,21 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>10개(1판)</t>
+          <t>15개(1판+α)</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>화(계란찜4)+수(두부전2)</t>
+          <t>화(계란말이5)+수(파계란국3)+금(새우전3·두부전2)</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>3주차 구매</t>
+          <t>4주차 구매</t>
         </is>
       </c>
       <c r="E21" s="139" t="n">
-        <v>3000</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="22" ht="18.5" customHeight="1" s="90">
@@ -4440,150 +4270,166 @@
     <row r="23" ht="18.5" customHeight="1" s="90">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>비엔나소시지</t>
+          <t>당면</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>1팩(200g)</t>
+          <t>200g</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>금(소시지야채볶음)</t>
+          <t>화(잡채)</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>3주차 구매</t>
+          <t>4주차 구매</t>
         </is>
       </c>
       <c r="E23" s="139" t="n">
-        <v>3500</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="24" ht="18.5" customHeight="1" s="90">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>옥수수</t>
+          <t>옥수수캔</t>
         </is>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>3개</t>
+          <t>1개</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>수(간식)</t>
+          <t>수(콘샐러드)</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>3주차 구매</t>
+          <t>4주차 구매</t>
         </is>
       </c>
       <c r="E24" s="139" t="n">
-        <v>3000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="25" ht="18.5" customHeight="1" s="90">
-      <c r="A25" s="35" t="inlineStr">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>인절미 (시판)</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>1팩</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>금(간식)</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>4주차 구매</t>
+        </is>
+      </c>
+      <c r="E25" s="139" t="n">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="26" ht="18.5" customHeight="1" s="90">
+      <c r="A26" s="35" t="inlineStr">
         <is>
           <t>양념/기타</t>
         </is>
       </c>
-      <c r="B25" s="40" t="n"/>
-      <c r="C25" s="40" t="n"/>
-      <c r="D25" s="40" t="n"/>
-      <c r="E25" s="40" t="n"/>
-    </row>
-    <row r="26" ht="18.5" customHeight="1" s="90">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>카레가루</t>
-        </is>
-      </c>
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>1팩</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>금(카레소스)</t>
-        </is>
-      </c>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t>3주차 구매</t>
-        </is>
-      </c>
-      <c r="E26" s="139" t="n">
-        <v>2000</v>
-      </c>
+      <c r="B26" s="40" t="n"/>
+      <c r="C26" s="40" t="n"/>
+      <c r="D26" s="40" t="n"/>
+      <c r="E26" s="40" t="n"/>
     </row>
     <row r="27" ht="18.5" customHeight="1" s="90">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>코인육수</t>
-        </is>
-      </c>
-      <c r="B27" s="8" t="inlineStr">
-        <is>
-          <t>1개</t>
+          <t>굴소스</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>재고 확인</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>화(된장국)</t>
-        </is>
-      </c>
-      <c r="D27" s="8" t="inlineStr">
-        <is>
-          <t>3주차 구매</t>
-        </is>
-      </c>
-      <c r="E27" s="139" t="n">
-        <v>800</v>
+          <t>수(굴소스볶음)</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>재고</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>재고</t>
+        </is>
       </c>
     </row>
     <row r="28" ht="18.5" customHeight="1" s="90">
-      <c r="A28" s="42" t="inlineStr">
-        <is>
-          <t>잔여재료 (구매 불필요)</t>
-        </is>
-      </c>
-      <c r="B28" s="43" t="n"/>
-      <c r="C28" s="43" t="n"/>
-      <c r="D28" s="43" t="n"/>
-      <c r="E28" s="43" t="n"/>
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>매실액</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>재고 확인</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>수(굴소스볶음)</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>재고</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>재고</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="18.5" customHeight="1" s="90">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>가래떡 (재고)</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>적당량</t>
+          <t>코인육수</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>1개</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>화(가래떡구이)</t>
-        </is>
-      </c>
-      <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t>재고</t>
-        </is>
-      </c>
-      <c r="E29" s="7" t="inlineStr">
-        <is>
-          <t>재고</t>
-        </is>
+          <t>금(된장국)</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>4주차 구매</t>
+        </is>
+      </c>
+      <c r="E29" s="139" t="n">
+        <v>800</v>
       </c>
     </row>
     <row r="30" ht="18.5" customHeight="1" s="90"/>
@@ -4597,7 +4443,7 @@
       <c r="C31" s="36" t="n"/>
       <c r="D31" s="36" t="n"/>
       <c r="E31" s="147" t="n">
-        <v>70100</v>
+        <v>69600</v>
       </c>
     </row>
   </sheetData>
@@ -4647,164 +4493,157 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="265" customHeight="1" s="90">
+    <row r="2" ht="366.5" customHeight="1" s="90">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>화 (6/9)</t>
+          <t>화 (6/16)</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>오야코동 (닭+달걀 덮밥)
-+ 오뎅탕 (도우미님 조리)
-+ 복숭아</t>
+          <t>돼지안심 소금구이
++ 배추된장국
++ 계란찜 + 감자채볶음
++ 가래떡구이 (간식)</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>[오야코동 — 닭다리살 덮밥]
-1. 닭다리살 700g → 한입 크기(2cm)로 자르기
-2. 밑간: 소금 약간 + 후추 + 맛술 2큰술
-3. 양파 1.5개 → 0.5cm 채썰기
-4. 대파 1대 → 어슷썰기
-5. 소스: 간장4T + 맛술3T + 설탕2T + 물250ml 섞어 냉장
-   (쯔유 있으면 쯔유5T+물250ml로 대체)
-6. 달걀 5개 → 젓가락 10회만 가볍게 풀기 → 냉장
-[오뎅탕 — 도우미님 조리]
-7. 어묵 꼬치 세팅 (재고 소진)
-8. 무 100g 나박썰기, 대파 1대 준비
-※ 복숭아는 당일 깎아서 제공</t>
+          <t>[돼지안심 소금구이]
+1. 돼지안심 600g → 1cm 두께로 썰기
+2. 소금 1t + 후추 → 양면에 고루 뿌려 냉장
+[배추된장국]
+3. 배추 3~4잎 → 한입 크기로 썰기
+4. 두부 1/2모 → 깍둑썰기
+5. 대파 1대 → 어슷썰기
+6. 냄비에 물 1L + 코인육수 1개 세팅
+[계란찜]
+7. 계란 4개 + 물 200ml + 소금 1/2t 섞어 냉장
+   ※ 새우젓 1/2t 넣으면 감칠맛 UP
+[감자채볶음]
+8. 감자 2개 → 가늘게 채썰기 → 찬물 10분 전분 빼기
+※ 가래떡은 재고분 사용</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
+          <t>★ 식사 25분 전 시작
+[배추된장국 — 먼저]
+1. 물+코인육수 센불로 끓이기
+2. 된장 2T 풀고 배추 중불 3분
+3. 두부+다진마늘 3분
+4. 대파 마무리
+[계란찜]
+5. 뚝배기에 계란물 넣고 중불
+6. 가장자리 익으면 섞기 → 뚜껑 약불 5분
+7. 참기름+깨 마무리
+[감자채볶음]
+8. 팬에 기름, 감자채 중불 3~4분
+9. 소금+후추, 투명해지면 완성
+[돼지안심 소금구이 — 스텐팬]
+10. 예열 → 물방울 테스트 → 기름
+11. 안심 한쪽 2분 → 뒤집어 2분
+    ※ 핑크빛 남을 때 꺼내기!
+[가래떡구이]
+12. 팬에 기름, 중불 앞뒤 노릇
+13. 간장 1T + 설탕 1T 졸이기 → 깨</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="250.5" customHeight="1" s="90">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>수 (6/17)</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>삼치 데리야끼강정
++ 두부전 + 김구이
++ 옥수수 (간식)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>[삼치 데리야끼강정]
+1. 냉동 삼치살 → 냉장 해동
+2. 키친타올로 물기 완전 제거
+3. 한입 크기로 자르기 (아이들 먹기 좋게)
+4. 소금 1/2t + 후추 → 밑간 후 냉장
+5. 데리야끼 소스: 간장 3T + 미림 2T + 설탕 1.5T + 물 2T → 섞어 냉장
+6. 감자전분 별도 준비
+[두부전]
+7. 두부 1모 → 1cm 두께, 물기 빼기
+8. 부침가루 3T
+9. 계란 2개 풀어 냉장
+[옥수수]
+10. 옥수수 3개 → 삶아서 냉장</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
           <t>★ 식사 20분 전 시작
-[오뎅탕 — 도우미님]
-1. 냄비에 물 1.5L + 다시팩 + 무 센불
-2. 끓으면 다시팩 빼고 중불 10분
-3. 어묵 꼬치 넣고 5분
-4. 간장 1T + 맛술 1T로 간
-5. 대파 넣어 마무리
-[오야코동 — 스텐팬]
-6. 스텐팬 중불 예열 → 물방울 테스트 → 기름
-7. 소스+양파 넣고 끓이기 (양파 투명 2분)
-8. 닭 넣고 뚜껑 중불 3분
-9. 달걀 절반 둥글게 부어 뚜껑 1분
-10. 나머지 달걀 부어 불 끄고 뚜껑 20초
-    ※ 반숙 상태로! 밥 위에 올려 완성
-[복숭아] 깎아서 접시에 담기</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="337.5" customHeight="1" s="90">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>수 (6/10)</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>삼치 소금구이
-+ 맑은 양지국
-+ 감자전 (넉넉히, 간식 겸용)</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>[삼치 소금구이]
-1. 냉장 삼치 토막 4조각 → 키친타올로 물기 완벽 제거
-2. 밑간: 맛술 1T 뿌려 5분 → 키친타올로 닦기
-3. 양면에 소금 0.5t씩 고루 뿌리기 → 냉장
-[맑은 양지국]
-4. 양지머리 200g(냉동 잔여) 해동
-   → 찬물에 30분 핏물 빼기
-5. 냄비에 물 1.2L + 대파 뿌리 세팅
-[감자전 — 넉넉히 (간식 겸용)]
-6. 감자 3~4개 → 껍질 벗겨 강판에 갈기
-   → 면보로 물기 꼭 짜기
-7. 전분 1.5T + 소금 약간 섞어 냉장
-   ※ 반죽 넉넉히! 식사+간식용</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
+[삼치 데리야끼강정 — 먼저]
+1. 삼치에 감자전분 고루 묻히기 (여분 털기)
+2. 팬에 기름 넉넉히, 중불
+3. 앞뒤 각 3분씩 바삭하게 튀기기
+4. 키친타올에 기름 빼기
+5. 다른 팬에 데리야끼 소스 → 중불 졸이기
+6. 걸쭉해지면 삼치 넣고 소스 끼얹기 → 깨 뿌려 마무리
+[두부전]
+7. 부침가루 묻히기
+8. 계란물에 담가 중불 부치기
+9. 앞뒤 각 2분
+[김구이] 참기름 발라 약불 구이 (또는 시판 구운김)
+[옥수수] 전자레인지 2분 데우기</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="279.5" customHeight="1" s="90">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>금 (6/19)</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>닭다리살 카레소스구이
++ 레토르트 미역국(소진)
++ 소시지야채볶음
++ 제철 과일 (간식)</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>[닭다리살 카레소스구이]
+1. 닭다리살 700g → 한입 크기
+2. 카레소스: 카레가루 2T + 간장 2T + 설탕 1T
+   + 다진마늘 1T + 맛술 1T → 섞기
+3. 닭에 버무려 냉장 (하룻밤)
+[레토르트 미역국]
+4. 냉동실 레토르트 미역국 꺼내 냉장 해동
+[소시지야채볶음]
+5. 비엔나소시지 1팩(200g) → 칼집
+6. 양파 1/2개 채썰기, 당근 1/4개 채썰기</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>★ 식사 25분 전 시작
-[맑은 양지국 — 먼저 (시간 필요)]
-1. 냄비에 물+양지+대파뿌리 센불
-2. 끓으면 거품 걷고 중불 20분
-3. 양지 건져 먹기좋게 썰어 다시 넣기
-4. 국간장 1T + 소금 + 대파 마무리
-[감자전 — 스텐팬]
-5. 스텐팬 중불 예열 1~2분
-   → 물방울 테스트 (구슬처럼 굴러가면 OK)
-   → 기름 넉넉히 두르기
-6. 감자반죽 한 숟가락씩 납작하게 올리기
-7. 앞뒤 각 3분씩 노릇하게
-   ※ 뒤집기 전 충분히 익혀야 안 붙음!
-   ※ 넉넉히 부쳐서 일부는 간식용으로 따로 담기
-[삼치구이 — 마지막, 코팅팬]
-8. 코팅팬 중불로 달구기 + 기름 1T
-9. 삼치 껍질면 아래로 올리기
-10. 껍질면 4분 (바삭해질 때까지)
-11. 뒤집어서 약불 3분
-    ※ 생선은 코팅팬 사용! 스텐팬은 눌어붙음 위험</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="352" customHeight="1" s="90">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>금 (6/12)</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>에비마요 (새우마요네즈)
-+ 파달걀국
-+ 오리 장조림 + 꿀떡꼬치</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>[에비마요 — 튀기지 않는 버전]
-1. 신선 새우 400g → 껍질·내장 제거 → 물에 씻기 → 물기 제거
-2. 밑간: 청주(맛술) 2T + 후추 → 버무려 냉장
-3. 전분가루 3T 별도 준비
-4. 마요소스: 마요4T + 케첩1T + 설탕2t + 레몬즙(식초)1T → 섞어 냉장
-[오리 장조림 — 전날 완성]
-5. 오리 슬라이스 250g(재고)
-6. 간장 3T + 맛술 2T + 올리고당 2T + 물 100ml
-   + 통마늘 5알 + 대파 흰 부분 1토막
-7. 냄비에 소스 끓인 뒤 오리 넣고 중약불 15분 졸이기
-   → 식혀서 냉장 (당일 꺼내기만)
-[파달걀국]
-8. 대파 1대 → 송송썰기
-9. 달걀 3개 풀어두기 → 냉장
-[꿀떡꼬치]
-10. 가래떡 200g → 4cm 길이로 잘라 꼬치에 3~4개씩
-11. 소스: 간장1T + 올리고당2T + 물1T + 참기름 약간 섞기</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>★ 식사 20분 전 시작
-[파달걀국 — 먼저]
-1. 냄비에 물 800ml 센불로 끓이기
-2. 대파 넣고 국간장 1T + 소금 간
-3. 달걀 풀어 가늘게 돌려 붓기
-4. 10초 후 불 끄기
-[꿀떡꼬치]
-5. 끓는 물에 떡꼬치 1분 삶아 말랑하게
-6. 팬에 기름 살짝, 중불에 앞뒤 노릇하게 굽기
-7. 소스 끼얹으며 중불 1분 졸이기 → 깨 뿌리기
-[에비마요 — 마지막, 스텐팬]
-8. 새우에 전분가루 고루 묻히기 (하나하나 떼어서)
-9. 스텐팬 중불 예열 → 물방울 테스트 → 기름 넉넉히
-10. 새우 올려 한쪽 2분 → 뒤집어 2분 (노릇바삭)
-11. 불 끄고 마요소스 넣어 재빨리 버무리기
-    ※ 잔열로만! 소스 분리 방지
-[오리 장조림]
-12. 냉장 보관된 오리 장조림 꺼내 접시에 담기</t>
+[레토르트 미역국 — 먼저]
+1. 냄비에 레토르트 미역국 붓고 중불 데우기
+2. 끓으면 약불 보온
+   ※ 재고 소진 목적 — 간 확인 후 필요시 국간장 추가
+[소시지야채볶음]
+3. 팬에 기름, 소시지 중불 2분 (칼집 벌어질 때까지)
+4. 양파+당근 넣고 2분 더 볶기
+5. 간장 1T + 설탕 1/2T → 깨
+[닭다리살 카레소스구이 — 마지막]
+6. 팬에 기름 넉넉히, 중불
+7. 닭 껍질면 아래로 3분 (바삭하게)
+8. 뒤집어 2분 → 남은 양념 끼얹으며 약불 2분
+   ※ 카레 양념이 탈 수 있으니 불 조절 주의
+[제철 과일] 씻어서 접시에 담기</t>
         </is>
       </c>
     </row>
@@ -4820,7 +4659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
   <cols>
     <col width="25" customWidth="1" style="90" min="1" max="1"/>
@@ -4833,7 +4672,7 @@
     <row r="1" ht="25" customHeight="1" s="90">
       <c r="A1" s="94" t="inlineStr">
         <is>
-          <t>6월 2주차 장보기 목록  (잔여: 양지머리·오리슬라이스·복숭아 / 도우미님: 오뎅탕 재료)</t>
+          <t>6월 3주차 장보기 목록  (재고: 가래떡)</t>
         </is>
       </c>
     </row>
@@ -4878,493 +4717,561 @@
     <row r="4" ht="18.5" customHeight="1" s="90">
       <c r="A4" s="7" t="inlineStr">
         <is>
+          <t>돼지안심 (냉장)</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>600g</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>화(소금구이)</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>3주차 구매</t>
+        </is>
+      </c>
+      <c r="E4" s="139" t="n">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="5" ht="18.5" customHeight="1" s="90">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
           <t>닭다리살 (순살, 냉장)</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>700g</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>화(오야코동)</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>2주차 구매</t>
-        </is>
-      </c>
-      <c r="E4" s="139" t="n">
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>금(카레소스구이)</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>3주차 구매</t>
+        </is>
+      </c>
+      <c r="E5" s="139" t="n">
         <v>9000</v>
       </c>
-    </row>
-    <row r="5" ht="18.5" customHeight="1" s="90">
-      <c r="A5" s="105" t="inlineStr">
-        <is>
-          <t>수산</t>
-        </is>
-      </c>
-      <c r="B5" s="105" t="n"/>
-      <c r="C5" s="105" t="n"/>
-      <c r="D5" s="105" t="n"/>
-      <c r="E5" s="105" t="n"/>
     </row>
     <row r="6" ht="18.5" customHeight="1" s="90">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>삼치 토막 (손질, 냉장)</t>
+          <t>양지머리</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>4조각</t>
+          <t>300g</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>수(삼치구이)</t>
+          <t>금(미역국)</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>2주차 구매</t>
+          <t>3주차 구매</t>
         </is>
       </c>
       <c r="E6" s="139" t="n">
-        <v>10000</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="7" ht="18.5" customHeight="1" s="90">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>신선 새우 (중하)</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>400g</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>금(에비마요)</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>2주차 구매</t>
-        </is>
-      </c>
-      <c r="E7" s="139" t="n">
-        <v>14000</v>
-      </c>
+      <c r="A7" s="105" t="inlineStr">
+        <is>
+          <t>수산</t>
+        </is>
+      </c>
+      <c r="B7" s="105" t="n"/>
+      <c r="C7" s="105" t="n"/>
+      <c r="D7" s="105" t="n"/>
+      <c r="E7" s="105" t="n"/>
     </row>
     <row r="8" ht="18.5" customHeight="1" s="90">
-      <c r="A8" s="96" t="inlineStr">
-        <is>
-          <t>채소</t>
-        </is>
-      </c>
-      <c r="B8" s="96" t="n"/>
-      <c r="C8" s="96" t="n"/>
-      <c r="D8" s="96" t="n"/>
-      <c r="E8" s="96" t="n"/>
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>대구살 필렛 (냉장)</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>수(간장무조림)</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>3주차 구매</t>
+        </is>
+      </c>
+      <c r="E8" s="139" t="n">
+        <v>12000</v>
+      </c>
     </row>
     <row r="9" ht="18.5" customHeight="1" s="90">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>양파</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>2개</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>화(오야코동)+수(양지국)</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>2주차 구매</t>
-        </is>
-      </c>
-      <c r="E9" s="139" t="n">
-        <v>1000</v>
-      </c>
+      <c r="A9" s="101" t="inlineStr">
+        <is>
+          <t>두부류</t>
+        </is>
+      </c>
+      <c r="B9" s="101" t="n"/>
+      <c r="C9" s="101" t="n"/>
+      <c r="D9" s="101" t="n"/>
+      <c r="E9" s="101" t="n"/>
     </row>
     <row r="10" ht="18.5" customHeight="1" s="90">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>대파</t>
+          <t>두부</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>3대</t>
+          <t>1.5모</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>화·수·금 전체</t>
+          <t>화(된장국)+수(두부전)</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>2주차 구매</t>
+          <t>3주차 구매</t>
         </is>
       </c>
       <c r="E10" s="139" t="n">
-        <v>1500</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="11" ht="18.5" customHeight="1" s="90">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>감자</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>2개 (추가분)</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>수(감자전 넉넉히)</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>2주차 구매</t>
-        </is>
-      </c>
-      <c r="E11" s="139" t="n">
-        <v>1500</v>
-      </c>
+      <c r="A11" s="98" t="inlineStr">
+        <is>
+          <t>해조류</t>
+        </is>
+      </c>
+      <c r="B11" s="98" t="n"/>
+      <c r="C11" s="98" t="n"/>
+      <c r="D11" s="98" t="n"/>
+      <c r="E11" s="98" t="n"/>
     </row>
     <row r="12" ht="18.5" customHeight="1" s="90">
       <c r="A12" s="7" t="inlineStr">
         <is>
+          <t>염장미역</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>50g</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>금(미역국)</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>3주차 구매</t>
+        </is>
+      </c>
+      <c r="E12" s="139" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="13" ht="18.5" customHeight="1" s="90">
+      <c r="A13" s="96" t="inlineStr">
+        <is>
+          <t>채소</t>
+        </is>
+      </c>
+      <c r="B13" s="96" t="n"/>
+      <c r="C13" s="96" t="n"/>
+      <c r="D13" s="96" t="n"/>
+      <c r="E13" s="96" t="n"/>
+    </row>
+    <row r="14" ht="18.5" customHeight="1" s="90">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>배추</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>1/4포기</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>화(된장국)</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>3주차 구매</t>
+        </is>
+      </c>
+      <c r="E14" s="139" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="15" ht="18.5" customHeight="1" s="90">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
           <t>무</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>1/4쪽</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>화(오뎅탕)+수(양지국)</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>2주차 구매</t>
-        </is>
-      </c>
-      <c r="E12" s="139" t="n">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="13" ht="18.5" customHeight="1" s="90">
-      <c r="A13" s="25" t="inlineStr">
-        <is>
-          <t>달걀</t>
-        </is>
-      </c>
-      <c r="B13" s="44" t="n"/>
-      <c r="C13" s="44" t="n"/>
-      <c r="D13" s="44" t="n"/>
-      <c r="E13" s="44" t="n"/>
-    </row>
-    <row r="14" ht="33" customHeight="1" s="90">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>달걀</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>10개(1판)</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>화(오야코동5)+금(달걀국3+장조림)</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>2주차 구매</t>
-        </is>
-      </c>
-      <c r="E14" s="139" t="n">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="15" ht="18.5" customHeight="1" s="90">
-      <c r="A15" s="26" t="inlineStr">
-        <is>
-          <t>가공식품</t>
-        </is>
-      </c>
-      <c r="B15" s="45" t="n"/>
-      <c r="C15" s="45" t="n"/>
-      <c r="D15" s="45" t="n"/>
-      <c r="E15" s="45" t="n"/>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>1/2개</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>수(대구조림)</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>3주차 구매</t>
+        </is>
+      </c>
+      <c r="E15" s="139" t="n">
+        <v>1500</v>
+      </c>
     </row>
     <row r="16" ht="18.5" customHeight="1" s="90">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>가래떡</t>
+          <t>감자</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>200g</t>
+          <t>2개</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>금(꿀떡꼬치)</t>
+          <t>화(감자채볶음)</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>2주차 구매</t>
+          <t>3주차 구매</t>
         </is>
       </c>
       <c r="E16" s="139" t="n">
-        <v>2500</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="17" ht="18.5" customHeight="1" s="90">
-      <c r="A17" s="35" t="inlineStr">
-        <is>
-          <t>양념/기타</t>
-        </is>
-      </c>
-      <c r="B17" s="46" t="n"/>
-      <c r="C17" s="46" t="n"/>
-      <c r="D17" s="46" t="n"/>
-      <c r="E17" s="46" t="n"/>
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>양파</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>1개</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>금(소시지볶음)</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>3주차 구매</t>
+        </is>
+      </c>
+      <c r="E17" s="139" t="n">
+        <v>500</v>
+      </c>
     </row>
     <row r="18" ht="18.5" customHeight="1" s="90">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>마요네즈</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>재고 확인</t>
+          <t>당근</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>1개</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>금(에비마요)</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>재고</t>
-        </is>
-      </c>
-      <c r="E18" s="47" t="n"/>
+          <t>금(소시지볶음)</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>3주차 구매</t>
+        </is>
+      </c>
+      <c r="E18" s="139" t="n">
+        <v>800</v>
+      </c>
     </row>
     <row r="19" ht="18.5" customHeight="1" s="90">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>케첩</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>재고 확인</t>
+          <t>대파</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>3대</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>금(에비마요 소스)</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>재고</t>
-        </is>
-      </c>
-      <c r="E19" s="47" t="n"/>
+          <t>화·수·금 전체</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>3주차 구매</t>
+        </is>
+      </c>
+      <c r="E19" s="139" t="n">
+        <v>1500</v>
+      </c>
     </row>
     <row r="20" ht="18.5" customHeight="1" s="90">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>전분가루</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>재고 확인</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>금(에비마요)+수(감자전)</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>재고</t>
-        </is>
-      </c>
-      <c r="E20" s="47" t="n"/>
+      <c r="A20" s="25" t="inlineStr">
+        <is>
+          <t>달걀</t>
+        </is>
+      </c>
+      <c r="B20" s="38" t="n"/>
+      <c r="C20" s="38" t="n"/>
+      <c r="D20" s="38" t="n"/>
+      <c r="E20" s="38" t="n"/>
     </row>
     <row r="21" ht="18.5" customHeight="1" s="90">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>올리고당</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>재고 확인</t>
+          <t>달걀</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>10개(1판)</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>금(오리장조림+떡꼬치)</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>재고</t>
-        </is>
-      </c>
-      <c r="E21" s="47" t="n"/>
+          <t>화(계란찜4)+수(두부전2)</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>3주차 구매</t>
+        </is>
+      </c>
+      <c r="E21" s="139" t="n">
+        <v>3000</v>
+      </c>
     </row>
     <row r="22" ht="18.5" customHeight="1" s="90">
-      <c r="A22" s="42" t="inlineStr">
-        <is>
-          <t>잔여재료 (구매 불필요)</t>
-        </is>
-      </c>
-      <c r="B22" s="48" t="n"/>
-      <c r="C22" s="48" t="n"/>
-      <c r="D22" s="48" t="n"/>
-      <c r="E22" s="48" t="n"/>
+      <c r="A22" s="26" t="inlineStr">
+        <is>
+          <t>가공식품</t>
+        </is>
+      </c>
+      <c r="B22" s="39" t="n"/>
+      <c r="C22" s="39" t="n"/>
+      <c r="D22" s="39" t="n"/>
+      <c r="E22" s="39" t="n"/>
     </row>
     <row r="23" ht="18.5" customHeight="1" s="90">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>양지머리 (냉동)</t>
+          <t>비엔나소시지</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>200g</t>
+          <t>1팩(200g)</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>수(양지국) — 잔여</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>잔여</t>
-        </is>
-      </c>
-      <c r="E23" s="47" t="n"/>
+          <t>금(소시지야채볶음)</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>3주차 구매</t>
+        </is>
+      </c>
+      <c r="E23" s="139" t="n">
+        <v>3500</v>
+      </c>
     </row>
     <row r="24" ht="18.5" customHeight="1" s="90">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>오리 슬라이스</t>
+          <t>옥수수</t>
         </is>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>250g</t>
+          <t>3개</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>금(오리장조림) — 재고</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>잔여</t>
-        </is>
-      </c>
-      <c r="E24" s="47" t="n"/>
+          <t>수(간식)</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>3주차 구매</t>
+        </is>
+      </c>
+      <c r="E24" s="139" t="n">
+        <v>3000</v>
+      </c>
     </row>
     <row r="25" ht="18.5" customHeight="1" s="90">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>감자 (잔여)</t>
-        </is>
-      </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>2개</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>수(감자전) — 잔여</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>잔여</t>
-        </is>
-      </c>
-      <c r="E25" s="47" t="n"/>
+      <c r="A25" s="35" t="inlineStr">
+        <is>
+          <t>양념/기타</t>
+        </is>
+      </c>
+      <c r="B25" s="40" t="n"/>
+      <c r="C25" s="40" t="n"/>
+      <c r="D25" s="40" t="n"/>
+      <c r="E25" s="40" t="n"/>
     </row>
     <row r="26" ht="18.5" customHeight="1" s="90">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>복숭아 (재고)</t>
+          <t>카레가루</t>
         </is>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>2~3개</t>
+          <t>1팩</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>화(간식) — 집에 있음</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>잔여</t>
-        </is>
-      </c>
-      <c r="E26" s="47" t="n"/>
-    </row>
-    <row r="27" ht="18.5" customHeight="1" s="90"/>
-    <row r="28" ht="33" customHeight="1" s="90">
-      <c r="A28" s="32" t="inlineStr">
-        <is>
-          <t>예상 합계 (잔여재료 제외 신규 구매분)</t>
-        </is>
-      </c>
-      <c r="B28" s="32" t="n"/>
-      <c r="C28" s="32" t="n"/>
-      <c r="D28" s="32" t="n"/>
-      <c r="E28" s="148" t="n">
-        <v>43500</v>
+          <t>금(카레소스)</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>3주차 구매</t>
+        </is>
+      </c>
+      <c r="E26" s="139" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="27" ht="18.5" customHeight="1" s="90">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>코인육수</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>1개</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>화(된장국)</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>3주차 구매</t>
+        </is>
+      </c>
+      <c r="E27" s="139" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="28" ht="18.5" customHeight="1" s="90">
+      <c r="A28" s="42" t="inlineStr">
+        <is>
+          <t>잔여재료 (구매 불필요)</t>
+        </is>
+      </c>
+      <c r="B28" s="43" t="n"/>
+      <c r="C28" s="43" t="n"/>
+      <c r="D28" s="43" t="n"/>
+      <c r="E28" s="43" t="n"/>
+    </row>
+    <row r="29" ht="18.5" customHeight="1" s="90">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>가래떡 (재고)</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>적당량</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>화(가래떡구이)</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>재고</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>재고</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="18.5" customHeight="1" s="90"/>
+    <row r="31" ht="33" customHeight="1" s="90">
+      <c r="A31" s="36" t="inlineStr">
+        <is>
+          <t>예상 합계 (재고 제외 신규 구매분)</t>
+        </is>
+      </c>
+      <c r="B31" s="36" t="n"/>
+      <c r="C31" s="36" t="n"/>
+      <c r="D31" s="36" t="n"/>
+      <c r="E31" s="147" t="n">
+        <v>70100</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
@@ -5408,6 +5315,1462 @@
         </is>
       </c>
     </row>
+    <row r="2" ht="265" customHeight="1" s="90">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>화 (6/9)</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>오야코동 (닭+달걀 덮밥)
++ 오뎅탕 (도우미님 조리)
++ 복숭아</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>[오야코동 — 닭다리살 덮밥]
+1. 닭다리살 700g → 한입 크기(2cm)로 자르기
+2. 밑간: 소금 약간 + 후추 + 맛술 2큰술
+3. 양파 1.5개 → 0.5cm 채썰기
+4. 대파 1대 → 어슷썰기
+5. 소스: 간장4T + 맛술3T + 설탕2T + 물250ml 섞어 냉장
+   (쯔유 있으면 쯔유5T+물250ml로 대체)
+6. 달걀 5개 → 젓가락 10회만 가볍게 풀기 → 냉장
+[오뎅탕 — 도우미님 조리]
+7. 어묵 꼬치 세팅 (재고 소진)
+8. 무 100g 나박썰기, 대파 1대 준비
+※ 복숭아는 당일 깎아서 제공</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>★ 식사 20분 전 시작
+[오뎅탕 — 도우미님]
+1. 냄비에 물 1.5L + 다시팩 + 무 센불
+2. 끓으면 다시팩 빼고 중불 10분
+3. 어묵 꼬치 넣고 5분
+4. 간장 1T + 맛술 1T로 간
+5. 대파 넣어 마무리
+[오야코동 — 스텐팬]
+6. 스텐팬 중불 예열 → 물방울 테스트 → 기름
+7. 소스+양파 넣고 끓이기 (양파 투명 2분)
+8. 닭 넣고 뚜껑 중불 3분
+9. 달걀 절반 둥글게 부어 뚜껑 1분
+10. 나머지 달걀 부어 불 끄고 뚜껑 20초
+    ※ 반숙 상태로! 밥 위에 올려 완성
+[복숭아] 깎아서 접시에 담기</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="337.5" customHeight="1" s="90">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>수 (6/10)</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>삼치 소금구이
++ 맑은 양지국
++ 감자전 (넉넉히, 간식 겸용)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>[삼치 소금구이]
+1. 냉장 삼치 토막 4조각 → 키친타올로 물기 완벽 제거
+2. 밑간: 맛술 1T 뿌려 5분 → 키친타올로 닦기
+3. 양면에 소금 0.5t씩 고루 뿌리기 → 냉장
+[맑은 양지국]
+4. 양지머리 200g(냉동 잔여) 해동
+   → 찬물에 30분 핏물 빼기
+5. 냄비에 물 1.2L + 대파 뿌리 세팅
+[감자전 — 넉넉히 (간식 겸용)]
+6. 감자 3~4개 → 껍질 벗겨 강판에 갈기
+   → 면보로 물기 꼭 짜기
+7. 전분 1.5T + 소금 약간 섞어 냉장
+   ※ 반죽 넉넉히! 식사+간식용</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>★ 식사 25분 전 시작
+[맑은 양지국 — 먼저 (시간 필요)]
+1. 냄비에 물+양지+대파뿌리 센불
+2. 끓으면 거품 걷고 중불 20분
+3. 양지 건져 먹기좋게 썰어 다시 넣기
+4. 국간장 1T + 소금 + 대파 마무리
+[감자전 — 스텐팬]
+5. 스텐팬 중불 예열 1~2분
+   → 물방울 테스트 (구슬처럼 굴러가면 OK)
+   → 기름 넉넉히 두르기
+6. 감자반죽 한 숟가락씩 납작하게 올리기
+7. 앞뒤 각 3분씩 노릇하게
+   ※ 뒤집기 전 충분히 익혀야 안 붙음!
+   ※ 넉넉히 부쳐서 일부는 간식용으로 따로 담기
+[삼치구이 — 마지막, 코팅팬]
+8. 코팅팬 중불로 달구기 + 기름 1T
+9. 삼치 껍질면 아래로 올리기
+10. 껍질면 4분 (바삭해질 때까지)
+11. 뒤집어서 약불 3분
+    ※ 생선은 코팅팬 사용! 스텐팬은 눌어붙음 위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="352" customHeight="1" s="90">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>금 (6/12)</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>에비마요 (새우마요네즈)
++ 파달걀국
++ 오리 장조림 + 꿀떡꼬치</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>[에비마요 — 튀기지 않는 버전]
+1. 신선 새우 400g → 껍질·내장 제거 → 물에 씻기 → 물기 제거
+2. 밑간: 청주(맛술) 2T + 후추 → 버무려 냉장
+3. 전분가루 3T 별도 준비
+4. 마요소스: 마요4T + 케첩1T + 설탕2t + 레몬즙(식초)1T → 섞어 냉장
+[오리 장조림 — 전날 완성]
+5. 오리 슬라이스 250g(재고)
+6. 간장 3T + 맛술 2T + 올리고당 2T + 물 100ml
+   + 통마늘 5알 + 대파 흰 부분 1토막
+7. 냄비에 소스 끓인 뒤 오리 넣고 중약불 15분 졸이기
+   → 식혀서 냉장 (당일 꺼내기만)
+[파달걀국]
+8. 대파 1대 → 송송썰기
+9. 달걀 3개 풀어두기 → 냉장
+[꿀떡꼬치]
+10. 가래떡 200g → 4cm 길이로 잘라 꼬치에 3~4개씩
+11. 소스: 간장1T + 올리고당2T + 물1T + 참기름 약간 섞기</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>★ 식사 20분 전 시작
+[파달걀국 — 먼저]
+1. 냄비에 물 800ml 센불로 끓이기
+2. 대파 넣고 국간장 1T + 소금 간
+3. 달걀 풀어 가늘게 돌려 붓기
+4. 10초 후 불 끄기
+[꿀떡꼬치]
+5. 끓는 물에 떡꼬치 1분 삶아 말랑하게
+6. 팬에 기름 살짝, 중불에 앞뒤 노릇하게 굽기
+7. 소스 끼얹으며 중불 1분 졸이기 → 깨 뿌리기
+[에비마요 — 마지막, 스텐팬]
+8. 새우에 전분가루 고루 묻히기 (하나하나 떼어서)
+9. 스텐팬 중불 예열 → 물방울 테스트 → 기름 넉넉히
+10. 새우 올려 한쪽 2분 → 뒤집어 2분 (노릇바삭)
+11. 불 끄고 마요소스 넣어 재빨리 버무리기
+    ※ 잔열로만! 소스 분리 방지
+[오리 장조림]
+12. 냉장 보관된 오리 장조림 꺼내 접시에 담기</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.4" right="0.4" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" style="90" min="1" max="1"/>
+    <col width="14" customWidth="1" style="90" min="2" max="2"/>
+    <col width="28" customWidth="1" style="90" min="3" max="3"/>
+    <col width="16" customWidth="1" style="90" min="4" max="4"/>
+    <col width="14" customWidth="1" style="90" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1" s="90">
+      <c r="A1" s="121" t="inlineStr">
+        <is>
+          <t>8월 3주차 장보기 (8/11~8/14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="118" t="inlineStr">
+        <is>
+          <t>재료</t>
+        </is>
+      </c>
+      <c r="B2" s="118" t="inlineStr">
+        <is>
+          <t>수량</t>
+        </is>
+      </c>
+      <c r="C2" s="118" t="inlineStr">
+        <is>
+          <t>사용 메뉴</t>
+        </is>
+      </c>
+      <c r="D2" s="118" t="inlineStr">
+        <is>
+          <t>구매 시기</t>
+        </is>
+      </c>
+      <c r="E2" s="118" t="inlineStr">
+        <is>
+          <t>예상 금액</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="122" t="inlineStr">
+        <is>
+          <t>정육</t>
+        </is>
+      </c>
+      <c r="B3" s="123" t="n"/>
+      <c r="C3" s="123" t="n"/>
+      <c r="D3" s="123" t="n"/>
+      <c r="E3" s="123" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="124" t="inlineStr">
+        <is>
+          <t>부채살 (소고기)</t>
+        </is>
+      </c>
+      <c r="B4" s="124" t="inlineStr">
+        <is>
+          <t>600g</t>
+        </is>
+      </c>
+      <c r="C4" s="124" t="inlineStr">
+        <is>
+          <t>소고기 찹스테이크</t>
+        </is>
+      </c>
+      <c r="D4" s="124" t="inlineStr">
+        <is>
+          <t>8/10 구매</t>
+        </is>
+      </c>
+      <c r="E4" s="125" t="n">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="124" t="inlineStr">
+        <is>
+          <t>돼지 앞다리살</t>
+        </is>
+      </c>
+      <c r="B5" s="124" t="inlineStr">
+        <is>
+          <t>600g</t>
+        </is>
+      </c>
+      <c r="C5" s="124" t="inlineStr">
+        <is>
+          <t>앞다리살 데리야끼</t>
+        </is>
+      </c>
+      <c r="D5" s="124" t="inlineStr">
+        <is>
+          <t>8/11 구매</t>
+        </is>
+      </c>
+      <c r="E5" s="125" t="n">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="124" t="inlineStr">
+        <is>
+          <t>닭다리살</t>
+        </is>
+      </c>
+      <c r="B6" s="124" t="inlineStr">
+        <is>
+          <t>400g</t>
+        </is>
+      </c>
+      <c r="C6" s="124" t="inlineStr">
+        <is>
+          <t>오야코동</t>
+        </is>
+      </c>
+      <c r="D6" s="124" t="inlineStr">
+        <is>
+          <t>8/13 구매</t>
+        </is>
+      </c>
+      <c r="E6" s="125" t="n">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="124" t="inlineStr">
+        <is>
+          <t>양지머리</t>
+        </is>
+      </c>
+      <c r="B7" s="124" t="inlineStr">
+        <is>
+          <t>250g</t>
+        </is>
+      </c>
+      <c r="C7" s="124" t="inlineStr">
+        <is>
+          <t>양지 미역국</t>
+        </is>
+      </c>
+      <c r="D7" s="124" t="inlineStr">
+        <is>
+          <t>8/11 구매</t>
+        </is>
+      </c>
+      <c r="E7" s="125" t="n">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="126" t="inlineStr">
+        <is>
+          <t>수산</t>
+        </is>
+      </c>
+      <c r="B8" s="127" t="n"/>
+      <c r="C8" s="127" t="n"/>
+      <c r="D8" s="127" t="n"/>
+      <c r="E8" s="127" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="124" t="inlineStr">
+        <is>
+          <t>국물용 멸치</t>
+        </is>
+      </c>
+      <c r="B9" s="124" t="inlineStr">
+        <is>
+          <t>1봉</t>
+        </is>
+      </c>
+      <c r="C9" s="124" t="inlineStr">
+        <is>
+          <t>만능육수 전부</t>
+        </is>
+      </c>
+      <c r="D9" s="124" t="inlineStr">
+        <is>
+          <t>8/10 구매</t>
+        </is>
+      </c>
+      <c r="E9" s="125" t="n">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="124" t="inlineStr">
+        <is>
+          <t>다시마</t>
+        </is>
+      </c>
+      <c r="B10" s="124" t="inlineStr">
+        <is>
+          <t>1봉</t>
+        </is>
+      </c>
+      <c r="C10" s="124" t="inlineStr">
+        <is>
+          <t>만능육수 전부</t>
+        </is>
+      </c>
+      <c r="D10" s="124" t="inlineStr">
+        <is>
+          <t>8/10 구매</t>
+        </is>
+      </c>
+      <c r="E10" s="125" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="124" t="inlineStr">
+        <is>
+          <t>건새우</t>
+        </is>
+      </c>
+      <c r="B11" s="124" t="inlineStr">
+        <is>
+          <t>1봉</t>
+        </is>
+      </c>
+      <c r="C11" s="124" t="inlineStr">
+        <is>
+          <t>만능육수(감칠맛)</t>
+        </is>
+      </c>
+      <c r="D11" s="124" t="inlineStr">
+        <is>
+          <t>8/10 구매</t>
+        </is>
+      </c>
+      <c r="E11" s="125" t="n">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="128" t="inlineStr">
+        <is>
+          <t>채소</t>
+        </is>
+      </c>
+      <c r="B12" s="129" t="n"/>
+      <c r="C12" s="129" t="n"/>
+      <c r="D12" s="129" t="n"/>
+      <c r="E12" s="129" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="124" t="inlineStr">
+        <is>
+          <t>양파</t>
+        </is>
+      </c>
+      <c r="B13" s="124" t="inlineStr">
+        <is>
+          <t>3개</t>
+        </is>
+      </c>
+      <c r="C13" s="124" t="inlineStr">
+        <is>
+          <t>찹스테이크/데리야끼/오야코동</t>
+        </is>
+      </c>
+      <c r="D13" s="124" t="inlineStr">
+        <is>
+          <t>8/10 구매</t>
+        </is>
+      </c>
+      <c r="E13" s="125" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="124" t="inlineStr">
+        <is>
+          <t>파프리카</t>
+        </is>
+      </c>
+      <c r="B14" s="124" t="inlineStr">
+        <is>
+          <t>1개</t>
+        </is>
+      </c>
+      <c r="C14" s="124" t="inlineStr">
+        <is>
+          <t>찹스테이크</t>
+        </is>
+      </c>
+      <c r="D14" s="124" t="inlineStr">
+        <is>
+          <t>8/10 구매</t>
+        </is>
+      </c>
+      <c r="E14" s="125" t="n">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="124" t="inlineStr">
+        <is>
+          <t>양송이버섯</t>
+        </is>
+      </c>
+      <c r="B15" s="124" t="inlineStr">
+        <is>
+          <t>1팩</t>
+        </is>
+      </c>
+      <c r="C15" s="124" t="inlineStr">
+        <is>
+          <t>찹스테이크</t>
+        </is>
+      </c>
+      <c r="D15" s="124" t="inlineStr">
+        <is>
+          <t>8/10 구매</t>
+        </is>
+      </c>
+      <c r="E15" s="125" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="124" t="inlineStr">
+        <is>
+          <t>감자</t>
+        </is>
+      </c>
+      <c r="B16" s="124" t="inlineStr">
+        <is>
+          <t>3개</t>
+        </is>
+      </c>
+      <c r="C16" s="124" t="inlineStr">
+        <is>
+          <t>매쉬포테이토</t>
+        </is>
+      </c>
+      <c r="D16" s="124" t="inlineStr">
+        <is>
+          <t>8/10 구매</t>
+        </is>
+      </c>
+      <c r="E16" s="125" t="n">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="124" t="inlineStr">
+        <is>
+          <t>콩나물</t>
+        </is>
+      </c>
+      <c r="B17" s="124" t="inlineStr">
+        <is>
+          <t>1봉</t>
+        </is>
+      </c>
+      <c r="C17" s="124" t="inlineStr">
+        <is>
+          <t>콩나물국</t>
+        </is>
+      </c>
+      <c r="D17" s="124" t="inlineStr">
+        <is>
+          <t>8/10 구매</t>
+        </is>
+      </c>
+      <c r="E17" s="125" t="n">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="124" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="B18" s="124" t="inlineStr">
+        <is>
+          <t>1개</t>
+        </is>
+      </c>
+      <c r="C18" s="124" t="inlineStr">
+        <is>
+          <t>무국/육수</t>
+        </is>
+      </c>
+      <c r="D18" s="124" t="inlineStr">
+        <is>
+          <t>8/10 구매</t>
+        </is>
+      </c>
+      <c r="E18" s="125" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="124" t="inlineStr">
+        <is>
+          <t>애호박</t>
+        </is>
+      </c>
+      <c r="B19" s="124" t="inlineStr">
+        <is>
+          <t>1개</t>
+        </is>
+      </c>
+      <c r="C19" s="124" t="inlineStr">
+        <is>
+          <t>애호박전</t>
+        </is>
+      </c>
+      <c r="D19" s="124" t="inlineStr">
+        <is>
+          <t>8/13 구매</t>
+        </is>
+      </c>
+      <c r="E19" s="125" t="n">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="124" t="inlineStr">
+        <is>
+          <t>대파</t>
+        </is>
+      </c>
+      <c r="B20" s="124" t="inlineStr">
+        <is>
+          <t>2대</t>
+        </is>
+      </c>
+      <c r="C20" s="124" t="inlineStr">
+        <is>
+          <t>국·요리 전반</t>
+        </is>
+      </c>
+      <c r="D20" s="124" t="inlineStr">
+        <is>
+          <t>8/10 구매</t>
+        </is>
+      </c>
+      <c r="E20" s="125" t="n">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="132" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="B21" s="133" t="n"/>
+      <c r="C21" s="133" t="n"/>
+      <c r="D21" s="133" t="n"/>
+      <c r="E21" s="133" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="124" t="inlineStr">
+        <is>
+          <t>어린이김치(키즈김치)</t>
+        </is>
+      </c>
+      <c r="B22" s="124" t="inlineStr">
+        <is>
+          <t>1팩</t>
+        </is>
+      </c>
+      <c r="C22" s="124" t="inlineStr">
+        <is>
+          <t>상시 반찬(매 끼니)</t>
+        </is>
+      </c>
+      <c r="D22" s="124" t="inlineStr">
+        <is>
+          <t>8/10 구매</t>
+        </is>
+      </c>
+      <c r="E22" s="125" t="n">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="124" t="inlineStr">
+        <is>
+          <t>염장미역</t>
+        </is>
+      </c>
+      <c r="B23" s="124" t="inlineStr">
+        <is>
+          <t>1팩</t>
+        </is>
+      </c>
+      <c r="C23" s="124" t="inlineStr">
+        <is>
+          <t>양지 미역국</t>
+        </is>
+      </c>
+      <c r="D23" s="124" t="inlineStr">
+        <is>
+          <t>8/10 구매</t>
+        </is>
+      </c>
+      <c r="E23" s="125" t="n">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="124" t="inlineStr">
+        <is>
+          <t>달걀</t>
+        </is>
+      </c>
+      <c r="B24" s="124" t="inlineStr">
+        <is>
+          <t>15개입</t>
+        </is>
+      </c>
+      <c r="C24" s="124" t="inlineStr">
+        <is>
+          <t>계란말이/오야코동</t>
+        </is>
+      </c>
+      <c r="D24" s="124" t="inlineStr">
+        <is>
+          <t>8/10 구매</t>
+        </is>
+      </c>
+      <c r="E24" s="125" t="n">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="124" t="inlineStr">
+        <is>
+          <t>스테이크소스</t>
+        </is>
+      </c>
+      <c r="B25" s="124" t="inlineStr">
+        <is>
+          <t>1병(상비 가능)</t>
+        </is>
+      </c>
+      <c r="C25" s="124" t="inlineStr">
+        <is>
+          <t>찹스테이크</t>
+        </is>
+      </c>
+      <c r="D25" s="124" t="inlineStr">
+        <is>
+          <t>상비 확인</t>
+        </is>
+      </c>
+      <c r="E25" s="125" t="n">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="124" t="inlineStr">
+        <is>
+          <t>마른표고·멸치액젓</t>
+        </is>
+      </c>
+      <c r="B26" s="124" t="inlineStr">
+        <is>
+          <t>상비 확인</t>
+        </is>
+      </c>
+      <c r="C26" s="124" t="inlineStr">
+        <is>
+          <t>육수 감칠맛</t>
+        </is>
+      </c>
+      <c r="D26" s="124" t="inlineStr">
+        <is>
+          <t>상비 확인</t>
+        </is>
+      </c>
+      <c r="E26" s="125" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="124" t="inlineStr">
+        <is>
+          <t>수박</t>
+        </is>
+      </c>
+      <c r="B27" s="124" t="inlineStr">
+        <is>
+          <t>1통</t>
+        </is>
+      </c>
+      <c r="C27" s="124" t="inlineStr">
+        <is>
+          <t>간식</t>
+        </is>
+      </c>
+      <c r="D27" s="124" t="inlineStr">
+        <is>
+          <t>8/10 구매</t>
+        </is>
+      </c>
+      <c r="E27" s="125" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="124" t="inlineStr">
+        <is>
+          <t>참외</t>
+        </is>
+      </c>
+      <c r="B28" s="124" t="inlineStr">
+        <is>
+          <t>4개</t>
+        </is>
+      </c>
+      <c r="C28" s="124" t="inlineStr">
+        <is>
+          <t>간식</t>
+        </is>
+      </c>
+      <c r="D28" s="124" t="inlineStr">
+        <is>
+          <t>8/11 구매</t>
+        </is>
+      </c>
+      <c r="E28" s="125" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="124" t="inlineStr">
+        <is>
+          <t>옥수수</t>
+        </is>
+      </c>
+      <c r="B29" s="124" t="inlineStr">
+        <is>
+          <t>2개</t>
+        </is>
+      </c>
+      <c r="C29" s="124" t="inlineStr">
+        <is>
+          <t>간식</t>
+        </is>
+      </c>
+      <c r="D29" s="124" t="inlineStr">
+        <is>
+          <t>8/10 구매</t>
+        </is>
+      </c>
+      <c r="E29" s="125" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="134" t="inlineStr">
+        <is>
+          <t>합계</t>
+        </is>
+      </c>
+      <c r="B30" s="134" t="n"/>
+      <c r="C30" s="134" t="n"/>
+      <c r="D30" s="135" t="inlineStr">
+        <is>
+          <t>가격 합계</t>
+        </is>
+      </c>
+      <c r="E30" s="136" t="n">
+        <v>107000</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.4" right="0.4" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E28"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
+  <cols>
+    <col width="25" customWidth="1" style="90" min="1" max="1"/>
+    <col width="14" customWidth="1" style="90" min="2" max="2"/>
+    <col width="28" customWidth="1" style="90" min="3" max="3"/>
+    <col width="16" customWidth="1" style="90" min="4" max="4"/>
+    <col width="14" customWidth="1" style="90" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="25" customHeight="1" s="90">
+      <c r="A1" s="94" t="inlineStr">
+        <is>
+          <t>6월 2주차 장보기 목록  (잔여: 양지머리·오리슬라이스·복숭아 / 도우미님: 오뎅탕 재료)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18.5" customHeight="1" s="90">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>재료</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>수량</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>사용 메뉴</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>구매 시기</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>예상 금액</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18.5" customHeight="1" s="90">
+      <c r="A3" s="104" t="inlineStr">
+        <is>
+          <t>정육</t>
+        </is>
+      </c>
+      <c r="B3" s="104" t="n"/>
+      <c r="C3" s="104" t="n"/>
+      <c r="D3" s="104" t="n"/>
+      <c r="E3" s="104" t="n"/>
+    </row>
+    <row r="4" ht="18.5" customHeight="1" s="90">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>닭다리살 (순살, 냉장)</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>700g</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>화(오야코동)</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>2주차 구매</t>
+        </is>
+      </c>
+      <c r="E4" s="139" t="n">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="5" ht="18.5" customHeight="1" s="90">
+      <c r="A5" s="105" t="inlineStr">
+        <is>
+          <t>수산</t>
+        </is>
+      </c>
+      <c r="B5" s="105" t="n"/>
+      <c r="C5" s="105" t="n"/>
+      <c r="D5" s="105" t="n"/>
+      <c r="E5" s="105" t="n"/>
+    </row>
+    <row r="6" ht="18.5" customHeight="1" s="90">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>삼치 토막 (손질, 냉장)</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>4조각</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>수(삼치구이)</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>2주차 구매</t>
+        </is>
+      </c>
+      <c r="E6" s="139" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="7" ht="18.5" customHeight="1" s="90">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>신선 새우 (중하)</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>400g</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>금(에비마요)</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>2주차 구매</t>
+        </is>
+      </c>
+      <c r="E7" s="139" t="n">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="8" ht="18.5" customHeight="1" s="90">
+      <c r="A8" s="96" t="inlineStr">
+        <is>
+          <t>채소</t>
+        </is>
+      </c>
+      <c r="B8" s="96" t="n"/>
+      <c r="C8" s="96" t="n"/>
+      <c r="D8" s="96" t="n"/>
+      <c r="E8" s="96" t="n"/>
+    </row>
+    <row r="9" ht="18.5" customHeight="1" s="90">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>양파</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>2개</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>화(오야코동)+수(양지국)</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>2주차 구매</t>
+        </is>
+      </c>
+      <c r="E9" s="139" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="10" ht="18.5" customHeight="1" s="90">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>대파</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>3대</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>화·수·금 전체</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>2주차 구매</t>
+        </is>
+      </c>
+      <c r="E10" s="139" t="n">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="11" ht="18.5" customHeight="1" s="90">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>감자</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>2개 (추가분)</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>수(감자전 넉넉히)</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>2주차 구매</t>
+        </is>
+      </c>
+      <c r="E11" s="139" t="n">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="12" ht="18.5" customHeight="1" s="90">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>1/4쪽</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>화(오뎅탕)+수(양지국)</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>2주차 구매</t>
+        </is>
+      </c>
+      <c r="E12" s="139" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="13" ht="18.5" customHeight="1" s="90">
+      <c r="A13" s="25" t="inlineStr">
+        <is>
+          <t>달걀</t>
+        </is>
+      </c>
+      <c r="B13" s="44" t="n"/>
+      <c r="C13" s="44" t="n"/>
+      <c r="D13" s="44" t="n"/>
+      <c r="E13" s="44" t="n"/>
+    </row>
+    <row r="14" ht="33" customHeight="1" s="90">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>달걀</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>10개(1판)</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>화(오야코동5)+금(달걀국3+장조림)</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>2주차 구매</t>
+        </is>
+      </c>
+      <c r="E14" s="139" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="15" ht="18.5" customHeight="1" s="90">
+      <c r="A15" s="26" t="inlineStr">
+        <is>
+          <t>가공식품</t>
+        </is>
+      </c>
+      <c r="B15" s="45" t="n"/>
+      <c r="C15" s="45" t="n"/>
+      <c r="D15" s="45" t="n"/>
+      <c r="E15" s="45" t="n"/>
+    </row>
+    <row r="16" ht="18.5" customHeight="1" s="90">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>가래떡</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>200g</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>금(꿀떡꼬치)</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>2주차 구매</t>
+        </is>
+      </c>
+      <c r="E16" s="139" t="n">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="17" ht="18.5" customHeight="1" s="90">
+      <c r="A17" s="35" t="inlineStr">
+        <is>
+          <t>양념/기타</t>
+        </is>
+      </c>
+      <c r="B17" s="46" t="n"/>
+      <c r="C17" s="46" t="n"/>
+      <c r="D17" s="46" t="n"/>
+      <c r="E17" s="46" t="n"/>
+    </row>
+    <row r="18" ht="18.5" customHeight="1" s="90">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>마요네즈</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>재고 확인</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>금(에비마요)</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>재고</t>
+        </is>
+      </c>
+      <c r="E18" s="47" t="n"/>
+    </row>
+    <row r="19" ht="18.5" customHeight="1" s="90">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>케첩</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>재고 확인</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>금(에비마요 소스)</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>재고</t>
+        </is>
+      </c>
+      <c r="E19" s="47" t="n"/>
+    </row>
+    <row r="20" ht="18.5" customHeight="1" s="90">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>전분가루</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>재고 확인</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>금(에비마요)+수(감자전)</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>재고</t>
+        </is>
+      </c>
+      <c r="E20" s="47" t="n"/>
+    </row>
+    <row r="21" ht="18.5" customHeight="1" s="90">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>올리고당</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>재고 확인</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>금(오리장조림+떡꼬치)</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>재고</t>
+        </is>
+      </c>
+      <c r="E21" s="47" t="n"/>
+    </row>
+    <row r="22" ht="18.5" customHeight="1" s="90">
+      <c r="A22" s="42" t="inlineStr">
+        <is>
+          <t>잔여재료 (구매 불필요)</t>
+        </is>
+      </c>
+      <c r="B22" s="48" t="n"/>
+      <c r="C22" s="48" t="n"/>
+      <c r="D22" s="48" t="n"/>
+      <c r="E22" s="48" t="n"/>
+    </row>
+    <row r="23" ht="18.5" customHeight="1" s="90">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>양지머리 (냉동)</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>200g</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>수(양지국) — 잔여</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>잔여</t>
+        </is>
+      </c>
+      <c r="E23" s="47" t="n"/>
+    </row>
+    <row r="24" ht="18.5" customHeight="1" s="90">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>오리 슬라이스</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>250g</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>금(오리장조림) — 재고</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>잔여</t>
+        </is>
+      </c>
+      <c r="E24" s="47" t="n"/>
+    </row>
+    <row r="25" ht="18.5" customHeight="1" s="90">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>감자 (잔여)</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>2개</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>수(감자전) — 잔여</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>잔여</t>
+        </is>
+      </c>
+      <c r="E25" s="47" t="n"/>
+    </row>
+    <row r="26" ht="18.5" customHeight="1" s="90">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>복숭아 (재고)</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>2~3개</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>화(간식) — 집에 있음</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>잔여</t>
+        </is>
+      </c>
+      <c r="E26" s="47" t="n"/>
+    </row>
+    <row r="27" ht="18.5" customHeight="1" s="90"/>
+    <row r="28" ht="33" customHeight="1" s="90">
+      <c r="A28" s="32" t="inlineStr">
+        <is>
+          <t>예상 합계 (잔여재료 제외 신규 구매분)</t>
+        </is>
+      </c>
+      <c r="B28" s="32" t="n"/>
+      <c r="C28" s="32" t="n"/>
+      <c r="D28" s="32" t="n"/>
+      <c r="E28" s="148" t="n">
+        <v>43500</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.4" right="0.4" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
+  <cols>
+    <col width="8" customWidth="1" style="90" min="1" max="1"/>
+    <col width="18" customWidth="1" style="90" min="2" max="2"/>
+    <col width="55" customWidth="1" style="90" min="3" max="3"/>
+    <col width="65" customWidth="1" style="90" min="4" max="4"/>
+    <col hidden="1" width="1" customWidth="1" style="90" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="25" customHeight="1" s="90">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>요일</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>메뉴</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>전날 밤 준비</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>당일 조리</t>
+        </is>
+      </c>
+    </row>
     <row r="2" ht="279.5" customHeight="1" s="90">
       <c r="A2" s="50" t="inlineStr">
         <is>
@@ -5579,563 +6942,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:E25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="25" customWidth="1" style="90" min="1" max="1"/>
-    <col width="14" customWidth="1" style="90" min="2" max="2"/>
-    <col width="28" customWidth="1" style="90" min="3" max="3"/>
-    <col width="16" customWidth="1" style="90" min="4" max="4"/>
-    <col width="14" customWidth="1" style="90" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1" s="90">
-      <c r="A1" s="121" t="inlineStr">
-        <is>
-          <t>8월 2주차 장보기 (8/4~8/7)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="118" t="inlineStr">
-        <is>
-          <t>재료</t>
-        </is>
-      </c>
-      <c r="B2" s="118" t="inlineStr">
-        <is>
-          <t>수량</t>
-        </is>
-      </c>
-      <c r="C2" s="118" t="inlineStr">
-        <is>
-          <t>사용 메뉴</t>
-        </is>
-      </c>
-      <c r="D2" s="118" t="inlineStr">
-        <is>
-          <t>구매 시기</t>
-        </is>
-      </c>
-      <c r="E2" s="118" t="inlineStr">
-        <is>
-          <t>예상 금액</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="122" t="inlineStr">
-        <is>
-          <t>정육</t>
-        </is>
-      </c>
-      <c r="B3" s="123" t="n"/>
-      <c r="C3" s="123" t="n"/>
-      <c r="D3" s="123" t="n"/>
-      <c r="E3" s="123" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="124" t="inlineStr">
-        <is>
-          <t>돼지안심</t>
-        </is>
-      </c>
-      <c r="B4" s="124" t="inlineStr">
-        <is>
-          <t>500g</t>
-        </is>
-      </c>
-      <c r="C4" s="124" t="inlineStr">
-        <is>
-          <t>청경채 굴소스볶음</t>
-        </is>
-      </c>
-      <c r="D4" s="124" t="inlineStr">
-        <is>
-          <t>8/4 구매</t>
-        </is>
-      </c>
-      <c r="E4" s="125" t="n">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="126" t="inlineStr">
-        <is>
-          <t>수산</t>
-        </is>
-      </c>
-      <c r="B5" s="127" t="n"/>
-      <c r="C5" s="127" t="n"/>
-      <c r="D5" s="127" t="n"/>
-      <c r="E5" s="127" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="124" t="inlineStr">
-        <is>
-          <t>순살 가자미</t>
-        </is>
-      </c>
-      <c r="B6" s="124" t="inlineStr">
-        <is>
-          <t>1팩(4~5쪽)</t>
-        </is>
-      </c>
-      <c r="C6" s="124" t="inlineStr">
-        <is>
-          <t>가자미 데리야끼구이</t>
-        </is>
-      </c>
-      <c r="D6" s="124" t="inlineStr">
-        <is>
-          <t>8/3 구매</t>
-        </is>
-      </c>
-      <c r="E6" s="125" t="n">
-        <v>12000</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="124" t="inlineStr">
-        <is>
-          <t>새우살 (냉장)</t>
-        </is>
-      </c>
-      <c r="B7" s="124" t="inlineStr">
-        <is>
-          <t>400g</t>
-        </is>
-      </c>
-      <c r="C7" s="124" t="inlineStr">
-        <is>
-          <t>감바스</t>
-        </is>
-      </c>
-      <c r="D7" s="124" t="inlineStr">
-        <is>
-          <t>8/6 구매</t>
-        </is>
-      </c>
-      <c r="E7" s="125" t="n">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="128" t="inlineStr">
-        <is>
-          <t>채소</t>
-        </is>
-      </c>
-      <c r="B8" s="129" t="n"/>
-      <c r="C8" s="129" t="n"/>
-      <c r="D8" s="129" t="n"/>
-      <c r="E8" s="129" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="124" t="inlineStr">
-        <is>
-          <t>알배추</t>
-        </is>
-      </c>
-      <c r="B9" s="124" t="inlineStr">
-        <is>
-          <t>1/2통</t>
-        </is>
-      </c>
-      <c r="C9" s="124" t="inlineStr">
-        <is>
-          <t>맑은 배추국</t>
-        </is>
-      </c>
-      <c r="D9" s="124" t="inlineStr">
-        <is>
-          <t>8/3 구매</t>
-        </is>
-      </c>
-      <c r="E9" s="125" t="n">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="124" t="inlineStr">
-        <is>
-          <t>청경채</t>
-        </is>
-      </c>
-      <c r="B10" s="124" t="inlineStr">
-        <is>
-          <t>1봉</t>
-        </is>
-      </c>
-      <c r="C10" s="124" t="inlineStr">
-        <is>
-          <t>청경채 볶음</t>
-        </is>
-      </c>
-      <c r="D10" s="124" t="inlineStr">
-        <is>
-          <t>8/4 구매</t>
-        </is>
-      </c>
-      <c r="E10" s="125" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="124" t="inlineStr">
-        <is>
-          <t>오이</t>
-        </is>
-      </c>
-      <c r="B11" s="124" t="inlineStr">
-        <is>
-          <t>2개</t>
-        </is>
-      </c>
-      <c r="C11" s="124" t="inlineStr">
-        <is>
-          <t>크래미 오이무침</t>
-        </is>
-      </c>
-      <c r="D11" s="124" t="inlineStr">
-        <is>
-          <t>8/3 구매</t>
-        </is>
-      </c>
-      <c r="E11" s="125" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="124" t="inlineStr">
-        <is>
-          <t>양파</t>
-        </is>
-      </c>
-      <c r="B12" s="124" t="inlineStr">
-        <is>
-          <t>1개</t>
-        </is>
-      </c>
-      <c r="C12" s="124" t="inlineStr">
-        <is>
-          <t>청경채/옥수수스프</t>
-        </is>
-      </c>
-      <c r="D12" s="124" t="inlineStr">
-        <is>
-          <t>8/3 구매</t>
-        </is>
-      </c>
-      <c r="E12" s="125" t="n">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="124" t="inlineStr">
-        <is>
-          <t>대파</t>
-        </is>
-      </c>
-      <c r="B13" s="124" t="inlineStr">
-        <is>
-          <t>2대</t>
-        </is>
-      </c>
-      <c r="C13" s="124" t="inlineStr">
-        <is>
-          <t>국 전반</t>
-        </is>
-      </c>
-      <c r="D13" s="124" t="inlineStr">
-        <is>
-          <t>8/3 구매</t>
-        </is>
-      </c>
-      <c r="E13" s="125" t="n">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="124" t="inlineStr">
-        <is>
-          <t>깐마늘</t>
-        </is>
-      </c>
-      <c r="B14" s="124" t="inlineStr">
-        <is>
-          <t>1봉</t>
-        </is>
-      </c>
-      <c r="C14" s="124" t="inlineStr">
-        <is>
-          <t>감바스(듬뿍)·전반</t>
-        </is>
-      </c>
-      <c r="D14" s="124" t="inlineStr">
-        <is>
-          <t>8/3 구매</t>
-        </is>
-      </c>
-      <c r="E14" s="125" t="n">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="124" t="inlineStr">
-        <is>
-          <t>방울토마토</t>
-        </is>
-      </c>
-      <c r="B15" s="124" t="inlineStr">
-        <is>
-          <t>1팩</t>
-        </is>
-      </c>
-      <c r="C15" s="124" t="inlineStr">
-        <is>
-          <t>감바스/간식</t>
-        </is>
-      </c>
-      <c r="D15" s="124" t="inlineStr">
-        <is>
-          <t>8/6 구매</t>
-        </is>
-      </c>
-      <c r="E15" s="125" t="n">
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="130" t="inlineStr">
-        <is>
-          <t>두부류</t>
-        </is>
-      </c>
-      <c r="B16" s="131" t="n"/>
-      <c r="C16" s="131" t="n"/>
-      <c r="D16" s="131" t="n"/>
-      <c r="E16" s="131" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="124" t="inlineStr">
-        <is>
-          <t>두부</t>
-        </is>
-      </c>
-      <c r="B17" s="124" t="inlineStr">
-        <is>
-          <t>1모</t>
-        </is>
-      </c>
-      <c r="C17" s="124" t="inlineStr">
-        <is>
-          <t>두부 맑은국</t>
-        </is>
-      </c>
-      <c r="D17" s="124" t="inlineStr">
-        <is>
-          <t>8/4 구매</t>
-        </is>
-      </c>
-      <c r="E17" s="125" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="132" t="inlineStr">
-        <is>
-          <t>기타</t>
-        </is>
-      </c>
-      <c r="B18" s="133" t="n"/>
-      <c r="C18" s="133" t="n"/>
-      <c r="D18" s="133" t="n"/>
-      <c r="E18" s="133" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="124" t="inlineStr">
-        <is>
-          <t>크래미 (게맛살)</t>
-        </is>
-      </c>
-      <c r="B19" s="124" t="inlineStr">
-        <is>
-          <t>1팩</t>
-        </is>
-      </c>
-      <c r="C19" s="124" t="inlineStr">
-        <is>
-          <t>크래미 오이무침</t>
-        </is>
-      </c>
-      <c r="D19" s="124" t="inlineStr">
-        <is>
-          <t>8/3 구매</t>
-        </is>
-      </c>
-      <c r="E19" s="125" t="n">
-        <v>3500</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="124" t="inlineStr">
-        <is>
-          <t>스위트콘</t>
-        </is>
-      </c>
-      <c r="B20" s="124" t="inlineStr">
-        <is>
-          <t>1캔</t>
-        </is>
-      </c>
-      <c r="C20" s="124" t="inlineStr">
-        <is>
-          <t>옥수수 스프</t>
-        </is>
-      </c>
-      <c r="D20" s="124" t="inlineStr">
-        <is>
-          <t>8/3 구매</t>
-        </is>
-      </c>
-      <c r="E20" s="125" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="124" t="inlineStr">
-        <is>
-          <t>구이김</t>
-        </is>
-      </c>
-      <c r="B21" s="124" t="inlineStr">
-        <is>
-          <t>1봉</t>
-        </is>
-      </c>
-      <c r="C21" s="124" t="inlineStr">
-        <is>
-          <t>김구이</t>
-        </is>
-      </c>
-      <c r="D21" s="124" t="inlineStr">
-        <is>
-          <t>8/3 구매</t>
-        </is>
-      </c>
-      <c r="E21" s="125" t="n">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="124" t="inlineStr">
-        <is>
-          <t>김가루</t>
-        </is>
-      </c>
-      <c r="B22" s="124" t="inlineStr">
-        <is>
-          <t>1봉</t>
-        </is>
-      </c>
-      <c r="C22" s="124" t="inlineStr">
-        <is>
-          <t>미니 주먹밥</t>
-        </is>
-      </c>
-      <c r="D22" s="124" t="inlineStr">
-        <is>
-          <t>8/6 구매</t>
-        </is>
-      </c>
-      <c r="E22" s="125" t="n">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="124" t="inlineStr">
-        <is>
-          <t>가래떡</t>
-        </is>
-      </c>
-      <c r="B23" s="124" t="inlineStr">
-        <is>
-          <t>1팩</t>
-        </is>
-      </c>
-      <c r="C23" s="124" t="inlineStr">
-        <is>
-          <t>간식</t>
-        </is>
-      </c>
-      <c r="D23" s="124" t="inlineStr">
-        <is>
-          <t>8/4 구매</t>
-        </is>
-      </c>
-      <c r="E23" s="125" t="n">
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="124" t="inlineStr">
-        <is>
-          <t>제철과일 (복숭아 등)</t>
-        </is>
-      </c>
-      <c r="B24" s="124" t="inlineStr">
-        <is>
-          <t>1팩</t>
-        </is>
-      </c>
-      <c r="C24" s="124" t="inlineStr">
-        <is>
-          <t>간식</t>
-        </is>
-      </c>
-      <c r="D24" s="124" t="inlineStr">
-        <is>
-          <t>8/6 구매</t>
-        </is>
-      </c>
-      <c r="E24" s="125" t="n">
-        <v>8000</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="134" t="inlineStr">
-        <is>
-          <t>합계</t>
-        </is>
-      </c>
-      <c r="B25" s="134" t="n"/>
-      <c r="C25" s="134" t="n"/>
-      <c r="D25" s="135" t="inlineStr">
-        <is>
-          <t>가격 합계</t>
-        </is>
-      </c>
-      <c r="E25" s="136" t="n">
-        <v>72800</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.4" right="0.4" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6770,7 +7577,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6977,7 +7784,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7578,7 +8385,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7784,7 +8591,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8365,7 +9172,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8575,7 +9382,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9206,7 +10013,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9361,7 +10168,190 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" style="90" min="1" max="1"/>
+    <col width="18" customWidth="1" style="90" min="2" max="2"/>
+    <col width="55" customWidth="1" style="90" min="3" max="3"/>
+    <col width="65" customWidth="1" style="90" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1" s="90">
+      <c r="A1" s="118" t="inlineStr">
+        <is>
+          <t>요일</t>
+        </is>
+      </c>
+      <c r="B1" s="118" t="inlineStr">
+        <is>
+          <t>메뉴</t>
+        </is>
+      </c>
+      <c r="C1" s="118" t="inlineStr">
+        <is>
+          <t>전날 밤 준비</t>
+        </is>
+      </c>
+      <c r="D1" s="118" t="inlineStr">
+        <is>
+          <t>당일 조리</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="276" customHeight="1" s="90">
+      <c r="A2" s="119" t="inlineStr">
+        <is>
+          <t>화 (8/4)</t>
+        </is>
+      </c>
+      <c r="B2" s="120" t="inlineStr">
+        <is>
+          <t>순살 가자미 데리야끼 구이
++ 맑은 배추국
++ 크래미 오이무침
++ 제철과일 (간식)</t>
+        </is>
+      </c>
+      <c r="C2" s="120" t="inlineStr">
+        <is>
+          <t>[순살 가자미 데리야끼 구이]
+1. 순살 가자미 4~5쪽 → 냉장실에서
+   천천히 해동, 키친타월로 물기 완전 제거
+2. 소금 살짝 + 미림(청주) 발라 10분
+   → 다시 물기 제거 (비린내 제거)
+3. 데리야끼: 간장 3T + 미림 1.5T
+   + 설탕 1T + 물 2T → 섞어 냉장
+   (당일 밀가루/전분 얇게 입힘)
+[맑은 배추국]
+4. 알배추 3~4잎 채썰기 / 두부 약간 / 대파 → 냉장
+5. 물 1L + 멸치·다시마육수</t>
+        </is>
+      </c>
+      <c r="D2" s="120" t="inlineStr">
+        <is>
+          <t>★ 식사 20분 전 시작
+[맑은 배추국 — 먼저]
+1. 육수+배추 8분
+2. 국간장 1T+소금, 대파 마무리 (시원 담백)
+[크래미 오이무침]
+3. 오이 반달 + 크래미 찢기
+   → 식초 1T + 설탕 1t + 소금 살짝 무치기
+[순살 가자미 데리야끼 — 마지막]
+4. 가자미 물기 제거 후 밀가루 얇게
+5. 팬 충분히 예열+기름 → 껍질면부터 3~4분
+   딱 한 번만 뒤집어 3분 (안 부서지게)
+6. 데리야끼 부어 조려 글레이즈 코팅(윤기)
+   ※ 아이용은 살 발라 접시에 + 소스 살짝
+[제철과일] 씻어서</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="216" customHeight="1" s="90">
+      <c r="A3" s="119" t="inlineStr">
+        <is>
+          <t>수 (8/5)</t>
+        </is>
+      </c>
+      <c r="B3" s="120" t="inlineStr">
+        <is>
+          <t>돼지안심 청경채 굴소스볶음
++ 두부 맑은국
++ 김구이
++ 가래떡구이 (간식)</t>
+        </is>
+      </c>
+      <c r="C3" s="120" t="inlineStr">
+        <is>
+          <t>[돼지안심 청경채 굴소스볶음]
+1. 돼지안심 500g → 0.7cm 썰어
+   밑간: 청주·소금·후추 + 전분 1t → 냉장
+2. 청경채 4~5포기 밑동 손질 / 양파 / 대파
+   / 마늘 → 냉장
+3. 소스: 굴소스 2T + 간장 1T + 설탕 1t
+   + 물 3T + 전분 1t → 섞어 냉장
+[두부 맑은국]
+4. 두부 1/2모 깍둑 / 무 약간 / 대파 → 냉장
+5. 물 1L + 육수</t>
+        </is>
+      </c>
+      <c r="D3" s="120" t="inlineStr">
+        <is>
+          <t>★ 식사 20분 전 시작
+[두부 맑은국 — 먼저]
+1. 육수 끓여 국간장 1T+소금
+2. 두부 넣고 5분, 대파 마무리
+[돼지안심 청경채 굴소스볶음 — 마지막]
+3. 팬에 기름, 마늘+돼지 센불 볶기
+4. 양파 1분, 청경채 줄기 먼저 30초
+5. 소스 붓고 센불, 청경채 잎+대파
+   → 숨 죽으면 완성 (밝은 윤기)
+[김구이] 참기름 약불 구이
+[가래떡구이] 노릇 구워 꿀</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="291" customHeight="1" s="90">
+      <c r="A4" s="119" t="inlineStr">
+        <is>
+          <t>금 (8/7)</t>
+        </is>
+      </c>
+      <c r="B4" s="120" t="inlineStr">
+        <is>
+          <t>감바스 (마늘새우)
++ 옥수수 스프
++ 미니 주먹밥
++ 과일 (간식)</t>
+        </is>
+      </c>
+      <c r="C4" s="120" t="inlineStr">
+        <is>
+          <t>[감바스]
+1. 새우살 400g → 소금·후추 밑간 → 냉장
+2. 마늘 10~15쪽 편썰기 → 냉장
+   (페페론치노는 아이용이라 생략/아주 조금)
+3. 올리브오일·방울토마토·파슬리 준비
+[옥수수 스프]
+4. 스위트콘 1캔 / 양파 1/4 / 우유
+   / 버터 조금 준비 (당일 갈기)
+[미니 주먹밥]
+5. 밥 + 참기름 + 소금 + 김가루 (당일 뭉치기)</t>
+        </is>
+      </c>
+      <c r="D4" s="120" t="inlineStr">
+        <is>
+          <t>★ 식사 20분 전 시작
+[옥수수 스프 — 먼저]
+1. 양파 버터에 살짝 볶다 콘+물 조금 끓이기
+2. 믹서에 곱게 갈기 → 냄비에 우유 넣고
+   소금·후추로 데우기 (부드럽게)
+[미니 주먹밥]
+3. 밥에 참기름·소금·김가루 섞어
+   한입 크기로 동글동글
+[감바스 — 마지막]
+4. 작은 팬에 올리브오일 넉넉 + 편마늘
+   약불로 향 내기 (마늘 안 태우게!)
+5. 새우 넣고 잠기듯 약~중불 3~4분
+6. 방울토마토·파슬리 마무리
+   → 주먹밥/빵에 오일 찍어먹기
+[과일] 접시에</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.4" right="0.4" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9936,7 +10926,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10094,193 +11084,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="8" customWidth="1" style="90" min="1" max="1"/>
-    <col width="18" customWidth="1" style="90" min="2" max="2"/>
-    <col width="55" customWidth="1" style="90" min="3" max="3"/>
-    <col width="65" customWidth="1" style="90" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="22" customHeight="1" s="90">
-      <c r="A1" s="118" t="inlineStr">
-        <is>
-          <t>요일</t>
-        </is>
-      </c>
-      <c r="B1" s="118" t="inlineStr">
-        <is>
-          <t>메뉴</t>
-        </is>
-      </c>
-      <c r="C1" s="118" t="inlineStr">
-        <is>
-          <t>전날 밤 준비</t>
-        </is>
-      </c>
-      <c r="D1" s="118" t="inlineStr">
-        <is>
-          <t>당일 조리</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="261" customHeight="1" s="90">
-      <c r="A2" s="119" t="inlineStr">
-        <is>
-          <t>화 (7/28)</t>
-        </is>
-      </c>
-      <c r="B2" s="120" t="inlineStr">
-        <is>
-          <t>돼지 탕수육
-+ 맑은 감자국
-+ 브로콜리 데침
-+ 수박 (간식)</t>
-        </is>
-      </c>
-      <c r="C2" s="120" t="inlineStr">
-        <is>
-          <t>[돼지 탕수육]
-1. 돼지고기(등심/안심) 600g → 길게 썰어
-   밑간: 소금·후추 + 청주 1T + 생강즙 약간 → 냉장
-2. 감자전분 1컵 계량(당일 물 섞어 반죽)
-3. 채소: 양파 1/2 + 당근 1/3 + 파프리카 1/2
-   → 한입크기 → 냉장
-4. 소스(안맵게): 물 250ml + 케첩 3T
-   + 설탕 2.5T + 식초 1T + 간장 1T → 냉장
-   / 전분물(감자전분 2T + 물 3T) 따로
-[맑은 감자국]
-5. 감자 1개 나박 / 양파 1/4 / 대파 → 냉장
-6. 물 1L + 멸치·다시마육수(멸치 10~12마리 + 다시마 1장)
-[브로콜리]
-7. 브로콜리 1개 한입크기 → 냉장</t>
-        </is>
-      </c>
-      <c r="D2" s="120" t="inlineStr">
-        <is>
-          <t>★ 식사 30분 전 시작
-[맑은 감자국 — 먼저]
-1. 육수+감자 중불 8분
-2. 국간장 1T+소금, 양파 3분, 대파 마무리
-[브로콜리 데침]
-3. 끓는 물+소금 → 1분30초 데쳐 찬물 헹굼
-[돼지 탕수육 — 마지막]
-4. 감자전분에 물 넣어 되직 반죽 → 고기 버무리기
-5. 170℃ 3~4분 튀기기 → 건져 기름빼기
-6. 180℃ 올려 30초~1분 2차 튀김(겉바속촉)
-7. 팬에 소스+채소 끓이다 전분물로 농도
-   → 튀긴 고기 버무리기 (부먹은 따로도 OK)
-[수박] 잘라서 접시에</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="246" customHeight="1" s="90">
-      <c r="A3" s="119" t="inlineStr">
-        <is>
-          <t>수 (7/29)</t>
-        </is>
-      </c>
-      <c r="B3" s="120" t="inlineStr">
-        <is>
-          <t>소불고기 팽이버섯볶음
-+ 애호박 새우젓 맑은국
-+ 계란찜
-+ 포도 (간식)</t>
-        </is>
-      </c>
-      <c r="C3" s="120" t="inlineStr">
-        <is>
-          <t>[소불고기 팽이버섯볶음]
-1. 소불고기용 600g → 양념: 간장 3T
-   + 설탕 1.5T + 배즙 3T + 다진마늘 1T
-   + 참기름 1T + 후추 → 버무려 냉장
-2. 양파 1/2 채썰기 / 팽이 1봉 밑동제거
-   / 대파 → 냉장
-[애호박 새우젓 맑은국]
-3. 애호박 1/2 반달 / 두부 1/4모 / 대파 → 냉장
-4. 물 1L + 멸치육수 / 새우젓 준비
-[계란찜]
-5. 달걀 4개 + 물 1컵 + 소금 풀어 냉장 / 대파</t>
-        </is>
-      </c>
-      <c r="D3" s="120" t="inlineStr">
-        <is>
-          <t>★ 식사 25분 전 시작
-[애호박 새우젓 맑은국 — 먼저]
-1. 육수+애호박 3분
-2. 새우젓 1t+소금 간, 두부 2분, 대파 마무리
-[계란찜]
-3. 뚝배기 달걀물+대파 중불 저으며 익히기
-4. 부풀면 약불 뚜껑 2분 → 참기름
-[소불고기 팽이버섯볶음 — 마지막]
-5. 팬 달궈 양념고기 센불 볶기
-6. 양파+팽이 넣고 숨죽을 때까지 2분
-7. 대파+참기름 마무리
-[포도] 씻어서 접시에</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="261" customHeight="1" s="90">
-      <c r="A4" s="119" t="inlineStr">
-        <is>
-          <t>금 (7/31)</t>
-        </is>
-      </c>
-      <c r="B4" s="120" t="inlineStr">
-        <is>
-          <t>닭다리살 간장마늘구이
-+ 바지락 맑은국
-+ 감자채볶음
-+ 옥수수 (간식)</t>
-        </is>
-      </c>
-      <c r="C4" s="120" t="inlineStr">
-        <is>
-          <t>[닭다리살 간장마늘구이]
-1. 닭다리살 600g → 한입크기, 소금·후추 밑간
-2. 양념: 간장 3T + 설탕 1T + 올리고당 1T
-   + 다진마늘 1.5T + 참기름 1T + 청주 1T
-   → 버무려 냉장 (조림 아닌 구이용, 밝게)
-3. 대파 채썰기(파채) → 냉장
-[바지락 맑은국]
-4. 바지락 1봉 소금물 30분 해감 → 냉장
-5. 무 약간 / 대파 / 다진마늘 / 물 1L
-[감자채볶음]
-6. 감자 2개 채썰어 물에 담가 전분빼기 → 냉장</t>
-        </is>
-      </c>
-      <c r="D4" s="120" t="inlineStr">
-        <is>
-          <t>★ 식사 25분 전 시작
-[바지락 맑은국 — 먼저]
-1. 물+무 끓이기 → 바지락 넣고 입 벌릴 때까지
-2. 다진마늘+국간장 조금+소금, 대파 마무리
-   (개운하고 시원한 국물)
-[감자채볶음]
-3. 물기 뺀 감자채 기름에 볶다 소금
-   → 아삭하게 참기름
-[닭다리살 간장마늘구이 — 마지막]
-4. 팬에 기름, 양념 닭 중불 굽기
-   ※ 양념 타지 않게 불조절 (검게 X, 윤기 O)
-5. 속까지 익으면 파채 살짝 → 완성
-[옥수수] 물 잠기게 센불 후 15분</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.4" right="0.4" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10985,7 +11789,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11190,7 +11994,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11752,7 +12556,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11946,7 +12750,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12457,7 +13261,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12756,7 +13560,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13308,7 +14112,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13522,7 +14326,563 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" style="90" min="1" max="1"/>
+    <col width="14" customWidth="1" style="90" min="2" max="2"/>
+    <col width="28" customWidth="1" style="90" min="3" max="3"/>
+    <col width="16" customWidth="1" style="90" min="4" max="4"/>
+    <col width="14" customWidth="1" style="90" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1" s="90">
+      <c r="A1" s="121" t="inlineStr">
+        <is>
+          <t>8월 2주차 장보기 (8/4~8/7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="118" t="inlineStr">
+        <is>
+          <t>재료</t>
+        </is>
+      </c>
+      <c r="B2" s="118" t="inlineStr">
+        <is>
+          <t>수량</t>
+        </is>
+      </c>
+      <c r="C2" s="118" t="inlineStr">
+        <is>
+          <t>사용 메뉴</t>
+        </is>
+      </c>
+      <c r="D2" s="118" t="inlineStr">
+        <is>
+          <t>구매 시기</t>
+        </is>
+      </c>
+      <c r="E2" s="118" t="inlineStr">
+        <is>
+          <t>예상 금액</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="122" t="inlineStr">
+        <is>
+          <t>정육</t>
+        </is>
+      </c>
+      <c r="B3" s="123" t="n"/>
+      <c r="C3" s="123" t="n"/>
+      <c r="D3" s="123" t="n"/>
+      <c r="E3" s="123" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="124" t="inlineStr">
+        <is>
+          <t>돼지안심</t>
+        </is>
+      </c>
+      <c r="B4" s="124" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="C4" s="124" t="inlineStr">
+        <is>
+          <t>청경채 굴소스볶음</t>
+        </is>
+      </c>
+      <c r="D4" s="124" t="inlineStr">
+        <is>
+          <t>8/4 구매</t>
+        </is>
+      </c>
+      <c r="E4" s="125" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="126" t="inlineStr">
+        <is>
+          <t>수산</t>
+        </is>
+      </c>
+      <c r="B5" s="127" t="n"/>
+      <c r="C5" s="127" t="n"/>
+      <c r="D5" s="127" t="n"/>
+      <c r="E5" s="127" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="124" t="inlineStr">
+        <is>
+          <t>순살 가자미</t>
+        </is>
+      </c>
+      <c r="B6" s="124" t="inlineStr">
+        <is>
+          <t>1팩(4~5쪽)</t>
+        </is>
+      </c>
+      <c r="C6" s="124" t="inlineStr">
+        <is>
+          <t>가자미 데리야끼구이</t>
+        </is>
+      </c>
+      <c r="D6" s="124" t="inlineStr">
+        <is>
+          <t>8/3 구매</t>
+        </is>
+      </c>
+      <c r="E6" s="125" t="n">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="124" t="inlineStr">
+        <is>
+          <t>새우살 (냉장)</t>
+        </is>
+      </c>
+      <c r="B7" s="124" t="inlineStr">
+        <is>
+          <t>400g</t>
+        </is>
+      </c>
+      <c r="C7" s="124" t="inlineStr">
+        <is>
+          <t>감바스</t>
+        </is>
+      </c>
+      <c r="D7" s="124" t="inlineStr">
+        <is>
+          <t>8/6 구매</t>
+        </is>
+      </c>
+      <c r="E7" s="125" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="128" t="inlineStr">
+        <is>
+          <t>채소</t>
+        </is>
+      </c>
+      <c r="B8" s="129" t="n"/>
+      <c r="C8" s="129" t="n"/>
+      <c r="D8" s="129" t="n"/>
+      <c r="E8" s="129" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="124" t="inlineStr">
+        <is>
+          <t>알배추</t>
+        </is>
+      </c>
+      <c r="B9" s="124" t="inlineStr">
+        <is>
+          <t>1/2통</t>
+        </is>
+      </c>
+      <c r="C9" s="124" t="inlineStr">
+        <is>
+          <t>맑은 배추국</t>
+        </is>
+      </c>
+      <c r="D9" s="124" t="inlineStr">
+        <is>
+          <t>8/3 구매</t>
+        </is>
+      </c>
+      <c r="E9" s="125" t="n">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="124" t="inlineStr">
+        <is>
+          <t>청경채</t>
+        </is>
+      </c>
+      <c r="B10" s="124" t="inlineStr">
+        <is>
+          <t>1봉</t>
+        </is>
+      </c>
+      <c r="C10" s="124" t="inlineStr">
+        <is>
+          <t>청경채 볶음</t>
+        </is>
+      </c>
+      <c r="D10" s="124" t="inlineStr">
+        <is>
+          <t>8/4 구매</t>
+        </is>
+      </c>
+      <c r="E10" s="125" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="124" t="inlineStr">
+        <is>
+          <t>오이</t>
+        </is>
+      </c>
+      <c r="B11" s="124" t="inlineStr">
+        <is>
+          <t>2개</t>
+        </is>
+      </c>
+      <c r="C11" s="124" t="inlineStr">
+        <is>
+          <t>크래미 오이무침</t>
+        </is>
+      </c>
+      <c r="D11" s="124" t="inlineStr">
+        <is>
+          <t>8/3 구매</t>
+        </is>
+      </c>
+      <c r="E11" s="125" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="124" t="inlineStr">
+        <is>
+          <t>양파</t>
+        </is>
+      </c>
+      <c r="B12" s="124" t="inlineStr">
+        <is>
+          <t>1개</t>
+        </is>
+      </c>
+      <c r="C12" s="124" t="inlineStr">
+        <is>
+          <t>청경채/옥수수스프</t>
+        </is>
+      </c>
+      <c r="D12" s="124" t="inlineStr">
+        <is>
+          <t>8/3 구매</t>
+        </is>
+      </c>
+      <c r="E12" s="125" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="124" t="inlineStr">
+        <is>
+          <t>대파</t>
+        </is>
+      </c>
+      <c r="B13" s="124" t="inlineStr">
+        <is>
+          <t>2대</t>
+        </is>
+      </c>
+      <c r="C13" s="124" t="inlineStr">
+        <is>
+          <t>국 전반</t>
+        </is>
+      </c>
+      <c r="D13" s="124" t="inlineStr">
+        <is>
+          <t>8/3 구매</t>
+        </is>
+      </c>
+      <c r="E13" s="125" t="n">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="124" t="inlineStr">
+        <is>
+          <t>깐마늘</t>
+        </is>
+      </c>
+      <c r="B14" s="124" t="inlineStr">
+        <is>
+          <t>1봉</t>
+        </is>
+      </c>
+      <c r="C14" s="124" t="inlineStr">
+        <is>
+          <t>감바스(듬뿍)·전반</t>
+        </is>
+      </c>
+      <c r="D14" s="124" t="inlineStr">
+        <is>
+          <t>8/3 구매</t>
+        </is>
+      </c>
+      <c r="E14" s="125" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="124" t="inlineStr">
+        <is>
+          <t>방울토마토</t>
+        </is>
+      </c>
+      <c r="B15" s="124" t="inlineStr">
+        <is>
+          <t>1팩</t>
+        </is>
+      </c>
+      <c r="C15" s="124" t="inlineStr">
+        <is>
+          <t>감바스/간식</t>
+        </is>
+      </c>
+      <c r="D15" s="124" t="inlineStr">
+        <is>
+          <t>8/6 구매</t>
+        </is>
+      </c>
+      <c r="E15" s="125" t="n">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="130" t="inlineStr">
+        <is>
+          <t>두부류</t>
+        </is>
+      </c>
+      <c r="B16" s="131" t="n"/>
+      <c r="C16" s="131" t="n"/>
+      <c r="D16" s="131" t="n"/>
+      <c r="E16" s="131" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="124" t="inlineStr">
+        <is>
+          <t>두부</t>
+        </is>
+      </c>
+      <c r="B17" s="124" t="inlineStr">
+        <is>
+          <t>1모</t>
+        </is>
+      </c>
+      <c r="C17" s="124" t="inlineStr">
+        <is>
+          <t>두부 맑은국</t>
+        </is>
+      </c>
+      <c r="D17" s="124" t="inlineStr">
+        <is>
+          <t>8/4 구매</t>
+        </is>
+      </c>
+      <c r="E17" s="125" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="132" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="B18" s="133" t="n"/>
+      <c r="C18" s="133" t="n"/>
+      <c r="D18" s="133" t="n"/>
+      <c r="E18" s="133" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="124" t="inlineStr">
+        <is>
+          <t>크래미 (게맛살)</t>
+        </is>
+      </c>
+      <c r="B19" s="124" t="inlineStr">
+        <is>
+          <t>1팩</t>
+        </is>
+      </c>
+      <c r="C19" s="124" t="inlineStr">
+        <is>
+          <t>크래미 오이무침</t>
+        </is>
+      </c>
+      <c r="D19" s="124" t="inlineStr">
+        <is>
+          <t>8/3 구매</t>
+        </is>
+      </c>
+      <c r="E19" s="125" t="n">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="124" t="inlineStr">
+        <is>
+          <t>스위트콘</t>
+        </is>
+      </c>
+      <c r="B20" s="124" t="inlineStr">
+        <is>
+          <t>1캔</t>
+        </is>
+      </c>
+      <c r="C20" s="124" t="inlineStr">
+        <is>
+          <t>옥수수 스프</t>
+        </is>
+      </c>
+      <c r="D20" s="124" t="inlineStr">
+        <is>
+          <t>8/3 구매</t>
+        </is>
+      </c>
+      <c r="E20" s="125" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="124" t="inlineStr">
+        <is>
+          <t>구이김</t>
+        </is>
+      </c>
+      <c r="B21" s="124" t="inlineStr">
+        <is>
+          <t>1봉</t>
+        </is>
+      </c>
+      <c r="C21" s="124" t="inlineStr">
+        <is>
+          <t>김구이</t>
+        </is>
+      </c>
+      <c r="D21" s="124" t="inlineStr">
+        <is>
+          <t>8/3 구매</t>
+        </is>
+      </c>
+      <c r="E21" s="125" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="124" t="inlineStr">
+        <is>
+          <t>김가루</t>
+        </is>
+      </c>
+      <c r="B22" s="124" t="inlineStr">
+        <is>
+          <t>1봉</t>
+        </is>
+      </c>
+      <c r="C22" s="124" t="inlineStr">
+        <is>
+          <t>미니 주먹밥</t>
+        </is>
+      </c>
+      <c r="D22" s="124" t="inlineStr">
+        <is>
+          <t>8/6 구매</t>
+        </is>
+      </c>
+      <c r="E22" s="125" t="n">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="124" t="inlineStr">
+        <is>
+          <t>가래떡</t>
+        </is>
+      </c>
+      <c r="B23" s="124" t="inlineStr">
+        <is>
+          <t>1팩</t>
+        </is>
+      </c>
+      <c r="C23" s="124" t="inlineStr">
+        <is>
+          <t>간식</t>
+        </is>
+      </c>
+      <c r="D23" s="124" t="inlineStr">
+        <is>
+          <t>8/4 구매</t>
+        </is>
+      </c>
+      <c r="E23" s="125" t="n">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="124" t="inlineStr">
+        <is>
+          <t>제철과일 (복숭아 등)</t>
+        </is>
+      </c>
+      <c r="B24" s="124" t="inlineStr">
+        <is>
+          <t>1팩</t>
+        </is>
+      </c>
+      <c r="C24" s="124" t="inlineStr">
+        <is>
+          <t>간식</t>
+        </is>
+      </c>
+      <c r="D24" s="124" t="inlineStr">
+        <is>
+          <t>8/6 구매</t>
+        </is>
+      </c>
+      <c r="E24" s="125" t="n">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="134" t="inlineStr">
+        <is>
+          <t>합계</t>
+        </is>
+      </c>
+      <c r="B25" s="134" t="n"/>
+      <c r="C25" s="134" t="n"/>
+      <c r="D25" s="135" t="inlineStr">
+        <is>
+          <t>가격 합계</t>
+        </is>
+      </c>
+      <c r="E25" s="136" t="n">
+        <v>72800</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.4" right="0.4" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14360,7 +15720,193 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" style="90" min="1" max="1"/>
+    <col width="18" customWidth="1" style="90" min="2" max="2"/>
+    <col width="55" customWidth="1" style="90" min="3" max="3"/>
+    <col width="65" customWidth="1" style="90" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1" s="90">
+      <c r="A1" s="118" t="inlineStr">
+        <is>
+          <t>요일</t>
+        </is>
+      </c>
+      <c r="B1" s="118" t="inlineStr">
+        <is>
+          <t>메뉴</t>
+        </is>
+      </c>
+      <c r="C1" s="118" t="inlineStr">
+        <is>
+          <t>전날 밤 준비</t>
+        </is>
+      </c>
+      <c r="D1" s="118" t="inlineStr">
+        <is>
+          <t>당일 조리</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="261" customHeight="1" s="90">
+      <c r="A2" s="119" t="inlineStr">
+        <is>
+          <t>화 (7/28)</t>
+        </is>
+      </c>
+      <c r="B2" s="120" t="inlineStr">
+        <is>
+          <t>돼지 탕수육
++ 맑은 감자국
++ 브로콜리 데침
++ 수박 (간식)</t>
+        </is>
+      </c>
+      <c r="C2" s="120" t="inlineStr">
+        <is>
+          <t>[돼지 탕수육]
+1. 돼지고기(등심/안심) 600g → 길게 썰어
+   밑간: 소금·후추 + 청주 1T + 생강즙 약간 → 냉장
+2. 감자전분 1컵 계량(당일 물 섞어 반죽)
+3. 채소: 양파 1/2 + 당근 1/3 + 파프리카 1/2
+   → 한입크기 → 냉장
+4. 소스(안맵게): 물 250ml + 케첩 3T
+   + 설탕 2.5T + 식초 1T + 간장 1T → 냉장
+   / 전분물(감자전분 2T + 물 3T) 따로
+[맑은 감자국]
+5. 감자 1개 나박 / 양파 1/4 / 대파 → 냉장
+6. 물 1L + 멸치·다시마육수(멸치 10~12마리 + 다시마 1장)
+[브로콜리]
+7. 브로콜리 1개 한입크기 → 냉장</t>
+        </is>
+      </c>
+      <c r="D2" s="120" t="inlineStr">
+        <is>
+          <t>★ 식사 30분 전 시작
+[맑은 감자국 — 먼저]
+1. 육수+감자 중불 8분
+2. 국간장 1T+소금, 양파 3분, 대파 마무리
+[브로콜리 데침]
+3. 끓는 물+소금 → 1분30초 데쳐 찬물 헹굼
+[돼지 탕수육 — 마지막]
+4. 감자전분에 물 넣어 되직 반죽 → 고기 버무리기
+5. 170℃ 3~4분 튀기기 → 건져 기름빼기
+6. 180℃ 올려 30초~1분 2차 튀김(겉바속촉)
+7. 팬에 소스+채소 끓이다 전분물로 농도
+   → 튀긴 고기 버무리기 (부먹은 따로도 OK)
+[수박] 잘라서 접시에</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="246" customHeight="1" s="90">
+      <c r="A3" s="119" t="inlineStr">
+        <is>
+          <t>수 (7/29)</t>
+        </is>
+      </c>
+      <c r="B3" s="120" t="inlineStr">
+        <is>
+          <t>소불고기 팽이버섯볶음
++ 애호박 새우젓 맑은국
++ 계란찜
++ 포도 (간식)</t>
+        </is>
+      </c>
+      <c r="C3" s="120" t="inlineStr">
+        <is>
+          <t>[소불고기 팽이버섯볶음]
+1. 소불고기용 600g → 양념: 간장 3T
+   + 설탕 1.5T + 배즙 3T + 다진마늘 1T
+   + 참기름 1T + 후추 → 버무려 냉장
+2. 양파 1/2 채썰기 / 팽이 1봉 밑동제거
+   / 대파 → 냉장
+[애호박 새우젓 맑은국]
+3. 애호박 1/2 반달 / 두부 1/4모 / 대파 → 냉장
+4. 물 1L + 멸치육수 / 새우젓 준비
+[계란찜]
+5. 달걀 4개 + 물 1컵 + 소금 풀어 냉장 / 대파</t>
+        </is>
+      </c>
+      <c r="D3" s="120" t="inlineStr">
+        <is>
+          <t>★ 식사 25분 전 시작
+[애호박 새우젓 맑은국 — 먼저]
+1. 육수+애호박 3분
+2. 새우젓 1t+소금 간, 두부 2분, 대파 마무리
+[계란찜]
+3. 뚝배기 달걀물+대파 중불 저으며 익히기
+4. 부풀면 약불 뚜껑 2분 → 참기름
+[소불고기 팽이버섯볶음 — 마지막]
+5. 팬 달궈 양념고기 센불 볶기
+6. 양파+팽이 넣고 숨죽을 때까지 2분
+7. 대파+참기름 마무리
+[포도] 씻어서 접시에</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="261" customHeight="1" s="90">
+      <c r="A4" s="119" t="inlineStr">
+        <is>
+          <t>금 (7/31)</t>
+        </is>
+      </c>
+      <c r="B4" s="120" t="inlineStr">
+        <is>
+          <t>닭다리살 간장마늘구이
++ 바지락 맑은국
++ 감자채볶음
++ 옥수수 (간식)</t>
+        </is>
+      </c>
+      <c r="C4" s="120" t="inlineStr">
+        <is>
+          <t>[닭다리살 간장마늘구이]
+1. 닭다리살 600g → 한입크기, 소금·후추 밑간
+2. 양념: 간장 3T + 설탕 1T + 올리고당 1T
+   + 다진마늘 1.5T + 참기름 1T + 청주 1T
+   → 버무려 냉장 (조림 아닌 구이용, 밝게)
+3. 대파 채썰기(파채) → 냉장
+[바지락 맑은국]
+4. 바지락 1봉 소금물 30분 해감 → 냉장
+5. 무 약간 / 대파 / 다진마늘 / 물 1L
+[감자채볶음]
+6. 감자 2개 채썰어 물에 담가 전분빼기 → 냉장</t>
+        </is>
+      </c>
+      <c r="D4" s="120" t="inlineStr">
+        <is>
+          <t>★ 식사 25분 전 시작
+[바지락 맑은국 — 먼저]
+1. 물+무 끓이기 → 바지락 넣고 입 벌릴 때까지
+2. 다진마늘+국간장 조금+소금, 대파 마무리
+   (개운하고 시원한 국물)
+[감자채볶음]
+3. 물기 뺀 감자채 기름에 볶다 소금
+   → 아삭하게 참기름
+[닭다리살 간장마늘구이 — 마지막]
+4. 팬에 기름, 양념 닭 중불 굽기
+   ※ 양념 타지 않게 불조절 (검게 X, 윤기 O)
+5. 속까지 익으면 파채 살짝 → 완성
+[옥수수] 물 잠기게 센불 후 15분</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.4" right="0.4" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14991,7 +16537,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -15203,7 +16749,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -15984,7 +17530,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -16129,654 +17675,4 @@
   <pageMargins left="0.4" right="0.4" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
   <pageSetup orientation="portrait" paperSize="9" scale="65" horizontalDpi="4294967293"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:E20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
-  <cols>
-    <col width="25" customWidth="1" style="90" min="1" max="1"/>
-    <col width="14" customWidth="1" style="90" min="2" max="2"/>
-    <col width="28" customWidth="1" style="90" min="3" max="3"/>
-    <col width="16" customWidth="1" style="90" min="4" max="4"/>
-    <col width="14" customWidth="1" style="90" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1" s="90">
-      <c r="A1" s="89" t="inlineStr">
-        <is>
-          <t>7월 3주차 장보기 (7/14~7/15)</t>
-        </is>
-      </c>
-      <c r="B1" s="137" t="n"/>
-      <c r="C1" s="137" t="n"/>
-      <c r="D1" s="137" t="n"/>
-      <c r="E1" s="138" t="n"/>
-    </row>
-    <row r="2" ht="25" customHeight="1" s="90">
-      <c r="A2" s="78" t="inlineStr">
-        <is>
-          <t>재료</t>
-        </is>
-      </c>
-      <c r="B2" s="78" t="inlineStr">
-        <is>
-          <t>수량</t>
-        </is>
-      </c>
-      <c r="C2" s="78" t="inlineStr">
-        <is>
-          <t>사용 메뉴</t>
-        </is>
-      </c>
-      <c r="D2" s="78" t="inlineStr">
-        <is>
-          <t>구매 시기</t>
-        </is>
-      </c>
-      <c r="E2" s="78" t="inlineStr">
-        <is>
-          <t>예상 금액</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="22" customHeight="1" s="90">
-      <c r="A3" s="81" t="inlineStr">
-        <is>
-          <t>정육</t>
-        </is>
-      </c>
-      <c r="B3" s="81" t="n"/>
-      <c r="C3" s="81" t="n"/>
-      <c r="D3" s="81" t="n"/>
-      <c r="E3" s="81" t="n"/>
-    </row>
-    <row r="4" ht="22" customHeight="1" s="90">
-      <c r="A4" s="80" t="inlineStr">
-        <is>
-          <t>돼지목살</t>
-        </is>
-      </c>
-      <c r="B4" s="79" t="inlineStr">
-        <is>
-          <t>800g</t>
-        </is>
-      </c>
-      <c r="C4" s="80" t="inlineStr">
-        <is>
-          <t>간장구이</t>
-        </is>
-      </c>
-      <c r="D4" s="79" t="inlineStr">
-        <is>
-          <t>첫째주</t>
-        </is>
-      </c>
-      <c r="E4" s="82" t="n">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="5" ht="22" customHeight="1" s="90">
-      <c r="A5" s="80" t="inlineStr">
-        <is>
-          <t>닭다리살</t>
-        </is>
-      </c>
-      <c r="B5" s="79" t="inlineStr">
-        <is>
-          <t>800g</t>
-        </is>
-      </c>
-      <c r="C5" s="80" t="inlineStr">
-        <is>
-          <t>간장조림</t>
-        </is>
-      </c>
-      <c r="D5" s="79" t="inlineStr">
-        <is>
-          <t>첫째주</t>
-        </is>
-      </c>
-      <c r="E5" s="82" t="n">
-        <v>8000</v>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1" s="90">
-      <c r="A6" s="80" t="inlineStr">
-        <is>
-          <t>차돌박이</t>
-        </is>
-      </c>
-      <c r="B6" s="79" t="inlineStr">
-        <is>
-          <t>250g</t>
-        </is>
-      </c>
-      <c r="C6" s="80" t="inlineStr">
-        <is>
-          <t>차돌미역국</t>
-        </is>
-      </c>
-      <c r="D6" s="79" t="inlineStr">
-        <is>
-          <t>첫째주</t>
-        </is>
-      </c>
-      <c r="E6" s="82" t="n">
-        <v>12000</v>
-      </c>
-    </row>
-    <row r="7" ht="22" customHeight="1" s="90">
-      <c r="A7" s="83" t="inlineStr">
-        <is>
-          <t>수산</t>
-        </is>
-      </c>
-      <c r="B7" s="83" t="n"/>
-      <c r="C7" s="83" t="n"/>
-      <c r="D7" s="83" t="n"/>
-      <c r="E7" s="83" t="n"/>
-    </row>
-    <row r="8" ht="22" customHeight="1" s="90">
-      <c r="A8" s="80" t="inlineStr">
-        <is>
-          <t>(이번 주차 해당 없음)</t>
-        </is>
-      </c>
-      <c r="B8" s="79" t="n"/>
-      <c r="C8" s="80" t="n"/>
-      <c r="D8" s="79" t="n"/>
-      <c r="E8" s="80" t="n"/>
-    </row>
-    <row r="9" ht="22" customHeight="1" s="90">
-      <c r="A9" s="84" t="inlineStr">
-        <is>
-          <t>채소</t>
-        </is>
-      </c>
-      <c r="B9" s="84" t="n"/>
-      <c r="C9" s="84" t="n"/>
-      <c r="D9" s="84" t="n"/>
-      <c r="E9" s="84" t="n"/>
-    </row>
-    <row r="10" ht="22" customHeight="1" s="90">
-      <c r="A10" s="80" t="inlineStr">
-        <is>
-          <t>양파</t>
-        </is>
-      </c>
-      <c r="B10" s="79" t="inlineStr">
-        <is>
-          <t>2개</t>
-        </is>
-      </c>
-      <c r="C10" s="80" t="inlineStr">
-        <is>
-          <t>간장구이/간장조림</t>
-        </is>
-      </c>
-      <c r="D10" s="79" t="inlineStr">
-        <is>
-          <t>첫째주</t>
-        </is>
-      </c>
-      <c r="E10" s="82" t="n">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="11" ht="22" customHeight="1" s="90">
-      <c r="A11" s="80" t="inlineStr">
-        <is>
-          <t>대파</t>
-        </is>
-      </c>
-      <c r="B11" s="79" t="inlineStr">
-        <is>
-          <t>2대</t>
-        </is>
-      </c>
-      <c r="C11" s="80" t="inlineStr">
-        <is>
-          <t>콩나물국/간장조림</t>
-        </is>
-      </c>
-      <c r="D11" s="79" t="inlineStr">
-        <is>
-          <t>첫째주</t>
-        </is>
-      </c>
-      <c r="E11" s="82" t="n">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="12" ht="22" customHeight="1" s="90">
-      <c r="A12" s="80" t="inlineStr">
-        <is>
-          <t>감자</t>
-        </is>
-      </c>
-      <c r="B12" s="79" t="inlineStr">
-        <is>
-          <t>2개</t>
-        </is>
-      </c>
-      <c r="C12" s="80" t="inlineStr">
-        <is>
-          <t>감자채볶음</t>
-        </is>
-      </c>
-      <c r="D12" s="79" t="inlineStr">
-        <is>
-          <t>첫째주</t>
-        </is>
-      </c>
-      <c r="E12" s="82" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1" s="90">
-      <c r="A13" s="80" t="inlineStr">
-        <is>
-          <t>당근</t>
-        </is>
-      </c>
-      <c r="B13" s="79" t="inlineStr">
-        <is>
-          <t>1/3개</t>
-        </is>
-      </c>
-      <c r="C13" s="80" t="inlineStr">
-        <is>
-          <t>간장조림</t>
-        </is>
-      </c>
-      <c r="D13" s="79" t="inlineStr">
-        <is>
-          <t>첫째주</t>
-        </is>
-      </c>
-      <c r="E13" s="82" t="n">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="14" ht="22" customHeight="1" s="90">
-      <c r="A14" s="80" t="inlineStr">
-        <is>
-          <t>콩나물</t>
-        </is>
-      </c>
-      <c r="B14" s="79" t="inlineStr">
-        <is>
-          <t>1봉지</t>
-        </is>
-      </c>
-      <c r="C14" s="80" t="inlineStr">
-        <is>
-          <t>콩나물국</t>
-        </is>
-      </c>
-      <c r="D14" s="79" t="inlineStr">
-        <is>
-          <t>첫째주</t>
-        </is>
-      </c>
-      <c r="E14" s="82" t="n">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="15" ht="22" customHeight="1" s="90">
-      <c r="A15" s="85" t="inlineStr">
-        <is>
-          <t>두부류</t>
-        </is>
-      </c>
-      <c r="B15" s="85" t="n"/>
-      <c r="C15" s="85" t="n"/>
-      <c r="D15" s="85" t="n"/>
-      <c r="E15" s="85" t="n"/>
-    </row>
-    <row r="16" ht="22" customHeight="1" s="90">
-      <c r="A16" s="80" t="inlineStr">
-        <is>
-          <t>염장미역</t>
-        </is>
-      </c>
-      <c r="B16" s="79" t="inlineStr">
-        <is>
-          <t>1팩</t>
-        </is>
-      </c>
-      <c r="C16" s="80" t="inlineStr">
-        <is>
-          <t>차돌미역국</t>
-        </is>
-      </c>
-      <c r="D16" s="79" t="inlineStr">
-        <is>
-          <t>첫째주</t>
-        </is>
-      </c>
-      <c r="E16" s="82" t="n">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="17" ht="22" customHeight="1" s="90">
-      <c r="A17" s="86" t="inlineStr">
-        <is>
-          <t>기타</t>
-        </is>
-      </c>
-      <c r="B17" s="86" t="n"/>
-      <c r="C17" s="86" t="n"/>
-      <c r="D17" s="86" t="n"/>
-      <c r="E17" s="86" t="n"/>
-    </row>
-    <row r="18" ht="22" customHeight="1" s="90">
-      <c r="A18" s="80" t="inlineStr">
-        <is>
-          <t>달걀</t>
-        </is>
-      </c>
-      <c r="B18" s="79" t="inlineStr">
-        <is>
-          <t>10개입</t>
-        </is>
-      </c>
-      <c r="C18" s="80" t="inlineStr">
-        <is>
-          <t>계란말이/각종</t>
-        </is>
-      </c>
-      <c r="D18" s="79" t="inlineStr">
-        <is>
-          <t>첫째주</t>
-        </is>
-      </c>
-      <c r="E18" s="82" t="n">
-        <v>3500</v>
-      </c>
-    </row>
-    <row r="19" ht="22" customHeight="1" s="90">
-      <c r="A19" s="80" t="inlineStr">
-        <is>
-          <t>옥수수</t>
-        </is>
-      </c>
-      <c r="B19" s="79" t="inlineStr">
-        <is>
-          <t>2개</t>
-        </is>
-      </c>
-      <c r="C19" s="80" t="inlineStr">
-        <is>
-          <t>간식</t>
-        </is>
-      </c>
-      <c r="D19" s="79" t="inlineStr">
-        <is>
-          <t>첫째주</t>
-        </is>
-      </c>
-      <c r="E19" s="82" t="n">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="20" ht="25" customHeight="1" s="90">
-      <c r="A20" s="87" t="inlineStr">
-        <is>
-          <t>합계</t>
-        </is>
-      </c>
-      <c r="B20" s="87" t="n"/>
-      <c r="C20" s="87" t="n"/>
-      <c r="D20" s="87" t="n"/>
-      <c r="E20" s="88" t="n">
-        <v>50300</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.4" right="0.4" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
-  <cols>
-    <col width="8" customWidth="1" style="90" min="1" max="1"/>
-    <col width="18" customWidth="1" style="90" min="2" max="2"/>
-    <col width="55" customWidth="1" style="90" min="3" max="3"/>
-    <col width="65" customWidth="1" style="90" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="25" customHeight="1" s="90">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>요일</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>메뉴</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>전날 밤 준비</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>당일 조리</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="352" customHeight="1" s="90">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>화 (7/7)</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>닭다리살 카레소스구이
-+ 오뎅탕
-+ 콩나물무침
-+ 제철 과일 (간식)</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>[닭다리살 카레소스구이]
-1. 닭다리살 600g(재고+추가) → 한입 크기
-2. 밑간: 소금 + 후추 → 30분
-3. 소스: 카레가루 2T + 간장 1T + 꿀(또는 설탕) 1T
-   + 다진마늘 1T + 올리브오일 1T → 섞어 냉장
-4. 양파 1개 → 굵게 채썰기
-[오뎅탕]
-5. 오뎅 1/2팩(재고) → 먹기 좋게 자르기
-6. 무 1/6개 → 나박썰기
-7. 대파 1대 → 어슷
-8. 냄비에 물 1L + 다시마 1조각 세팅
-[콩나물무침]
-9. 콩나물 1팩(재고) → 씻기
-10. 양념: 참기름 1T + 국간장 1T + 다진마늘 1/2t
-    + 깨소금 → 소스컵에</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>★ 식사 25분 전 시작
-[콩나물 — 먼저]
-1. 냄비에 물 넉넉히 끓이기
-2. 콩나물 넣고 뚜껑 닫고 중불 7분
-   ※ 중간에 뚜껑 열지 않기!
-3. 찬물에 헹궈 물기 빼기
-4. 양념 넣고 조물조물 무치기
-[오뎅탕]
-5. 냄비에 물+다시마 센불
-6. 끓기 직전 다시마 건지기
-7. 무 넣고 중불 5분
-8. 오뎅 넣고 3분
-9. 국간장 1T + 소금 → 대파 마무리
-[닭다리살 카레소스구이 — 마지막]
-10. 팬에 기름, 닭다리살 센불 겉면 2분
-11. 중불로 낮추고 양파 넣어 3분
-12. 카레소스 부어 중불 5분
-    (뒤적이며 소스 코팅)
-13. 완성 후 접시에 담기
-[제철 과일] 씻어서 접시에</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="409.6" customHeight="1" s="90">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>수 (7/8)</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>오리 굴소스 채소볶음
-+ 안심 스테이크
-+ 달걀국
-+ 두부구이
-+ 가래떡구이 (간식)</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>[오리 굴소스 채소볶음] ★아이 부드럽게 핵심
-1. 오리 슬라이스(재고) → 한입보다 작게 자르기
-2. ★연육: 양파 1/2개 갈아서 즙 내기
-   → 오리에 양파즙 + 맛술 1T + 후추
-   → 버무려 냉장 (하룻밤 재우기 = 연육 핵심)
-3. 양파 1개 → 굵게 채썰기 → 냉장
-4. 대파 1대 → 어슷 → 냉장
-5. 청경채 2~3포기 → 반으로 자르기 → 냉장
-6. 소스: 굴소스 2T + 간장 1T + 설탕 1T
-   + 참기름 1T → 소스컵
-[안심 스테이크]
-7. 안심 200g(재고) → 키친타올로 핏물 제거
-8. 아이들용: 0.5cm 얇게 슬라이스
-   어른용: 두께 유지
-9. 소금 + 후추 양면 → 냉장
-[달걀국]
-10. 대파 1대 → 송송썰기
-11. 달걀 3개 풀어 냉장
-12. 냄비에 물 800ml 세팅
-[두부구이]
-13. 두부(재고) → 1cm 두께
-    → 키친타올 물기 제거
-[가래떡구이]
-14. 가래떡 적당량 → 한입 크기</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>★ 식사 25분 전 시작
-[달걀국 — 먼저]
-1. 물 센불로 끓이기
-2. 국간장 1T + 소금 → 대파 넣기
-3. 달걀 풀어 돌려 붓기, 10초 후 불 끄기
-[가래떡구이]
-4. 팬에 기름 살짝, 중불 앞뒤 노릇 구이
-[두부구이]
-5. 같은 팬에 기름, 두부 중불 앞뒤 각 2분
-6. 소금 살짝 뿌려 완성
-[안심 스테이크]
-7. 팬 센불로 달구기 (연기 날 정도)
-8. 기름 두르고 안심 올리기
-   - 아이용(얇은 슬라이스): 앞뒤 각 30초 (웰던)
-   - 어른용(두꺼운 덩어리): 앞뒤 각 2분 (미디엄)
-9. 종이호일 감싸 3분 레스팅
-[오리 굴소스 채소볶음 — 마지막]
-10. 팬에 기름 없이(오리 기름 나옴) 센불
-11. ★ 양파즙 양념째로 오리 올려 빠르게 볶기
-    ※ 센불 2분! 오래 볶으면 질겨짐!
-12. 고기 80% 익으면 양파+청경채 넣고 1분
-13. 소스(굴소스+간장+설탕) 부어 30초 볶기
-14. 대파+참기름 → 불 끄기
-15. 접시에 담고 참깨 뿌리기</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="352" customHeight="1" s="90">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>금 (7/10)</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>에비마요 (새우마요)
-+ 양지미역국
-+ 소시지야채볶음
-+ 옥수수 (간식)</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>[에비마요]
-1. 새우살 400g → 껍질·내장 제거
-   → 흐르는 물에 씻어 물기 제거 → 냉장
-2. 밑간: 청주 1T + 후추 → 버무려 냉장
-3. 감자전분 3T 별도 준비
-4. 마요소스: 마요네즈 4T + 케첩 1T
-   + 설탕 1T + 레몬즙 1T → 섞어 냉장
-[양지미역국]
-5. 양지머리 250g → 한입 크기
-6. 염장 미역 → 물에 30분 불리기 → 짜서 냉장
-7. 냄비에 물 1.2L 세팅
-[소시지야채볶음]
-8. 소시지 6개 → 칼집 넣기
-9. 양파 1/2개 → 채썰기
-10. 당근 1/4개 → 채썰기
-[옥수수]
-11. 스위트콘 1캔 준비</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>★ 식사 30분 전 시작
-[양지미역국 — 먼저]
-1. 냄비에 참기름, 양지 중불 2분 볶기
-2. 미역 넣고 1분 볶기
-3. 물 1.2L 붓고 센불
-4. 끓으면 중불 15분
-5. 국간장 1T + 다진마늘 + 소금
-[소시지야채볶음]
-6. 팬에 기름, 소시지 중불 2분
-7. 양파+당근 넣고 1분
-8. 케첩 2T + 설탕 1t → 볶아 완성
-[에비마요 — 마지막]
-9. 새우에 감자전분 고루 묻히기
-10. 팬에 기름 넉넉히, 중불
-11. 하나씩 올려 앞뒤 각 2분 노릇하게
-    ※ 한번에 부으면 뭉치니 하나씩!
-12. 노릇해지면 마요소스 넣고 불 끄기
-13. 잔열로 소스 고루 버무리기
-14. 접시에 담기
-[옥수수] 스위트콘 데워서 접시에</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.4" right="0.4" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="65" horizontalDpi="4294967293" verticalDpi="300"/>
-</worksheet>
 </file>
--- a/26년도_2주간_식단.xlsx
+++ b/26년도_2주간_식단.xlsx
@@ -1440,7 +1440,7 @@
           <t>[새우전]
 1. 새우살 480g → 반은 다지고 반은 굵게
    (씹는 맛) → 소금·후추+전분 1T 섞어 반죽
-2. 당근·부추 조금 다져 섞기 → 냉장
+2. 당근·대파(파란 부분) 조금 다져 섞기 → 냉장
 3. 부침가루·계란 준비(당일 옷)
 [아욱 된장국]
 4. 아욱 손질(바락바락 치대어 풋내 제거)
@@ -5581,7 +5581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" style="90" min="1" max="1"/>
@@ -5811,22 +5811,22 @@
     <row r="12">
       <c r="A12" s="124" t="inlineStr">
         <is>
-          <t>부추</t>
+          <t>대파</t>
         </is>
       </c>
       <c r="B12" s="124" t="inlineStr">
         <is>
-          <t>1줌</t>
+          <t>2대</t>
         </is>
       </c>
       <c r="C12" s="124" t="inlineStr">
         <is>
-          <t>새우전</t>
+          <t>국·요리 전반</t>
         </is>
       </c>
       <c r="D12" s="124" t="inlineStr">
         <is>
-          <t>8/20 구매</t>
+          <t>8/17 밤 주문</t>
         </is>
       </c>
       <c r="E12" s="125" t="n">
@@ -5834,111 +5834,111 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="124" t="inlineStr">
-        <is>
-          <t>대파</t>
-        </is>
-      </c>
-      <c r="B13" s="124" t="inlineStr">
-        <is>
-          <t>2대</t>
-        </is>
-      </c>
-      <c r="C13" s="124" t="inlineStr">
-        <is>
-          <t>국·요리 전반</t>
-        </is>
-      </c>
-      <c r="D13" s="124" t="inlineStr">
-        <is>
-          <t>8/17 밤 주문</t>
-        </is>
-      </c>
-      <c r="E13" s="125" t="n">
-        <v>1500</v>
-      </c>
+      <c r="A13" s="130" t="inlineStr">
+        <is>
+          <t>두부류</t>
+        </is>
+      </c>
+      <c r="B13" s="131" t="n"/>
+      <c r="C13" s="131" t="n"/>
+      <c r="D13" s="131" t="n"/>
+      <c r="E13" s="131" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="130" t="inlineStr">
-        <is>
-          <t>두부류</t>
-        </is>
-      </c>
-      <c r="B14" s="131" t="n"/>
-      <c r="C14" s="131" t="n"/>
-      <c r="D14" s="131" t="n"/>
-      <c r="E14" s="131" t="n"/>
+      <c r="A14" s="124" t="inlineStr">
+        <is>
+          <t>두부</t>
+        </is>
+      </c>
+      <c r="B14" s="124" t="inlineStr">
+        <is>
+          <t>1모</t>
+        </is>
+      </c>
+      <c r="C14" s="124" t="inlineStr">
+        <is>
+          <t>두부구이</t>
+        </is>
+      </c>
+      <c r="D14" s="124" t="inlineStr">
+        <is>
+          <t>8/18 구매</t>
+        </is>
+      </c>
+      <c r="E14" s="125" t="n">
+        <v>2000</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="124" t="inlineStr">
         <is>
-          <t>두부</t>
+          <t>유부</t>
         </is>
       </c>
       <c r="B15" s="124" t="inlineStr">
         <is>
-          <t>1모</t>
+          <t>1봉</t>
         </is>
       </c>
       <c r="C15" s="124" t="inlineStr">
         <is>
-          <t>두부구이</t>
+          <t>유부 맑은장국</t>
         </is>
       </c>
       <c r="D15" s="124" t="inlineStr">
         <is>
-          <t>8/18 구매</t>
+          <t>8/17 밤 주문</t>
         </is>
       </c>
       <c r="E15" s="125" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="132" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="B16" s="133" t="n"/>
+      <c r="C16" s="133" t="n"/>
+      <c r="D16" s="133" t="n"/>
+      <c r="E16" s="133" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="124" t="inlineStr">
+        <is>
+          <t>스위트콘</t>
+        </is>
+      </c>
+      <c r="B17" s="124" t="inlineStr">
+        <is>
+          <t>1캔</t>
+        </is>
+      </c>
+      <c r="C17" s="124" t="inlineStr">
+        <is>
+          <t>콘치즈</t>
+        </is>
+      </c>
+      <c r="D17" s="124" t="inlineStr">
+        <is>
+          <t>8/17 밤 주문</t>
+        </is>
+      </c>
+      <c r="E17" s="125" t="n">
         <v>2000</v>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="124" t="inlineStr">
-        <is>
-          <t>유부</t>
-        </is>
-      </c>
-      <c r="B16" s="124" t="inlineStr">
-        <is>
-          <t>1봉</t>
-        </is>
-      </c>
-      <c r="C16" s="124" t="inlineStr">
-        <is>
-          <t>유부 맑은장국</t>
-        </is>
-      </c>
-      <c r="D16" s="124" t="inlineStr">
-        <is>
-          <t>8/17 밤 주문</t>
-        </is>
-      </c>
-      <c r="E16" s="125" t="n">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="132" t="inlineStr">
-        <is>
-          <t>기타</t>
-        </is>
-      </c>
-      <c r="B17" s="133" t="n"/>
-      <c r="C17" s="133" t="n"/>
-      <c r="D17" s="133" t="n"/>
-      <c r="E17" s="133" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="124" t="inlineStr">
         <is>
-          <t>스위트콘</t>
+          <t>모짜렐라치즈</t>
         </is>
       </c>
       <c r="B18" s="124" t="inlineStr">
         <is>
-          <t>1캔</t>
+          <t>1봉</t>
         </is>
       </c>
       <c r="C18" s="124" t="inlineStr">
@@ -5952,23 +5952,23 @@
         </is>
       </c>
       <c r="E18" s="125" t="n">
-        <v>2000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="124" t="inlineStr">
         <is>
-          <t>모짜렐라치즈</t>
+          <t>달걀</t>
         </is>
       </c>
       <c r="B19" s="124" t="inlineStr">
         <is>
-          <t>1봉</t>
+          <t>15개입</t>
         </is>
       </c>
       <c r="C19" s="124" t="inlineStr">
         <is>
-          <t>콘치즈</t>
+          <t>달걀국/계란찜/새우전</t>
         </is>
       </c>
       <c r="D19" s="124" t="inlineStr">
@@ -5977,23 +5977,23 @@
         </is>
       </c>
       <c r="E19" s="125" t="n">
-        <v>6000</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="124" t="inlineStr">
         <is>
-          <t>달걀</t>
+          <t>배즙</t>
         </is>
       </c>
       <c r="B20" s="124" t="inlineStr">
         <is>
-          <t>15개입</t>
+          <t>1팩</t>
         </is>
       </c>
       <c r="C20" s="124" t="inlineStr">
         <is>
-          <t>달걀국/계란찜/새우전</t>
+          <t>제육 양념</t>
         </is>
       </c>
       <c r="D20" s="124" t="inlineStr">
@@ -6002,38 +6002,38 @@
         </is>
       </c>
       <c r="E20" s="125" t="n">
-        <v>4000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="124" t="inlineStr">
         <is>
-          <t>배즙</t>
+          <t>카레가루</t>
         </is>
       </c>
       <c r="B21" s="124" t="inlineStr">
         <is>
-          <t>1팩</t>
+          <t>상비 확인</t>
         </is>
       </c>
       <c r="C21" s="124" t="inlineStr">
         <is>
-          <t>제육 양념</t>
+          <t>카레소스구이</t>
         </is>
       </c>
       <c r="D21" s="124" t="inlineStr">
         <is>
-          <t>8/17 밤 주문</t>
+          <t>상비</t>
         </is>
       </c>
       <c r="E21" s="125" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="124" t="inlineStr">
         <is>
-          <t>카레가루</t>
+          <t>부침가루</t>
         </is>
       </c>
       <c r="B22" s="124" t="inlineStr">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="C22" s="124" t="inlineStr">
         <is>
-          <t>카레소스구이</t>
+          <t>새우전</t>
         </is>
       </c>
       <c r="D22" s="124" t="inlineStr">
@@ -6058,22 +6058,22 @@
     <row r="23">
       <c r="A23" s="124" t="inlineStr">
         <is>
-          <t>부침가루</t>
+          <t>어린이김치</t>
         </is>
       </c>
       <c r="B23" s="124" t="inlineStr">
         <is>
-          <t>상비 확인</t>
+          <t>지난주 구매분</t>
         </is>
       </c>
       <c r="C23" s="124" t="inlineStr">
         <is>
-          <t>새우전</t>
+          <t>상시 반찬(부족시 추가)</t>
         </is>
       </c>
       <c r="D23" s="124" t="inlineStr">
         <is>
-          <t>상비</t>
+          <t>보유</t>
         </is>
       </c>
       <c r="E23" s="125" t="n">
@@ -6083,7 +6083,7 @@
     <row r="24">
       <c r="A24" s="124" t="inlineStr">
         <is>
-          <t>어린이김치</t>
+          <t>국물멸치·다시마·건새우</t>
         </is>
       </c>
       <c r="B24" s="124" t="inlineStr">
@@ -6093,7 +6093,7 @@
       </c>
       <c r="C24" s="124" t="inlineStr">
         <is>
-          <t>상시 반찬(부족시 추가)</t>
+          <t>만능육수</t>
         </is>
       </c>
       <c r="D24" s="124" t="inlineStr">
@@ -6108,17 +6108,17 @@
     <row r="25">
       <c r="A25" s="124" t="inlineStr">
         <is>
-          <t>국물멸치·다시마·건새우</t>
+          <t>간식(복숭아·방울토마토)</t>
         </is>
       </c>
       <c r="B25" s="124" t="inlineStr">
         <is>
-          <t>지난주 구매분</t>
+          <t>집에 넉넉</t>
         </is>
       </c>
       <c r="C25" s="124" t="inlineStr">
         <is>
-          <t>만능육수</t>
+          <t>간식</t>
         </is>
       </c>
       <c r="D25" s="124" t="inlineStr">
@@ -6131,45 +6131,20 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="124" t="inlineStr">
-        <is>
-          <t>간식(복숭아·방울토마토)</t>
-        </is>
-      </c>
-      <c r="B26" s="124" t="inlineStr">
-        <is>
-          <t>집에 넉넉</t>
-        </is>
-      </c>
-      <c r="C26" s="124" t="inlineStr">
-        <is>
-          <t>간식</t>
-        </is>
-      </c>
-      <c r="D26" s="124" t="inlineStr">
-        <is>
-          <t>보유</t>
-        </is>
-      </c>
-      <c r="E26" s="125" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="134" t="inlineStr">
+      <c r="A26" s="134" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
       </c>
-      <c r="B27" s="134" t="n"/>
-      <c r="C27" s="134" t="n"/>
-      <c r="D27" s="135" t="inlineStr">
+      <c r="B26" s="134" t="n"/>
+      <c r="C26" s="134" t="n"/>
+      <c r="D26" s="135" t="inlineStr">
         <is>
           <t>구매분 합계</t>
         </is>
       </c>
-      <c r="E27" s="136" t="n">
-        <v>56500</v>
+      <c r="E26" s="136" t="n">
+        <v>55000</v>
       </c>
     </row>
   </sheetData>

--- a/26년도_2주간_식단.xlsx
+++ b/26년도_2주간_식단.xlsx
@@ -1333,8 +1333,8 @@
       <c r="B2" s="120" t="inlineStr">
         <is>
           <t>닭다리살 간장마늘구이
-+ 유부 맑은장국
-+ 두부구이(칼슘)
++ 두부 맑은국(칼슘)
++ 브로콜리 데침(칼슘)
 + 키즈김치
 + 포도 (간식)</t>
         </is>
@@ -1347,34 +1347,33 @@
    +다진마늘 1.5T+참기름 1T+청주 1T
    → 버무려 냉장 (조림 아닌 구이, 밝게)
 3. 대파 채썰기(파채) → 냉장
-[유부 맑은장국 — 감칠맛 만능육수]
-4. 유부 5장 채썰기 / 대파 어슷 → 냉장
+[두부 맑은국 — 칼슘 + 감칠맛 만능육수]
+4. 두부 1모 깍둑썰기 / 대파 어슷 → 냉장
 5. 육수: 물 1.2L + 국물멸치 15마리
    (머리·내장 제거 → 마른팬 30초 볶기)
    + 다시마 1장 + 건새우 1줌
-[두부구이 — 칼슘]
-6. 두부 1모 도톰하게 썰어
-   키친타월로 물기 빼 냉장
+[브로콜리 — 칼슘]
+6. 브로콜리 1개 한입크기로 잘라 냉장
 [키즈김치] 어린이김치 통 준비</t>
         </is>
       </c>
       <c r="D2" s="120" t="inlineStr">
         <is>
           <t>★ 식사 25분 전
-[유부 맑은장국 — 먼저]
+[두부 맑은국 — 먼저]
 1. 육수재료 찬물부터 → 끓으면 다시마 건지고
    중불 10분 → 체에 거르기
-2. 유부 넣고 5분
+2. 두부 넣고 5분
 3. 간: 국간장 1.5T+소금+다진마늘
    +멸치액젓 1t (감칠맛), 대파 마무리
    ※ 맛보고 싱거우면 무조건 간 더!
-[두부구이 — 칼슘]
-4. 팬에 기름, 두부 앞뒤 노릇하게
-5. 간장 살짝+통깨 마무리
+[브로콜리 데침 — 칼슘]
+4. 끓는 물+소금에 1분30초 데쳐
+   찬물에 헹궈 물기 빼기
 [닭다리살 간장마늘구이 — 마지막]
-6. 팬에 기름, 양념 닭 중불 굽기
+5. 팬에 기름, 양념 닭 중불 굽기
    ※ 양념 타지 않게 불조절(검게 X, 윤기 O)
-7. 속까지 익으면 파채 살짝 → 완성
+6. 속까지 익으면 파채 살짝 → 완성
 [키즈김치] 접시에 / [포도] 씻어서</t>
         </is>
       </c>
@@ -1389,7 +1388,7 @@
         <is>
           <t>소고기 찹스테이크
 + 맑은 무국
-+ 브로콜리 데침(칼슘)
++ 감자채볶음
 + 키즈김치
 + 사과 (간식)</t>
         </is>
@@ -1407,8 +1406,9 @@
 [맑은 무국]
 4. 무 1/4개 나박썰기 / 대파 어슷 → 냉장
 5. 육수재료(멸치 볶기+다시마+건새우)
-[브로콜리 — 칼슘]
-6. 브로콜리 1개 한입크기로 잘라 냉장
+[감자채볶음]
+6. 감자 2개 채썰어 물에 담가
+   전분 빼고 냉장
 [키즈김치] 통 준비</t>
         </is>
       </c>
@@ -1420,9 +1420,9 @@
    (무 투명해질 때까지)
 2. 간: 국간장 1.5T+소금+다진마늘+액젓 1t
    대파 마무리 ※ 싱거우면 간 더!
-[브로콜리 데침 — 칼슘]
-3. 끓는 물+소금에 1분30초 데쳐
-   찬물에 헹궈 물기 빼기
+[감자채볶음]
+3. 물기 뺀 감자채 기름에 볶다 소금
+   → 아삭하게, 참기름 마무리
 [소고기 찹스테이크 — 마지막]
 4. 팬 뜨겁게, 고기 센불로 겉면만
    익혀 꺼내기 (1~2분, 육즙 유지)
@@ -1433,7 +1433,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="291" customHeight="1" s="90">
+    <row r="4" ht="306" customHeight="1" s="90">
       <c r="A4" s="119" t="inlineStr">
         <is>
           <t>금 (9/4)</t>
@@ -1441,46 +1441,47 @@
       </c>
       <c r="B4" s="120" t="inlineStr">
         <is>
-          <t>새우전
-+ 아욱 된장국
-+ 계란찜(비타민D)
+          <t>새우 덮밥 (에비동)
++ 배추 된장국
++ 김구이
 + 키즈김치
 + 가래떡구이 (간식)</t>
         </is>
       </c>
       <c r="C4" s="120" t="inlineStr">
         <is>
-          <t>[새우전]
-1. 새우살 480g → 반은 다지고 반은 굵게
-   (씹는 맛) 소금·후추+전분 1T 섞어 반죽
-2. 당근·대파(파란 부분) 조금 다져 섞기
-   → 냉장
-3. 부침가루·계란 준비(당일 옷)
-[아욱 된장국]
-4. 아욱 손질(바락바락 치대어 풋내 제거)
-5. 육수재료(멸치 볶기+다시마+건새우)
+          <t>[새우 덮밥 — 에비동] ★검증 호평
+1. 새우살 480g → 물기 제거
+   밑간: 청주 1T+소금·후추 → 냉장
+2. 양파 1개 채썰기 / 대파 → 냉장
+3. 달걀 4개 풀어 냉장 (덮밥 위 반숙용)
+4. 덮밥소스: 간장 3T+미림 2T+설탕 1T
+   +물 200ml (당일 멸치육수 조금 섞으면
+   감칠맛↑) → 섞어 냉장
+[배추 된장국]
+5. 알배추 3~4잎 한입크기 / 대파 → 냉장
+6. 육수재료(멸치 볶기+다시마+건새우)
    / 된장 2T
-[계란찜 — 비타민D]
-6. 달걀 4개+물 1컵+소금 풀어 냉장
-   / 대파 조금
+[김구이] 구이김 준비
 [키즈김치] 통 준비</t>
         </is>
       </c>
       <c r="D4" s="120" t="inlineStr">
         <is>
           <t>★ 식사 20분 전
-[아욱 된장국 — 먼저]
+[배추 된장국 — 먼저]
 1. 만능육수 우려 거르고 된장 2T 풀기
-2. 아욱 넣고 중불 10분
+2. 배추 넣고 중불 8분 (부드럽게)
 3. 다진마늘+국간장으로 간
    ※ 싱거우면 간 더! (맹맹 방지)
-[계란찜 — 비타민D]
-4. 뚝배기 달걀물+대파 중불 저으며 익히기
-5. 부풀면 약불 뚜껑 2분 → 참기름
-[새우전 — 마지막]
-6. 반죽 한 스푼씩 → 부침가루 → 계란옷
-7. 팬에 기름, 중불 앞뒤 노릇하게 부치기
-   (속까지 익게, 너무 두껍지 않게)
+[김구이]
+4. 김 앞뒤 살짝 구워 잘라 접시에
+[새우 덮밥 — 마지막]
+5. 팬에 덮밥소스+양파 넣고 끓이기
+6. 새우 넣어 2~3분 익히기
+   (오래 익히면 질겨짐)
+7. 달걀 풀어 붓고 반숙으로 익히기
+8. 밥 위에 올리고 대파 → 완성
 [키즈김치] 접시에
 [가래떡구이] 노릇 구워 꿀</t>
         </is>
@@ -5674,7 +5675,7 @@
       </c>
       <c r="C7" s="124" t="inlineStr">
         <is>
-          <t>새우전</t>
+          <t>새우 덮밥(에비동)</t>
         </is>
       </c>
       <c r="D7" s="124" t="inlineStr">
@@ -5705,12 +5706,12 @@
       </c>
       <c r="B9" s="124" t="inlineStr">
         <is>
-          <t>2개</t>
+          <t>3개</t>
         </is>
       </c>
       <c r="C9" s="124" t="inlineStr">
         <is>
-          <t>찹스테이크</t>
+          <t>찹스테이크/에비동</t>
         </is>
       </c>
       <c r="D9" s="124" t="inlineStr">
@@ -5719,7 +5720,7 @@
         </is>
       </c>
       <c r="E9" s="125" t="n">
-        <v>1500</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="10">
@@ -5825,17 +5826,17 @@
     <row r="14">
       <c r="A14" s="124" t="inlineStr">
         <is>
-          <t>당근</t>
+          <t>감자</t>
         </is>
       </c>
       <c r="B14" s="124" t="inlineStr">
         <is>
-          <t>1개</t>
+          <t>3개</t>
         </is>
       </c>
       <c r="C14" s="124" t="inlineStr">
         <is>
-          <t>새우전</t>
+          <t>감자채볶음</t>
         </is>
       </c>
       <c r="D14" s="124" t="inlineStr">
@@ -5844,23 +5845,23 @@
         </is>
       </c>
       <c r="E14" s="125" t="n">
-        <v>1000</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="124" t="inlineStr">
         <is>
-          <t>아욱</t>
+          <t>알배추</t>
         </is>
       </c>
       <c r="B15" s="124" t="inlineStr">
         <is>
-          <t>1단</t>
+          <t>1/2통</t>
         </is>
       </c>
       <c r="C15" s="124" t="inlineStr">
         <is>
-          <t>아욱 된장국</t>
+          <t>배추 된장국</t>
         </is>
       </c>
       <c r="D15" s="124" t="inlineStr">
@@ -5869,7 +5870,7 @@
         </is>
       </c>
       <c r="E15" s="125" t="n">
-        <v>2000</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="16">
@@ -5921,7 +5922,7 @@
       </c>
       <c r="C18" s="124" t="inlineStr">
         <is>
-          <t>두부구이(칼슘)</t>
+          <t>두부 맑은국(칼슘)</t>
         </is>
       </c>
       <c r="D18" s="124" t="inlineStr">
@@ -5934,55 +5935,55 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="124" t="inlineStr">
-        <is>
-          <t>유부</t>
-        </is>
-      </c>
-      <c r="B19" s="124" t="inlineStr">
-        <is>
-          <t>1봉</t>
-        </is>
-      </c>
-      <c r="C19" s="124" t="inlineStr">
-        <is>
-          <t>유부 맑은장국</t>
-        </is>
-      </c>
-      <c r="D19" s="124" t="inlineStr">
+      <c r="A19" s="132" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="B19" s="133" t="n"/>
+      <c r="C19" s="133" t="n"/>
+      <c r="D19" s="133" t="n"/>
+      <c r="E19" s="133" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="124" t="inlineStr">
+        <is>
+          <t>달걀</t>
+        </is>
+      </c>
+      <c r="B20" s="124" t="inlineStr">
+        <is>
+          <t>15개입</t>
+        </is>
+      </c>
+      <c r="C20" s="124" t="inlineStr">
+        <is>
+          <t>에비동</t>
+        </is>
+      </c>
+      <c r="D20" s="124" t="inlineStr">
         <is>
           <t>8/31 밤 주문</t>
         </is>
       </c>
-      <c r="E19" s="125" t="n">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="132" t="inlineStr">
-        <is>
-          <t>기타</t>
-        </is>
-      </c>
-      <c r="B20" s="133" t="n"/>
-      <c r="C20" s="133" t="n"/>
-      <c r="D20" s="133" t="n"/>
-      <c r="E20" s="133" t="n"/>
+      <c r="E20" s="125" t="n">
+        <v>4000</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="124" t="inlineStr">
         <is>
-          <t>달걀</t>
+          <t>구이김</t>
         </is>
       </c>
       <c r="B21" s="124" t="inlineStr">
         <is>
-          <t>15개입</t>
+          <t>1봉</t>
         </is>
       </c>
       <c r="C21" s="124" t="inlineStr">
         <is>
-          <t>계란찜/새우전</t>
+          <t>김구이</t>
         </is>
       </c>
       <c r="D21" s="124" t="inlineStr">
@@ -5991,7 +5992,7 @@
         </is>
       </c>
       <c r="E21" s="125" t="n">
-        <v>4000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="22">
@@ -6097,7 +6098,7 @@
     <row r="26">
       <c r="A26" s="124" t="inlineStr">
         <is>
-          <t>부침가루</t>
+          <t>된장</t>
         </is>
       </c>
       <c r="B26" s="124" t="inlineStr">
@@ -6107,7 +6108,7 @@
       </c>
       <c r="C26" s="124" t="inlineStr">
         <is>
-          <t>새우전</t>
+          <t>배추 된장국</t>
         </is>
       </c>
       <c r="D26" s="124" t="inlineStr">
@@ -6183,7 +6184,7 @@
         </is>
       </c>
       <c r="E29" s="136" t="n">
-        <v>82000</v>
+        <v>84500</v>
       </c>
     </row>
   </sheetData>

--- a/26년도_2주간_식단.xlsx
+++ b/26년도_2주간_식단.xlsx
@@ -640,7 +640,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="153">
+  <cellXfs count="154">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1034,6 +1034,9 @@
     <xf numFmtId="164" fontId="8" fillId="21" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1324,7 +1327,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="306" customHeight="1" s="90">
+    <row r="2" ht="336" customHeight="1" s="90">
       <c r="A2" s="119" t="inlineStr">
         <is>
           <t>화 (9/1)</t>
@@ -1332,7 +1335,7 @@
       </c>
       <c r="B2" s="120" t="inlineStr">
         <is>
-          <t>닭다리살 간장마늘구이
+          <t>한우 소불고기 덮밥 (재고)
 + 두부 맑은국(칼슘)
 + 브로콜리 데침(칼슘)
 + 키즈김치
@@ -1341,12 +1344,13 @@
       </c>
       <c r="C2" s="120" t="inlineStr">
         <is>
-          <t>[닭다리살 간장마늘구이]
-1. 닭다리살 600g 한입크기, 소금·후추 밑간
-2. 양념: 간장 3T+설탕 1T+올리고당 1T
-   +다진마늘 1.5T+참기름 1T+청주 1T
-   → 버무려 냉장 (조림 아닌 구이, 밝게)
-3. 대파 채썰기(파채) → 냉장
+          <t>[한우 소불고기 덮밥] ※ 재고 소진 (유통기한 9/4)
+1. 한우 불고기용 1팩 (냉장고 재고)
+2. 양념: 간장 3T+설탕 1.5T+배즙(또는 배·양파 간것) 3T
+   +다진마늘 1T+참기름 1T+후추
+   → 고기에 버무려 냉장 (30분 이상 재우면 부드러움)
+3. 양파 1개 채썰기 / 대파 어슷 → 냉장
+   ※ 한우는 질기지 않으니 센불에 빠르게
 [두부 맑은국 — 칼슘 + 감칠맛 만능육수]
 4. 두부 1모 깍둑썰기 / 대파 어슷 → 냉장
 5. 육수: 물 1.2L + 국물멸치 15마리
@@ -1359,7 +1363,7 @@
       </c>
       <c r="D2" s="120" t="inlineStr">
         <is>
-          <t>★ 식사 25분 전
+          <t>★ 식사 20분 전
 [두부 맑은국 — 먼저]
 1. 육수재료 찬물부터 → 끓으면 다시마 건지고
    중불 10분 → 체에 거르기
@@ -1370,10 +1374,12 @@
 [브로콜리 데침 — 칼슘]
 4. 끓는 물+소금에 1분30초 데쳐
    찬물에 헹궈 물기 빼기
-[닭다리살 간장마늘구이 — 마지막]
-5. 팬에 기름, 양념 닭 중불 굽기
-   ※ 양념 타지 않게 불조절(검게 X, 윤기 O)
-6. 속까지 익으면 파채 살짝 → 완성
+[한우 소불고기 덮밥 — 마지막]
+5. 팬 뜨겁게 달궈 양념 고기 펼쳐 올리기
+6. 센불에서 빠르게 볶기 (한우는 오래 익히면
+   질겨짐 — 겉면 익으면 바로)
+7. 양파 넣고 숨 죽을 때까지 1~2분
+8. 대파+참기름 마무리 → 밥 위에 올리기
 [키즈김치] 접시에 / [포도] 씻어서</t>
         </is>
       </c>
@@ -1433,7 +1439,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="306" customHeight="1" s="90">
+    <row r="4" ht="276" customHeight="1" s="90">
       <c r="A4" s="119" t="inlineStr">
         <is>
           <t>금 (9/4)</t>
@@ -1441,7 +1447,7 @@
       </c>
       <c r="B4" s="120" t="inlineStr">
         <is>
-          <t>새우 덮밥 (에비동)
+          <t>닭다리살 간장마늘구이
 + 배추 된장국
 + 김구이
 + 키즈김치
@@ -1450,25 +1456,24 @@
       </c>
       <c r="C4" s="120" t="inlineStr">
         <is>
-          <t>[새우 덮밥 — 에비동] ★검증 호평
-1. 새우살 480g → 물기 제거
-   밑간: 청주 1T+소금·후추 → 냉장
-2. 양파 1개 채썰기 / 대파 → 냉장
-3. 달걀 4개 풀어 냉장 (덮밥 위 반숙용)
-4. 덮밥소스: 간장 3T+미림 2T+설탕 1T
-   +물 200ml (당일 멸치육수 조금 섞으면
-   감칠맛↑) → 섞어 냉장
+          <t>[닭다리살 간장마늘구이]
+1. 닭다리살 500~600g 한입크기, 소금·후추 밑간
+2. 양념: 간장 3T+설탕 1T+올리고당 1T
+   +다진마늘 1.5T+참기름 1T+청주 1T
+   → 버무려 냉장 (조림 아닌 구이, 밝게)
+3. 대파 채썰기(파채) → 냉장
 [배추 된장국]
-5. 알배추 3~4잎 한입크기 / 대파 → 냉장
-6. 육수재료(멸치 볶기+다시마+건새우)
+4. 알배추 3~4잎 한입크기 / 대파 → 냉장
+5. 육수재료(멸치 볶기+다시마+건새우)
    / 된장 2T
 [김구이] 구이김 준비
-[키즈김치] 통 준비</t>
+[키즈김치] 통 준비
+※ 새우살(냉동)은 이번주 미사용 → 다음주 활용</t>
         </is>
       </c>
       <c r="D4" s="120" t="inlineStr">
         <is>
-          <t>★ 식사 20분 전
+          <t>★ 식사 25분 전
 [배추 된장국 — 먼저]
 1. 만능육수 우려 거르고 된장 2T 풀기
 2. 배추 넣고 중불 8분 (부드럽게)
@@ -1476,12 +1481,10 @@
    ※ 싱거우면 간 더! (맹맹 방지)
 [김구이]
 4. 김 앞뒤 살짝 구워 잘라 접시에
-[새우 덮밥 — 마지막]
-5. 팬에 덮밥소스+양파 넣고 끓이기
-6. 새우 넣어 2~3분 익히기
-   (오래 익히면 질겨짐)
-7. 달걀 풀어 붓고 반숙으로 익히기
-8. 밥 위에 올리고 대파 → 완성
+[닭다리살 간장마늘구이 — 마지막]
+5. 팬에 기름, 양념 닭 중불 굽기
+   ※ 양념 타지 않게 불조절(검게 X, 윤기 O)
+6. 속까지 익으면 파채 살짝 올려 완성
 [키즈김치] 접시에
 [가래떡구이] 노릇 구워 꿀</t>
         </is>
@@ -5546,7 +5549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" style="90" min="1" max="1"/>
@@ -5614,7 +5617,7 @@
       </c>
       <c r="C4" s="124" t="inlineStr">
         <is>
-          <t>간장마늘구이</t>
+          <t>금(간장마늘구이)</t>
         </is>
       </c>
       <c r="D4" s="124" t="inlineStr">
@@ -5652,91 +5655,91 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="126" t="inlineStr">
+      <c r="A6" s="124" t="inlineStr">
+        <is>
+          <t>한우 불고기용 (재고)</t>
+        </is>
+      </c>
+      <c r="B6" s="124" t="inlineStr">
+        <is>
+          <t>1팩</t>
+        </is>
+      </c>
+      <c r="C6" s="124" t="inlineStr">
+        <is>
+          <t>화(소불고기 덮밥) ※유통기한 9/4</t>
+        </is>
+      </c>
+      <c r="D6" s="124" t="inlineStr">
+        <is>
+          <t>보유</t>
+        </is>
+      </c>
+      <c r="E6" s="153" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="126" t="inlineStr">
         <is>
           <t>수산</t>
         </is>
       </c>
-      <c r="B6" s="127" t="n"/>
-      <c r="C6" s="127" t="n"/>
-      <c r="D6" s="127" t="n"/>
-      <c r="E6" s="127" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="124" t="inlineStr">
-        <is>
-          <t>새우살 (냉장)</t>
-        </is>
-      </c>
-      <c r="B7" s="124" t="inlineStr">
+      <c r="B7" s="127" t="n"/>
+      <c r="C7" s="127" t="n"/>
+      <c r="D7" s="127" t="n"/>
+      <c r="E7" s="127" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="124" t="inlineStr">
+        <is>
+          <t>새우살 (냉동·구매완료)</t>
+        </is>
+      </c>
+      <c r="B8" s="124" t="inlineStr">
         <is>
           <t>480g</t>
         </is>
       </c>
-      <c r="C7" s="124" t="inlineStr">
-        <is>
-          <t>새우 덮밥(에비동)</t>
-        </is>
-      </c>
-      <c r="D7" s="124" t="inlineStr">
-        <is>
-          <t>9/3 구매</t>
-        </is>
-      </c>
-      <c r="E7" s="125" t="n">
+      <c r="C8" s="124" t="inlineStr">
+        <is>
+          <t>※ 이번주 미사용 → 다음주 이월</t>
+        </is>
+      </c>
+      <c r="D8" s="124" t="inlineStr">
+        <is>
+          <t>구매완료</t>
+        </is>
+      </c>
+      <c r="E8" s="125" t="n">
         <v>11000</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="128" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="128" t="inlineStr">
         <is>
           <t>채소</t>
         </is>
       </c>
-      <c r="B8" s="129" t="n"/>
-      <c r="C8" s="129" t="n"/>
-      <c r="D8" s="129" t="n"/>
-      <c r="E8" s="129" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="124" t="inlineStr">
-        <is>
-          <t>양파</t>
-        </is>
-      </c>
-      <c r="B9" s="124" t="inlineStr">
-        <is>
-          <t>3개</t>
-        </is>
-      </c>
-      <c r="C9" s="124" t="inlineStr">
-        <is>
-          <t>찹스테이크/에비동</t>
-        </is>
-      </c>
-      <c r="D9" s="124" t="inlineStr">
-        <is>
-          <t>8/31 밤 주문</t>
-        </is>
-      </c>
-      <c r="E9" s="125" t="n">
-        <v>2000</v>
-      </c>
+      <c r="B9" s="129" t="n"/>
+      <c r="C9" s="129" t="n"/>
+      <c r="D9" s="129" t="n"/>
+      <c r="E9" s="129" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="124" t="inlineStr">
         <is>
-          <t>파프리카</t>
+          <t>양파</t>
         </is>
       </c>
       <c r="B10" s="124" t="inlineStr">
         <is>
-          <t>1개</t>
+          <t>3개</t>
         </is>
       </c>
       <c r="C10" s="124" t="inlineStr">
         <is>
-          <t>찹스테이크</t>
+          <t>찹스테이크/에비동</t>
         </is>
       </c>
       <c r="D10" s="124" t="inlineStr">
@@ -5745,18 +5748,18 @@
         </is>
       </c>
       <c r="E10" s="125" t="n">
-        <v>1500</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="124" t="inlineStr">
         <is>
-          <t>양송이버섯</t>
+          <t>파프리카</t>
         </is>
       </c>
       <c r="B11" s="124" t="inlineStr">
         <is>
-          <t>1팩(8개)</t>
+          <t>1개</t>
         </is>
       </c>
       <c r="C11" s="124" t="inlineStr">
@@ -5770,23 +5773,23 @@
         </is>
       </c>
       <c r="E11" s="125" t="n">
-        <v>3000</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="124" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>양송이버섯</t>
         </is>
       </c>
       <c r="B12" s="124" t="inlineStr">
         <is>
-          <t>1개</t>
+          <t>1팩(8개)</t>
         </is>
       </c>
       <c r="C12" s="124" t="inlineStr">
         <is>
-          <t>맑은 무국</t>
+          <t>찹스테이크</t>
         </is>
       </c>
       <c r="D12" s="124" t="inlineStr">
@@ -5795,13 +5798,13 @@
         </is>
       </c>
       <c r="E12" s="125" t="n">
-        <v>2000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="124" t="inlineStr">
         <is>
-          <t>브로콜리</t>
+          <t>무</t>
         </is>
       </c>
       <c r="B13" s="124" t="inlineStr">
@@ -5811,7 +5814,7 @@
       </c>
       <c r="C13" s="124" t="inlineStr">
         <is>
-          <t>브로콜리 데침(칼슘)</t>
+          <t>맑은 무국</t>
         </is>
       </c>
       <c r="D13" s="124" t="inlineStr">
@@ -5820,23 +5823,23 @@
         </is>
       </c>
       <c r="E13" s="125" t="n">
-        <v>2500</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="124" t="inlineStr">
         <is>
-          <t>감자</t>
+          <t>브로콜리</t>
         </is>
       </c>
       <c r="B14" s="124" t="inlineStr">
         <is>
-          <t>3개</t>
+          <t>1개</t>
         </is>
       </c>
       <c r="C14" s="124" t="inlineStr">
         <is>
-          <t>감자채볶음</t>
+          <t>브로콜리 데침(칼슘)</t>
         </is>
       </c>
       <c r="D14" s="124" t="inlineStr">
@@ -5851,22 +5854,22 @@
     <row r="15">
       <c r="A15" s="124" t="inlineStr">
         <is>
-          <t>알배추</t>
+          <t>감자</t>
         </is>
       </c>
       <c r="B15" s="124" t="inlineStr">
         <is>
-          <t>1/2통</t>
+          <t>3개</t>
         </is>
       </c>
       <c r="C15" s="124" t="inlineStr">
         <is>
-          <t>배추 된장국</t>
+          <t>감자채볶음</t>
         </is>
       </c>
       <c r="D15" s="124" t="inlineStr">
         <is>
-          <t>9/3 구매</t>
+          <t>8/31 밤 주문</t>
         </is>
       </c>
       <c r="E15" s="125" t="n">
@@ -5876,114 +5879,114 @@
     <row r="16">
       <c r="A16" s="124" t="inlineStr">
         <is>
+          <t>알배추</t>
+        </is>
+      </c>
+      <c r="B16" s="124" t="inlineStr">
+        <is>
+          <t>1/2통</t>
+        </is>
+      </c>
+      <c r="C16" s="124" t="inlineStr">
+        <is>
+          <t>배추 된장국(금)</t>
+        </is>
+      </c>
+      <c r="D16" s="124" t="inlineStr">
+        <is>
+          <t>9/3 구매</t>
+        </is>
+      </c>
+      <c r="E16" s="125" t="n">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="124" t="inlineStr">
+        <is>
           <t>대파</t>
         </is>
       </c>
-      <c r="B16" s="124" t="inlineStr">
+      <c r="B17" s="124" t="inlineStr">
         <is>
           <t>2대</t>
         </is>
       </c>
-      <c r="C16" s="124" t="inlineStr">
+      <c r="C17" s="124" t="inlineStr">
         <is>
           <t>국·요리 전반</t>
         </is>
       </c>
-      <c r="D16" s="124" t="inlineStr">
+      <c r="D17" s="124" t="inlineStr">
         <is>
           <t>8/31 밤 주문</t>
         </is>
       </c>
-      <c r="E16" s="125" t="n">
+      <c r="E17" s="125" t="n">
         <v>1500</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="130" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="130" t="inlineStr">
         <is>
           <t>두부류</t>
         </is>
       </c>
-      <c r="B17" s="131" t="n"/>
-      <c r="C17" s="131" t="n"/>
-      <c r="D17" s="131" t="n"/>
-      <c r="E17" s="131" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="124" t="inlineStr">
+      <c r="B18" s="131" t="n"/>
+      <c r="C18" s="131" t="n"/>
+      <c r="D18" s="131" t="n"/>
+      <c r="E18" s="131" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="124" t="inlineStr">
         <is>
           <t>두부</t>
         </is>
       </c>
-      <c r="B18" s="124" t="inlineStr">
+      <c r="B19" s="124" t="inlineStr">
         <is>
           <t>1모</t>
         </is>
       </c>
-      <c r="C18" s="124" t="inlineStr">
+      <c r="C19" s="124" t="inlineStr">
         <is>
           <t>두부 맑은국(칼슘)</t>
         </is>
       </c>
-      <c r="D18" s="124" t="inlineStr">
+      <c r="D19" s="124" t="inlineStr">
         <is>
           <t>8/31 밤 주문</t>
         </is>
       </c>
-      <c r="E18" s="125" t="n">
+      <c r="E19" s="125" t="n">
         <v>2000</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="132" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="132" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="B19" s="133" t="n"/>
-      <c r="C19" s="133" t="n"/>
-      <c r="D19" s="133" t="n"/>
-      <c r="E19" s="133" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="124" t="inlineStr">
-        <is>
-          <t>달걀</t>
-        </is>
-      </c>
-      <c r="B20" s="124" t="inlineStr">
-        <is>
-          <t>15개입</t>
-        </is>
-      </c>
-      <c r="C20" s="124" t="inlineStr">
-        <is>
-          <t>에비동</t>
-        </is>
-      </c>
-      <c r="D20" s="124" t="inlineStr">
-        <is>
-          <t>8/31 밤 주문</t>
-        </is>
-      </c>
-      <c r="E20" s="125" t="n">
-        <v>4000</v>
-      </c>
+      <c r="B20" s="133" t="n"/>
+      <c r="C20" s="133" t="n"/>
+      <c r="D20" s="133" t="n"/>
+      <c r="E20" s="133" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="124" t="inlineStr">
         <is>
-          <t>구이김</t>
+          <t>달걀</t>
         </is>
       </c>
       <c r="B21" s="124" t="inlineStr">
         <is>
-          <t>1봉</t>
+          <t>15개입</t>
         </is>
       </c>
       <c r="C21" s="124" t="inlineStr">
         <is>
-          <t>김구이</t>
+          <t>에비동</t>
         </is>
       </c>
       <c r="D21" s="124" t="inlineStr">
@@ -5992,68 +5995,68 @@
         </is>
       </c>
       <c r="E21" s="125" t="n">
-        <v>3000</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="124" t="inlineStr">
         <is>
-          <t>가래떡</t>
+          <t>구이김</t>
         </is>
       </c>
       <c r="B22" s="124" t="inlineStr">
         <is>
-          <t>1팩</t>
+          <t>1봉</t>
         </is>
       </c>
       <c r="C22" s="124" t="inlineStr">
         <is>
-          <t>간식(가래떡구이)</t>
+          <t>김구이</t>
         </is>
       </c>
       <c r="D22" s="124" t="inlineStr">
         <is>
-          <t>9/3 구매</t>
+          <t>8/31 밤 주문</t>
         </is>
       </c>
       <c r="E22" s="125" t="n">
-        <v>4000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="124" t="inlineStr">
         <is>
-          <t>포도</t>
+          <t>가래떡</t>
         </is>
       </c>
       <c r="B23" s="124" t="inlineStr">
         <is>
-          <t>1송이</t>
+          <t>1팩</t>
         </is>
       </c>
       <c r="C23" s="124" t="inlineStr">
         <is>
-          <t>간식</t>
+          <t>간식(가래떡구이)</t>
         </is>
       </c>
       <c r="D23" s="124" t="inlineStr">
         <is>
-          <t>8/31 밤 주문</t>
+          <t>9/3 구매</t>
         </is>
       </c>
       <c r="E23" s="125" t="n">
-        <v>8000</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="124" t="inlineStr">
         <is>
-          <t>사과</t>
+          <t>포도</t>
         </is>
       </c>
       <c r="B24" s="124" t="inlineStr">
         <is>
-          <t>4~5개</t>
+          <t>1송이</t>
         </is>
       </c>
       <c r="C24" s="124" t="inlineStr">
@@ -6067,38 +6070,38 @@
         </is>
       </c>
       <c r="E24" s="125" t="n">
-        <v>9000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="124" t="inlineStr">
         <is>
-          <t>스테이크소스</t>
+          <t>사과</t>
         </is>
       </c>
       <c r="B25" s="124" t="inlineStr">
         <is>
-          <t>상비 확인</t>
+          <t>4~5개</t>
         </is>
       </c>
       <c r="C25" s="124" t="inlineStr">
         <is>
-          <t>찹스테이크</t>
+          <t>간식</t>
         </is>
       </c>
       <c r="D25" s="124" t="inlineStr">
         <is>
-          <t>상비</t>
+          <t>8/31 밤 주문</t>
         </is>
       </c>
       <c r="E25" s="125" t="n">
-        <v>0</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="124" t="inlineStr">
         <is>
-          <t>된장</t>
+          <t>스테이크소스</t>
         </is>
       </c>
       <c r="B26" s="124" t="inlineStr">
@@ -6108,7 +6111,7 @@
       </c>
       <c r="C26" s="124" t="inlineStr">
         <is>
-          <t>배추 된장국</t>
+          <t>찹스테이크</t>
         </is>
       </c>
       <c r="D26" s="124" t="inlineStr">
@@ -6123,22 +6126,22 @@
     <row r="27">
       <c r="A27" s="124" t="inlineStr">
         <is>
-          <t>어린이김치</t>
+          <t>된장</t>
         </is>
       </c>
       <c r="B27" s="124" t="inlineStr">
         <is>
-          <t>보유분 확인</t>
+          <t>상비 확인</t>
         </is>
       </c>
       <c r="C27" s="124" t="inlineStr">
         <is>
-          <t>상시 반찬</t>
+          <t>배추 된장국</t>
         </is>
       </c>
       <c r="D27" s="124" t="inlineStr">
         <is>
-          <t>보유</t>
+          <t>상비</t>
         </is>
       </c>
       <c r="E27" s="125" t="n">
@@ -6148,7 +6151,7 @@
     <row r="28">
       <c r="A28" s="124" t="inlineStr">
         <is>
-          <t>국물멸치·다시마·건새우</t>
+          <t>어린이김치</t>
         </is>
       </c>
       <c r="B28" s="124" t="inlineStr">
@@ -6158,7 +6161,7 @@
       </c>
       <c r="C28" s="124" t="inlineStr">
         <is>
-          <t>만능육수</t>
+          <t>상시 반찬</t>
         </is>
       </c>
       <c r="D28" s="124" t="inlineStr">
@@ -6171,19 +6174,44 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="134" t="inlineStr">
+      <c r="A29" s="124" t="inlineStr">
+        <is>
+          <t>국물멸치·다시마·건새우</t>
+        </is>
+      </c>
+      <c r="B29" s="124" t="inlineStr">
+        <is>
+          <t>보유분 확인</t>
+        </is>
+      </c>
+      <c r="C29" s="124" t="inlineStr">
+        <is>
+          <t>만능육수</t>
+        </is>
+      </c>
+      <c r="D29" s="124" t="inlineStr">
+        <is>
+          <t>보유</t>
+        </is>
+      </c>
+      <c r="E29" s="125" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="134" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
       </c>
-      <c r="B29" s="134" t="n"/>
-      <c r="C29" s="134" t="n"/>
-      <c r="D29" s="135" t="inlineStr">
+      <c r="B30" s="134" t="n"/>
+      <c r="C30" s="134" t="n"/>
+      <c r="D30" s="135" t="inlineStr">
         <is>
           <t>구매분 합계</t>
         </is>
       </c>
-      <c r="E29" s="136" t="n">
+      <c r="E30" s="136" t="n">
         <v>84500</v>
       </c>
     </row>

--- a/26년도_2주간_식단.xlsx
+++ b/26년도_2주간_식단.xlsx
@@ -5549,7 +5549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" style="90" min="1" max="1"/>
@@ -5626,7 +5626,7 @@
         </is>
       </c>
       <c r="E4" s="125" t="n">
-        <v>8000</v>
+        <v>10735</v>
       </c>
     </row>
     <row r="5">
@@ -5651,7 +5651,7 @@
         </is>
       </c>
       <c r="E5" s="125" t="n">
-        <v>18000</v>
+        <v>19990</v>
       </c>
     </row>
     <row r="6">
@@ -5691,55 +5691,55 @@
       <c r="E7" s="127" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="124" t="inlineStr">
-        <is>
-          <t>새우살 (냉동·구매완료)</t>
-        </is>
-      </c>
-      <c r="B8" s="124" t="inlineStr">
-        <is>
-          <t>480g</t>
-        </is>
-      </c>
-      <c r="C8" s="124" t="inlineStr">
-        <is>
-          <t>※ 이번주 미사용 → 다음주 이월</t>
-        </is>
-      </c>
-      <c r="D8" s="124" t="inlineStr">
-        <is>
-          <t>구매완료</t>
-        </is>
-      </c>
-      <c r="E8" s="125" t="n">
-        <v>11000</v>
-      </c>
+      <c r="A8" s="128" t="inlineStr">
+        <is>
+          <t>채소</t>
+        </is>
+      </c>
+      <c r="B8" s="129" t="n"/>
+      <c r="C8" s="129" t="n"/>
+      <c r="D8" s="129" t="n"/>
+      <c r="E8" s="129" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="128" t="inlineStr">
-        <is>
-          <t>채소</t>
-        </is>
-      </c>
-      <c r="B9" s="129" t="n"/>
-      <c r="C9" s="129" t="n"/>
-      <c r="D9" s="129" t="n"/>
-      <c r="E9" s="129" t="n"/>
+      <c r="A9" s="124" t="inlineStr">
+        <is>
+          <t>양파</t>
+        </is>
+      </c>
+      <c r="B9" s="124" t="inlineStr">
+        <is>
+          <t>3개</t>
+        </is>
+      </c>
+      <c r="C9" s="124" t="inlineStr">
+        <is>
+          <t>찹스테이크/에비동</t>
+        </is>
+      </c>
+      <c r="D9" s="124" t="inlineStr">
+        <is>
+          <t>8/31 밤 주문</t>
+        </is>
+      </c>
+      <c r="E9" s="125" t="n">
+        <v>3490</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="124" t="inlineStr">
         <is>
-          <t>양파</t>
+          <t>파프리카</t>
         </is>
       </c>
       <c r="B10" s="124" t="inlineStr">
         <is>
-          <t>3개</t>
+          <t>1개</t>
         </is>
       </c>
       <c r="C10" s="124" t="inlineStr">
         <is>
-          <t>찹스테이크/에비동</t>
+          <t>찹스테이크</t>
         </is>
       </c>
       <c r="D10" s="124" t="inlineStr">
@@ -5748,18 +5748,18 @@
         </is>
       </c>
       <c r="E10" s="125" t="n">
-        <v>2000</v>
+        <v>5490</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="124" t="inlineStr">
         <is>
-          <t>파프리카</t>
+          <t>양송이버섯</t>
         </is>
       </c>
       <c r="B11" s="124" t="inlineStr">
         <is>
-          <t>1개</t>
+          <t>1팩(8개)</t>
         </is>
       </c>
       <c r="C11" s="124" t="inlineStr">
@@ -5773,23 +5773,23 @@
         </is>
       </c>
       <c r="E11" s="125" t="n">
-        <v>1500</v>
+        <v>3490</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="124" t="inlineStr">
         <is>
-          <t>양송이버섯</t>
+          <t>무</t>
         </is>
       </c>
       <c r="B12" s="124" t="inlineStr">
         <is>
-          <t>1팩(8개)</t>
+          <t>1개</t>
         </is>
       </c>
       <c r="C12" s="124" t="inlineStr">
         <is>
-          <t>찹스테이크</t>
+          <t>맑은 무국</t>
         </is>
       </c>
       <c r="D12" s="124" t="inlineStr">
@@ -5798,13 +5798,13 @@
         </is>
       </c>
       <c r="E12" s="125" t="n">
-        <v>3000</v>
+        <v>2490</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="124" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>브로콜리</t>
         </is>
       </c>
       <c r="B13" s="124" t="inlineStr">
@@ -5814,7 +5814,7 @@
       </c>
       <c r="C13" s="124" t="inlineStr">
         <is>
-          <t>맑은 무국</t>
+          <t>브로콜리 데침(칼슘)</t>
         </is>
       </c>
       <c r="D13" s="124" t="inlineStr">
@@ -5823,23 +5823,23 @@
         </is>
       </c>
       <c r="E13" s="125" t="n">
-        <v>2000</v>
+        <v>4290</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="124" t="inlineStr">
         <is>
-          <t>브로콜리</t>
+          <t>감자</t>
         </is>
       </c>
       <c r="B14" s="124" t="inlineStr">
         <is>
-          <t>1개</t>
+          <t>3개</t>
         </is>
       </c>
       <c r="C14" s="124" t="inlineStr">
         <is>
-          <t>브로콜리 데침(칼슘)</t>
+          <t>감자채볶음</t>
         </is>
       </c>
       <c r="D14" s="124" t="inlineStr">
@@ -5848,145 +5848,145 @@
         </is>
       </c>
       <c r="E14" s="125" t="n">
-        <v>2500</v>
+        <v>3990</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="124" t="inlineStr">
         <is>
-          <t>감자</t>
+          <t>알배추</t>
         </is>
       </c>
       <c r="B15" s="124" t="inlineStr">
         <is>
-          <t>3개</t>
+          <t>1/2통</t>
         </is>
       </c>
       <c r="C15" s="124" t="inlineStr">
         <is>
-          <t>감자채볶음</t>
+          <t>배추 된장국(금)</t>
         </is>
       </c>
       <c r="D15" s="124" t="inlineStr">
         <is>
-          <t>8/31 밤 주문</t>
+          <t>9/3 구매</t>
         </is>
       </c>
       <c r="E15" s="125" t="n">
-        <v>2500</v>
+        <v>3990</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="124" t="inlineStr">
         <is>
-          <t>알배추</t>
+          <t>대파</t>
         </is>
       </c>
       <c r="B16" s="124" t="inlineStr">
         <is>
-          <t>1/2통</t>
+          <t>2대</t>
         </is>
       </c>
       <c r="C16" s="124" t="inlineStr">
         <is>
-          <t>배추 된장국(금)</t>
+          <t>국·요리 전반</t>
         </is>
       </c>
       <c r="D16" s="124" t="inlineStr">
         <is>
-          <t>9/3 구매</t>
+          <t>8/31 밤 주문</t>
         </is>
       </c>
       <c r="E16" s="125" t="n">
-        <v>2500</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="124" t="inlineStr">
-        <is>
-          <t>대파</t>
-        </is>
-      </c>
-      <c r="B17" s="124" t="inlineStr">
-        <is>
-          <t>2대</t>
-        </is>
-      </c>
-      <c r="C17" s="124" t="inlineStr">
-        <is>
-          <t>국·요리 전반</t>
-        </is>
-      </c>
-      <c r="D17" s="124" t="inlineStr">
+      <c r="A17" s="130" t="inlineStr">
+        <is>
+          <t>두부류</t>
+        </is>
+      </c>
+      <c r="B17" s="131" t="n"/>
+      <c r="C17" s="131" t="n"/>
+      <c r="D17" s="131" t="n"/>
+      <c r="E17" s="131" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="124" t="inlineStr">
+        <is>
+          <t>두부</t>
+        </is>
+      </c>
+      <c r="B18" s="124" t="inlineStr">
+        <is>
+          <t>1모</t>
+        </is>
+      </c>
+      <c r="C18" s="124" t="inlineStr">
+        <is>
+          <t>두부 맑은국(칼슘)</t>
+        </is>
+      </c>
+      <c r="D18" s="124" t="inlineStr">
         <is>
           <t>8/31 밤 주문</t>
         </is>
       </c>
-      <c r="E17" s="125" t="n">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="130" t="inlineStr">
-        <is>
-          <t>두부류</t>
-        </is>
-      </c>
-      <c r="B18" s="131" t="n"/>
-      <c r="C18" s="131" t="n"/>
-      <c r="D18" s="131" t="n"/>
-      <c r="E18" s="131" t="n"/>
+      <c r="E18" s="125" t="n">
+        <v>2200</v>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="124" t="inlineStr">
-        <is>
-          <t>두부</t>
-        </is>
-      </c>
-      <c r="B19" s="124" t="inlineStr">
-        <is>
-          <t>1모</t>
-        </is>
-      </c>
-      <c r="C19" s="124" t="inlineStr">
-        <is>
-          <t>두부 맑은국(칼슘)</t>
-        </is>
-      </c>
-      <c r="D19" s="124" t="inlineStr">
+      <c r="A19" s="132" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="B19" s="133" t="n"/>
+      <c r="C19" s="133" t="n"/>
+      <c r="D19" s="133" t="n"/>
+      <c r="E19" s="133" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="124" t="inlineStr">
+        <is>
+          <t>달걀</t>
+        </is>
+      </c>
+      <c r="B20" s="124" t="inlineStr">
+        <is>
+          <t>15개입</t>
+        </is>
+      </c>
+      <c r="C20" s="124" t="inlineStr">
+        <is>
+          <t>상비(이번주 달걀요리 없음)</t>
+        </is>
+      </c>
+      <c r="D20" s="124" t="inlineStr">
         <is>
           <t>8/31 밤 주문</t>
         </is>
       </c>
-      <c r="E19" s="125" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="132" t="inlineStr">
-        <is>
-          <t>기타</t>
-        </is>
-      </c>
-      <c r="B20" s="133" t="n"/>
-      <c r="C20" s="133" t="n"/>
-      <c r="D20" s="133" t="n"/>
-      <c r="E20" s="133" t="n"/>
+      <c r="E20" s="125" t="n">
+        <v>5562</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="124" t="inlineStr">
         <is>
-          <t>달걀</t>
+          <t>구이김</t>
         </is>
       </c>
       <c r="B21" s="124" t="inlineStr">
         <is>
-          <t>15개입</t>
+          <t>1봉</t>
         </is>
       </c>
       <c r="C21" s="124" t="inlineStr">
         <is>
-          <t>에비동</t>
+          <t>김구이</t>
         </is>
       </c>
       <c r="D21" s="124" t="inlineStr">
@@ -5995,68 +5995,68 @@
         </is>
       </c>
       <c r="E21" s="125" t="n">
-        <v>4000</v>
+        <v>4390</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="124" t="inlineStr">
         <is>
-          <t>구이김</t>
+          <t>가래떡</t>
         </is>
       </c>
       <c r="B22" s="124" t="inlineStr">
         <is>
-          <t>1봉</t>
+          <t>1팩</t>
         </is>
       </c>
       <c r="C22" s="124" t="inlineStr">
         <is>
-          <t>김구이</t>
+          <t>간식(가래떡구이)</t>
         </is>
       </c>
       <c r="D22" s="124" t="inlineStr">
         <is>
-          <t>8/31 밤 주문</t>
+          <t>9/3 구매</t>
         </is>
       </c>
       <c r="E22" s="125" t="n">
-        <v>3000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="124" t="inlineStr">
         <is>
-          <t>가래떡</t>
+          <t>포도</t>
         </is>
       </c>
       <c r="B23" s="124" t="inlineStr">
         <is>
-          <t>1팩</t>
+          <t>1송이</t>
         </is>
       </c>
       <c r="C23" s="124" t="inlineStr">
         <is>
-          <t>간식(가래떡구이)</t>
+          <t>간식</t>
         </is>
       </c>
       <c r="D23" s="124" t="inlineStr">
         <is>
-          <t>9/3 구매</t>
+          <t>8/31 밤 주문</t>
         </is>
       </c>
       <c r="E23" s="125" t="n">
-        <v>4000</v>
+        <v>12900</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="124" t="inlineStr">
         <is>
-          <t>포도</t>
+          <t>사과</t>
         </is>
       </c>
       <c r="B24" s="124" t="inlineStr">
         <is>
-          <t>1송이</t>
+          <t>4~5개</t>
         </is>
       </c>
       <c r="C24" s="124" t="inlineStr">
@@ -6070,38 +6070,38 @@
         </is>
       </c>
       <c r="E24" s="125" t="n">
-        <v>8000</v>
+        <v>19900</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="124" t="inlineStr">
         <is>
-          <t>사과</t>
+          <t>스테이크소스</t>
         </is>
       </c>
       <c r="B25" s="124" t="inlineStr">
         <is>
-          <t>4~5개</t>
+          <t>상비 확인</t>
         </is>
       </c>
       <c r="C25" s="124" t="inlineStr">
         <is>
-          <t>간식</t>
+          <t>찹스테이크</t>
         </is>
       </c>
       <c r="D25" s="124" t="inlineStr">
         <is>
-          <t>8/31 밤 주문</t>
+          <t>구매</t>
         </is>
       </c>
       <c r="E25" s="125" t="n">
-        <v>9000</v>
+        <v>3900</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="124" t="inlineStr">
         <is>
-          <t>스테이크소스</t>
+          <t>된장</t>
         </is>
       </c>
       <c r="B26" s="124" t="inlineStr">
@@ -6111,37 +6111,37 @@
       </c>
       <c r="C26" s="124" t="inlineStr">
         <is>
-          <t>찹스테이크</t>
+          <t>배추 된장국</t>
         </is>
       </c>
       <c r="D26" s="124" t="inlineStr">
         <is>
-          <t>상비</t>
+          <t>구매</t>
         </is>
       </c>
       <c r="E26" s="125" t="n">
-        <v>0</v>
+        <v>2690</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="124" t="inlineStr">
         <is>
-          <t>된장</t>
+          <t>어린이김치</t>
         </is>
       </c>
       <c r="B27" s="124" t="inlineStr">
         <is>
-          <t>상비 확인</t>
+          <t>보유분 확인</t>
         </is>
       </c>
       <c r="C27" s="124" t="inlineStr">
         <is>
-          <t>배추 된장국</t>
+          <t>상시 반찬</t>
         </is>
       </c>
       <c r="D27" s="124" t="inlineStr">
         <is>
-          <t>상비</t>
+          <t>보유</t>
         </is>
       </c>
       <c r="E27" s="125" t="n">
@@ -6151,7 +6151,7 @@
     <row r="28">
       <c r="A28" s="124" t="inlineStr">
         <is>
-          <t>어린이김치</t>
+          <t>국물멸치·다시마·건새우</t>
         </is>
       </c>
       <c r="B28" s="124" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="C28" s="124" t="inlineStr">
         <is>
-          <t>상시 반찬</t>
+          <t>만능육수</t>
         </is>
       </c>
       <c r="D28" s="124" t="inlineStr">
@@ -6174,45 +6174,20 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="124" t="inlineStr">
-        <is>
-          <t>국물멸치·다시마·건새우</t>
-        </is>
-      </c>
-      <c r="B29" s="124" t="inlineStr">
-        <is>
-          <t>보유분 확인</t>
-        </is>
-      </c>
-      <c r="C29" s="124" t="inlineStr">
-        <is>
-          <t>만능육수</t>
-        </is>
-      </c>
-      <c r="D29" s="124" t="inlineStr">
-        <is>
-          <t>보유</t>
-        </is>
-      </c>
-      <c r="E29" s="125" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="134" t="inlineStr">
+      <c r="A29" s="134" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
       </c>
-      <c r="B30" s="134" t="n"/>
-      <c r="C30" s="134" t="n"/>
-      <c r="D30" s="135" t="inlineStr">
-        <is>
-          <t>구매분 합계</t>
-        </is>
-      </c>
-      <c r="E30" s="136" t="n">
-        <v>84500</v>
+      <c r="B29" s="134" t="n"/>
+      <c r="C29" s="134" t="n"/>
+      <c r="D29" s="135" t="inlineStr">
+        <is>
+          <t>실제 결제예정(컬리)</t>
+        </is>
+      </c>
+      <c r="E29" s="136" t="n">
+        <v>116587</v>
       </c>
     </row>
   </sheetData>

--- a/26년도_2주간_식단.xlsx
+++ b/26년도_2주간_식단.xlsx
@@ -1465,7 +1465,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="351" customHeight="1" s="110">
+    <row r="4" ht="411" customHeight="1" s="110">
       <c r="A4" s="90" t="inlineStr">
         <is>
           <t>수 (9/16)</t>
@@ -1483,12 +1483,14 @@
       <c r="C4" s="91" t="inlineStr">
         <is>
           <t>[소고기 카레라이스] ★신메뉴 (아이 국민메뉴)
-1. 소고기(국거리/불고기용) 500g 한입크기
-   밑간: 소금·후추 → 냉장
+   ※ 국거리 사용 → 오래 끓여야 부드러움
+1. 소고기 국거리 300g → 2~3cm 큐브
+   (너무 작게 썰면 퍽퍽해짐)
+   밑간: 소금·후추 + 전분 1t 버무려 냉장
+   (전분이 육즙 보호)
 2. 감자 2개·당근 1개 한입크기
    / 양파 1개 큼직하게 → 냉장
-3. 순한맛 카레(고형 또는 가루) 준비
-   물 700ml 계량 (카레 봉지 기준 조정)
+3. 순한맛 카레(고형) 준비, 물 700ml 계량
 [맑은 북엇국]
 4. 북어채 2줌 물에 살짝 불려 짜기
 5. 무 약간 나박 / 두부 1/2모 / 대파 → 냉장
@@ -1503,26 +1505,29 @@
       </c>
       <c r="D4" s="91" t="inlineStr">
         <is>
-          <t>★ 식사 30분 전
-[맑은 북엇국 — 먼저]
-1. 냄비에 참기름 살짝, 북어채 1분 볶기
-2. 만능육수+무 넣고 끓이기
-3. 국간장 1T+다진마늘+소금+액젓 1t
+          <t>★ 식사 50분 전 (카레 끓이는 시간 확보)
+[소고기 카레라이스 — 먼저 시작]
+1. 냄비에 기름, 소고기 센불 1~2분
+   겉면만 빠르게 (육즙 봉인)
+2. 양파 넣고 투명해질 때까지 볶기
+3. 물 700ml 붓고 끓으면 뚜껑 덮어
+   ★ 중약불 15분 (고기 먼저 부드럽게)
+4. 감자·당근 넣고 뚜껑 덮어 ★ 15분 더
+   (총 30분 → 국거리 콜라겐이 녹아 부드러움)
+5. 불 끄고 카레 넣어 완전히 풀기
+6. 약불 5분 저으며 걸쭉하게
+   ※ 고기 하나 먹어봐서 질기면 5~10분 더
+   ※ 아이용은 순한맛, 어른은 후추 살짝
+[맑은 북엇국 — 카레 끓는 동안]
+7. 냄비에 참기름 살짝, 북어채 1분 볶기
+8. 만능육수+무 넣고 끓이기
+9. 국간장 1T+다진마늘+소금+액젓 1t
    → 두부 넣고 5분, 대파 마무리
    ※ 싱거우면 간 더!
-[소고기 카레라이스 — 메인]
-4. 냄비에 기름, 소고기 센불 겉면 익히기
-5. 양파 넣고 투명해질 때까지 볶기
-6. 감자·당근 넣고 1분 볶기
-7. 물 700ml 붓고 끓으면 중불 12~15분
-   (감자 익을 때까지)
-8. 불 끄고 카레 넣어 완전히 풀기
-9. 다시 약불 3~5분 저으며 걸쭉하게
-   ※ 아이용은 순한맛, 어른은 후추 살짝
-10. 밥 위에 넉넉히
 [오이 피클] 절임물에서 건져 접시에
 [키즈김치] 접시에
-[가래떡구이] 노릇 구워 꿀</t>
+[가래떡구이] 노릇 구워 꿀
+→ 밥 위에 카레 넉넉히</t>
         </is>
       </c>
     </row>

--- a/26년도_2주간_식단.xlsx
+++ b/26년도_2주간_식단.xlsx
@@ -1445,7 +1445,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="396" customHeight="1" s="110">
+    <row r="2" ht="516" customHeight="1" s="110">
       <c r="A2" s="156" t="inlineStr">
         <is>
           <t>화 (9/29)</t>
@@ -1455,7 +1455,7 @@
         <is>
           <t>순살 치즈 닭갈비 (안맵게)
 + 맑은 무국
-+ 브로콜리 데침(칼슘)
++ 브로콜리 새우 마늘볶음(칼슘)
 + 키즈김치
 + 포도 (간식)</t>
         </is>
@@ -1480,8 +1480,13 @@
 7. 육수: 물 1.2L + 국물멸치 15마리
    (머리·내장 제거 → 마른팬 30초 볶기)
    + 다시마 1장 + 건새우 1줌
-[브로콜리 — 칼슘]
+[브로콜리 새우 마늘볶음 — 칼슘]
 8. 브로콜리 1개 한입크기로 잘라 냉장
+9. 새우살 100g 정도 덜어 밑간(소금·후추)
+   → 냉장 (나머지는 수요일 새우전용)
+10. 마늘 4~5쪽 편썰기 → 냉장
+    ※ 다진마늘(상비)도 OK — 단 타기 쉬우니
+      기름에 먼저 넣지 말고 새우와 함께 투입
 [키즈김치] 어린이김치 통 준비</t>
         </is>
       </c>
@@ -1494,9 +1499,17 @@
 2. 무 넣고 중불 8분 (투명해질 때까지)
 3. 간: 국간장 1.5T+소금+다진마늘+액젓 1t
    대파 마무리 ※ 싱거우면 무조건 간 더!
-[브로콜리 데침 — 칼슘]
-4. 끓는 물+소금에 1분30초 데쳐
-   찬물에 헹궈 물기 빼기
+[브로콜리 새우 마늘볶음 — 칼슘]
+4. 브로콜리 끓는 물+소금에 1분30초 데쳐
+   찬물에 헹궈 물기 완전히 빼기 (중요)
+5. 팬에 올리브유, 편마늘 약불 1분 향 내기
+   (태우지 않게)
+   ※ 다진마늘이면 이 단계 생략 → 6번에서 같이
+6. 새우 넣고 중불 1~2분 익히기
+   (다진마늘 쓸 경우 여기서 함께 넣고 30초)
+7. 브로콜리 넣고 센불 1분 볶다가
+   굴소스 1t + 소금·후추로 간
+   ※ 데침과 달리 마늘향·굴소스로 감칠맛
 [순살 치즈 닭갈비 — 마지막]
 5. 넓은 팬에 기름, 양념 닭 센불 3분
    (겉면 익히기)
@@ -5710,7 +5723,7 @@
       </c>
       <c r="C6" s="161" t="inlineStr">
         <is>
-          <t>수 새우전</t>
+          <t>화 브로콜리볶음(100g) + 수 새우전</t>
         </is>
       </c>
       <c r="D6" s="161" t="inlineStr">
@@ -5846,7 +5859,7 @@
       </c>
       <c r="C12" s="161" t="inlineStr">
         <is>
-          <t>화 브로콜리 데침(칼슘)</t>
+          <t>화 브로콜리 새우 마늘볶음(칼슘)</t>
         </is>
       </c>
       <c r="D12" s="161" t="inlineStr">

--- a/26년도_2주간_식단.xlsx
+++ b/26년도_2주간_식단.xlsx
@@ -1414,7 +1414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" style="110" min="1" max="1"/>
@@ -1525,7 +1525,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="306" customHeight="1" s="110">
+    <row r="3" ht="276" customHeight="1" s="110">
       <c r="A3" s="156" t="inlineStr">
         <is>
           <t>수 (9/30)</t>
@@ -1573,8 +1573,82 @@
 5. 반죽 한 스푼씩 → 부침가루 → 계란옷
 6. 팬에 기름, 중불 앞뒤 노릇하게 부치기
    (속까지 익게, 너무 두껍지 않게)
-[키즈김치] 접시에 / [단감] 깎아서
-※ 금(10/2)은 여행으로 식단 없음</t>
+[키즈김치] 접시에 / [단감] 깎아서</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="471" customHeight="1" s="110">
+      <c r="A4" s="156" t="inlineStr">
+        <is>
+          <t>금 (10/2)</t>
+        </is>
+      </c>
+      <c r="B4" s="157" t="inlineStr">
+        <is>
+          <t>소고기 찹스테이크
++ 유부 맑은장국
++ 매쉬포테이토(칼슘)
++ 키즈김치
++ 배 (간식)</t>
+        </is>
+      </c>
+      <c r="C4" s="157" t="inlineStr">
+        <is>
+          <t>[소고기 찹스테이크] ★아주 호평 — 관건은 "부드러움"
+1. 부채살 600g → 사방 3cm 큐브
+   ※ 부채살 = 결이 부드러운 부위 (안심·등심보다
+     아이에게 적합). 너무 크게 썰면 속 안 익어
+     오래 굽게 되고 → 질겨짐
+2. 키친타월로 핏물·물기 완전 제거
+   (수분 남으면 구워지지 않고 삶아져 질김)
+3. 밑간: 올리브유 1T + 다진마늘 1T + 후추
+   → 냉장
+   ※ 소금은 굽기 직전에! (미리 넣으면 수분이
+     빠져나와 고기가 뻣뻣해짐)
+4. 파프리카 1개 + 양송이 8개 + 양파 1개
+   한입크기 → 냉장
+5. 소스: 스테이크소스 4T + 케첩 2T
+   + 굴소스 1T + 다진마늘 1t + 물 1T → 냉장
+[유부 맑은장국 — 감칠맛 만능육수]
+6. 유부 5장 채썰기 / 대파 어슷 → 냉장
+7. 육수: 물 1.2L + 국물멸치 15마리
+   (머리·내장 제거 → 마른팬 30초 볶기)
+   + 다시마 1장 + 건새우 1줌
+[매쉬포테이토 — 칼슘(우유)]
+8. 감자 3개 껍질 벗겨 큼직하게
+   → 물에 담가 냉장
+[키즈김치] 어린이김치 통 준비</t>
+        </is>
+      </c>
+      <c r="D4" s="157" t="inlineStr">
+        <is>
+          <t>★ 식사 30분 전
+★ 고기는 굽기 30분 전 냉장고에서 꺼내 실온에!
+  (찬 고기를 바로 구우면 속까지 익히느라
+   오래 굽게 되고 = 질겨짐)
+[유부 맑은장국 — 먼저]
+1. 육수재료 찬물부터 → 끓으면 다시마 건지고
+   중불 10분 → 체에 거르기
+2. 유부 넣고 5분
+3. 간: 국간장 1.5T+소금+다진마늘+액젓 1t
+   대파 마무리 ※ 싱거우면 무조건 간 더!
+[매쉬포테이토 — 칼슘]
+4. 감자 삶기(15분) → 뜨거울 때 곱게 으깨기
+5. 우유 3~4T + 소금 → 부드럽게 섞기
+[소고기 찹스테이크 — 마지막] ※ 부드러움 5원칙
+6. 굽기 직전 소금 뿌리기
+7. 팬을 아주 뜨겁게 예열 (스텐=물방울테스트)
+   + 기름 넉넉히
+8. ★ 고기를 한 번에 다 넣지 말고 2번에 나눠
+   굽기 (많이 넣으면 팬 온도 떨어져 삶아짐)
+9. ★ 센불에서 겉면만 1~2분! 속은 덜 익은 채로
+   꺼내기 (미디엄) — 여기서 더 익히면 질겨짐
+10. 같은 팬에 채소 센불 1분 볶기
+11. 고기 다시 넣고 소스 부어 센불 1~2분만
+    빠르게 졸이기 (잔열로 속까지 완성)
+12. 불 끄고 2~3분 그대로 두기 (육즙 재분배)
+    → 접시에
+[키즈김치] 접시에 / [배] 깎아서</t>
         </is>
       </c>
     </row>
@@ -5619,7 +5693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" style="110" min="1" max="1"/>
@@ -5632,7 +5706,7 @@
     <row r="1" ht="24" customHeight="1" s="110">
       <c r="A1" s="158" t="inlineStr">
         <is>
-          <t>10월 1주차 장보기 (9/29~9/30, 화·수 / 금 여행)</t>
+          <t>10월 1주차 장보기 (9/29~10/2, 화·수·금)</t>
         </is>
       </c>
     </row>
@@ -5700,86 +5774,86 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="163" t="inlineStr">
+      <c r="A5" s="161" t="inlineStr">
+        <is>
+          <t>부채살 (소고기)</t>
+        </is>
+      </c>
+      <c r="B5" s="161" t="inlineStr">
+        <is>
+          <t>600g</t>
+        </is>
+      </c>
+      <c r="C5" s="161" t="inlineStr">
+        <is>
+          <t>금 찹스테이크</t>
+        </is>
+      </c>
+      <c r="D5" s="161" t="inlineStr">
+        <is>
+          <t>9/30 구매</t>
+        </is>
+      </c>
+      <c r="E5" s="162" t="n">
+        <v>19000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="163" t="inlineStr">
         <is>
           <t>수산</t>
         </is>
       </c>
-      <c r="B5" s="164" t="n"/>
-      <c r="C5" s="164" t="n"/>
-      <c r="D5" s="164" t="n"/>
-      <c r="E5" s="164" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="161" t="inlineStr">
+      <c r="B6" s="164" t="n"/>
+      <c r="C6" s="164" t="n"/>
+      <c r="D6" s="164" t="n"/>
+      <c r="E6" s="164" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="161" t="inlineStr">
         <is>
           <t>새우살 (냉장)</t>
         </is>
       </c>
-      <c r="B6" s="161" t="inlineStr">
+      <c r="B7" s="161" t="inlineStr">
         <is>
           <t>480g</t>
         </is>
       </c>
-      <c r="C6" s="161" t="inlineStr">
+      <c r="C7" s="161" t="inlineStr">
         <is>
           <t>화 브로콜리볶음(100g) + 수 새우전</t>
         </is>
       </c>
-      <c r="D6" s="161" t="inlineStr">
+      <c r="D7" s="161" t="inlineStr">
         <is>
           <t>9/29 구매</t>
         </is>
       </c>
-      <c r="E6" s="162" t="n">
+      <c r="E7" s="162" t="n">
         <v>12000</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="165" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="165" t="inlineStr">
         <is>
           <t>채소</t>
         </is>
       </c>
-      <c r="B7" s="166" t="n"/>
-      <c r="C7" s="166" t="n"/>
-      <c r="D7" s="166" t="n"/>
-      <c r="E7" s="166" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="161" t="inlineStr">
-        <is>
-          <t>양배추</t>
-        </is>
-      </c>
-      <c r="B8" s="161" t="inlineStr">
-        <is>
-          <t>1/4~1/2통</t>
-        </is>
-      </c>
-      <c r="C8" s="161" t="inlineStr">
-        <is>
-          <t>화 닭갈비</t>
-        </is>
-      </c>
-      <c r="D8" s="161" t="inlineStr">
-        <is>
-          <t>9/28 밤 주문</t>
-        </is>
-      </c>
-      <c r="E8" s="162" t="n">
-        <v>2500</v>
-      </c>
+      <c r="B8" s="166" t="n"/>
+      <c r="C8" s="166" t="n"/>
+      <c r="D8" s="166" t="n"/>
+      <c r="E8" s="166" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="161" t="inlineStr">
         <is>
-          <t>양파</t>
+          <t>양배추</t>
         </is>
       </c>
       <c r="B9" s="161" t="inlineStr">
         <is>
-          <t>1개</t>
+          <t>1/4~1/2통</t>
         </is>
       </c>
       <c r="C9" s="161" t="inlineStr">
@@ -5793,13 +5867,13 @@
         </is>
       </c>
       <c r="E9" s="162" t="n">
-        <v>1500</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="161" t="inlineStr">
         <is>
-          <t>고구마</t>
+          <t>양파</t>
         </is>
       </c>
       <c r="B10" s="161" t="inlineStr">
@@ -5809,7 +5883,7 @@
       </c>
       <c r="C10" s="161" t="inlineStr">
         <is>
-          <t>화 닭갈비</t>
+          <t>화 닭갈비 + 금 찹스테이크</t>
         </is>
       </c>
       <c r="D10" s="161" t="inlineStr">
@@ -5818,13 +5892,13 @@
         </is>
       </c>
       <c r="E10" s="162" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="161" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>고구마</t>
         </is>
       </c>
       <c r="B11" s="161" t="inlineStr">
@@ -5834,7 +5908,7 @@
       </c>
       <c r="C11" s="161" t="inlineStr">
         <is>
-          <t>화 맑은 무국</t>
+          <t>화 닭갈비</t>
         </is>
       </c>
       <c r="D11" s="161" t="inlineStr">
@@ -5849,7 +5923,7 @@
     <row r="12">
       <c r="A12" s="161" t="inlineStr">
         <is>
-          <t>브로콜리</t>
+          <t>무</t>
         </is>
       </c>
       <c r="B12" s="161" t="inlineStr">
@@ -5859,7 +5933,7 @@
       </c>
       <c r="C12" s="161" t="inlineStr">
         <is>
-          <t>화 브로콜리 새우 마늘볶음(칼슘)</t>
+          <t>화 맑은 무국</t>
         </is>
       </c>
       <c r="D12" s="161" t="inlineStr">
@@ -5868,23 +5942,23 @@
         </is>
       </c>
       <c r="E12" s="162" t="n">
-        <v>2500</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="161" t="inlineStr">
         <is>
-          <t>감자</t>
+          <t>브로콜리</t>
         </is>
       </c>
       <c r="B13" s="161" t="inlineStr">
         <is>
-          <t>2~3개</t>
+          <t>1개</t>
         </is>
       </c>
       <c r="C13" s="161" t="inlineStr">
         <is>
-          <t>수 감자채볶음</t>
+          <t>화 브로콜리 새우 마늘볶음(칼슘)</t>
         </is>
       </c>
       <c r="D13" s="161" t="inlineStr">
@@ -5899,17 +5973,17 @@
     <row r="14">
       <c r="A14" s="161" t="inlineStr">
         <is>
-          <t>당근</t>
+          <t>감자</t>
         </is>
       </c>
       <c r="B14" s="161" t="inlineStr">
         <is>
-          <t>1개</t>
+          <t>1kg</t>
         </is>
       </c>
       <c r="C14" s="161" t="inlineStr">
         <is>
-          <t>수 새우전</t>
+          <t>수 감자채볶음 + 금 매쉬포테이토</t>
         </is>
       </c>
       <c r="D14" s="161" t="inlineStr">
@@ -5918,53 +5992,53 @@
         </is>
       </c>
       <c r="E14" s="162" t="n">
-        <v>1000</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="161" t="inlineStr">
         <is>
-          <t>아욱</t>
+          <t>당근</t>
         </is>
       </c>
       <c r="B15" s="161" t="inlineStr">
         <is>
-          <t>1단</t>
+          <t>1개</t>
         </is>
       </c>
       <c r="C15" s="161" t="inlineStr">
         <is>
-          <t>수 아욱 된장국</t>
+          <t>수 새우전</t>
         </is>
       </c>
       <c r="D15" s="161" t="inlineStr">
         <is>
-          <t>9/29 구매</t>
+          <t>9/28 밤 주문</t>
         </is>
       </c>
       <c r="E15" s="162" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="161" t="inlineStr">
         <is>
-          <t>대파</t>
+          <t>아욱</t>
         </is>
       </c>
       <c r="B16" s="161" t="inlineStr">
         <is>
-          <t>2대</t>
+          <t>1단</t>
         </is>
       </c>
       <c r="C16" s="161" t="inlineStr">
         <is>
-          <t>전반</t>
+          <t>수 아욱 된장국</t>
         </is>
       </c>
       <c r="D16" s="161" t="inlineStr">
         <is>
-          <t>9/28 밤 주문</t>
+          <t>9/29 구매</t>
         </is>
       </c>
       <c r="E16" s="162" t="n">
@@ -5972,105 +6046,105 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="167" t="inlineStr">
-        <is>
-          <t>기타</t>
-        </is>
-      </c>
-      <c r="B17" s="168" t="n"/>
-      <c r="C17" s="168" t="n"/>
-      <c r="D17" s="168" t="n"/>
-      <c r="E17" s="168" t="n"/>
+      <c r="A17" s="161" t="inlineStr">
+        <is>
+          <t>대파</t>
+        </is>
+      </c>
+      <c r="B17" s="161" t="inlineStr">
+        <is>
+          <t>2대</t>
+        </is>
+      </c>
+      <c r="C17" s="161" t="inlineStr">
+        <is>
+          <t>전반</t>
+        </is>
+      </c>
+      <c r="D17" s="161" t="inlineStr">
+        <is>
+          <t>9/28 밤 주문</t>
+        </is>
+      </c>
+      <c r="E17" s="162" t="n">
+        <v>2000</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="161" t="inlineStr">
         <is>
-          <t>모짜렐라치즈</t>
+          <t>파프리카</t>
         </is>
       </c>
       <c r="B18" s="161" t="inlineStr">
         <is>
-          <t>1봉</t>
+          <t>1개</t>
         </is>
       </c>
       <c r="C18" s="161" t="inlineStr">
         <is>
-          <t>화 치즈 닭갈비(칼슘)</t>
+          <t>금 찹스테이크</t>
         </is>
       </c>
       <c r="D18" s="161" t="inlineStr">
         <is>
-          <t>9/28 밤 주문</t>
+          <t>9/30 구매</t>
         </is>
       </c>
       <c r="E18" s="162" t="n">
-        <v>9000</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="161" t="inlineStr">
         <is>
-          <t>떡볶이떡</t>
+          <t>양송이버섯</t>
         </is>
       </c>
       <c r="B19" s="161" t="inlineStr">
         <is>
-          <t>1줌(선택)</t>
+          <t>1팩</t>
         </is>
       </c>
       <c r="C19" s="161" t="inlineStr">
         <is>
-          <t>화 닭갈비</t>
+          <t>금 찹스테이크</t>
         </is>
       </c>
       <c r="D19" s="161" t="inlineStr">
         <is>
-          <t>9/28 밤 주문</t>
+          <t>9/30 구매</t>
         </is>
       </c>
       <c r="E19" s="162" t="n">
-        <v>3000</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="161" t="inlineStr">
-        <is>
-          <t>달걀</t>
-        </is>
-      </c>
-      <c r="B20" s="161" t="inlineStr">
-        <is>
-          <t>10~15개입</t>
-        </is>
-      </c>
-      <c r="C20" s="161" t="inlineStr">
-        <is>
-          <t>수 새우전 옷</t>
-        </is>
-      </c>
-      <c r="D20" s="161" t="inlineStr">
-        <is>
-          <t>9/28 밤 주문</t>
-        </is>
-      </c>
-      <c r="E20" s="162" t="n">
-        <v>6000</v>
-      </c>
+      <c r="A20" s="167" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="B20" s="168" t="n"/>
+      <c r="C20" s="168" t="n"/>
+      <c r="D20" s="168" t="n"/>
+      <c r="E20" s="168" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="161" t="inlineStr">
         <is>
-          <t>포도</t>
+          <t>모짜렐라치즈</t>
         </is>
       </c>
       <c r="B21" s="161" t="inlineStr">
         <is>
-          <t>1송이</t>
+          <t>1봉</t>
         </is>
       </c>
       <c r="C21" s="161" t="inlineStr">
         <is>
-          <t>화 간식</t>
+          <t>화 치즈 닭갈비(칼슘)</t>
         </is>
       </c>
       <c r="D21" s="161" t="inlineStr">
@@ -6079,23 +6153,23 @@
         </is>
       </c>
       <c r="E21" s="162" t="n">
-        <v>10000</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="161" t="inlineStr">
         <is>
-          <t>단감</t>
+          <t>떡볶이떡</t>
         </is>
       </c>
       <c r="B22" s="161" t="inlineStr">
         <is>
-          <t>4~5개</t>
+          <t>1줌(선택)</t>
         </is>
       </c>
       <c r="C22" s="161" t="inlineStr">
         <is>
-          <t>수 간식</t>
+          <t>화 닭갈비</t>
         </is>
       </c>
       <c r="D22" s="161" t="inlineStr">
@@ -6104,103 +6178,103 @@
         </is>
       </c>
       <c r="E22" s="162" t="n">
-        <v>9000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="161" t="inlineStr">
         <is>
-          <t>부침가루</t>
+          <t>달걀</t>
         </is>
       </c>
       <c r="B23" s="161" t="inlineStr">
         <is>
-          <t>상비 확인</t>
+          <t>10~15개입</t>
         </is>
       </c>
       <c r="C23" s="161" t="inlineStr">
         <is>
-          <t>수 새우전</t>
+          <t>수 새우전 옷</t>
         </is>
       </c>
       <c r="D23" s="161" t="inlineStr">
         <is>
-          <t>상비</t>
+          <t>9/28 밤 주문</t>
         </is>
       </c>
       <c r="E23" s="162" t="n">
-        <v>0</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="161" t="inlineStr">
         <is>
-          <t>굴소스·간장·미림</t>
+          <t>포도</t>
         </is>
       </c>
       <c r="B24" s="161" t="inlineStr">
         <is>
-          <t>상비 확인</t>
+          <t>1송이</t>
         </is>
       </c>
       <c r="C24" s="161" t="inlineStr">
         <is>
-          <t>화 닭갈비 양념</t>
+          <t>화 간식</t>
         </is>
       </c>
       <c r="D24" s="161" t="inlineStr">
         <is>
-          <t>상비</t>
+          <t>9/28 밤 주문</t>
         </is>
       </c>
       <c r="E24" s="162" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="161" t="inlineStr">
         <is>
-          <t>된장</t>
+          <t>단감</t>
         </is>
       </c>
       <c r="B25" s="161" t="inlineStr">
         <is>
-          <t>상비 확인</t>
+          <t>4~5개</t>
         </is>
       </c>
       <c r="C25" s="161" t="inlineStr">
         <is>
-          <t>수 아욱 된장국</t>
+          <t>수 간식</t>
         </is>
       </c>
       <c r="D25" s="161" t="inlineStr">
         <is>
-          <t>상비</t>
+          <t>9/28 밤 주문</t>
         </is>
       </c>
       <c r="E25" s="162" t="n">
-        <v>0</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="161" t="inlineStr">
         <is>
-          <t>어린이김치</t>
+          <t>부침가루</t>
         </is>
       </c>
       <c r="B26" s="161" t="inlineStr">
         <is>
-          <t>보유분 확인</t>
+          <t>상비 확인</t>
         </is>
       </c>
       <c r="C26" s="161" t="inlineStr">
         <is>
-          <t>상시 반찬</t>
+          <t>수 새우전</t>
         </is>
       </c>
       <c r="D26" s="161" t="inlineStr">
         <is>
-          <t>보유</t>
+          <t>상비</t>
         </is>
       </c>
       <c r="E26" s="162" t="n">
@@ -6210,22 +6284,22 @@
     <row r="27">
       <c r="A27" s="161" t="inlineStr">
         <is>
-          <t>국물멸치·다시마·건새우</t>
+          <t>굴소스·간장·미림</t>
         </is>
       </c>
       <c r="B27" s="161" t="inlineStr">
         <is>
-          <t>보유분 확인</t>
+          <t>상비 확인</t>
         </is>
       </c>
       <c r="C27" s="161" t="inlineStr">
         <is>
-          <t>만능육수</t>
+          <t>화 닭갈비 양념</t>
         </is>
       </c>
       <c r="D27" s="161" t="inlineStr">
         <is>
-          <t>보유</t>
+          <t>상비</t>
         </is>
       </c>
       <c r="E27" s="162" t="n">
@@ -6233,20 +6307,170 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="169" t="inlineStr">
+      <c r="A28" s="161" t="inlineStr">
+        <is>
+          <t>된장</t>
+        </is>
+      </c>
+      <c r="B28" s="161" t="inlineStr">
+        <is>
+          <t>상비 확인</t>
+        </is>
+      </c>
+      <c r="C28" s="161" t="inlineStr">
+        <is>
+          <t>수 아욱 된장국</t>
+        </is>
+      </c>
+      <c r="D28" s="161" t="inlineStr">
+        <is>
+          <t>상비</t>
+        </is>
+      </c>
+      <c r="E28" s="162" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="161" t="inlineStr">
+        <is>
+          <t>어린이김치</t>
+        </is>
+      </c>
+      <c r="B29" s="161" t="inlineStr">
+        <is>
+          <t>보유분 확인</t>
+        </is>
+      </c>
+      <c r="C29" s="161" t="inlineStr">
+        <is>
+          <t>상시 반찬</t>
+        </is>
+      </c>
+      <c r="D29" s="161" t="inlineStr">
+        <is>
+          <t>보유</t>
+        </is>
+      </c>
+      <c r="E29" s="162" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="161" t="inlineStr">
+        <is>
+          <t>국물멸치·다시마·건새우</t>
+        </is>
+      </c>
+      <c r="B30" s="161" t="inlineStr">
+        <is>
+          <t>보유분 확인</t>
+        </is>
+      </c>
+      <c r="C30" s="161" t="inlineStr">
+        <is>
+          <t>만능육수</t>
+        </is>
+      </c>
+      <c r="D30" s="161" t="inlineStr">
+        <is>
+          <t>보유</t>
+        </is>
+      </c>
+      <c r="E30" s="162" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="161" t="inlineStr">
+        <is>
+          <t>유부</t>
+        </is>
+      </c>
+      <c r="B31" s="161" t="inlineStr">
+        <is>
+          <t>1봉</t>
+        </is>
+      </c>
+      <c r="C31" s="161" t="inlineStr">
+        <is>
+          <t>금 유부 맑은장국</t>
+        </is>
+      </c>
+      <c r="D31" s="161" t="inlineStr">
+        <is>
+          <t>9/30 구매</t>
+        </is>
+      </c>
+      <c r="E31" s="162" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="161" t="inlineStr">
+        <is>
+          <t>우유</t>
+        </is>
+      </c>
+      <c r="B32" s="161" t="inlineStr">
+        <is>
+          <t>1L</t>
+        </is>
+      </c>
+      <c r="C32" s="161" t="inlineStr">
+        <is>
+          <t>금 매쉬포테이토(칼슘)</t>
+        </is>
+      </c>
+      <c r="D32" s="161" t="inlineStr">
+        <is>
+          <t>9/30 구매</t>
+        </is>
+      </c>
+      <c r="E32" s="162" t="n">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="161" t="inlineStr">
+        <is>
+          <t>배</t>
+        </is>
+      </c>
+      <c r="B33" s="161" t="inlineStr">
+        <is>
+          <t>2~3개</t>
+        </is>
+      </c>
+      <c r="C33" s="161" t="inlineStr">
+        <is>
+          <t>금 간식</t>
+        </is>
+      </c>
+      <c r="D33" s="161" t="inlineStr">
+        <is>
+          <t>9/30 구매</t>
+        </is>
+      </c>
+      <c r="E33" s="162" t="n">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="169" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
       </c>
-      <c r="B28" s="169" t="n"/>
-      <c r="C28" s="169" t="n"/>
-      <c r="D28" s="170" t="inlineStr">
+      <c r="B34" s="169" t="n"/>
+      <c r="C34" s="169" t="n"/>
+      <c r="D34" s="170" t="inlineStr">
         <is>
           <t>구매분(추정)</t>
         </is>
       </c>
-      <c r="E28" s="171" t="n">
-        <v>76000</v>
+      <c r="E34" s="171" t="n">
+        <v>116500</v>
       </c>
     </row>
   </sheetData>

--- a/26년도_2주간_식단.xlsx
+++ b/26년도_2주간_식단.xlsx
@@ -1577,7 +1577,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="471" customHeight="1" s="110">
+    <row r="4" ht="486" customHeight="1" s="110">
       <c r="A4" s="156" t="inlineStr">
         <is>
           <t>금 (10/2)</t>
@@ -1595,10 +1595,11 @@
       <c r="C4" s="157" t="inlineStr">
         <is>
           <t>[소고기 찹스테이크] ★아주 호평 — 관건은 "부드러움"
-1. 부채살 600g → 사방 3cm 큐브
-   ※ 부채살 = 결이 부드러운 부위 (안심·등심보다
-     아이에게 적합). 너무 크게 썰면 속 안 익어
-     오래 굽게 되고 → 질겨짐
+1. 부채살 600g → ★ 큐브 아닌 "1cm 두께로
+   저며 썰기" (결 반대 방향으로)
+   ※ 큐브는 속까지 익히느라 오래 구워 질겨짐.
+     얇게 저미면 40초~1분만에 익어 훨씬 부드러움
+   ※ 부채살 = 결이 고운 부위라 저며 썰기에 최적
 2. 키친타월로 핏물·물기 완전 제거
    (수분 남으면 구워지지 않고 삶아져 질김)
 3. 밑간: 올리브유 1T + 다진마늘 1T + 후추
@@ -1641,8 +1642,9 @@
    + 기름 넉넉히
 8. ★ 고기를 한 번에 다 넣지 말고 2번에 나눠
    굽기 (많이 넣으면 팬 온도 떨어져 삶아짐)
-9. ★ 센불에서 겉면만 1~2분! 속은 덜 익은 채로
-   꺼내기 (미디엄) — 여기서 더 익히면 질겨짐
+9. ★ 얇게 저몄으니 센불에서 한 면 40초~1분!
+   앞뒤 겉면만 익혀 바로 꺼내기 (미디엄)
+   — 여기서 더 익히면 질겨짐
 10. 같은 팬에 채소 센불 1분 볶기
 11. 고기 다시 넣고 소스 부어 센불 1~2분만
     빠르게 졸이기 (잔열로 속까지 완성)

--- a/26년도_2주간_식단.xlsx
+++ b/26년도_2주간_식단.xlsx
@@ -245,7 +245,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="47">
+  <fills count="49">
     <fill>
       <patternFill/>
     </fill>
@@ -501,6 +501,16 @@
         <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE699"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D9D9"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="18">
     <border>
@@ -724,7 +734,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="172">
+  <cellXfs count="178">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1155,6 +1165,24 @@
     <xf numFmtId="3" fontId="25" fillId="46" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="44" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="23" fillId="44" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="47" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="23" fillId="47" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="48" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="23" fillId="48" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -5708,7 +5736,7 @@
     <row r="1" ht="24" customHeight="1" s="110">
       <c r="A1" s="158" t="inlineStr">
         <is>
-          <t>10월 1주차 장보기 (9/29~10/2, 화·수·금)</t>
+          <t>10월 1주차 장보기 (9/29~10/2) — ✅화·수 주문완료 / 🔔금요일분 10/1(목) 주문</t>
         </is>
       </c>
     </row>
@@ -5751,52 +5779,52 @@
       <c r="E3" s="160" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="161" t="inlineStr">
+      <c r="A4" s="172" t="inlineStr">
         <is>
           <t>닭다리살 (순살)</t>
         </is>
       </c>
-      <c r="B4" s="161" t="inlineStr">
+      <c r="B4" s="172" t="inlineStr">
         <is>
           <t>600g</t>
         </is>
       </c>
-      <c r="C4" s="161" t="inlineStr">
+      <c r="C4" s="172" t="inlineStr">
         <is>
           <t>화 치즈 닭갈비</t>
         </is>
       </c>
-      <c r="D4" s="161" t="inlineStr">
-        <is>
-          <t>9/28 밤 주문</t>
-        </is>
-      </c>
-      <c r="E4" s="162" t="n">
-        <v>9000</v>
+      <c r="D4" s="172" t="inlineStr">
+        <is>
+          <t>✅ 주문완료(9/28밤)</t>
+        </is>
+      </c>
+      <c r="E4" s="173" t="n">
+        <v>18990</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="161" t="inlineStr">
+      <c r="A5" s="174" t="inlineStr">
         <is>
           <t>부채살 (소고기)</t>
         </is>
       </c>
-      <c r="B5" s="161" t="inlineStr">
+      <c r="B5" s="174" t="inlineStr">
         <is>
           <t>600g</t>
         </is>
       </c>
-      <c r="C5" s="161" t="inlineStr">
+      <c r="C5" s="174" t="inlineStr">
         <is>
           <t>금 찹스테이크</t>
         </is>
       </c>
-      <c r="D5" s="161" t="inlineStr">
-        <is>
-          <t>9/30 구매</t>
-        </is>
-      </c>
-      <c r="E5" s="162" t="n">
+      <c r="D5" s="174" t="inlineStr">
+        <is>
+          <t>🔔 10/1(목) 주문 예정</t>
+        </is>
+      </c>
+      <c r="E5" s="175" t="n">
         <v>19000</v>
       </c>
     </row>
@@ -5812,28 +5840,28 @@
       <c r="E6" s="164" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="161" t="inlineStr">
+      <c r="A7" s="172" t="inlineStr">
         <is>
           <t>새우살 (냉장)</t>
         </is>
       </c>
-      <c r="B7" s="161" t="inlineStr">
+      <c r="B7" s="172" t="inlineStr">
         <is>
           <t>480g</t>
         </is>
       </c>
-      <c r="C7" s="161" t="inlineStr">
+      <c r="C7" s="172" t="inlineStr">
         <is>
           <t>화 브로콜리볶음(100g) + 수 새우전</t>
         </is>
       </c>
-      <c r="D7" s="161" t="inlineStr">
-        <is>
-          <t>9/29 구매</t>
-        </is>
-      </c>
-      <c r="E7" s="162" t="n">
-        <v>12000</v>
+      <c r="D7" s="172" t="inlineStr">
+        <is>
+          <t>✅ 주문완료(9/28밤)</t>
+        </is>
+      </c>
+      <c r="E7" s="173" t="n">
+        <v>15700</v>
       </c>
     </row>
     <row r="8">
@@ -5848,277 +5876,277 @@
       <c r="E8" s="166" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="161" t="inlineStr">
+      <c r="A9" s="172" t="inlineStr">
         <is>
           <t>양배추</t>
         </is>
       </c>
-      <c r="B9" s="161" t="inlineStr">
+      <c r="B9" s="172" t="inlineStr">
         <is>
           <t>1/4~1/2통</t>
         </is>
       </c>
-      <c r="C9" s="161" t="inlineStr">
+      <c r="C9" s="172" t="inlineStr">
         <is>
           <t>화 닭갈비</t>
         </is>
       </c>
-      <c r="D9" s="161" t="inlineStr">
-        <is>
-          <t>9/28 밤 주문</t>
-        </is>
-      </c>
-      <c r="E9" s="162" t="n">
+      <c r="D9" s="172" t="inlineStr">
+        <is>
+          <t>✅ 주문완료(9/28밤)</t>
+        </is>
+      </c>
+      <c r="E9" s="173" t="n">
+        <v>2290</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="172" t="inlineStr">
+        <is>
+          <t>양파</t>
+        </is>
+      </c>
+      <c r="B10" s="172" t="inlineStr">
+        <is>
+          <t>1개</t>
+        </is>
+      </c>
+      <c r="C10" s="172" t="inlineStr">
+        <is>
+          <t>화 닭갈비 + 금 찹스테이크</t>
+        </is>
+      </c>
+      <c r="D10" s="172" t="inlineStr">
+        <is>
+          <t>✅ 주문완료(9/28밤)</t>
+        </is>
+      </c>
+      <c r="E10" s="173" t="n">
+        <v>4490</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="172" t="inlineStr">
+        <is>
+          <t>고구마</t>
+        </is>
+      </c>
+      <c r="B11" s="172" t="inlineStr">
+        <is>
+          <t>1개</t>
+        </is>
+      </c>
+      <c r="C11" s="172" t="inlineStr">
+        <is>
+          <t>화 닭갈비</t>
+        </is>
+      </c>
+      <c r="D11" s="172" t="inlineStr">
+        <is>
+          <t>✅ 주문완료(9/28밤)</t>
+        </is>
+      </c>
+      <c r="E11" s="173" t="n">
+        <v>5990</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="172" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="B12" s="172" t="inlineStr">
+        <is>
+          <t>1개</t>
+        </is>
+      </c>
+      <c r="C12" s="172" t="inlineStr">
+        <is>
+          <t>화 맑은 무국</t>
+        </is>
+      </c>
+      <c r="D12" s="172" t="inlineStr">
+        <is>
+          <t>✅ 주문완료(9/28밤)</t>
+        </is>
+      </c>
+      <c r="E12" s="173" t="n">
+        <v>2490</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="172" t="inlineStr">
+        <is>
+          <t>브로콜리</t>
+        </is>
+      </c>
+      <c r="B13" s="172" t="inlineStr">
+        <is>
+          <t>1개</t>
+        </is>
+      </c>
+      <c r="C13" s="172" t="inlineStr">
+        <is>
+          <t>화 브로콜리 새우 마늘볶음(칼슘)</t>
+        </is>
+      </c>
+      <c r="D13" s="172" t="inlineStr">
+        <is>
+          <t>✅ 주문완료(9/28밤)</t>
+        </is>
+      </c>
+      <c r="E13" s="173" t="n">
+        <v>4290</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="172" t="inlineStr">
+        <is>
+          <t>감자</t>
+        </is>
+      </c>
+      <c r="B14" s="172" t="inlineStr">
+        <is>
+          <t>1kg</t>
+        </is>
+      </c>
+      <c r="C14" s="172" t="inlineStr">
+        <is>
+          <t>수 감자채볶음 + 금 매쉬포테이토</t>
+        </is>
+      </c>
+      <c r="D14" s="172" t="inlineStr">
+        <is>
+          <t>✅ 주문완료(9/28밤)</t>
+        </is>
+      </c>
+      <c r="E14" s="173" t="n">
+        <v>3990</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="172" t="inlineStr">
+        <is>
+          <t>당근</t>
+        </is>
+      </c>
+      <c r="B15" s="172" t="inlineStr">
+        <is>
+          <t>1개</t>
+        </is>
+      </c>
+      <c r="C15" s="172" t="inlineStr">
+        <is>
+          <t>수 새우전</t>
+        </is>
+      </c>
+      <c r="D15" s="172" t="inlineStr">
+        <is>
+          <t>✅ 주문완료(9/28밤)</t>
+        </is>
+      </c>
+      <c r="E15" s="173" t="n">
+        <v>1990</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="172" t="inlineStr">
+        <is>
+          <t>아욱</t>
+        </is>
+      </c>
+      <c r="B16" s="172" t="inlineStr">
+        <is>
+          <t>1단</t>
+        </is>
+      </c>
+      <c r="C16" s="172" t="inlineStr">
+        <is>
+          <t>수 아욱 된장국</t>
+        </is>
+      </c>
+      <c r="D16" s="172" t="inlineStr">
+        <is>
+          <t>✅ 주문완료(9/28밤)</t>
+        </is>
+      </c>
+      <c r="E16" s="173" t="n">
+        <v>3990</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="172" t="inlineStr">
+        <is>
+          <t>대파</t>
+        </is>
+      </c>
+      <c r="B17" s="172" t="inlineStr">
+        <is>
+          <t>2대</t>
+        </is>
+      </c>
+      <c r="C17" s="172" t="inlineStr">
+        <is>
+          <t>전반</t>
+        </is>
+      </c>
+      <c r="D17" s="172" t="inlineStr">
+        <is>
+          <t>✅ 주문완료(9/28밤)</t>
+        </is>
+      </c>
+      <c r="E17" s="173" t="n">
+        <v>2090</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="174" t="inlineStr">
+        <is>
+          <t>파프리카</t>
+        </is>
+      </c>
+      <c r="B18" s="174" t="inlineStr">
+        <is>
+          <t>1개</t>
+        </is>
+      </c>
+      <c r="C18" s="174" t="inlineStr">
+        <is>
+          <t>금 찹스테이크</t>
+        </is>
+      </c>
+      <c r="D18" s="174" t="inlineStr">
+        <is>
+          <t>🔔 10/1(목) 주문 예정</t>
+        </is>
+      </c>
+      <c r="E18" s="175" t="n">
         <v>2500</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="161" t="inlineStr">
-        <is>
-          <t>양파</t>
-        </is>
-      </c>
-      <c r="B10" s="161" t="inlineStr">
-        <is>
-          <t>1개</t>
-        </is>
-      </c>
-      <c r="C10" s="161" t="inlineStr">
-        <is>
-          <t>화 닭갈비 + 금 찹스테이크</t>
-        </is>
-      </c>
-      <c r="D10" s="161" t="inlineStr">
-        <is>
-          <t>9/28 밤 주문</t>
-        </is>
-      </c>
-      <c r="E10" s="162" t="n">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="161" t="inlineStr">
-        <is>
-          <t>고구마</t>
-        </is>
-      </c>
-      <c r="B11" s="161" t="inlineStr">
-        <is>
-          <t>1개</t>
-        </is>
-      </c>
-      <c r="C11" s="161" t="inlineStr">
-        <is>
-          <t>화 닭갈비</t>
-        </is>
-      </c>
-      <c r="D11" s="161" t="inlineStr">
-        <is>
-          <t>9/28 밤 주문</t>
-        </is>
-      </c>
-      <c r="E11" s="162" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="161" t="inlineStr">
-        <is>
-          <t>무</t>
-        </is>
-      </c>
-      <c r="B12" s="161" t="inlineStr">
-        <is>
-          <t>1개</t>
-        </is>
-      </c>
-      <c r="C12" s="161" t="inlineStr">
-        <is>
-          <t>화 맑은 무국</t>
-        </is>
-      </c>
-      <c r="D12" s="161" t="inlineStr">
-        <is>
-          <t>9/28 밤 주문</t>
-        </is>
-      </c>
-      <c r="E12" s="162" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="161" t="inlineStr">
-        <is>
-          <t>브로콜리</t>
-        </is>
-      </c>
-      <c r="B13" s="161" t="inlineStr">
-        <is>
-          <t>1개</t>
-        </is>
-      </c>
-      <c r="C13" s="161" t="inlineStr">
-        <is>
-          <t>화 브로콜리 새우 마늘볶음(칼슘)</t>
-        </is>
-      </c>
-      <c r="D13" s="161" t="inlineStr">
-        <is>
-          <t>9/28 밤 주문</t>
-        </is>
-      </c>
-      <c r="E13" s="162" t="n">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="161" t="inlineStr">
-        <is>
-          <t>감자</t>
-        </is>
-      </c>
-      <c r="B14" s="161" t="inlineStr">
-        <is>
-          <t>1kg</t>
-        </is>
-      </c>
-      <c r="C14" s="161" t="inlineStr">
-        <is>
-          <t>수 감자채볶음 + 금 매쉬포테이토</t>
-        </is>
-      </c>
-      <c r="D14" s="161" t="inlineStr">
-        <is>
-          <t>9/28 밤 주문</t>
-        </is>
-      </c>
-      <c r="E14" s="162" t="n">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="161" t="inlineStr">
-        <is>
-          <t>당근</t>
-        </is>
-      </c>
-      <c r="B15" s="161" t="inlineStr">
-        <is>
-          <t>1개</t>
-        </is>
-      </c>
-      <c r="C15" s="161" t="inlineStr">
-        <is>
-          <t>수 새우전</t>
-        </is>
-      </c>
-      <c r="D15" s="161" t="inlineStr">
-        <is>
-          <t>9/28 밤 주문</t>
-        </is>
-      </c>
-      <c r="E15" s="162" t="n">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="161" t="inlineStr">
-        <is>
-          <t>아욱</t>
-        </is>
-      </c>
-      <c r="B16" s="161" t="inlineStr">
-        <is>
-          <t>1단</t>
-        </is>
-      </c>
-      <c r="C16" s="161" t="inlineStr">
-        <is>
-          <t>수 아욱 된장국</t>
-        </is>
-      </c>
-      <c r="D16" s="161" t="inlineStr">
-        <is>
-          <t>9/29 구매</t>
-        </is>
-      </c>
-      <c r="E16" s="162" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="161" t="inlineStr">
-        <is>
-          <t>대파</t>
-        </is>
-      </c>
-      <c r="B17" s="161" t="inlineStr">
-        <is>
-          <t>2대</t>
-        </is>
-      </c>
-      <c r="C17" s="161" t="inlineStr">
-        <is>
-          <t>전반</t>
-        </is>
-      </c>
-      <c r="D17" s="161" t="inlineStr">
-        <is>
-          <t>9/28 밤 주문</t>
-        </is>
-      </c>
-      <c r="E17" s="162" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="161" t="inlineStr">
-        <is>
-          <t>파프리카</t>
-        </is>
-      </c>
-      <c r="B18" s="161" t="inlineStr">
-        <is>
-          <t>1개</t>
-        </is>
-      </c>
-      <c r="C18" s="161" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="174" t="inlineStr">
+        <is>
+          <t>양송이버섯</t>
+        </is>
+      </c>
+      <c r="B19" s="174" t="inlineStr">
+        <is>
+          <t>1팩</t>
+        </is>
+      </c>
+      <c r="C19" s="174" t="inlineStr">
         <is>
           <t>금 찹스테이크</t>
         </is>
       </c>
-      <c r="D18" s="161" t="inlineStr">
-        <is>
-          <t>9/30 구매</t>
-        </is>
-      </c>
-      <c r="E18" s="162" t="n">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="161" t="inlineStr">
-        <is>
-          <t>양송이버섯</t>
-        </is>
-      </c>
-      <c r="B19" s="161" t="inlineStr">
-        <is>
-          <t>1팩</t>
-        </is>
-      </c>
-      <c r="C19" s="161" t="inlineStr">
-        <is>
-          <t>금 찹스테이크</t>
-        </is>
-      </c>
-      <c r="D19" s="161" t="inlineStr">
-        <is>
-          <t>9/30 구매</t>
-        </is>
-      </c>
-      <c r="E19" s="162" t="n">
+      <c r="D19" s="174" t="inlineStr">
+        <is>
+          <t>🔔 10/1(목) 주문 예정</t>
+        </is>
+      </c>
+      <c r="E19" s="175" t="n">
         <v>3500</v>
       </c>
     </row>
@@ -6134,327 +6162,327 @@
       <c r="E20" s="168" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="161" t="inlineStr">
+      <c r="A21" s="172" t="inlineStr">
         <is>
           <t>모짜렐라치즈</t>
         </is>
       </c>
-      <c r="B21" s="161" t="inlineStr">
+      <c r="B21" s="172" t="inlineStr">
         <is>
           <t>1봉</t>
         </is>
       </c>
-      <c r="C21" s="161" t="inlineStr">
+      <c r="C21" s="172" t="inlineStr">
         <is>
           <t>화 치즈 닭갈비(칼슘)</t>
         </is>
       </c>
-      <c r="D21" s="161" t="inlineStr">
-        <is>
-          <t>9/28 밤 주문</t>
-        </is>
-      </c>
-      <c r="E21" s="162" t="n">
-        <v>9000</v>
+      <c r="D21" s="172" t="inlineStr">
+        <is>
+          <t>✅ 주문완료(9/28밤)</t>
+        </is>
+      </c>
+      <c r="E21" s="173" t="n">
+        <v>9980</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="161" t="inlineStr">
+      <c r="A22" s="172" t="inlineStr">
         <is>
           <t>떡볶이떡</t>
         </is>
       </c>
-      <c r="B22" s="161" t="inlineStr">
+      <c r="B22" s="172" t="inlineStr">
         <is>
           <t>1줌(선택)</t>
         </is>
       </c>
-      <c r="C22" s="161" t="inlineStr">
+      <c r="C22" s="172" t="inlineStr">
         <is>
           <t>화 닭갈비</t>
         </is>
       </c>
-      <c r="D22" s="161" t="inlineStr">
-        <is>
-          <t>9/28 밤 주문</t>
-        </is>
-      </c>
-      <c r="E22" s="162" t="n">
+      <c r="D22" s="172" t="inlineStr">
+        <is>
+          <t>✅ 주문완료(9/28밤)</t>
+        </is>
+      </c>
+      <c r="E22" s="173" t="n">
+        <v>2480</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="172" t="inlineStr">
+        <is>
+          <t>달걀</t>
+        </is>
+      </c>
+      <c r="B23" s="172" t="inlineStr">
+        <is>
+          <t>10~15개입</t>
+        </is>
+      </c>
+      <c r="C23" s="172" t="inlineStr">
+        <is>
+          <t>수 새우전 옷</t>
+        </is>
+      </c>
+      <c r="D23" s="172" t="inlineStr">
+        <is>
+          <t>✅ 주문완료(9/28밤)</t>
+        </is>
+      </c>
+      <c r="E23" s="173" t="n">
+        <v>8690</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="172" t="inlineStr">
+        <is>
+          <t>포도</t>
+        </is>
+      </c>
+      <c r="B24" s="172" t="inlineStr">
+        <is>
+          <t>1송이</t>
+        </is>
+      </c>
+      <c r="C24" s="172" t="inlineStr">
+        <is>
+          <t>화 간식</t>
+        </is>
+      </c>
+      <c r="D24" s="172" t="inlineStr">
+        <is>
+          <t>✅ 주문완료(9/28밤)</t>
+        </is>
+      </c>
+      <c r="E24" s="173" t="n">
+        <v>9990</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="176" t="inlineStr">
+        <is>
+          <t>단감</t>
+        </is>
+      </c>
+      <c r="B25" s="176" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C25" s="176" t="inlineStr">
+        <is>
+          <t>수 간식 → 제철 전이라 미확보(집에 있는 과일로 대체)</t>
+        </is>
+      </c>
+      <c r="D25" s="176" t="inlineStr">
+        <is>
+          <t>❌ 스킵</t>
+        </is>
+      </c>
+      <c r="E25" s="177" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="176" t="inlineStr">
+        <is>
+          <t>부침가루</t>
+        </is>
+      </c>
+      <c r="B26" s="176" t="inlineStr">
+        <is>
+          <t>상비 확인</t>
+        </is>
+      </c>
+      <c r="C26" s="176" t="inlineStr">
+        <is>
+          <t>수 새우전</t>
+        </is>
+      </c>
+      <c r="D26" s="176" t="inlineStr">
+        <is>
+          <t>상비</t>
+        </is>
+      </c>
+      <c r="E26" s="177" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="176" t="inlineStr">
+        <is>
+          <t>굴소스·간장·미림</t>
+        </is>
+      </c>
+      <c r="B27" s="176" t="inlineStr">
+        <is>
+          <t>상비 확인</t>
+        </is>
+      </c>
+      <c r="C27" s="176" t="inlineStr">
+        <is>
+          <t>화 닭갈비 양념</t>
+        </is>
+      </c>
+      <c r="D27" s="176" t="inlineStr">
+        <is>
+          <t>상비</t>
+        </is>
+      </c>
+      <c r="E27" s="177" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="176" t="inlineStr">
+        <is>
+          <t>된장</t>
+        </is>
+      </c>
+      <c r="B28" s="176" t="inlineStr">
+        <is>
+          <t>상비 확인</t>
+        </is>
+      </c>
+      <c r="C28" s="176" t="inlineStr">
+        <is>
+          <t>수 아욱 된장국</t>
+        </is>
+      </c>
+      <c r="D28" s="176" t="inlineStr">
+        <is>
+          <t>상비</t>
+        </is>
+      </c>
+      <c r="E28" s="177" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="176" t="inlineStr">
+        <is>
+          <t>어린이김치</t>
+        </is>
+      </c>
+      <c r="B29" s="176" t="inlineStr">
+        <is>
+          <t>보유분 확인</t>
+        </is>
+      </c>
+      <c r="C29" s="176" t="inlineStr">
+        <is>
+          <t>상시 반찬</t>
+        </is>
+      </c>
+      <c r="D29" s="176" t="inlineStr">
+        <is>
+          <t>보유</t>
+        </is>
+      </c>
+      <c r="E29" s="177" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="176" t="inlineStr">
+        <is>
+          <t>국물멸치·다시마·건새우</t>
+        </is>
+      </c>
+      <c r="B30" s="176" t="inlineStr">
+        <is>
+          <t>보유분 확인</t>
+        </is>
+      </c>
+      <c r="C30" s="176" t="inlineStr">
+        <is>
+          <t>만능육수</t>
+        </is>
+      </c>
+      <c r="D30" s="176" t="inlineStr">
+        <is>
+          <t>보유</t>
+        </is>
+      </c>
+      <c r="E30" s="177" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="174" t="inlineStr">
+        <is>
+          <t>유부</t>
+        </is>
+      </c>
+      <c r="B31" s="174" t="inlineStr">
+        <is>
+          <t>1봉</t>
+        </is>
+      </c>
+      <c r="C31" s="174" t="inlineStr">
+        <is>
+          <t>금 유부 맑은장국</t>
+        </is>
+      </c>
+      <c r="D31" s="174" t="inlineStr">
+        <is>
+          <t>🔔 10/1(목) 주문 예정</t>
+        </is>
+      </c>
+      <c r="E31" s="175" t="n">
         <v>3000</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="161" t="inlineStr">
-        <is>
-          <t>달걀</t>
-        </is>
-      </c>
-      <c r="B23" s="161" t="inlineStr">
-        <is>
-          <t>10~15개입</t>
-        </is>
-      </c>
-      <c r="C23" s="161" t="inlineStr">
-        <is>
-          <t>수 새우전 옷</t>
-        </is>
-      </c>
-      <c r="D23" s="161" t="inlineStr">
-        <is>
-          <t>9/28 밤 주문</t>
-        </is>
-      </c>
-      <c r="E23" s="162" t="n">
-        <v>6000</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="161" t="inlineStr">
-        <is>
-          <t>포도</t>
-        </is>
-      </c>
-      <c r="B24" s="161" t="inlineStr">
-        <is>
-          <t>1송이</t>
-        </is>
-      </c>
-      <c r="C24" s="161" t="inlineStr">
-        <is>
-          <t>화 간식</t>
-        </is>
-      </c>
-      <c r="D24" s="161" t="inlineStr">
-        <is>
-          <t>9/28 밤 주문</t>
-        </is>
-      </c>
-      <c r="E24" s="162" t="n">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="161" t="inlineStr">
-        <is>
-          <t>단감</t>
-        </is>
-      </c>
-      <c r="B25" s="161" t="inlineStr">
-        <is>
-          <t>4~5개</t>
-        </is>
-      </c>
-      <c r="C25" s="161" t="inlineStr">
-        <is>
-          <t>수 간식</t>
-        </is>
-      </c>
-      <c r="D25" s="161" t="inlineStr">
-        <is>
-          <t>9/28 밤 주문</t>
-        </is>
-      </c>
-      <c r="E25" s="162" t="n">
-        <v>9000</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="161" t="inlineStr">
-        <is>
-          <t>부침가루</t>
-        </is>
-      </c>
-      <c r="B26" s="161" t="inlineStr">
-        <is>
-          <t>상비 확인</t>
-        </is>
-      </c>
-      <c r="C26" s="161" t="inlineStr">
-        <is>
-          <t>수 새우전</t>
-        </is>
-      </c>
-      <c r="D26" s="161" t="inlineStr">
-        <is>
-          <t>상비</t>
-        </is>
-      </c>
-      <c r="E26" s="162" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="161" t="inlineStr">
-        <is>
-          <t>굴소스·간장·미림</t>
-        </is>
-      </c>
-      <c r="B27" s="161" t="inlineStr">
-        <is>
-          <t>상비 확인</t>
-        </is>
-      </c>
-      <c r="C27" s="161" t="inlineStr">
-        <is>
-          <t>화 닭갈비 양념</t>
-        </is>
-      </c>
-      <c r="D27" s="161" t="inlineStr">
-        <is>
-          <t>상비</t>
-        </is>
-      </c>
-      <c r="E27" s="162" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="161" t="inlineStr">
-        <is>
-          <t>된장</t>
-        </is>
-      </c>
-      <c r="B28" s="161" t="inlineStr">
-        <is>
-          <t>상비 확인</t>
-        </is>
-      </c>
-      <c r="C28" s="161" t="inlineStr">
-        <is>
-          <t>수 아욱 된장국</t>
-        </is>
-      </c>
-      <c r="D28" s="161" t="inlineStr">
-        <is>
-          <t>상비</t>
-        </is>
-      </c>
-      <c r="E28" s="162" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="161" t="inlineStr">
-        <is>
-          <t>어린이김치</t>
-        </is>
-      </c>
-      <c r="B29" s="161" t="inlineStr">
-        <is>
-          <t>보유분 확인</t>
-        </is>
-      </c>
-      <c r="C29" s="161" t="inlineStr">
-        <is>
-          <t>상시 반찬</t>
-        </is>
-      </c>
-      <c r="D29" s="161" t="inlineStr">
-        <is>
-          <t>보유</t>
-        </is>
-      </c>
-      <c r="E29" s="162" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="161" t="inlineStr">
-        <is>
-          <t>국물멸치·다시마·건새우</t>
-        </is>
-      </c>
-      <c r="B30" s="161" t="inlineStr">
-        <is>
-          <t>보유분 확인</t>
-        </is>
-      </c>
-      <c r="C30" s="161" t="inlineStr">
-        <is>
-          <t>만능육수</t>
-        </is>
-      </c>
-      <c r="D30" s="161" t="inlineStr">
-        <is>
-          <t>보유</t>
-        </is>
-      </c>
-      <c r="E30" s="162" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="161" t="inlineStr">
-        <is>
-          <t>유부</t>
-        </is>
-      </c>
-      <c r="B31" s="161" t="inlineStr">
-        <is>
-          <t>1봉</t>
-        </is>
-      </c>
-      <c r="C31" s="161" t="inlineStr">
-        <is>
-          <t>금 유부 맑은장국</t>
-        </is>
-      </c>
-      <c r="D31" s="161" t="inlineStr">
-        <is>
-          <t>9/30 구매</t>
-        </is>
-      </c>
-      <c r="E31" s="162" t="n">
-        <v>3000</v>
-      </c>
-    </row>
     <row r="32">
-      <c r="A32" s="161" t="inlineStr">
+      <c r="A32" s="174" t="inlineStr">
         <is>
           <t>우유</t>
         </is>
       </c>
-      <c r="B32" s="161" t="inlineStr">
+      <c r="B32" s="174" t="inlineStr">
         <is>
           <t>1L</t>
         </is>
       </c>
-      <c r="C32" s="161" t="inlineStr">
+      <c r="C32" s="174" t="inlineStr">
         <is>
           <t>금 매쉬포테이토(칼슘)</t>
         </is>
       </c>
-      <c r="D32" s="161" t="inlineStr">
-        <is>
-          <t>9/30 구매</t>
-        </is>
-      </c>
-      <c r="E32" s="162" t="n">
+      <c r="D32" s="174" t="inlineStr">
+        <is>
+          <t>🔔 10/1(목) 주문 예정</t>
+        </is>
+      </c>
+      <c r="E32" s="175" t="n">
         <v>3500</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="161" t="inlineStr">
+      <c r="A33" s="174" t="inlineStr">
         <is>
           <t>배</t>
         </is>
       </c>
-      <c r="B33" s="161" t="inlineStr">
+      <c r="B33" s="174" t="inlineStr">
         <is>
           <t>2~3개</t>
         </is>
       </c>
-      <c r="C33" s="161" t="inlineStr">
+      <c r="C33" s="174" t="inlineStr">
         <is>
           <t>금 간식</t>
         </is>
       </c>
-      <c r="D33" s="161" t="inlineStr">
-        <is>
-          <t>9/30 구매</t>
-        </is>
-      </c>
-      <c r="E33" s="162" t="n">
+      <c r="D33" s="174" t="inlineStr">
+        <is>
+          <t>🔔 10/1(목) 주문 예정</t>
+        </is>
+      </c>
+      <c r="E33" s="175" t="n">
         <v>9000</v>
       </c>
     </row>
@@ -6465,14 +6493,18 @@
         </is>
       </c>
       <c r="B34" s="169" t="n"/>
-      <c r="C34" s="169" t="n"/>
+      <c r="C34" s="169" t="inlineStr">
+        <is>
+          <t>✅ 주문완료 97,440원</t>
+        </is>
+      </c>
       <c r="D34" s="170" t="inlineStr">
         <is>
-          <t>구매분(추정)</t>
+          <t>🔔 목요일 예정</t>
         </is>
       </c>
       <c r="E34" s="171" t="n">
-        <v>116500</v>
+        <v>40500</v>
       </c>
     </row>
   </sheetData>

--- a/26년도_2주간_식단.xlsx
+++ b/26년도_2주간_식단.xlsx
@@ -1562,7 +1562,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="471" customHeight="1" s="110">
+    <row r="3" ht="771" customHeight="1" s="110">
       <c r="A3" s="156" t="inlineStr">
         <is>
           <t>수 (10/14)</t>
@@ -1571,7 +1571,7 @@
       <c r="B3" s="157" t="inlineStr">
         <is>
           <t>대구살 두부전 (다져서 뭉친 전)
-+ 배추 된장국
++ 배추 된장국 🧊냉동OK
 + 애호박볶음
 + 키즈김치
 + 단감 (간식)
@@ -1608,13 +1608,31 @@
       <c r="D3" s="157" t="inlineStr">
         <is>
           <t>★ 식사 40분 전 시작
-[배추 된장국 — 먼저]
+[배추 된장국 — 먼저] ★맛 보강판 (Fable 점검: 된장 농도 2배·배추 된장에 무쳐 넣기)
+   🧊냉동OK — 2배로 끓여 절반 냉동하면 아침 예비팩
 1. 만능육수 1.2L 만들기 (찬물부터, 다시마 먼저 건지고
-   중불 10~12분 → 거르기)
-2. 된장 2T 체에 풀고 배추 넣어 중불 8~10분
-   (배추가 투명하고 달아질 때까지)
-3. 간: 국간장 1t + 다진마늘 1t + 액젓 1t
-   → 대파 마무리 ※ 싱거우면 된장 1/2T 더
+   중불 10~12분 → 거르기) ※ 가능하면 물 대신 쌀뜨물로
+2. 알배추 400g 한입 크기 → 볼에 배추 + 된장 2T
+   + 다진마늘 1T 넣고 손으로 무쳐 5분 두기
+   (배추가 된장을 머금어야 국이 밍밍하지 않음)
+3. 끓는 육수에 무 100g(얇게 나박) + 양파 1/2개(채)
+   먼저 넣고 중불 5분 (단맛·구수함)
+4. 된장 1T 체에 걸러 풀고 → 무친 배추 넣기
+5. 중불 7~8분 — 배추 숨 죽고 투명해지면 끝
+   ※ 10분 넘기면 된장이 텁텁해짐
+6. 국간장 1T → 맛보기 → 멸치액젓 1T → 대파
+   → 불 끄고 들기름 몇 방울(선택)
+★ 맛보기: 구수함 부족=된장 1/2T / 깊이 부족=액젓 1/2t
+  / 간만 부족=소금 (국간장 더 넣으면 색 탁해짐)
+  뜨거울 때 "살짝 싱겁다" 정도가 적정 (식으면 간 배임)
+※ 아이 그릇은 국물 반·건더기 위주 / 어른만 고춧가루
+[🧊 2배로 끓여 냉동할 때]
+- 육수 2.4L · 배추 800g(부족하면 무 늘리기) · 무·양파 2배
+  · 된장 5.5T · 국간장 2T · 액젓 2T · 마늘 2T
+  · 시간은 ③ 7분 · ⑤ 10분
+- 냉동분은 ⑤까지만 덜기 — 대파·들기름 넣기 전, 간은 80%
+- 식혀서 냉동 지퍼백에 80%만 채워 납작하게, 날짜·국이름 적기
+- 데울 때: 끓으면 된장 1/2t + 액젓 1/2t 다시 풀고 대파·달걀
 [애호박볶음 — 국 끓는 동안]
 4. 애호박에 새우젓 1/2T 버무려 10분
 5. 기름 + 다진마늘 1t 약불 → 애호박 중불 3분

--- a/26년도_2주간_식단.xlsx
+++ b/26년도_2주간_식단.xlsx
@@ -5977,7 +5977,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" style="110" min="1" max="1"/>
@@ -5990,7 +5990,7 @@
     <row r="1" ht="24" customHeight="1" s="110">
       <c r="A1" s="158" t="inlineStr">
         <is>
-          <t>10월 4주차 장보기 (10/20~10/23) — 화·수분 10/19(월) 밤 / 금·아침분 10/22(목) 밤</t>
+          <t>10월 4주차 장보기 (10/20~10/23) — 화·수분 10/19 컬리 담음(결제예정 110,960원) / 금·아침분 10/22(목) 밤</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="B4" s="161" t="inlineStr">
         <is>
-          <t>500g</t>
+          <t>600g (한돈 다짐육)</t>
         </is>
       </c>
       <c r="C4" s="161" t="inlineStr">
@@ -6050,11 +6050,11 @@
       </c>
       <c r="D4" s="161" t="inlineStr">
         <is>
-          <t>10/19(월) 밤 주문</t>
+          <t>10/19 컬리 담음</t>
         </is>
       </c>
       <c r="E4" s="162" t="n">
-        <v>8000</v>
+        <v>7790</v>
       </c>
     </row>
     <row r="5">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="B5" s="161" t="inlineStr">
         <is>
-          <t>300g</t>
+          <t>400g (육우 200g×2) — 무국에 전부 사용</t>
         </is>
       </c>
       <c r="C5" s="161" t="inlineStr">
@@ -6075,11 +6075,11 @@
       </c>
       <c r="D5" s="161" t="inlineStr">
         <is>
-          <t>10/19(월) 밤 주문</t>
+          <t>10/19 컬리 담음</t>
         </is>
       </c>
       <c r="E5" s="162" t="n">
-        <v>13000</v>
+        <v>20560</v>
       </c>
     </row>
     <row r="6">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="B8" s="161" t="inlineStr">
         <is>
-          <t>400g</t>
+          <t>360g (냉장 생새우살 180g×2)</t>
         </is>
       </c>
       <c r="C8" s="161" t="inlineStr">
@@ -6136,11 +6136,11 @@
       </c>
       <c r="D8" s="161" t="inlineStr">
         <is>
-          <t>10/19(월) 밤 주문</t>
+          <t>10/19 컬리 담음</t>
         </is>
       </c>
       <c r="E8" s="162" t="n">
-        <v>13000</v>
+        <v>16580</v>
       </c>
     </row>
     <row r="9">
@@ -6187,7 +6187,7 @@
       </c>
       <c r="B11" s="161" t="inlineStr">
         <is>
-          <t>1개 (화 450g·수 100g·금 300g)</t>
+          <t>작은 무 400g (화 무국 전부 / 수 장국 무는 생략 가능)</t>
         </is>
       </c>
       <c r="C11" s="161" t="inlineStr">
@@ -6197,11 +6197,11 @@
       </c>
       <c r="D11" s="161" t="inlineStr">
         <is>
-          <t>10/19(월) 밤 주문</t>
+          <t>10/19 컬리 담음</t>
         </is>
       </c>
       <c r="E11" s="162" t="n">
-        <v>2500</v>
+        <v>2490</v>
       </c>
     </row>
     <row r="12">
@@ -6212,7 +6212,7 @@
       </c>
       <c r="B12" s="161" t="inlineStr">
         <is>
-          <t>1kg (화 1/2·금 2.5개)</t>
+          <t>900g</t>
         </is>
       </c>
       <c r="C12" s="161" t="inlineStr">
@@ -6222,11 +6222,11 @@
       </c>
       <c r="D12" s="161" t="inlineStr">
         <is>
-          <t>10/19(월) 밤 주문</t>
+          <t>10/19 컬리 담음</t>
         </is>
       </c>
       <c r="E12" s="162" t="n">
-        <v>3000</v>
+        <v>3990</v>
       </c>
     </row>
     <row r="13">
@@ -6237,7 +6237,7 @@
       </c>
       <c r="B13" s="161" t="inlineStr">
         <is>
-          <t>2개</t>
+          <t>1개 (화요일분)</t>
         </is>
       </c>
       <c r="C13" s="161" t="inlineStr">
@@ -6247,11 +6247,11 @@
       </c>
       <c r="D13" s="161" t="inlineStr">
         <is>
-          <t>10/19(월) 밤 주문</t>
+          <t>10/19 컬리 담음</t>
         </is>
       </c>
       <c r="E13" s="162" t="n">
-        <v>1500</v>
+        <v>1990</v>
       </c>
     </row>
     <row r="14">
@@ -6262,7 +6262,7 @@
       </c>
       <c r="B14" s="161" t="inlineStr">
         <is>
-          <t>1단</t>
+          <t>1단 850g</t>
         </is>
       </c>
       <c r="C14" s="161" t="inlineStr">
@@ -6272,27 +6272,27 @@
       </c>
       <c r="D14" s="161" t="inlineStr">
         <is>
-          <t>10/19(월) 밤 주문</t>
+          <t>10/19 컬리 담음</t>
         </is>
       </c>
       <c r="E14" s="162" t="n">
-        <v>2500</v>
+        <v>3290</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="161" t="inlineStr">
         <is>
-          <t>양송이버섯</t>
+          <t>무</t>
         </is>
       </c>
       <c r="B15" s="161" t="inlineStr">
         <is>
-          <t>150g</t>
+          <t>1/2개 (300g)</t>
         </is>
       </c>
       <c r="C15" s="161" t="inlineStr">
         <is>
-          <t>금 키마카레</t>
+          <t>금 북엇국</t>
         </is>
       </c>
       <c r="D15" s="161" t="inlineStr">
@@ -6301,23 +6301,23 @@
         </is>
       </c>
       <c r="E15" s="162" t="n">
-        <v>3500</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="161" t="inlineStr">
         <is>
-          <t>오이</t>
+          <t>당근</t>
         </is>
       </c>
       <c r="B16" s="161" t="inlineStr">
         <is>
-          <t>3개</t>
+          <t>1개</t>
         </is>
       </c>
       <c r="C16" s="161" t="inlineStr">
         <is>
-          <t>금 오이 피클 (목 밤 담그기)</t>
+          <t>금 키마카레</t>
         </is>
       </c>
       <c r="D16" s="161" t="inlineStr">
@@ -6326,23 +6326,23 @@
         </is>
       </c>
       <c r="E16" s="162" t="n">
-        <v>3000</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="161" t="inlineStr">
         <is>
-          <t>고구마</t>
+          <t>양송이버섯</t>
         </is>
       </c>
       <c r="B17" s="161" t="inlineStr">
         <is>
-          <t>2~3개</t>
+          <t>150g</t>
         </is>
       </c>
       <c r="C17" s="161" t="inlineStr">
         <is>
-          <t>일 아침 고구마밥</t>
+          <t>금 키마카레</t>
         </is>
       </c>
       <c r="D17" s="161" t="inlineStr">
@@ -6351,95 +6351,109 @@
         </is>
       </c>
       <c r="E17" s="162" t="n">
-        <v>4000</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="178" t="inlineStr">
-        <is>
-          <t>두부류</t>
-        </is>
-      </c>
-      <c r="B18" s="179" t="n"/>
-      <c r="C18" s="179" t="n"/>
-      <c r="D18" s="179" t="n"/>
-      <c r="E18" s="179" t="n"/>
+      <c r="A18" s="161" t="inlineStr">
+        <is>
+          <t>오이</t>
+        </is>
+      </c>
+      <c r="B18" s="161" t="inlineStr">
+        <is>
+          <t>3개</t>
+        </is>
+      </c>
+      <c r="C18" s="161" t="inlineStr">
+        <is>
+          <t>금 오이 피클 (목 밤 담그기)</t>
+        </is>
+      </c>
+      <c r="D18" s="161" t="inlineStr">
+        <is>
+          <t>10/22(목) 밤 주문</t>
+        </is>
+      </c>
+      <c r="E18" s="162" t="n">
+        <v>3000</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="161" t="inlineStr">
         <is>
+          <t>고구마</t>
+        </is>
+      </c>
+      <c r="B19" s="161" t="inlineStr">
+        <is>
+          <t>2~3개</t>
+        </is>
+      </c>
+      <c r="C19" s="161" t="inlineStr">
+        <is>
+          <t>일 아침 고구마밥</t>
+        </is>
+      </c>
+      <c r="D19" s="161" t="inlineStr">
+        <is>
+          <t>10/22(목) 밤 주문</t>
+        </is>
+      </c>
+      <c r="E19" s="162" t="n">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="178" t="inlineStr">
+        <is>
+          <t>두부류</t>
+        </is>
+      </c>
+      <c r="B20" s="179" t="n"/>
+      <c r="C20" s="179" t="n"/>
+      <c r="D20" s="179" t="n"/>
+      <c r="E20" s="179" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="161" t="inlineStr">
+        <is>
           <t>두부</t>
         </is>
       </c>
-      <c r="B19" s="161" t="inlineStr">
+      <c r="B21" s="161" t="inlineStr">
         <is>
           <t>1모</t>
         </is>
       </c>
-      <c r="C19" s="161" t="inlineStr">
+      <c r="C21" s="161" t="inlineStr">
         <is>
           <t>화 동그랑땡</t>
         </is>
       </c>
-      <c r="D19" s="161" t="inlineStr">
+      <c r="D21" s="161" t="inlineStr">
         <is>
           <t>10/19(월) 밤 주문</t>
         </is>
       </c>
-      <c r="E19" s="162" t="n">
+      <c r="E21" s="162" t="n">
         <v>2200</v>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="161" t="inlineStr">
-        <is>
-          <t>유부</t>
-        </is>
-      </c>
-      <c r="B20" s="161" t="inlineStr">
-        <is>
-          <t>1봉</t>
-        </is>
-      </c>
-      <c r="C20" s="161" t="inlineStr">
-        <is>
-          <t>수 유부 맑은장국</t>
-        </is>
-      </c>
-      <c r="D20" s="161" t="inlineStr">
-        <is>
-          <t>10/19(월) 밤 주문</t>
-        </is>
-      </c>
-      <c r="E20" s="162" t="n">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="167" t="inlineStr">
-        <is>
-          <t>기타</t>
-        </is>
-      </c>
-      <c r="B21" s="168" t="n"/>
-      <c r="C21" s="168" t="n"/>
-      <c r="D21" s="168" t="n"/>
-      <c r="E21" s="168" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="161" t="inlineStr">
         <is>
-          <t>달걀</t>
+          <t>유부</t>
         </is>
       </c>
       <c r="B22" s="161" t="inlineStr">
         <is>
-          <t>20구</t>
+          <t>1봉</t>
         </is>
       </c>
       <c r="C22" s="161" t="inlineStr">
         <is>
-          <t>화 동그랑땡·계란찜 / 수 덮밥 / 아침 국밥</t>
+          <t>수 유부 맑은장국</t>
         </is>
       </c>
       <c r="D22" s="161" t="inlineStr">
@@ -6448,48 +6462,34 @@
         </is>
       </c>
       <c r="E22" s="162" t="n">
-        <v>9000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="161" t="inlineStr">
-        <is>
-          <t>옥수수콘 통조림</t>
-        </is>
-      </c>
-      <c r="B23" s="161" t="inlineStr">
-        <is>
-          <t>1캔</t>
-        </is>
-      </c>
-      <c r="C23" s="161" t="inlineStr">
-        <is>
-          <t>수 콘치즈</t>
-        </is>
-      </c>
-      <c r="D23" s="161" t="inlineStr">
-        <is>
-          <t>10/19(월) 밤 주문</t>
-        </is>
-      </c>
-      <c r="E23" s="162" t="n">
-        <v>2500</v>
-      </c>
+      <c r="A23" s="167" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="B23" s="168" t="n"/>
+      <c r="C23" s="168" t="n"/>
+      <c r="D23" s="168" t="n"/>
+      <c r="E23" s="168" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="161" t="inlineStr">
         <is>
-          <t>모짜렐라 치즈</t>
+          <t>달걀</t>
         </is>
       </c>
       <c r="B24" s="161" t="inlineStr">
         <is>
-          <t>1봉 (200g)</t>
+          <t>20구</t>
         </is>
       </c>
       <c r="C24" s="161" t="inlineStr">
         <is>
-          <t>수 콘치즈</t>
+          <t>화 동그랑땡·계란찜 / 수 덮밥 / 아침 국밥</t>
         </is>
       </c>
       <c r="D24" s="161" t="inlineStr">
@@ -6498,23 +6498,23 @@
         </is>
       </c>
       <c r="E24" s="162" t="n">
-        <v>5000</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="161" t="inlineStr">
         <is>
-          <t>우유</t>
+          <t>옥수수콘 통조림</t>
         </is>
       </c>
       <c r="B25" s="161" t="inlineStr">
         <is>
-          <t>1L</t>
+          <t>1캔</t>
         </is>
       </c>
       <c r="C25" s="161" t="inlineStr">
         <is>
-          <t>수 덮밥·콘치즈 / 아침</t>
+          <t>수 콘치즈</t>
         </is>
       </c>
       <c r="D25" s="161" t="inlineStr">
@@ -6523,198 +6523,198 @@
         </is>
       </c>
       <c r="E25" s="162" t="n">
-        <v>3000</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="161" t="inlineStr">
         <is>
-          <t>우유</t>
+          <t>모짜렐라 치즈</t>
         </is>
       </c>
       <c r="B26" s="161" t="inlineStr">
         <is>
-          <t>1L</t>
+          <t>1봉 (200g)</t>
         </is>
       </c>
       <c r="C26" s="161" t="inlineStr">
         <is>
-          <t>금 키마카레 / 아침</t>
+          <t>수 콘치즈</t>
         </is>
       </c>
       <c r="D26" s="161" t="inlineStr">
         <is>
-          <t>10/22(목) 밤 주문</t>
+          <t>10/19(월) 밤 주문</t>
         </is>
       </c>
       <c r="E26" s="162" t="n">
-        <v>3000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="161" t="inlineStr">
         <is>
-          <t>순한맛 카레 (고형 루)</t>
+          <t>우유</t>
         </is>
       </c>
       <c r="B27" s="161" t="inlineStr">
         <is>
-          <t>1개</t>
+          <t>1L</t>
         </is>
       </c>
       <c r="C27" s="161" t="inlineStr">
         <is>
-          <t>금 키마카레</t>
+          <t>수 덮밥·콘치즈 / 아침</t>
         </is>
       </c>
       <c r="D27" s="161" t="inlineStr">
         <is>
-          <t>10/22(목) 밤 주문</t>
+          <t>10/19(월) 밤 주문</t>
         </is>
       </c>
       <c r="E27" s="162" t="n">
-        <v>4000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="161" t="inlineStr">
         <is>
-          <t>귤</t>
+          <t>우유</t>
         </is>
       </c>
       <c r="B28" s="161" t="inlineStr">
         <is>
-          <t>1봉</t>
+          <t>1L</t>
         </is>
       </c>
       <c r="C28" s="161" t="inlineStr">
         <is>
-          <t>화 간식</t>
+          <t>금 키마카레 / 아침</t>
         </is>
       </c>
       <c r="D28" s="161" t="inlineStr">
         <is>
-          <t>10/19(월) 밤 주문</t>
+          <t>10/22(목) 밤 주문</t>
         </is>
       </c>
       <c r="E28" s="162" t="n">
-        <v>6000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="161" t="inlineStr">
         <is>
-          <t>사과</t>
+          <t>순한맛 카레 (고형 루)</t>
         </is>
       </c>
       <c r="B29" s="161" t="inlineStr">
         <is>
-          <t>4~5개</t>
+          <t>1개</t>
         </is>
       </c>
       <c r="C29" s="161" t="inlineStr">
         <is>
-          <t>수 간식</t>
+          <t>금 키마카레</t>
         </is>
       </c>
       <c r="D29" s="161" t="inlineStr">
         <is>
-          <t>10/19(월) 밤 주문</t>
+          <t>10/22(목) 밤 주문</t>
         </is>
       </c>
       <c r="E29" s="162" t="n">
-        <v>10000</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="161" t="inlineStr">
         <is>
-          <t>단감</t>
+          <t>귤</t>
         </is>
       </c>
       <c r="B30" s="161" t="inlineStr">
         <is>
-          <t>4~5개</t>
+          <t>1봉</t>
         </is>
       </c>
       <c r="C30" s="161" t="inlineStr">
         <is>
-          <t>금 간식</t>
+          <t>화 간식</t>
         </is>
       </c>
       <c r="D30" s="161" t="inlineStr">
         <is>
-          <t>10/22(목) 밤 주문</t>
+          <t>10/19(월) 밤 주문</t>
         </is>
       </c>
       <c r="E30" s="162" t="n">
-        <v>8000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="161" t="inlineStr">
         <is>
-          <t>슬라이스치즈</t>
+          <t>사과</t>
         </is>
       </c>
       <c r="B31" s="161" t="inlineStr">
         <is>
-          <t>보유분 확인 (3장 필요)</t>
+          <t>4~5개</t>
         </is>
       </c>
       <c r="C31" s="161" t="inlineStr">
         <is>
-          <t>금 키마카레</t>
+          <t>수 간식</t>
         </is>
       </c>
       <c r="D31" s="161" t="inlineStr">
         <is>
-          <t>보유 확인</t>
+          <t>10/19(월) 밤 주문</t>
         </is>
       </c>
       <c r="E31" s="162" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="161" t="inlineStr">
         <is>
-          <t>케첩·우스터소스</t>
+          <t>단감</t>
         </is>
       </c>
       <c r="B32" s="161" t="inlineStr">
         <is>
-          <t>보유분 확인 (없으면 우스터 생략)</t>
+          <t>4~5개</t>
         </is>
       </c>
       <c r="C32" s="161" t="inlineStr">
         <is>
-          <t>금 키마카레</t>
+          <t>금 간식</t>
         </is>
       </c>
       <c r="D32" s="161" t="inlineStr">
         <is>
-          <t>보유 확인</t>
+          <t>10/22(목) 밤 주문</t>
         </is>
       </c>
       <c r="E32" s="162" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="161" t="inlineStr">
         <is>
-          <t>빵가루·밀가루</t>
+          <t>슬라이스치즈</t>
         </is>
       </c>
       <c r="B33" s="161" t="inlineStr">
         <is>
-          <t>보유분 확인</t>
+          <t>보유분 확인 (3장 필요)</t>
         </is>
       </c>
       <c r="C33" s="161" t="inlineStr">
         <is>
-          <t>화 동그랑땡</t>
+          <t>금 키마카레</t>
         </is>
       </c>
       <c r="D33" s="161" t="inlineStr">
@@ -6729,12 +6729,12 @@
     <row r="34">
       <c r="A34" s="161" t="inlineStr">
         <is>
-          <t>생강</t>
+          <t>케첩·우스터소스</t>
         </is>
       </c>
       <c r="B34" s="161" t="inlineStr">
         <is>
-          <t>보유분 확인</t>
+          <t>보유분 확인 (없으면 우스터 생략)</t>
         </is>
       </c>
       <c r="C34" s="161" t="inlineStr">
@@ -6754,22 +6754,22 @@
     <row r="35">
       <c r="A35" s="161" t="inlineStr">
         <is>
-          <t>새우젓·굴소스·국간장·액젓·참기름</t>
+          <t>빵가루·밀가루</t>
         </is>
       </c>
       <c r="B35" s="161" t="inlineStr">
         <is>
-          <t>상비 확인</t>
+          <t>보유분 확인</t>
         </is>
       </c>
       <c r="C35" s="161" t="inlineStr">
         <is>
-          <t>전반</t>
+          <t>화 동그랑땡</t>
         </is>
       </c>
       <c r="D35" s="161" t="inlineStr">
         <is>
-          <t>상비</t>
+          <t>보유 확인</t>
         </is>
       </c>
       <c r="E35" s="162" t="n">
@@ -6779,22 +6779,22 @@
     <row r="36">
       <c r="A36" s="161" t="inlineStr">
         <is>
-          <t>식초·설탕·굵은소금</t>
+          <t>생강</t>
         </is>
       </c>
       <c r="B36" s="161" t="inlineStr">
         <is>
-          <t>상비 확인</t>
+          <t>보유분 확인</t>
         </is>
       </c>
       <c r="C36" s="161" t="inlineStr">
         <is>
-          <t>금 오이 피클</t>
+          <t>금 키마카레</t>
         </is>
       </c>
       <c r="D36" s="161" t="inlineStr">
         <is>
-          <t>상비</t>
+          <t>보유 확인</t>
         </is>
       </c>
       <c r="E36" s="162" t="n">
@@ -6804,22 +6804,22 @@
     <row r="37">
       <c r="A37" s="161" t="inlineStr">
         <is>
-          <t>어린이김치·김</t>
+          <t>새우젓·굴소스·국간장·액젓·참기름</t>
         </is>
       </c>
       <c r="B37" s="161" t="inlineStr">
         <is>
-          <t>보유분 확인</t>
+          <t>상비 확인</t>
         </is>
       </c>
       <c r="C37" s="161" t="inlineStr">
         <is>
-          <t>상시 반찬·아침</t>
+          <t>전반</t>
         </is>
       </c>
       <c r="D37" s="161" t="inlineStr">
         <is>
-          <t>보유</t>
+          <t>상비</t>
         </is>
       </c>
       <c r="E37" s="162" t="n">
@@ -6829,22 +6829,22 @@
     <row r="38">
       <c r="A38" s="161" t="inlineStr">
         <is>
-          <t>국물멸치·다시마·건새우·마른표고</t>
+          <t>식초·설탕·굵은소금</t>
         </is>
       </c>
       <c r="B38" s="161" t="inlineStr">
         <is>
-          <t>보유분 확인</t>
+          <t>상비 확인</t>
         </is>
       </c>
       <c r="C38" s="161" t="inlineStr">
         <is>
-          <t>만능육수</t>
+          <t>금 오이 피클</t>
         </is>
       </c>
       <c r="D38" s="161" t="inlineStr">
         <is>
-          <t>보유</t>
+          <t>상비</t>
         </is>
       </c>
       <c r="E38" s="162" t="n">
@@ -6852,24 +6852,74 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="169" t="inlineStr">
+      <c r="A39" s="161" t="inlineStr">
+        <is>
+          <t>어린이김치·김</t>
+        </is>
+      </c>
+      <c r="B39" s="161" t="inlineStr">
+        <is>
+          <t>보유분 확인</t>
+        </is>
+      </c>
+      <c r="C39" s="161" t="inlineStr">
+        <is>
+          <t>상시 반찬·아침</t>
+        </is>
+      </c>
+      <c r="D39" s="161" t="inlineStr">
+        <is>
+          <t>보유</t>
+        </is>
+      </c>
+      <c r="E39" s="162" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="161" t="inlineStr">
+        <is>
+          <t>국물멸치·다시마·건새우·마른표고</t>
+        </is>
+      </c>
+      <c r="B40" s="161" t="inlineStr">
+        <is>
+          <t>보유분 확인</t>
+        </is>
+      </c>
+      <c r="C40" s="161" t="inlineStr">
+        <is>
+          <t>만능육수</t>
+        </is>
+      </c>
+      <c r="D40" s="161" t="inlineStr">
+        <is>
+          <t>보유</t>
+        </is>
+      </c>
+      <c r="E40" s="162" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="169" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
       </c>
-      <c r="B39" s="169" t="n"/>
-      <c r="C39" s="169" t="inlineStr">
-        <is>
-          <t>월 84,200원 / 목 43,500원</t>
-        </is>
-      </c>
-      <c r="D39" s="170" t="inlineStr">
+      <c r="B41" s="169" t="n"/>
+      <c r="C41" s="169" t="inlineStr">
+        <is>
+          <t>월 97,390원(실제·할인 전) / 목 47,000원(추정)</t>
+        </is>
+      </c>
+      <c r="D41" s="170" t="inlineStr">
         <is>
           <t>전체(추정)</t>
         </is>
       </c>
-      <c r="E39" s="171" t="n">
-        <v>127700</v>
+      <c r="E41" s="171" t="n">
+        <v>144390</v>
       </c>
     </row>
   </sheetData>

--- a/26년도_2주간_식단.xlsx
+++ b/26년도_2주간_식단.xlsx
@@ -1646,7 +1646,8 @@
    → 모두 1cm 이하로 잘게 다지기 (아이 눈에 안 띄게)
    → 밀폐 냉장
 2. 소스 한 통에: 케첩 3T + 우스터소스 2T + 청주 4T
-3. 다진 소고기 500g 냉장 / 다진마늘 1T · 생강 1t
+3. 다진 소고기 600g — ★목요일 밤 냉동실→냉장실로 옮겨 해동
+   (월요일 일괄 주문분이라 받자마자 냉동해 둠) / 다진마늘 1T · 생강 1t
 4. 계량: 순한맛 카레(고형 루) 70g, 물 300ml,
    우유 200ml, 슬라이스치즈 3장
 [맑은 북엇국 — 🧊냉동OK · 토요일 아침 국밥용 포함]
@@ -5990,7 +5991,7 @@
     <row r="1" ht="24" customHeight="1" s="110">
       <c r="A1" s="158" t="inlineStr">
         <is>
-          <t>10월 4주차 장보기 (10/20~10/23) — 화·수분 10/19 컬리 담음(결제예정 110,960원) / 금·아침분 10/22(목) 밤</t>
+          <t>10월 4주차 장보기 (10/20~10/23) — 전체 10/19(월) 컬리 일괄 담음 · 결제예정 170,200원 (할인 후)</t>
         </is>
       </c>
     </row>
@@ -6090,7 +6091,7 @@
       </c>
       <c r="B6" s="161" t="inlineStr">
         <is>
-          <t>500g</t>
+          <t>600g (호주산 앞다리 300g×2) — 받자마자 냉동, 목 밤 냉장 해동</t>
         </is>
       </c>
       <c r="C6" s="161" t="inlineStr">
@@ -6100,11 +6101,11 @@
       </c>
       <c r="D6" s="161" t="inlineStr">
         <is>
-          <t>10/22(목) 밤 주문</t>
+          <t>10/19 컬리 담음</t>
         </is>
       </c>
       <c r="E6" s="162" t="n">
-        <v>12000</v>
+        <v>19980</v>
       </c>
     </row>
     <row r="7">
@@ -6151,7 +6152,7 @@
       </c>
       <c r="B9" s="161" t="inlineStr">
         <is>
-          <t>70g (1봉)</t>
+          <t>100g (손질형)</t>
         </is>
       </c>
       <c r="C9" s="161" t="inlineStr">
@@ -6161,11 +6162,11 @@
       </c>
       <c r="D9" s="161" t="inlineStr">
         <is>
-          <t>10/22(목) 밤 주문</t>
+          <t>10/19 컬리 담음</t>
         </is>
       </c>
       <c r="E9" s="162" t="n">
-        <v>6000</v>
+        <v>8690</v>
       </c>
     </row>
     <row r="10">
@@ -6287,7 +6288,7 @@
       </c>
       <c r="B15" s="161" t="inlineStr">
         <is>
-          <t>1/2개 (300g)</t>
+          <t>작은 무 400g</t>
         </is>
       </c>
       <c r="C15" s="161" t="inlineStr">
@@ -6297,11 +6298,11 @@
       </c>
       <c r="D15" s="161" t="inlineStr">
         <is>
-          <t>10/22(목) 밤 주문</t>
+          <t>10/19 컬리 담음</t>
         </is>
       </c>
       <c r="E15" s="162" t="n">
-        <v>2000</v>
+        <v>2490</v>
       </c>
     </row>
     <row r="16">
@@ -6322,11 +6323,11 @@
       </c>
       <c r="D16" s="161" t="inlineStr">
         <is>
-          <t>10/22(목) 밤 주문</t>
+          <t>10/19 컬리 담음</t>
         </is>
       </c>
       <c r="E16" s="162" t="n">
-        <v>1500</v>
+        <v>1990</v>
       </c>
     </row>
     <row r="17">
@@ -6347,11 +6348,11 @@
       </c>
       <c r="D17" s="161" t="inlineStr">
         <is>
-          <t>10/22(목) 밤 주문</t>
+          <t>10/19 컬리 담음</t>
         </is>
       </c>
       <c r="E17" s="162" t="n">
-        <v>3500</v>
+        <v>3990</v>
       </c>
     </row>
     <row r="18">
@@ -6362,7 +6363,7 @@
       </c>
       <c r="B18" s="161" t="inlineStr">
         <is>
-          <t>3개</t>
+          <t>3입</t>
         </is>
       </c>
       <c r="C18" s="161" t="inlineStr">
@@ -6372,11 +6373,11 @@
       </c>
       <c r="D18" s="161" t="inlineStr">
         <is>
-          <t>10/22(목) 밤 주문</t>
+          <t>10/19 컬리 담음</t>
         </is>
       </c>
       <c r="E18" s="162" t="n">
-        <v>3000</v>
+        <v>2490</v>
       </c>
     </row>
     <row r="19">
@@ -6387,7 +6388,7 @@
       </c>
       <c r="B19" s="161" t="inlineStr">
         <is>
-          <t>2~3개</t>
+          <t>800g (한입 꿀고구마)</t>
         </is>
       </c>
       <c r="C19" s="161" t="inlineStr">
@@ -6397,11 +6398,11 @@
       </c>
       <c r="D19" s="161" t="inlineStr">
         <is>
-          <t>10/22(목) 밤 주문</t>
+          <t>10/19 컬리 담음</t>
         </is>
       </c>
       <c r="E19" s="162" t="n">
-        <v>4000</v>
+        <v>4490</v>
       </c>
     </row>
     <row r="20">
@@ -6594,11 +6595,11 @@
       </c>
       <c r="D28" s="161" t="inlineStr">
         <is>
-          <t>10/22(목) 밤 주문</t>
+          <t>10/19 컬리 담음</t>
         </is>
       </c>
       <c r="E28" s="162" t="n">
-        <v>3000</v>
+        <v>2980</v>
       </c>
     </row>
     <row r="29">
@@ -6609,7 +6610,7 @@
       </c>
       <c r="B29" s="161" t="inlineStr">
         <is>
-          <t>1개</t>
+          <t>바몬드카레 순한맛 200g</t>
         </is>
       </c>
       <c r="C29" s="161" t="inlineStr">
@@ -6619,11 +6620,11 @@
       </c>
       <c r="D29" s="161" t="inlineStr">
         <is>
-          <t>10/22(목) 밤 주문</t>
+          <t>10/19 컬리 담음</t>
         </is>
       </c>
       <c r="E29" s="162" t="n">
-        <v>4000</v>
+        <v>4150</v>
       </c>
     </row>
     <row r="30">
@@ -6684,7 +6685,7 @@
       </c>
       <c r="B32" s="161" t="inlineStr">
         <is>
-          <t>4~5개</t>
+          <t>1kg (4~6입)</t>
         </is>
       </c>
       <c r="C32" s="161" t="inlineStr">
@@ -6694,11 +6695,11 @@
       </c>
       <c r="D32" s="161" t="inlineStr">
         <is>
-          <t>10/22(목) 밤 주문</t>
+          <t>10/19 컬리 담음</t>
         </is>
       </c>
       <c r="E32" s="162" t="n">
-        <v>8000</v>
+        <v>7990</v>
       </c>
     </row>
     <row r="33">
@@ -6910,16 +6911,16 @@
       <c r="B41" s="169" t="n"/>
       <c r="C41" s="169" t="inlineStr">
         <is>
-          <t>월 97,390원(실제·할인 전) / 목 47,000원(추정)</t>
+          <t>10/19 컬리 일괄 담음 (할인 전 156,630원)</t>
         </is>
       </c>
       <c r="D41" s="170" t="inlineStr">
         <is>
-          <t>전체(추정)</t>
+          <t>결제예정</t>
         </is>
       </c>
       <c r="E41" s="171" t="n">
-        <v>144390</v>
+        <v>170200</v>
       </c>
     </row>
   </sheetData>

--- a/26년도_2주간_식단.xlsx
+++ b/26년도_2주간_식단.xlsx
@@ -1576,7 +1576,7 @@
       <c r="C3" s="157" t="inlineStr">
         <is>
           <t>[오야코동] ★호평 메뉴 — 새우 달걀 덮밥처럼 "몽글하게"
-1. 닭다리살 600g → 껍질·노란 지방 떼고 1.5cm로 작게
+1. 닭다리살 500g → 껍질·노란 지방 떼고 1.5cm로 작게
    → 청주 1T + 소금 1/3t 밑간 → 냉장
 2. 양파 1개 채썰기 / 대파 송송 → 냉장
 3. 덮밥소스 한 통에: 만능육수 250ml + 간장 3T
@@ -6218,7 +6218,7 @@
     <row r="1" ht="24" customHeight="1" s="110">
       <c r="A1" s="158" t="inlineStr">
         <is>
-          <t>10월 5주차 장보기 (10/27~10/30) — 전체 10/26(월) 밤 일괄 주문</t>
+          <t>10월 5주차 장보기 (10/27~10/30) — 10/25 컬리 일괄 담음 · 결제예정 175,220원 (할인 후)</t>
         </is>
       </c>
     </row>
@@ -6268,7 +6268,7 @@
       </c>
       <c r="B4" s="161" t="inlineStr">
         <is>
-          <t>400g</t>
+          <t>400g (국내산 절단 국거리 200g×2)</t>
         </is>
       </c>
       <c r="C4" s="161" t="inlineStr">
@@ -6278,11 +6278,11 @@
       </c>
       <c r="D4" s="161" t="inlineStr">
         <is>
-          <t>10/26(월) 밤 주문</t>
+          <t>10/25 컬리 담음</t>
         </is>
       </c>
       <c r="E4" s="162" t="n">
-        <v>20000</v>
+        <v>20560</v>
       </c>
     </row>
     <row r="5">
@@ -6293,7 +6293,7 @@
       </c>
       <c r="B5" s="161" t="inlineStr">
         <is>
-          <t>600g</t>
+          <t>500g (무항생제) — 레시피 600g → 500g로</t>
         </is>
       </c>
       <c r="C5" s="161" t="inlineStr">
@@ -6303,11 +6303,11 @@
       </c>
       <c r="D5" s="161" t="inlineStr">
         <is>
-          <t>10/26(월) 밤 주문</t>
+          <t>10/25 컬리 담음</t>
         </is>
       </c>
       <c r="E5" s="162" t="n">
-        <v>10000</v>
+        <v>10170</v>
       </c>
     </row>
     <row r="6">
@@ -6318,7 +6318,7 @@
       </c>
       <c r="B6" s="161" t="inlineStr">
         <is>
-          <t>500g — 받자마자 냉동</t>
+          <t>600g (한돈) — 받자마자 냉동</t>
         </is>
       </c>
       <c r="C6" s="161" t="inlineStr">
@@ -6328,11 +6328,11 @@
       </c>
       <c r="D6" s="161" t="inlineStr">
         <is>
-          <t>10/26(월) 밤 주문</t>
+          <t>10/25 컬리 담음</t>
         </is>
       </c>
       <c r="E6" s="162" t="n">
-        <v>8000</v>
+        <v>7790</v>
       </c>
     </row>
     <row r="7">
@@ -6354,7 +6354,7 @@
       </c>
       <c r="B8" s="161" t="inlineStr">
         <is>
-          <t>600g — 화 아침 냉장 해동</t>
+          <t>600g (국내 손질 대구살 300g×2) — 화 아침 냉장 해동</t>
         </is>
       </c>
       <c r="C8" s="161" t="inlineStr">
@@ -6364,11 +6364,11 @@
       </c>
       <c r="D8" s="161" t="inlineStr">
         <is>
-          <t>10/26(월) 밤 주문</t>
+          <t>10/25 컬리 담음</t>
         </is>
       </c>
       <c r="E8" s="162" t="n">
-        <v>15000</v>
+        <v>35800</v>
       </c>
     </row>
     <row r="9">
@@ -6379,7 +6379,7 @@
       </c>
       <c r="B9" s="161" t="inlineStr">
         <is>
-          <t>1봉</t>
+          <t>200g (재고 적음 — 품절 시 대체)</t>
         </is>
       </c>
       <c r="C9" s="161" t="inlineStr">
@@ -6389,11 +6389,11 @@
       </c>
       <c r="D9" s="161" t="inlineStr">
         <is>
-          <t>10/26(월) 밤 주문</t>
+          <t>10/25 컬리 담음</t>
         </is>
       </c>
       <c r="E9" s="162" t="n">
-        <v>4000</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="10">
@@ -6440,7 +6440,7 @@
       </c>
       <c r="B12" s="161" t="inlineStr">
         <is>
-          <t>1kg</t>
+          <t>1.5kg</t>
         </is>
       </c>
       <c r="C12" s="161" t="inlineStr">
@@ -6450,11 +6450,11 @@
       </c>
       <c r="D12" s="161" t="inlineStr">
         <is>
-          <t>10/26(월) 밤 주문</t>
+          <t>10/25 컬리 담음</t>
         </is>
       </c>
       <c r="E12" s="162" t="n">
-        <v>4000</v>
+        <v>3990</v>
       </c>
     </row>
     <row r="13">
@@ -6475,11 +6475,11 @@
       </c>
       <c r="D13" s="161" t="inlineStr">
         <is>
-          <t>10/26(월) 밤 주문</t>
+          <t>10/25 컬리 담음</t>
         </is>
       </c>
       <c r="E13" s="162" t="n">
-        <v>2000</v>
+        <v>1990</v>
       </c>
     </row>
     <row r="14">
@@ -6490,7 +6490,7 @@
       </c>
       <c r="B14" s="161" t="inlineStr">
         <is>
-          <t>1~3입</t>
+          <t>다다기 5입</t>
         </is>
       </c>
       <c r="C14" s="161" t="inlineStr">
@@ -6500,11 +6500,11 @@
       </c>
       <c r="D14" s="161" t="inlineStr">
         <is>
-          <t>10/26(월) 밤 주문</t>
+          <t>10/25 컬리 담음</t>
         </is>
       </c>
       <c r="E14" s="162" t="n">
-        <v>2500</v>
+        <v>2990</v>
       </c>
     </row>
     <row r="15">
@@ -6515,7 +6515,7 @@
       </c>
       <c r="B15" s="161" t="inlineStr">
         <is>
-          <t>2~3개</t>
+          <t>600g</t>
         </is>
       </c>
       <c r="C15" s="161" t="inlineStr">
@@ -6525,11 +6525,11 @@
       </c>
       <c r="D15" s="161" t="inlineStr">
         <is>
-          <t>10/26(월) 밤 주문</t>
+          <t>10/25 컬리 담음</t>
         </is>
       </c>
       <c r="E15" s="162" t="n">
-        <v>3000</v>
+        <v>4290</v>
       </c>
     </row>
     <row r="16">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="B18" s="161" t="inlineStr">
         <is>
-          <t>1모</t>
+          <t>부침두부 380g</t>
         </is>
       </c>
       <c r="C18" s="161" t="inlineStr">
@@ -6586,11 +6586,11 @@
       </c>
       <c r="D18" s="161" t="inlineStr">
         <is>
-          <t>10/26(월) 밤 주문</t>
+          <t>10/25 컬리 담음</t>
         </is>
       </c>
       <c r="E18" s="162" t="n">
-        <v>2200</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="19">
@@ -6622,11 +6622,11 @@
       </c>
       <c r="D20" s="161" t="inlineStr">
         <is>
-          <t>10/26(월) 밤 주문</t>
+          <t>10/25 컬리 담음</t>
         </is>
       </c>
       <c r="E20" s="162" t="n">
-        <v>4500</v>
+        <v>4180</v>
       </c>
     </row>
     <row r="21">
@@ -6637,7 +6637,7 @@
       </c>
       <c r="B21" s="161" t="inlineStr">
         <is>
-          <t>500g</t>
+          <t>데체코 500g</t>
         </is>
       </c>
       <c r="C21" s="161" t="inlineStr">
@@ -6647,11 +6647,11 @@
       </c>
       <c r="D21" s="161" t="inlineStr">
         <is>
-          <t>10/26(월) 밤 주문</t>
+          <t>10/25 컬리 담음</t>
         </is>
       </c>
       <c r="E21" s="162" t="n">
-        <v>3500</v>
+        <v>5480</v>
       </c>
     </row>
     <row r="22">
@@ -6662,7 +6662,7 @@
       </c>
       <c r="B22" s="161" t="inlineStr">
         <is>
-          <t>1병</t>
+          <t>폰타나 뽀모도로 600g</t>
         </is>
       </c>
       <c r="C22" s="161" t="inlineStr">
@@ -6672,11 +6672,11 @@
       </c>
       <c r="D22" s="161" t="inlineStr">
         <is>
-          <t>10/26(월) 밤 주문</t>
+          <t>10/25 컬리 담음</t>
         </is>
       </c>
       <c r="E22" s="162" t="n">
-        <v>5000</v>
+        <v>5480</v>
       </c>
     </row>
     <row r="23">
@@ -6687,7 +6687,7 @@
       </c>
       <c r="B23" s="161" t="inlineStr">
         <is>
-          <t>200g</t>
+          <t>226g</t>
         </is>
       </c>
       <c r="C23" s="161" t="inlineStr">
@@ -6697,11 +6697,11 @@
       </c>
       <c r="D23" s="161" t="inlineStr">
         <is>
-          <t>10/26(월) 밤 주문</t>
+          <t>10/25 컬리 담음</t>
         </is>
       </c>
       <c r="E23" s="162" t="n">
-        <v>6000</v>
+        <v>8980</v>
       </c>
     </row>
     <row r="24">
@@ -6712,7 +6712,7 @@
       </c>
       <c r="B24" s="161" t="inlineStr">
         <is>
-          <t>2캔</t>
+          <t>340g × 2</t>
         </is>
       </c>
       <c r="C24" s="161" t="inlineStr">
@@ -6722,11 +6722,11 @@
       </c>
       <c r="D24" s="161" t="inlineStr">
         <is>
-          <t>10/26(월) 밤 주문</t>
+          <t>10/25 컬리 담음</t>
         </is>
       </c>
       <c r="E24" s="162" t="n">
-        <v>4000</v>
+        <v>3960</v>
       </c>
     </row>
     <row r="25">
@@ -6747,11 +6747,11 @@
       </c>
       <c r="D25" s="161" t="inlineStr">
         <is>
-          <t>10/26(월) 밤 주문</t>
+          <t>10/25 컬리 담음</t>
         </is>
       </c>
       <c r="E25" s="162" t="n">
-        <v>6000</v>
+        <v>5960</v>
       </c>
     </row>
     <row r="26">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="B26" s="161" t="inlineStr">
         <is>
-          <t>1봉</t>
+          <t>400g (찹쌀가루 소량 혼합)</t>
         </is>
       </c>
       <c r="C26" s="161" t="inlineStr">
@@ -6772,11 +6772,11 @@
       </c>
       <c r="D26" s="161" t="inlineStr">
         <is>
-          <t>10/26(월) 밤 주문</t>
+          <t>10/25 컬리 담음</t>
         </is>
       </c>
       <c r="E26" s="162" t="n">
-        <v>3000</v>
+        <v>5080</v>
       </c>
     </row>
     <row r="27">
@@ -6787,7 +6787,7 @@
       </c>
       <c r="B27" s="161" t="inlineStr">
         <is>
-          <t>1통</t>
+          <t>무가당 400g</t>
         </is>
       </c>
       <c r="C27" s="161" t="inlineStr">
@@ -6797,11 +6797,11 @@
       </c>
       <c r="D27" s="161" t="inlineStr">
         <is>
-          <t>10/26(월) 밤 주문</t>
+          <t>10/25 컬리 담음</t>
         </is>
       </c>
       <c r="E27" s="162" t="n">
-        <v>6000</v>
+        <v>3790</v>
       </c>
     </row>
     <row r="28">
@@ -6812,7 +6812,7 @@
       </c>
       <c r="B28" s="161" t="inlineStr">
         <is>
-          <t>1봉</t>
+          <t>저당 360g</t>
         </is>
       </c>
       <c r="C28" s="161" t="inlineStr">
@@ -6822,11 +6822,11 @@
       </c>
       <c r="D28" s="161" t="inlineStr">
         <is>
-          <t>10/26(월) 밤 주문</t>
+          <t>10/25 컬리 담음</t>
         </is>
       </c>
       <c r="E28" s="162" t="n">
-        <v>6000</v>
+        <v>6980</v>
       </c>
     </row>
     <row r="29">
@@ -6847,11 +6847,11 @@
       </c>
       <c r="D29" s="161" t="inlineStr">
         <is>
-          <t>10/26(월) 밤 주문</t>
+          <t>10/25 컬리 담음</t>
         </is>
       </c>
       <c r="E29" s="162" t="n">
-        <v>9000</v>
+        <v>9990</v>
       </c>
     </row>
     <row r="30">
@@ -6862,7 +6862,7 @@
       </c>
       <c r="B30" s="161" t="inlineStr">
         <is>
-          <t>2입</t>
+          <t>1kg (2입)</t>
         </is>
       </c>
       <c r="C30" s="161" t="inlineStr">
@@ -6872,11 +6872,11 @@
       </c>
       <c r="D30" s="161" t="inlineStr">
         <is>
-          <t>10/26(월) 밤 주문</t>
+          <t>10/25 컬리 담음</t>
         </is>
       </c>
       <c r="E30" s="162" t="n">
-        <v>9000</v>
+        <v>15900</v>
       </c>
     </row>
     <row r="31">
@@ -6897,11 +6897,11 @@
       </c>
       <c r="D31" s="161" t="inlineStr">
         <is>
-          <t>10/26(월) 밤 주문</t>
+          <t>10/25 컬리 담음</t>
         </is>
       </c>
       <c r="E31" s="162" t="n">
-        <v>8000</v>
+        <v>7990</v>
       </c>
     </row>
     <row r="32">
@@ -7036,14 +7036,18 @@
         </is>
       </c>
       <c r="B37" s="169" t="n"/>
-      <c r="C37" s="169" t="n"/>
+      <c r="C37" s="169" t="inlineStr">
+        <is>
+          <t>할인 전 175,220원</t>
+        </is>
+      </c>
       <c r="D37" s="170" t="inlineStr">
         <is>
-          <t>전체(추정)</t>
+          <t>결제예정</t>
         </is>
       </c>
       <c r="E37" s="171" t="n">
-        <v>140700</v>
+        <v>175220</v>
       </c>
     </row>
   </sheetData>

--- a/26년도_2주간_식단.xlsx
+++ b/26년도_2주간_식단.xlsx
@@ -7038,7 +7038,7 @@
       <c r="B37" s="169" t="n"/>
       <c r="C37" s="169" t="inlineStr">
         <is>
-          <t>할인 전 175,220원</t>
+          <t>담은 가격(할인 반영) 합계</t>
         </is>
       </c>
       <c r="D37" s="170" t="inlineStr">

--- a/26년도_2주간_식단.xlsx
+++ b/26년도_2주간_식단.xlsx
@@ -1488,7 +1488,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="411" customHeight="1" s="110">
+    <row r="2" ht="426" customHeight="1" s="110">
       <c r="A2" s="156" t="inlineStr">
         <is>
           <t>화 (10/27)</t>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="B2" s="157" t="inlineStr">
         <is>
-          <t>대구 순살 탕수 (생선 탕수육)
+          <t>대구 순살 탕수 (아이용 300g)
 + 양지 미역국 🧊냉동OK
 + 잔멸치볶음(칼슘)
 + 키즈김치
@@ -1508,16 +1508,17 @@
         <is>
           <t>[대구 순살 탕수] ★신메뉴 — 생선을 "호평 탕수육 형식"으로
    (검증: 만개 명태·가자미 탕수 + 일본 급식 白身魚の甘酢あん)
+   ※ 아이 2명분 300g (어른은 다른 반찬으로 대체)
 ※ 월요일 주문분 냉동 대구는 화요일 아침 도착하면
   바로 냉장실(키친타월 깔고 덮어서)로 → 저녁까지 해동
   ※ 급하면 밀폐해 찬물 해동(30분마다 물 교체), 실온·온수 X
 1. 소스 재료 계량해 한 통에:
-   육수(또는 물) 200ml + 케첩 3T + 설탕 1.5T
-   + 식초 2T + 소금 1/3t + 간장 1t (색 밝게, 추정 비율)
-2. 당근 1/3개 · 양파 1/2개 · 오이 1/2개 채썰기 → 냉장
+   육수(또는 물) 100ml + 케첩 1.5T + 설탕 2t
+   + 식초 1T + 소금 한 꼬집 + 간장 1/2t (색 밝게, 추정 비율)
+2. 당근 1/4개 · 양파 1/4개 · 오이 1/4개 채썰기 → 냉장
    ※ 전분 입히기는 당일에 (미리 하면 눅눅)
 [양지 미역국 — 🧊냉동OK · 수요일 아침 국밥용 포함]
-3. 양지 400g 한입크기 → 끓는 물에 데쳐 핏물·기름 빼기 → 냉장
+3. 양지 200g 한입크기 → 끓는 물에 데쳐 핏물·기름 빼기 → 냉장
 4. 염장미역 1줌 반 → 물에 담가 짠기 빼고 불려 꼭 짜서
    한입 크기로 → 냉장
 5. 만능육수 2L 만들어 식혀 냉장
@@ -1544,14 +1545,14 @@
    + 맛술 1t 약불 30초 → 아몬드·통깨
 [대구 탕수 — 마지막, 바로 먹을 수 있게]
 6. 대구 3cm로 썰고 가시 확인 (5세 주의)
-7. ★ 우유 100ml에 10분 담갔다가 물기만 닦기 (비린내 제거)
-8. 소금 1/2t + 후추 + 청주 1T → 10분 → 키친타월로 물기 꼼꼼히
-9. 달걀흰자 2T 버무리고 → 감자전분 약 100g 얇게 입혀 털기
-10. 170℃ 기름에 2~3번 나눠 2~3분 (떠오를 때까지 건드리지 않기)
+7. ★ 우유 50ml에 10분 담갔다가 물기만 닦기 (비린내 제거)
+8. 소금 1/4t + 후추 + 청주 1/2T → 10분 → 키친타월로 물기 꼼꼼히
+9. 달걀흰자 1T 버무리고 → 감자전분 약 50g 얇게 입혀 털기
+10. 170℃ 기름에 1~2번 나눠 2~3분 (떠오를 때까지 건드리지 않기)
     → 건져 잠깐 식혔다가 → 180℃에 30~60초 한 번 더 (바삭)
     ※ 한 번에 많이 넣으면 기름 먹음 / 속 하얗게 익었는지 확인
 11. 소스: 기름 1t에 채소 볶기 → 소스 붓고 끓으면
-    전분 1T + 물 2T로 걸쭉하게 → 맛보고 시면 설탕 조금
+    전분 1/2T + 물 1T로 걸쭉하게 → 맛보고 시면 설탕 조금
 12. ★ 튀김 위에 소스 끼얹기 (버무리면 눅눅) → 바로 식탁에
 [키즈김치] 접시에 / [귤]</t>
         </is>
@@ -1683,7 +1684,7 @@
           <t>🌅 아침 (장모님 오시는 주)
 수: 미역국 국밥
 토: 그릭요거트+그래놀라
-일: 옥수수밥
+일: 고구마밥
 ※ 월·화·목·금은 장모님</t>
         </is>
       </c>
@@ -1692,8 +1693,9 @@
           <t>[화 밤] 미역국 1/3 덜어 냉장 (수 아침용)
          + 남은 밥 1시간 내 식혀 냉장
 [금 밤] 과일 씻어 두기 (토 아침 꺼내기만)
-[토 밤] 쌀 씻어 안치고 스위트콘 1캔(물 빼서) 올려
-         예약취사 (일 아침 시간에 맞춰), 소금 한 꼬집
+[토 밤] 쌀 씻어 안치고 고구마 1개(지난주 남은 것) 깍둑썰어
+         올려 예약취사 (일 아침 시간에 맞춰)
+         ※ 고구마 없으면 일요일은 시리얼+우유+과일
          ※ 날고기·달걀은 예약취사에 넣지 않기
 ※ 월·목 밤 "내일 아침 국 있나?" 확인
    → 없으면 냉동 국팩(🧊) 언 채로 냄비 + 물 100ml</t>
@@ -1709,7 +1711,7 @@
 [토 아침 — 꺼내기만]
 4. 그릭요거트 + 그래놀라 + 과일(귤·단감 등) + 우유
 [일 아침 — 데울 것 없음]
-5. 옥수수밥 퍼서 김 · 키즈김치 · 우유 1컵</t>
+5. 고구마밥 퍼서 김 · 키즈김치 · 우유 1컵</t>
         </is>
       </c>
     </row>
@@ -6218,7 +6220,7 @@
     <row r="1" ht="24" customHeight="1" s="110">
       <c r="A1" s="158" t="inlineStr">
         <is>
-          <t>10월 5주차 장보기 (10/27~10/30) — 10/25 컬리 일괄 담음 · 결제예정 175,220원 (할인 후)</t>
+          <t>10월 5주차 장보기 (10/27~10/30) — 10/26 컬리 장바구니 19개 · 114,270원</t>
         </is>
       </c>
     </row>
@@ -6268,7 +6270,7 @@
       </c>
       <c r="B4" s="161" t="inlineStr">
         <is>
-          <t>400g (국내산 절단 국거리 200g×2)</t>
+          <t>200g</t>
         </is>
       </c>
       <c r="C4" s="161" t="inlineStr">
@@ -6282,7 +6284,7 @@
         </is>
       </c>
       <c r="E4" s="162" t="n">
-        <v>20560</v>
+        <v>10280</v>
       </c>
     </row>
     <row r="5">
@@ -6354,7 +6356,7 @@
       </c>
       <c r="B8" s="161" t="inlineStr">
         <is>
-          <t>600g (국내 손질 대구살 300g×2) — 화 아침 냉장 해동</t>
+          <t>300g (아이용) — 화 아침 냉장 해동</t>
         </is>
       </c>
       <c r="C8" s="161" t="inlineStr">
@@ -6368,7 +6370,7 @@
         </is>
       </c>
       <c r="E8" s="162" t="n">
-        <v>35800</v>
+        <v>17900</v>
       </c>
     </row>
     <row r="9">
@@ -6379,7 +6381,7 @@
       </c>
       <c r="B9" s="161" t="inlineStr">
         <is>
-          <t>200g (재고 적음 — 품절 시 대체)</t>
+          <t>200g</t>
         </is>
       </c>
       <c r="C9" s="161" t="inlineStr">
@@ -6393,7 +6395,7 @@
         </is>
       </c>
       <c r="E9" s="162" t="n">
-        <v>2250</v>
+        <v>2290</v>
       </c>
     </row>
     <row r="10">
@@ -6479,7 +6481,7 @@
         </is>
       </c>
       <c r="E13" s="162" t="n">
-        <v>1990</v>
+        <v>2290</v>
       </c>
     </row>
     <row r="14">
@@ -6626,7 +6628,7 @@
         </is>
       </c>
       <c r="E20" s="162" t="n">
-        <v>4180</v>
+        <v>3980</v>
       </c>
     </row>
     <row r="21">
@@ -6676,7 +6678,7 @@
         </is>
       </c>
       <c r="E22" s="162" t="n">
-        <v>5480</v>
+        <v>7480</v>
       </c>
     </row>
     <row r="23">
@@ -6701,7 +6703,7 @@
         </is>
       </c>
       <c r="E23" s="162" t="n">
-        <v>8980</v>
+        <v>9980</v>
       </c>
     </row>
     <row r="24">
@@ -6712,7 +6714,7 @@
       </c>
       <c r="B24" s="161" t="inlineStr">
         <is>
-          <t>340g × 2</t>
+          <t>1캔 (스프용) — 일 아침은 고구마밥 등으로</t>
         </is>
       </c>
       <c r="C24" s="161" t="inlineStr">
@@ -6726,7 +6728,7 @@
         </is>
       </c>
       <c r="E24" s="162" t="n">
-        <v>3960</v>
+        <v>2280</v>
       </c>
     </row>
     <row r="25">
@@ -6826,7 +6828,7 @@
         </is>
       </c>
       <c r="E28" s="162" t="n">
-        <v>6980</v>
+        <v>6630</v>
       </c>
     </row>
     <row r="29">
@@ -6837,7 +6839,7 @@
       </c>
       <c r="B29" s="161" t="inlineStr">
         <is>
-          <t>1kg</t>
+          <t>장바구니에서 뺌 (보유분 사용)</t>
         </is>
       </c>
       <c r="C29" s="161" t="inlineStr">
@@ -6847,11 +6849,11 @@
       </c>
       <c r="D29" s="161" t="inlineStr">
         <is>
-          <t>10/25 컬리 담음</t>
+          <t>제외</t>
         </is>
       </c>
       <c r="E29" s="162" t="n">
-        <v>9990</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -6862,7 +6864,7 @@
       </c>
       <c r="B30" s="161" t="inlineStr">
         <is>
-          <t>1kg (2입)</t>
+          <t>장바구니에서 뺌 (보유분 사용)</t>
         </is>
       </c>
       <c r="C30" s="161" t="inlineStr">
@@ -6872,11 +6874,11 @@
       </c>
       <c r="D30" s="161" t="inlineStr">
         <is>
-          <t>10/25 컬리 담음</t>
+          <t>제외</t>
         </is>
       </c>
       <c r="E30" s="162" t="n">
-        <v>15900</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -6887,7 +6889,7 @@
       </c>
       <c r="B31" s="161" t="inlineStr">
         <is>
-          <t>1kg</t>
+          <t>장바구니에서 뺌 (보유분 사용)</t>
         </is>
       </c>
       <c r="C31" s="161" t="inlineStr">
@@ -6897,11 +6899,11 @@
       </c>
       <c r="D31" s="161" t="inlineStr">
         <is>
-          <t>10/25 컬리 담음</t>
+          <t>제외</t>
         </is>
       </c>
       <c r="E31" s="162" t="n">
-        <v>7990</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -7038,7 +7040,7 @@
       <c r="B37" s="169" t="n"/>
       <c r="C37" s="169" t="inlineStr">
         <is>
-          <t>담은 가격(할인 반영) 합계</t>
+          <t>10/26 장바구니 기준 (19개)</t>
         </is>
       </c>
       <c r="D37" s="170" t="inlineStr">
@@ -7047,7 +7049,7 @@
         </is>
       </c>
       <c r="E37" s="171" t="n">
-        <v>175220</v>
+        <v>114270</v>
       </c>
     </row>
   </sheetData>

--- a/26년도_2주간_식단.xlsx
+++ b/26년도_2주간_식단.xlsx
@@ -83,7 +83,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0&quot;원&quot;"/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="39">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -252,8 +252,84 @@
       <b val="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Malgun Gothic"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Malgun Gothic"/>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <name val="Malgun Gothic"/>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Malgun Gothic"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Malgun Gothic"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Malgun Gothic"/>
+      <b val="1"/>
+      <color rgb="00375623"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <name val="Malgun Gothic"/>
+      <b val="1"/>
+      <color rgb="00375623"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Malgun Gothic"/>
+      <b val="1"/>
+      <color rgb="00843C0C"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <name val="Malgun Gothic"/>
+      <b val="1"/>
+      <color rgb="00843C0C"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Malgun Gothic"/>
+      <b val="1"/>
+      <color rgb="007F6000"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <name val="Malgun Gothic"/>
+      <b val="1"/>
+      <color rgb="007F6000"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Malgun Gothic"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <name val="Malgun Gothic"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="13"/>
+    </font>
   </fonts>
-  <fills count="50">
+  <fills count="51">
     <fill>
       <patternFill/>
     </fill>
@@ -524,8 +600,13 @@
         <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="18">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -743,11 +824,35 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="180">
+  <cellXfs count="204">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1198,6 +1303,64 @@
     </xf>
     <xf numFmtId="0" fontId="25" fillId="49" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="49" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="50" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="50" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="41" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="45" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="45" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="49" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="49" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="46" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="46" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="41" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="42" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="30" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="43" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="44" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="49" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="45" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="46" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="24" fillId="46" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1457,265 +1620,1450 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" style="110" min="1" max="1"/>
-    <col width="18" customWidth="1" style="110" min="2" max="2"/>
-    <col width="55" customWidth="1" style="110" min="3" max="3"/>
-    <col width="65" customWidth="1" style="110" min="4" max="4"/>
+    <col width="62" customWidth="1" style="110" min="1" max="1"/>
+    <col width="68" customWidth="1" style="110" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" s="110">
-      <c r="A1" s="155" t="inlineStr">
-        <is>
-          <t>요일</t>
-        </is>
-      </c>
-      <c r="B1" s="155" t="inlineStr">
-        <is>
-          <t>메뉴</t>
-        </is>
-      </c>
-      <c r="C1" s="155" t="inlineStr">
-        <is>
-          <t>전날 밤 준비</t>
-        </is>
-      </c>
-      <c r="D1" s="155" t="inlineStr">
-        <is>
-          <t>당일 조리</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="426" customHeight="1" s="110">
-      <c r="A2" s="156" t="inlineStr">
+    <row r="1" ht="30" customHeight="1" s="110">
+      <c r="A1" s="180" t="inlineStr">
+        <is>
+          <t>10월 5주차 식단 (10/27~10/30) · 장모님 오시는 주</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="70.55" customHeight="1" s="110">
+      <c r="A3" s="181" t="inlineStr">
         <is>
           <t>화 (10/27)</t>
         </is>
       </c>
-      <c r="B2" s="157" t="inlineStr">
-        <is>
-          <t>대구 순살 탕수 (아이용 300g)
-+ 양지 미역국 🧊냉동OK
-+ 잔멸치볶음(칼슘)
-+ 키즈김치
-+ 귤 (간식)
+      <c r="B3" s="182" t="inlineStr">
+        <is>
+          <t>대구 순살 탕수 (아이용 300g) + 양지 미역국 🧊냉동OK + 잔멸치볶음(칼슘) + 키즈김치 + 귤 (간식)
 ※ 생선 살리기 1탄·신메뉴 (튀김 7주 만)</t>
         </is>
       </c>
-      <c r="C2" s="157" t="inlineStr">
-        <is>
-          <t>[대구 순살 탕수] ★신메뉴 — 생선을 "호평 탕수육 형식"으로
-   (검증: 만개 명태·가자미 탕수 + 일본 급식 白身魚の甘酢あん)
-   ※ 아이 2명분 300g (어른은 다른 반찬으로 대체)
-※ 월요일 주문분 냉동 대구는 화요일 아침 도착하면
-  바로 냉장실(키친타월 깔고 덮어서)로 → 저녁까지 해동
-  ※ 급하면 밀폐해 찬물 해동(30분마다 물 교체), 실온·온수 X
-1. 소스 재료 계량해 한 통에:
-   육수(또는 물) 100ml + 케첩 1.5T + 설탕 2t
-   + 식초 1T + 소금 한 꼬집 + 간장 1/2t (색 밝게, 추정 비율)
-2. 당근 1/4개 · 양파 1/4개 · 오이 1/4개 채썰기 → 냉장
-   ※ 전분 입히기는 당일에 (미리 하면 눅눅)
-[양지 미역국 — 🧊냉동OK · 수요일 아침 국밥용 포함]
-3. 양지 200g 한입크기 → 끓는 물에 데쳐 핏물·기름 빼기 → 냉장
-4. 염장미역 1줌 반 → 물에 담가 짠기 빼고 불려 꼭 짜서
-   한입 크기로 → 냉장
-5. 만능육수 2L 만들어 식혀 냉장
-   (물 2L + 국물멸치 25마리 마른팬 30초 + 다시마
-    + 건새우 1줌 + 마른표고 2개 + 무 한토막)
-[잔멸치볶음 — 칼슘]
-6. 잔멸치 1컵 체에 쳐 가루 털고 마른팬에 살짝 볶기
-   / 아몬드 슬라이스 준비
-[키즈김치] 어린이김치 통 준비</t>
-        </is>
-      </c>
-      <c r="D2" s="157" t="inlineStr">
-        <is>
-          <t>★ 식사 50분 전 시작
-[양지 미역국 — 맨 먼저]
-1. 냄비에 데친 양지 + 미역 + 국간장 1T → 1분 볶기
-   (감칠맛 베이스) ※ 참기름은 향만 몇 방울
-2. 육수 2L 붓고 중불 20분 → 뜨는 기름 걷기
-3. 간: 국간장 1.5T + 액젓 1t + 다진마늘 1T → 소금
-   ※ 기름 뺐다고 밍밍하면 실패! 맛보고 간 확실히
-4. ★ 아침용 1/3 덜어 식혀 냉장 (수요일 아침 국밥)
-[잔멸치볶음 — 국 끓는 동안]
-5. 기름 살짝, 잔멸치 약불 1분 → 간장 1t + 올리고당 1T
-   + 맛술 1t 약불 30초 → 아몬드·통깨
-[대구 탕수 — 마지막, 바로 먹을 수 있게]
-6. 대구 3cm로 썰고 가시 확인 (5세 주의)
-7. ★ 우유 50ml에 10분 담갔다가 물기만 닦기 (비린내 제거)
-8. 소금 1/4t + 후추 + 청주 1/2T → 10분 → 키친타월로 물기 꼼꼼히
-9. 달걀흰자 1T 버무리고 → 감자전분 약 50g 얇게 입혀 털기
-10. 170℃ 기름에 1~2번 나눠 2~3분 (떠오를 때까지 건드리지 않기)
-    → 건져 잠깐 식혔다가 → 180℃에 30~60초 한 번 더 (바삭)
-    ※ 한 번에 많이 넣으면 기름 먹음 / 속 하얗게 익었는지 확인
-11. 소스: 기름 1t에 채소 볶기 → 소스 붓고 끓으면
-    전분 1/2T + 물 1T로 걸쭉하게 → 맛보고 시면 설탕 조금
-12. ★ 튀김 위에 소스 끼얹기 (버무리면 눅눅) → 바로 식탁에
-[키즈김치] 접시에 / [귤]</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="321" customHeight="1" s="110">
-      <c r="A3" s="156" t="inlineStr">
+    </row>
+    <row r="4" ht="22" customHeight="1" s="110">
+      <c r="A4" s="183" t="inlineStr">
+        <is>
+          <t>🌙 전날 밤 준비</t>
+        </is>
+      </c>
+      <c r="B4" s="183" t="inlineStr">
+        <is>
+          <t>🔥 당일 조리</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="269" customHeight="1" s="110">
+      <c r="A5" s="184" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <b val="1"/>
+              <color rgb="001F3864"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">[대구 순살 탕수] ★신메뉴 — 생선을 "호평 탕수육 형식"으로
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">   (검증: 만개 명태·가자미 탕수 + 일본 급식 白身魚の甘酢あん)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">   ※ 아이 2명분 300g (어른은 다른 반찬으로 대체)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">※ 월요일 주문분 냉동 대구는 화요일 아침 도착하면
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">  바로 냉장실(키친타월 깔고 덮어서)로 → 저녁까지 해동
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">  ※ 급하면 밀폐해 찬물 해동(30분마다 물 교체), 실온·온수 X
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">1. 소스 재료 계량해 한 통에:
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">   육수(또는 물) 100ml + 케첩 1.5T + 설탕 2t
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">   + 식초 1T + 소금 한 꼬집 + 간장 1/2t (색 밝게, 추정 비율)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">2. 당근 1/4개 · 양파 1/4개 · 오이 1/4개 채썰기 → 냉장
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">   ※ 전분 입히기는 당일에 (미리 하면 눅눅)</t>
+          </r>
+        </is>
+      </c>
+      <c r="B5" s="184" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <b val="1"/>
+              <color rgb="001F3864"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">★ 식사 50분 전 시작
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <b val="1"/>
+              <color rgb="001F3864"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">[양지 미역국 — 맨 먼저]
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">1. 냄비에 데친 양지 + 미역 + 국간장 1T → 1분 볶기
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">   (감칠맛 베이스) ※ 참기름은 향만 몇 방울
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">2. 육수 2L 붓고 중불 20분 → 뜨는 기름 걷기
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">3. 간: 국간장 1.5T + 액젓 1t + 다진마늘 1T → 소금
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">   ※ 기름 뺐다고 밍밍하면 실패! 맛보고 간 확실히
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">4. ★ 아침용 1/3 덜어 식혀 냉장 (수요일 아침 국밥)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <b val="1"/>
+              <color rgb="001F3864"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">[잔멸치볶음 — 국 끓는 동안]
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">5. 기름 살짝, 잔멸치 약불 1분 → 간장 1t + 올리고당 1T
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">   + 맛술 1t 약불 30초 → 아몬드·통깨</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="286.4" customHeight="1" s="110">
+      <c r="A6" s="185" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <b val="1"/>
+              <color rgb="001F3864"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">[양지 미역국 — 🧊냉동OK · 수요일 아침 국밥용 포함]
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">3. 양지 200g 한입크기 → 끓는 물에 데쳐 핏물·기름 빼기 → 냉장
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">4. 염장미역 1줌 반 → 물에 담가 짠기 빼고 불려 꼭 짜서
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">   한입 크기로 → 냉장
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">5. 만능육수 2L 만들어 식혀 냉장
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">   (물 2L + 국물멸치 25마리 마른팬 30초 + 다시마
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">    + 건새우 1줌 + 마른표고 2개 + 무 한토막)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <b val="1"/>
+              <color rgb="001F3864"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">[잔멸치볶음 — 칼슘]
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">6. 잔멸치 1컵 체에 쳐 가루 털고 마른팬에 살짝 볶기
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">   / 아몬드 슬라이스 준비
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <b val="1"/>
+              <color rgb="001F3864"/>
+              <sz val="12"/>
+            </rPr>
+            <t>[키즈김치] 어린이김치 통 준비</t>
+          </r>
+        </is>
+      </c>
+      <c r="B6" s="185" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <b val="1"/>
+              <color rgb="001F3864"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">[대구 탕수 — 마지막, 바로 먹을 수 있게]
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">6. 대구 3cm로 썰고 가시 확인 (5세 주의)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">7. ★ 우유 50ml에 10분 담갔다가 물기만 닦기 (비린내 제거)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">8. 소금 1/4t + 후추 + 청주 1/2T → 10분 → 키친타월로 물기 꼼꼼히
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">9. 달걀흰자 1T 버무리고 → 감자전분 약 50g 얇게 입혀 털기
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">10. 170℃ 기름에 1~2번 나눠 2~3분 (떠오를 때까지 건드리지 않기)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">    → 건져 잠깐 식혔다가 → 180℃에 30~60초 한 번 더 (바삭)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">    ※ 한 번에 많이 넣으면 기름 먹음 / 속 하얗게 익었는지 확인
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">11. 소스: 기름 1t에 채소 볶기 → 소스 붓고 끓으면
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">    전분 1/2T + 물 1T로 걸쭉하게 → 맛보고 시면 설탕 조금
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">12. ★ 튀김 위에 소스 끼얹기 (버무리면 눅눅) → 바로 식탁에
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <b val="1"/>
+              <color rgb="001F3864"/>
+              <sz val="12"/>
+            </rPr>
+            <t>[키즈김치] 접시에 / [귤]</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="70.55" customHeight="1" s="110">
+      <c r="A8" s="186" t="inlineStr">
         <is>
           <t>수 (10/28)</t>
         </is>
       </c>
-      <c r="B3" s="157" t="inlineStr">
-        <is>
-          <t>오야코동 (닭+몽글한 달걀)
-+ 두부 미소장국(칼슘)
-+ 감자채볶음
-+ 키즈김치
-+ 배 (간식)
+      <c r="B8" s="187" t="inlineStr">
+        <is>
+          <t>오야코동 (닭+몽글한 달걀) + 두부 미소장국(칼슘) + 감자채볶음 + 키즈김치 + 배 (간식)
 ※ 호평 메뉴 10주 만·새우 달걀 덮밥 방식 적용</t>
         </is>
       </c>
-      <c r="C3" s="157" t="inlineStr">
-        <is>
-          <t>[오야코동] ★호평 메뉴 — 새우 달걀 덮밥처럼 "몽글하게"
-1. 닭다리살 500g → 껍질·노란 지방 떼고 1.5cm로 작게
-   → 청주 1T + 소금 1/3t 밑간 → 냉장
-2. 양파 1개 채썰기 / 대파 송송 → 냉장
-3. 덮밥소스 한 통에: 만능육수 250ml + 간장 3T
-   + 미림 2T + 설탕 1T
-   (달걀 7개는 당일에 풀기)
-[두부 미소장국 — 칼슘]
-4. 두부 1/2모 깍둑 / 대파 / 만능육수 1L 준비
-[감자채볶음]
-5. 감자 2개 채썰어 물에 담가 전분 빼고 냉장
-[키즈김치] 통 준비</t>
-        </is>
-      </c>
-      <c r="D3" s="157" t="inlineStr">
-        <is>
-          <t>★ 식사 30분 전 시작
-[두부 미소장국 — 먼저]
-1. 육수 1L 끓이기 → 두부 넣고 3분
-2. 불 약하게 → 미소된장 2.5T 체에 풀기
-   ※ 미소는 끓이면 향 날아감, 넣고 바로 불 끄기 → 대파
-[감자채볶음]
-3. 감자채 물기 빼고 기름에 볶다 소금 → 참기름 마무리
-[오야코동 — 마지막]
-4. 넓은 팬에 덮밥소스 + 양파 → 중불 3분 (양파 투명하게)
-5. 닭 넣고 뚜껑 덮어 중약불 5~6분 → 속까지 익었는지 확인
-   ※ 닭이 작아서 금방 익음, 오래 끓이면 질겨짐
-6. ★ 달걀 7개 가볍게 풀어(흰자 덩어리 조금 남게)
-   → 2/3 먼저 둘러 붓고 뚜껑 30초
-   → 나머지 1/3 붓고 불 끄기 → 뚜껑 덮어 1분 (잔열로 몽글)
-   ※ 아이 것은 흐르지 않게 / 어른 것은 촉촉하게
-7. 밥 위에 국자로 떠 올리고 소스 조금 → 대파
-[키즈김치] 접시에 / [배] 깎아서</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="381" customHeight="1" s="110">
-      <c r="A4" s="156" t="inlineStr">
+    </row>
+    <row r="9" ht="22" customHeight="1" s="110">
+      <c r="A9" s="183" t="inlineStr">
+        <is>
+          <t>🌙 전날 밤 준비</t>
+        </is>
+      </c>
+      <c r="B9" s="183" t="inlineStr">
+        <is>
+          <t>🔥 당일 조리</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="373.4" customHeight="1" s="110">
+      <c r="A10" s="188" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <b val="1"/>
+              <color rgb="001F3864"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">[오야코동] ★호평 메뉴 — 새우 달걀 덮밥처럼 "몽글하게"
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">1. 닭다리살 500g → 껍질·노란 지방 떼고 1.5cm로 작게
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">   → 청주 1T + 소금 1/3t 밑간 → 냉장
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">2. 양파 1개 채썰기 / 대파 송송 → 냉장
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">3. 덮밥소스 한 통에: 만능육수 250ml + 간장 3T
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">   + 미림 2T + 설탕 1T
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">   (달걀 7개는 당일에 풀기)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <b val="1"/>
+              <color rgb="001F3864"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">[두부 미소장국 — 칼슘]
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">4. 두부 1/2모 깍둑 / 대파 / 만능육수 1L 준비
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <b val="1"/>
+              <color rgb="001F3864"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">[감자채볶음]
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">5. 감자 2개 채썰어 물에 담가 전분 빼고 냉장
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <b val="1"/>
+              <color rgb="001F3864"/>
+              <sz val="12"/>
+            </rPr>
+            <t>[키즈김치] 통 준비</t>
+          </r>
+        </is>
+      </c>
+      <c r="B10" s="188" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <b val="1"/>
+              <color rgb="001F3864"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">★ 식사 30분 전 시작
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <b val="1"/>
+              <color rgb="001F3864"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">[두부 미소장국 — 먼저]
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">1. 육수 1L 끓이기 → 두부 넣고 3분
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">2. 불 약하게 → 미소된장 2.5T 체에 풀기
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">   ※ 미소는 끓이면 향 날아감, 넣고 바로 불 끄기 → 대파
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <b val="1"/>
+              <color rgb="001F3864"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">[감자채볶음]
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">3. 감자채 물기 빼고 기름에 볶다 소금 → 참기름 마무리
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <b val="1"/>
+              <color rgb="001F3864"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">[오야코동 — 마지막]
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">4. 넓은 팬에 덮밥소스 + 양파 → 중불 3분 (양파 투명하게)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">5. 닭 넣고 뚜껑 덮어 중약불 5~6분 → 속까지 익었는지 확인
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">   ※ 닭이 작아서 금방 익음, 오래 끓이면 질겨짐
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">6. ★ 달걀 7개 가볍게 풀어(흰자 덩어리 조금 남게)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">   → 2/3 먼저 둘러 붓고 뚜껑 30초
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">   → 나머지 1/3 붓고 불 끄기 → 뚜껑 덮어 1분 (잔열로 몽글)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">   ※ 아이 것은 흐르지 않게 / 어른 것은 촉촉하게
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">7. 밥 위에 국자로 떠 올리고 소스 조금 → 대파
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <b val="1"/>
+              <color rgb="001F3864"/>
+              <sz val="12"/>
+            </rPr>
+            <t>[키즈김치] 접시에 / [배] 깎아서</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="70.55" customHeight="1" s="110">
+      <c r="A12" s="189" t="inlineStr">
         <is>
           <t>금 (10/30)</t>
         </is>
       </c>
-      <c r="B4" s="157" t="inlineStr">
-        <is>
-          <t>돼지고기 미트볼 토마토 파스타
-+ 옥수수 스프
-+ 키즈김치
-+ 단감 (간식)
+      <c r="B12" s="190" t="inlineStr">
+        <is>
+          <t>돼지고기 미트볼 토마토 파스타 + 옥수수 스프 + 키즈김치 + 단감 (간식)
 ※ 이갈이 S등급·신메뉴·치즈주1회(칼슘)</t>
         </is>
       </c>
-      <c r="C4" s="157" t="inlineStr">
-        <is>
-          <t>※ 돼지 다짐육: 월요일 주문분 → 받자마자 냉동,
-  목요일 아침 냉장실로 옮겨 해동
-[미트볼 토마토 파스타] ★신메뉴 — S등급(부드러운 미트볼)
-   (검증: 만개의레시피·DELISH KITCHEN 등 4곳)
-1. 빵가루 6T + 우유 5T 5분 불리기 + 두부 100g
-   (면보로 꼭 짜서 으깨기) → 섞기 (촉촉함의 핵심)
-2. 양파 1/2개 다져 전자레인지 1분 → 식히기
-3. 볼에 돼지 다짐육 500g + ①② + 달걀 1개
-   + 소금 3/4t + 후추 + 드라이 바질 1/2t + 파마산 3T(선택)
-   → 한 방향으로 점성 생길 때까지만 섞기
-   ※ 오래 치대면 단단해짐
-4. 지름 2.5~3cm로 빚어 접시에 한 겹 → 랩 → 냉장 맨 아래 칸
-   ※ 날고기 반죽은 24시간 내 사용
-[옥수수 스프]
-5. 양파 1/2개 채썰기 / 스위트콘 1캔(약 300g) 물 빼서 냉장
-[키즈김치] 통 준비</t>
-        </is>
-      </c>
-      <c r="D4" s="157" t="inlineStr">
-        <is>
-          <t>★ 식사 40분 전 시작
-[미트볼 — 굽기] (팬 또는 에어프라이어)
-1. 스텐팬 중불 예열(물방울 테스트) + 기름 2T
-   → 2번에 나눠 굽기, 처음 1~2분 건드리지 않기
-   (겉이 익으면 저절로 떨어짐) → 겉만 갈색이면 OK
-   ※ 에어프라이어: 180℃ 8분 → 뒤집어 3~4분
-2. 같은 팬에 순한 토마토소스 500g + 토마토 페이스트 1T
-   + 물 100ml + 설탕 1t → 미트볼 넣고 뚜껑, 약불 15분
-   (에어프라이어로 구웠으면 5~10분 더 끓이기)
-[옥수수 스프 — 미트볼 끓는 동안]
-3. 올리브유 1t에 양파 투명하게 → 콘 + 물 250ml 5분
-4. 믹서로 곱게 → 아이용은 체에 한 번 거르기
-5. 냄비에 우유 400ml 넣고 약불로 데우기 (끓어 넘치지 않게)
-   → 소금 1/3t, 필요하면 설탕 한 꼬집
-[파스타]
-6. 물 3L + 소금 1.5T, 펜네 400g → 포장 시간보다 1분 덜
-7. 면을 소스 팬에 넣고 모짜렐라 100g과 2~3분 섞기
-   (되직하면 면수 조금)
-8. 남은 모짜렐라 50g 올리고 뚜껑 덮어 녹이기
-   ※ 미트볼 하나 잘라 속 익었는지 확인
-[키즈김치] 접시에 / [단감] 깎아서</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="171" customHeight="1" s="110">
-      <c r="A5" s="156" t="inlineStr">
+    </row>
+    <row r="13" ht="22" customHeight="1" s="110">
+      <c r="A13" s="183" t="inlineStr">
+        <is>
+          <t>🌙 전날 밤 준비</t>
+        </is>
+      </c>
+      <c r="B13" s="183" t="inlineStr">
+        <is>
+          <t>🔥 당일 조리</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="408.2" customHeight="1" s="110">
+      <c r="A14" s="184" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">※ 돼지 다짐육: 월요일 주문분 → 받자마자 냉동,
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">  목요일 아침 냉장실로 옮겨 해동
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <b val="1"/>
+              <color rgb="001F3864"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">[미트볼 토마토 파스타] ★신메뉴 — S등급(부드러운 미트볼)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">   (검증: 만개의레시피·DELISH KITCHEN 등 4곳)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">1. 빵가루 6T + 우유 5T 5분 불리기 + 두부 100g
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">   (면보로 꼭 짜서 으깨기) → 섞기 (촉촉함의 핵심)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">2. 양파 1/2개 다져 전자레인지 1분 → 식히기
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">3. 볼에 돼지 다짐육 500g + ①② + 달걀 1개
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">   + 소금 3/4t + 후추 + 드라이 바질 1/2t + 파마산 3T(선택)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">   → 한 방향으로 점성 생길 때까지만 섞기
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">   ※ 오래 치대면 단단해짐
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">4. 지름 2.5~3cm로 빚어 접시에 한 겹 → 랩 → 냉장 맨 아래 칸
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">   ※ 날고기 반죽은 24시간 내 사용
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <b val="1"/>
+              <color rgb="001F3864"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">[옥수수 스프]
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">5. 양파 1/2개 채썰기 / 스위트콘 1캔(약 300g) 물 빼서 냉장
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <b val="1"/>
+              <color rgb="001F3864"/>
+              <sz val="12"/>
+            </rPr>
+            <t>[키즈김치] 통 준비</t>
+          </r>
+        </is>
+      </c>
+      <c r="B14" s="184" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <b val="1"/>
+              <color rgb="001F3864"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">★ 식사 40분 전 시작
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <b val="1"/>
+              <color rgb="001F3864"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">[미트볼 — 굽기] (팬 또는 에어프라이어)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">1. 스텐팬 중불 예열(물방울 테스트) + 기름 2T
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">   → 2번에 나눠 굽기, 처음 1~2분 건드리지 않기
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">   (겉이 익으면 저절로 떨어짐) → 겉만 갈색이면 OK
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">   ※ 에어프라이어: 180℃ 8분 → 뒤집어 3~4분
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">2. 같은 팬에 순한 토마토소스 500g + 토마토 페이스트 1T
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">   + 물 100ml + 설탕 1t → 미트볼 넣고 뚜껑, 약불 15분
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">   (에어프라이어로 구웠으면 5~10분 더 끓이기)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <b val="1"/>
+              <color rgb="001F3864"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">[옥수수 스프 — 미트볼 끓는 동안]
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">3. 올리브유 1t에 양파 투명하게 → 콘 + 물 250ml 5분
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">4. 믹서로 곱게 → 아이용은 체에 한 번 거르기
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">5. 냄비에 우유 400ml 넣고 약불로 데우기 (끓어 넘치지 않게)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">   → 소금 1/3t, 필요하면 설탕 한 꼬집
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <b val="1"/>
+              <color rgb="001F3864"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">[파스타]
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">6. 물 3L + 소금 1.5T, 펜네 400g → 포장 시간보다 1분 덜
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">7. 면을 소스 팬에 넣고 모짜렐라 100g과 2~3분 섞기
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">   (되직하면 면수 조금)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">8. 남은 모짜렐라 50g 올리고 뚜껑 덮어 녹이기
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">   ※ 미트볼 하나 잘라 속 익었는지 확인</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="25.4" customHeight="1" s="110">
+      <c r="A15" s="185" t="inlineStr"/>
+      <c r="B15" s="185" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <b val="1"/>
+              <color rgb="001F3864"/>
+              <sz val="12"/>
+            </rPr>
+            <t>[키즈김치] 접시에 / [단감] 깎아서</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="70.55" customHeight="1" s="110">
+      <c r="A17" s="191" t="inlineStr">
         <is>
           <t>아침 (수·토·일)</t>
         </is>
       </c>
-      <c r="B5" s="157" t="inlineStr">
-        <is>
-          <t>🌅 아침 (장모님 오시는 주)
-수: 미역국 국밥
-토: 그릭요거트+그래놀라
-일: 고구마밥
+      <c r="B17" s="192" t="inlineStr">
+        <is>
+          <t>🌅 아침 (장모님 오시는 주) + 수: 미역국 국밥 + 토: 그릭요거트+그래놀라 + 일: 고구마밥
 ※ 월·화·목·금은 장모님</t>
         </is>
       </c>
-      <c r="C5" s="157" t="inlineStr">
-        <is>
-          <t>[화 밤] 미역국 1/3 덜어 냉장 (수 아침용)
-         + 남은 밥 1시간 내 식혀 냉장
-[금 밤] 과일 씻어 두기 (토 아침 꺼내기만)
-[토 밤] 쌀 씻어 안치고 고구마 1개(지난주 남은 것) 깍둑썰어
-         올려 예약취사 (일 아침 시간에 맞춰)
-         ※ 고구마 없으면 일요일은 시리얼+우유+과일
-         ※ 날고기·달걀은 예약취사에 넣지 않기
-※ 월·목 밤 "내일 아침 국 있나?" 확인
-   → 없으면 냉동 국팩(🧊) 언 채로 냄비 + 물 100ml</t>
-        </is>
-      </c>
-      <c r="D5" s="157" t="inlineStr">
-        <is>
-          <t>[수 아침 — 국밥, 냄비 하나 5분]
-1. 미역국 먹을 만큼 냄비에 → 팔팔 끓으면 찬밥 2분
-2. 달걀 1~2개 풀어 30초
-3. 키즈김치 · 김 · 우유 1컵
-※ 아이 그릇은 국물 반, 건더기·밥 위주
-[토 아침 — 꺼내기만]
-4. 그릭요거트 + 그래놀라 + 과일(귤·단감 등) + 우유
-[일 아침 — 데울 것 없음]
-5. 고구마밥 퍼서 김 · 키즈김치 · 우유 1컵</t>
+    </row>
+    <row r="18" ht="22" customHeight="1" s="110">
+      <c r="A18" s="183" t="inlineStr">
+        <is>
+          <t>🌙 전날 밤 준비</t>
+        </is>
+      </c>
+      <c r="B18" s="183" t="inlineStr">
+        <is>
+          <t>🔥 당일 조리</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="234.2" customHeight="1" s="110">
+      <c r="A19" s="188" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <b val="1"/>
+              <color rgb="001F3864"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">[화 밤] 미역국 1/3 덜어 냉장 (수 아침용)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">         + 남은 밥 1시간 내 식혀 냉장
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <b val="1"/>
+              <color rgb="001F3864"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">[금 밤] 과일 씻어 두기 (토 아침 꺼내기만)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <b val="1"/>
+              <color rgb="001F3864"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">[토 밤] 쌀 씻어 안치고 고구마 1개(지난주 남은 것) 깍둑썰어
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">         올려 예약취사 (일 아침 시간에 맞춰)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">         ※ 고구마 없으면 일요일은 시리얼+우유+과일
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">         ※ 날고기·달걀은 예약취사에 넣지 않기
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">※ 월·목 밤 "내일 아침 국 있나?" 확인
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">   → 없으면 냉동 국팩(🧊) 언 채로 냄비 + 물 100ml</t>
+          </r>
+        </is>
+      </c>
+      <c r="B19" s="188" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <b val="1"/>
+              <color rgb="001F3864"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">[수 아침 — 국밥, 냄비 하나 5분]
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">1. 미역국 먹을 만큼 냄비에 → 팔팔 끓으면 찬밥 2분
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">2. 달걀 1~2개 풀어 30초
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">3. 키즈김치 · 김 · 우유 1컵
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">※ 아이 그릇은 국물 반, 건더기·밥 위주
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <b val="1"/>
+              <color rgb="001F3864"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">[토 아침 — 꺼내기만]
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">4. 그릭요거트 + 그래놀라 + 과일(귤·단감 등) + 우유
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <b val="1"/>
+              <color rgb="001F3864"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">[일 아침 — 데울 것 없음]
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t>5. 고구마밥 퍼서 김 · 키즈김치 · 우유 1컵</t>
+          </r>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -6210,49 +7558,49 @@
   <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="27" customWidth="1" style="110" min="1" max="1"/>
-    <col width="22" customWidth="1" style="110" min="2" max="2"/>
-    <col width="26" customWidth="1" style="110" min="3" max="3"/>
-    <col width="18" customWidth="1" style="110" min="4" max="4"/>
-    <col width="14" customWidth="1" style="110" min="5" max="5"/>
+    <col width="34" customWidth="1" style="110" min="1" max="1"/>
+    <col width="28" customWidth="1" style="110" min="2" max="2"/>
+    <col width="32" customWidth="1" style="110" min="3" max="3"/>
+    <col width="20" customWidth="1" style="110" min="4" max="4"/>
+    <col width="15" customWidth="1" style="110" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" s="110">
-      <c r="A1" s="158" t="inlineStr">
+    <row r="1" ht="30" customHeight="1" s="110">
+      <c r="A1" s="193" t="inlineStr">
         <is>
           <t>10월 5주차 장보기 (10/27~10/30) — 10/26 컬리 장바구니 19개 · 114,270원</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="155" t="inlineStr">
+    <row r="2" ht="26" customHeight="1" s="110">
+      <c r="A2" s="194" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B2" s="155" t="inlineStr">
+      <c r="B2" s="194" t="inlineStr">
         <is>
           <t>수량</t>
         </is>
       </c>
-      <c r="C2" s="155" t="inlineStr">
+      <c r="C2" s="194" t="inlineStr">
         <is>
           <t>사용 메뉴</t>
         </is>
       </c>
-      <c r="D2" s="155" t="inlineStr">
+      <c r="D2" s="194" t="inlineStr">
         <is>
           <t>구매 시기</t>
         </is>
       </c>
-      <c r="E2" s="155" t="inlineStr">
+      <c r="E2" s="194" t="inlineStr">
         <is>
           <t>예상 금액</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="159" t="inlineStr">
+    <row r="3" ht="24" customHeight="1" s="110">
+      <c r="A3" s="195" t="inlineStr">
         <is>
           <t>정육</t>
         </is>
@@ -6262,83 +7610,83 @@
       <c r="D3" s="160" t="n"/>
       <c r="E3" s="160" t="n"/>
     </row>
-    <row r="4">
-      <c r="A4" s="161" t="inlineStr">
+    <row r="4" ht="25.4" customHeight="1" s="110">
+      <c r="A4" s="196" t="inlineStr">
         <is>
           <t>소고기 양지 국거리</t>
         </is>
       </c>
-      <c r="B4" s="161" t="inlineStr">
+      <c r="B4" s="196" t="inlineStr">
         <is>
           <t>200g</t>
         </is>
       </c>
-      <c r="C4" s="161" t="inlineStr">
+      <c r="C4" s="196" t="inlineStr">
         <is>
           <t>화 미역국</t>
         </is>
       </c>
-      <c r="D4" s="161" t="inlineStr">
+      <c r="D4" s="196" t="inlineStr">
         <is>
           <t>10/25 컬리 담음</t>
         </is>
       </c>
-      <c r="E4" s="162" t="n">
+      <c r="E4" s="197" t="n">
         <v>10280</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="161" t="inlineStr">
+    <row r="5" ht="42.8" customHeight="1" s="110">
+      <c r="A5" s="196" t="inlineStr">
         <is>
           <t>닭다리살 정육</t>
         </is>
       </c>
-      <c r="B5" s="161" t="inlineStr">
+      <c r="B5" s="196" t="inlineStr">
         <is>
           <t>500g (무항생제) — 레시피 600g → 500g로</t>
         </is>
       </c>
-      <c r="C5" s="161" t="inlineStr">
+      <c r="C5" s="196" t="inlineStr">
         <is>
           <t>수 오야코동</t>
         </is>
       </c>
-      <c r="D5" s="161" t="inlineStr">
+      <c r="D5" s="196" t="inlineStr">
         <is>
           <t>10/25 컬리 담음</t>
         </is>
       </c>
-      <c r="E5" s="162" t="n">
+      <c r="E5" s="197" t="n">
         <v>10170</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="161" t="inlineStr">
+    <row r="6" ht="42.8" customHeight="1" s="110">
+      <c r="A6" s="196" t="inlineStr">
         <is>
           <t>돼지 다짐육 (앞다리)</t>
         </is>
       </c>
-      <c r="B6" s="161" t="inlineStr">
+      <c r="B6" s="196" t="inlineStr">
         <is>
           <t>600g (한돈) — 받자마자 냉동</t>
         </is>
       </c>
-      <c r="C6" s="161" t="inlineStr">
+      <c r="C6" s="196" t="inlineStr">
         <is>
           <t>금 미트볼</t>
         </is>
       </c>
-      <c r="D6" s="161" t="inlineStr">
+      <c r="D6" s="196" t="inlineStr">
         <is>
           <t>10/25 컬리 담음</t>
         </is>
       </c>
-      <c r="E6" s="162" t="n">
+      <c r="E6" s="197" t="n">
         <v>7790</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="163" t="inlineStr">
+    <row r="7" ht="24" customHeight="1" s="110">
+      <c r="A7" s="198" t="inlineStr">
         <is>
           <t>수산</t>
         </is>
@@ -6348,83 +7696,83 @@
       <c r="D7" s="164" t="n"/>
       <c r="E7" s="164" t="n"/>
     </row>
-    <row r="8">
-      <c r="A8" s="161" t="inlineStr">
+    <row r="8" ht="42.8" customHeight="1" s="110">
+      <c r="A8" s="196" t="inlineStr">
         <is>
           <t>대구 순살 (냉동)</t>
         </is>
       </c>
-      <c r="B8" s="161" t="inlineStr">
+      <c r="B8" s="196" t="inlineStr">
         <is>
           <t>300g (아이용) — 화 아침 냉장 해동</t>
         </is>
       </c>
-      <c r="C8" s="161" t="inlineStr">
+      <c r="C8" s="196" t="inlineStr">
         <is>
           <t>화 대구 탕수</t>
         </is>
       </c>
-      <c r="D8" s="161" t="inlineStr">
+      <c r="D8" s="196" t="inlineStr">
         <is>
           <t>10/25 컬리 담음</t>
         </is>
       </c>
-      <c r="E8" s="162" t="n">
+      <c r="E8" s="197" t="n">
         <v>17900</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="161" t="inlineStr">
+    <row r="9" ht="25.4" customHeight="1" s="110">
+      <c r="A9" s="196" t="inlineStr">
         <is>
           <t>염장 미역</t>
         </is>
       </c>
-      <c r="B9" s="161" t="inlineStr">
+      <c r="B9" s="196" t="inlineStr">
         <is>
           <t>200g</t>
         </is>
       </c>
-      <c r="C9" s="161" t="inlineStr">
+      <c r="C9" s="196" t="inlineStr">
         <is>
           <t>화 미역국</t>
         </is>
       </c>
-      <c r="D9" s="161" t="inlineStr">
+      <c r="D9" s="196" t="inlineStr">
         <is>
           <t>10/25 컬리 담음</t>
         </is>
       </c>
-      <c r="E9" s="162" t="n">
+      <c r="E9" s="197" t="n">
         <v>2290</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="161" t="inlineStr">
+    <row r="10" ht="25.4" customHeight="1" s="110">
+      <c r="A10" s="196" t="inlineStr">
         <is>
           <t>잔멸치</t>
         </is>
       </c>
-      <c r="B10" s="161" t="inlineStr">
+      <c r="B10" s="196" t="inlineStr">
         <is>
           <t>보유분 확인 (1컵 필요)</t>
         </is>
       </c>
-      <c r="C10" s="161" t="inlineStr">
+      <c r="C10" s="196" t="inlineStr">
         <is>
           <t>화 잔멸치볶음</t>
         </is>
       </c>
-      <c r="D10" s="161" t="inlineStr">
+      <c r="D10" s="196" t="inlineStr">
         <is>
           <t>보유 확인</t>
         </is>
       </c>
-      <c r="E10" s="162" t="n">
+      <c r="E10" s="197" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="165" t="inlineStr">
+    <row r="11" ht="24" customHeight="1" s="110">
+      <c r="A11" s="199" t="inlineStr">
         <is>
           <t>채소</t>
         </is>
@@ -6434,133 +7782,133 @@
       <c r="D11" s="166" t="n"/>
       <c r="E11" s="166" t="n"/>
     </row>
-    <row r="12">
-      <c r="A12" s="161" t="inlineStr">
+    <row r="12" ht="42.8" customHeight="1" s="110">
+      <c r="A12" s="196" t="inlineStr">
         <is>
           <t>양파</t>
         </is>
       </c>
-      <c r="B12" s="161" t="inlineStr">
+      <c r="B12" s="196" t="inlineStr">
         <is>
           <t>1.5kg</t>
         </is>
       </c>
-      <c r="C12" s="161" t="inlineStr">
+      <c r="C12" s="196" t="inlineStr">
         <is>
           <t>화 탕수·수 오야코동·금 미트볼/스프</t>
         </is>
       </c>
-      <c r="D12" s="161" t="inlineStr">
+      <c r="D12" s="196" t="inlineStr">
         <is>
           <t>10/25 컬리 담음</t>
         </is>
       </c>
-      <c r="E12" s="162" t="n">
+      <c r="E12" s="197" t="n">
         <v>3990</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="161" t="inlineStr">
+    <row r="13" ht="25.4" customHeight="1" s="110">
+      <c r="A13" s="196" t="inlineStr">
         <is>
           <t>당근</t>
         </is>
       </c>
-      <c r="B13" s="161" t="inlineStr">
+      <c r="B13" s="196" t="inlineStr">
         <is>
           <t>1개</t>
         </is>
       </c>
-      <c r="C13" s="161" t="inlineStr">
+      <c r="C13" s="196" t="inlineStr">
         <is>
           <t>화 탕수 소스</t>
         </is>
       </c>
-      <c r="D13" s="161" t="inlineStr">
+      <c r="D13" s="196" t="inlineStr">
         <is>
           <t>10/25 컬리 담음</t>
         </is>
       </c>
-      <c r="E13" s="162" t="n">
+      <c r="E13" s="197" t="n">
         <v>2290</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="161" t="inlineStr">
+    <row r="14" ht="25.4" customHeight="1" s="110">
+      <c r="A14" s="196" t="inlineStr">
         <is>
           <t>오이</t>
         </is>
       </c>
-      <c r="B14" s="161" t="inlineStr">
+      <c r="B14" s="196" t="inlineStr">
         <is>
           <t>다다기 5입</t>
         </is>
       </c>
-      <c r="C14" s="161" t="inlineStr">
+      <c r="C14" s="196" t="inlineStr">
         <is>
           <t>화 탕수 소스</t>
         </is>
       </c>
-      <c r="D14" s="161" t="inlineStr">
+      <c r="D14" s="196" t="inlineStr">
         <is>
           <t>10/25 컬리 담음</t>
         </is>
       </c>
-      <c r="E14" s="162" t="n">
+      <c r="E14" s="197" t="n">
         <v>2990</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="161" t="inlineStr">
+    <row r="15" ht="25.4" customHeight="1" s="110">
+      <c r="A15" s="196" t="inlineStr">
         <is>
           <t>감자</t>
         </is>
       </c>
-      <c r="B15" s="161" t="inlineStr">
+      <c r="B15" s="196" t="inlineStr">
         <is>
           <t>600g</t>
         </is>
       </c>
-      <c r="C15" s="161" t="inlineStr">
+      <c r="C15" s="196" t="inlineStr">
         <is>
           <t>수 감자채볶음</t>
         </is>
       </c>
-      <c r="D15" s="161" t="inlineStr">
+      <c r="D15" s="196" t="inlineStr">
         <is>
           <t>10/25 컬리 담음</t>
         </is>
       </c>
-      <c r="E15" s="162" t="n">
+      <c r="E15" s="197" t="n">
         <v>4290</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="161" t="inlineStr">
+    <row r="16" ht="25.4" customHeight="1" s="110">
+      <c r="A16" s="196" t="inlineStr">
         <is>
           <t>대파</t>
         </is>
       </c>
-      <c r="B16" s="161" t="inlineStr">
+      <c r="B16" s="196" t="inlineStr">
         <is>
           <t>보유분 확인 (지난주 1단)</t>
         </is>
       </c>
-      <c r="C16" s="161" t="inlineStr">
+      <c r="C16" s="196" t="inlineStr">
         <is>
           <t>전반</t>
         </is>
       </c>
-      <c r="D16" s="161" t="inlineStr">
+      <c r="D16" s="196" t="inlineStr">
         <is>
           <t>보유 확인</t>
         </is>
       </c>
-      <c r="E16" s="162" t="n">
+      <c r="E16" s="197" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="178" t="inlineStr">
+    <row r="17" ht="24" customHeight="1" s="110">
+      <c r="A17" s="200" t="inlineStr">
         <is>
           <t>두부류</t>
         </is>
@@ -6570,33 +7918,33 @@
       <c r="D17" s="179" t="n"/>
       <c r="E17" s="179" t="n"/>
     </row>
-    <row r="18">
-      <c r="A18" s="161" t="inlineStr">
+    <row r="18" ht="25.4" customHeight="1" s="110">
+      <c r="A18" s="196" t="inlineStr">
         <is>
           <t>두부</t>
         </is>
       </c>
-      <c r="B18" s="161" t="inlineStr">
+      <c r="B18" s="196" t="inlineStr">
         <is>
           <t>부침두부 380g</t>
         </is>
       </c>
-      <c r="C18" s="161" t="inlineStr">
+      <c r="C18" s="196" t="inlineStr">
         <is>
           <t>수 미소장국·금 미트볼</t>
         </is>
       </c>
-      <c r="D18" s="161" t="inlineStr">
+      <c r="D18" s="196" t="inlineStr">
         <is>
           <t>10/25 컬리 담음</t>
         </is>
       </c>
-      <c r="E18" s="162" t="n">
+      <c r="E18" s="197" t="n">
         <v>1620</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="167" t="inlineStr">
+    <row r="19" ht="24" customHeight="1" s="110">
+      <c r="A19" s="201" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
@@ -6606,449 +7954,445 @@
       <c r="D19" s="168" t="n"/>
       <c r="E19" s="168" t="n"/>
     </row>
-    <row r="20">
-      <c r="A20" s="161" t="inlineStr">
+    <row r="20" ht="42.8" customHeight="1" s="110">
+      <c r="A20" s="196" t="inlineStr">
         <is>
           <t>달걀</t>
         </is>
       </c>
-      <c r="B20" s="161" t="inlineStr">
+      <c r="B20" s="196" t="inlineStr">
         <is>
           <t>10구</t>
         </is>
       </c>
-      <c r="C20" s="161" t="inlineStr">
+      <c r="C20" s="196" t="inlineStr">
         <is>
           <t>수 오야코동·화 탕수·금 미트볼·아침</t>
         </is>
       </c>
-      <c r="D20" s="161" t="inlineStr">
+      <c r="D20" s="196" t="inlineStr">
         <is>
           <t>10/25 컬리 담음</t>
         </is>
       </c>
-      <c r="E20" s="162" t="n">
+      <c r="E20" s="197" t="n">
         <v>3980</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="161" t="inlineStr">
+    <row r="21" ht="25.4" customHeight="1" s="110">
+      <c r="A21" s="196" t="inlineStr">
         <is>
           <t>펜네</t>
         </is>
       </c>
-      <c r="B21" s="161" t="inlineStr">
+      <c r="B21" s="196" t="inlineStr">
         <is>
           <t>데체코 500g</t>
         </is>
       </c>
-      <c r="C21" s="161" t="inlineStr">
+      <c r="C21" s="196" t="inlineStr">
         <is>
           <t>금 파스타</t>
         </is>
       </c>
-      <c r="D21" s="161" t="inlineStr">
+      <c r="D21" s="196" t="inlineStr">
         <is>
           <t>10/25 컬리 담음</t>
         </is>
       </c>
-      <c r="E21" s="162" t="n">
+      <c r="E21" s="197" t="n">
         <v>5480</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="161" t="inlineStr">
+    <row r="22" ht="25.4" customHeight="1" s="110">
+      <c r="A22" s="196" t="inlineStr">
         <is>
           <t>토마토 파스타소스 (순한맛)</t>
         </is>
       </c>
-      <c r="B22" s="161" t="inlineStr">
+      <c r="B22" s="196" t="inlineStr">
         <is>
           <t>폰타나 뽀모도로 600g</t>
         </is>
       </c>
-      <c r="C22" s="161" t="inlineStr">
+      <c r="C22" s="196" t="inlineStr">
         <is>
           <t>금 파스타</t>
         </is>
       </c>
-      <c r="D22" s="161" t="inlineStr">
+      <c r="D22" s="196" t="inlineStr">
         <is>
           <t>10/25 컬리 담음</t>
         </is>
       </c>
-      <c r="E22" s="162" t="n">
+      <c r="E22" s="197" t="n">
         <v>7480</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="161" t="inlineStr">
+    <row r="23" ht="25.4" customHeight="1" s="110">
+      <c r="A23" s="196" t="inlineStr">
         <is>
           <t>모짜렐라 치즈</t>
         </is>
       </c>
-      <c r="B23" s="161" t="inlineStr">
+      <c r="B23" s="196" t="inlineStr">
         <is>
           <t>226g</t>
         </is>
       </c>
-      <c r="C23" s="161" t="inlineStr">
+      <c r="C23" s="196" t="inlineStr">
         <is>
           <t>금 파스타(칼슘)</t>
         </is>
       </c>
-      <c r="D23" s="161" t="inlineStr">
+      <c r="D23" s="196" t="inlineStr">
         <is>
           <t>10/25 컬리 담음</t>
         </is>
       </c>
-      <c r="E23" s="162" t="n">
+      <c r="E23" s="197" t="n">
         <v>9980</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="161" t="inlineStr">
+    <row r="24" ht="42.8" customHeight="1" s="110">
+      <c r="A24" s="196" t="inlineStr">
         <is>
           <t>스위트콘 통조림</t>
         </is>
       </c>
-      <c r="B24" s="161" t="inlineStr">
+      <c r="B24" s="196" t="inlineStr">
         <is>
           <t>1캔 (스프용) — 일 아침은 고구마밥 등으로</t>
         </is>
       </c>
-      <c r="C24" s="161" t="inlineStr">
+      <c r="C24" s="196" t="inlineStr">
         <is>
           <t>금 옥수수 스프·일 아침 옥수수밥</t>
         </is>
       </c>
-      <c r="D24" s="161" t="inlineStr">
+      <c r="D24" s="196" t="inlineStr">
         <is>
           <t>10/25 컬리 담음</t>
         </is>
       </c>
-      <c r="E24" s="162" t="n">
+      <c r="E24" s="197" t="n">
         <v>2280</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="161" t="inlineStr">
+    <row r="25" ht="25.4" customHeight="1" s="110">
+      <c r="A25" s="196" t="inlineStr">
         <is>
           <t>우유</t>
         </is>
       </c>
-      <c r="B25" s="161" t="inlineStr">
+      <c r="B25" s="196" t="inlineStr">
         <is>
           <t>1L × 2</t>
         </is>
       </c>
-      <c r="C25" s="161" t="inlineStr">
+      <c r="C25" s="196" t="inlineStr">
         <is>
           <t>금 미트볼·스프 / 아침</t>
         </is>
       </c>
-      <c r="D25" s="161" t="inlineStr">
+      <c r="D25" s="196" t="inlineStr">
         <is>
           <t>10/25 컬리 담음</t>
         </is>
       </c>
-      <c r="E25" s="162" t="n">
+      <c r="E25" s="197" t="n">
         <v>5960</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="161" t="inlineStr">
+    <row r="26" ht="25.4" customHeight="1" s="110">
+      <c r="A26" s="196" t="inlineStr">
         <is>
           <t>감자전분</t>
         </is>
       </c>
-      <c r="B26" s="161" t="inlineStr">
+      <c r="B26" s="196" t="inlineStr">
         <is>
           <t>400g (찹쌀가루 소량 혼합)</t>
         </is>
       </c>
-      <c r="C26" s="161" t="inlineStr">
+      <c r="C26" s="196" t="inlineStr">
         <is>
           <t>화 탕수</t>
         </is>
       </c>
-      <c r="D26" s="161" t="inlineStr">
+      <c r="D26" s="196" t="inlineStr">
         <is>
           <t>10/25 컬리 담음</t>
         </is>
       </c>
-      <c r="E26" s="162" t="n">
+      <c r="E26" s="197" t="n">
         <v>5080</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="161" t="inlineStr">
+    <row r="27" ht="25.4" customHeight="1" s="110">
+      <c r="A27" s="196" t="inlineStr">
         <is>
           <t>그릭요거트</t>
         </is>
       </c>
-      <c r="B27" s="161" t="inlineStr">
+      <c r="B27" s="196" t="inlineStr">
         <is>
           <t>무가당 400g</t>
         </is>
       </c>
-      <c r="C27" s="161" t="inlineStr">
+      <c r="C27" s="196" t="inlineStr">
         <is>
           <t>토 아침</t>
         </is>
       </c>
-      <c r="D27" s="161" t="inlineStr">
+      <c r="D27" s="196" t="inlineStr">
         <is>
           <t>10/25 컬리 담음</t>
         </is>
       </c>
-      <c r="E27" s="162" t="n">
+      <c r="E27" s="197" t="n">
         <v>3790</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="161" t="inlineStr">
+    <row r="28" ht="25.4" customHeight="1" s="110">
+      <c r="A28" s="196" t="inlineStr">
         <is>
           <t>그래놀라</t>
         </is>
       </c>
-      <c r="B28" s="161" t="inlineStr">
+      <c r="B28" s="196" t="inlineStr">
         <is>
           <t>저당 360g</t>
         </is>
       </c>
-      <c r="C28" s="161" t="inlineStr">
+      <c r="C28" s="196" t="inlineStr">
         <is>
           <t>토 아침</t>
         </is>
       </c>
-      <c r="D28" s="161" t="inlineStr">
+      <c r="D28" s="196" t="inlineStr">
         <is>
           <t>10/25 컬리 담음</t>
         </is>
       </c>
-      <c r="E28" s="162" t="n">
+      <c r="E28" s="197" t="n">
         <v>6630</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="161" t="inlineStr">
+    <row r="29" ht="42.8" customHeight="1" s="110">
+      <c r="A29" s="196" t="inlineStr">
         <is>
           <t>귤</t>
         </is>
       </c>
-      <c r="B29" s="161" t="inlineStr">
+      <c r="B29" s="196" t="inlineStr">
         <is>
           <t>장바구니에서 뺌 (보유분 사용)</t>
         </is>
       </c>
-      <c r="C29" s="161" t="inlineStr">
+      <c r="C29" s="196" t="inlineStr">
         <is>
           <t>화 간식·아침</t>
         </is>
       </c>
-      <c r="D29" s="161" t="inlineStr">
+      <c r="D29" s="196" t="inlineStr">
         <is>
           <t>제외</t>
         </is>
       </c>
-      <c r="E29" s="162" t="n">
+      <c r="E29" s="197" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="161" t="inlineStr">
+    <row r="30" ht="42.8" customHeight="1" s="110">
+      <c r="A30" s="196" t="inlineStr">
         <is>
           <t>배</t>
         </is>
       </c>
-      <c r="B30" s="161" t="inlineStr">
+      <c r="B30" s="196" t="inlineStr">
         <is>
           <t>장바구니에서 뺌 (보유분 사용)</t>
         </is>
       </c>
-      <c r="C30" s="161" t="inlineStr">
+      <c r="C30" s="196" t="inlineStr">
         <is>
           <t>수 간식</t>
         </is>
       </c>
-      <c r="D30" s="161" t="inlineStr">
+      <c r="D30" s="196" t="inlineStr">
         <is>
           <t>제외</t>
         </is>
       </c>
-      <c r="E30" s="162" t="n">
+      <c r="E30" s="197" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="161" t="inlineStr">
+    <row r="31" ht="42.8" customHeight="1" s="110">
+      <c r="A31" s="196" t="inlineStr">
         <is>
           <t>단감</t>
         </is>
       </c>
-      <c r="B31" s="161" t="inlineStr">
+      <c r="B31" s="196" t="inlineStr">
         <is>
           <t>장바구니에서 뺌 (보유분 사용)</t>
         </is>
       </c>
-      <c r="C31" s="161" t="inlineStr">
+      <c r="C31" s="196" t="inlineStr">
         <is>
           <t>금 간식·아침</t>
         </is>
       </c>
-      <c r="D31" s="161" t="inlineStr">
+      <c r="D31" s="196" t="inlineStr">
         <is>
           <t>제외</t>
         </is>
       </c>
-      <c r="E31" s="162" t="n">
+      <c r="E31" s="197" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="161" t="inlineStr">
+    <row r="32" ht="42.8" customHeight="1" s="110">
+      <c r="A32" s="196" t="inlineStr">
         <is>
           <t>토마토 페이스트·빵가루·파마산·바질</t>
         </is>
       </c>
-      <c r="B32" s="161" t="inlineStr">
+      <c r="B32" s="196" t="inlineStr">
         <is>
           <t>보유분 확인 (없으면 생략 가능)</t>
         </is>
       </c>
-      <c r="C32" s="161" t="inlineStr">
+      <c r="C32" s="196" t="inlineStr">
         <is>
           <t>금 미트볼</t>
         </is>
       </c>
-      <c r="D32" s="161" t="inlineStr">
+      <c r="D32" s="196" t="inlineStr">
         <is>
           <t>보유 확인</t>
         </is>
       </c>
-      <c r="E32" s="162" t="n">
+      <c r="E32" s="197" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="161" t="inlineStr">
+    <row r="33" ht="25.4" customHeight="1" s="110">
+      <c r="A33" s="196" t="inlineStr">
         <is>
           <t>케첩·식초·미소된장·미림</t>
         </is>
       </c>
-      <c r="B33" s="161" t="inlineStr">
+      <c r="B33" s="196" t="inlineStr">
         <is>
           <t>보유분 확인</t>
         </is>
       </c>
-      <c r="C33" s="161" t="inlineStr">
+      <c r="C33" s="196" t="inlineStr">
         <is>
           <t>화 탕수·수 장국/오야코동</t>
         </is>
       </c>
-      <c r="D33" s="161" t="inlineStr">
+      <c r="D33" s="196" t="inlineStr">
         <is>
           <t>보유 확인</t>
         </is>
       </c>
-      <c r="E33" s="162" t="n">
+      <c r="E33" s="197" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="161" t="inlineStr">
+    <row r="34" ht="25.4" customHeight="1" s="110">
+      <c r="A34" s="196" t="inlineStr">
         <is>
           <t>튀김용 식용유</t>
         </is>
       </c>
-      <c r="B34" s="161" t="inlineStr">
+      <c r="B34" s="196" t="inlineStr">
         <is>
           <t>보유분 확인 (약 1L)</t>
         </is>
       </c>
-      <c r="C34" s="161" t="inlineStr">
+      <c r="C34" s="196" t="inlineStr">
         <is>
           <t>화 탕수</t>
         </is>
       </c>
-      <c r="D34" s="161" t="inlineStr">
+      <c r="D34" s="196" t="inlineStr">
         <is>
           <t>보유 확인</t>
         </is>
       </c>
-      <c r="E34" s="162" t="n">
+      <c r="E34" s="197" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="161" t="inlineStr">
+    <row r="35" ht="25.4" customHeight="1" s="110">
+      <c r="A35" s="196" t="inlineStr">
         <is>
           <t>어린이김치·김</t>
         </is>
       </c>
-      <c r="B35" s="161" t="inlineStr">
+      <c r="B35" s="196" t="inlineStr">
         <is>
           <t>보유분 확인</t>
         </is>
       </c>
-      <c r="C35" s="161" t="inlineStr">
+      <c r="C35" s="196" t="inlineStr">
         <is>
           <t>상시 반찬·아침</t>
         </is>
       </c>
-      <c r="D35" s="161" t="inlineStr">
+      <c r="D35" s="196" t="inlineStr">
         <is>
           <t>보유</t>
         </is>
       </c>
-      <c r="E35" s="162" t="n">
+      <c r="E35" s="197" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="161" t="inlineStr">
+    <row r="36" ht="25.4" customHeight="1" s="110">
+      <c r="A36" s="196" t="inlineStr">
         <is>
           <t>국물멸치·다시마·건새우·마른표고</t>
         </is>
       </c>
-      <c r="B36" s="161" t="inlineStr">
+      <c r="B36" s="196" t="inlineStr">
         <is>
           <t>보유분 확인</t>
         </is>
       </c>
-      <c r="C36" s="161" t="inlineStr">
+      <c r="C36" s="196" t="inlineStr">
         <is>
           <t>만능육수</t>
         </is>
       </c>
-      <c r="D36" s="161" t="inlineStr">
+      <c r="D36" s="196" t="inlineStr">
         <is>
           <t>보유</t>
         </is>
       </c>
-      <c r="E36" s="162" t="n">
+      <c r="E36" s="197" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="169" t="inlineStr">
+    <row r="37" ht="26" customHeight="1" s="110">
+      <c r="A37" s="202" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
       </c>
-      <c r="B37" s="169" t="n"/>
-      <c r="C37" s="169" t="inlineStr">
+      <c r="B37" s="202" t="n"/>
+      <c r="C37" s="202" t="inlineStr">
         <is>
           <t>10/26 장바구니 기준 (19개)</t>
         </is>
       </c>
-      <c r="D37" s="170" t="inlineStr">
-        <is>
-          <t>결제예정</t>
-        </is>
-      </c>
-      <c r="E37" s="171" t="n">
+      <c r="D37" s="202" t="n"/>
+      <c r="E37" s="203" t="n">
         <v>114270</v>
       </c>
     </row>

--- a/26년도_2주간_식단.xlsx
+++ b/26년도_2주간_식단.xlsx
@@ -606,7 +606,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="20">
+  <borders count="23">
     <border>
       <left/>
       <right/>
@@ -848,11 +848,44 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="204">
+  <cellXfs count="205">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1361,6 +1394,7 @@
     <xf numFmtId="3" fontId="24" fillId="46" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1618,49 +1652,42 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" style="110" min="1" max="1"/>
     <col width="68" customWidth="1" style="110" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" s="110">
-      <c r="A1" s="180" t="inlineStr">
-        <is>
-          <t>10월 5주차 식단 (10/27~10/30) · 장모님 오시는 주</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="70.55" customHeight="1" s="110">
-      <c r="A3" s="181" t="inlineStr">
+    <row r="1" ht="70.55" customHeight="1" s="110">
+      <c r="A1" s="181" t="inlineStr">
         <is>
           <t>화 (10/27)</t>
         </is>
       </c>
-      <c r="B3" s="182" t="inlineStr">
+      <c r="B1" s="182" t="inlineStr">
         <is>
           <t>대구 순살 탕수 (아이용 300g) + 양지 미역국 🧊냉동OK + 잔멸치볶음(칼슘) + 키즈김치 + 귤 (간식)
 ※ 생선 살리기 1탄·신메뉴 (튀김 7주 만)</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="22" customHeight="1" s="110">
-      <c r="A4" s="183" t="inlineStr">
+    <row r="2" ht="22" customHeight="1" s="110">
+      <c r="A2" s="183" t="inlineStr">
         <is>
           <t>🌙 전날 밤 준비</t>
         </is>
       </c>
-      <c r="B4" s="183" t="inlineStr">
+      <c r="B2" s="183" t="inlineStr">
         <is>
           <t>🔥 당일 조리</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="269" customHeight="1" s="110">
-      <c r="A5" s="184" t="inlineStr">
+    <row r="3" ht="265" customHeight="1" s="110">
+      <c r="A3" s="188" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1678,99 +1705,15 @@
               <sz val="12"/>
             </rPr>
             <t xml:space="preserve">   (검증: 만개 명태·가자미 탕수 + 일본 급식 白身魚の甘酢あん)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">   ※ 아이 2명분 300g (어른은 다른 반찬으로 대체)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">※ 월요일 주문분 냉동 대구는 화요일 아침 도착하면
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">  바로 냉장실(키친타월 깔고 덮어서)로 → 저녁까지 해동
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">  ※ 급하면 밀폐해 찬물 해동(30분마다 물 교체), 실온·온수 X
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">1. 소스 재료 계량해 한 통에:
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">   육수(또는 물) 100ml + 케첩 1.5T + 설탕 2t
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">   + 식초 1T + 소금 한 꼬집 + 간장 1/2t (색 밝게, 추정 비율)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">2. 당근 1/4개 · 양파 1/4개 · 오이 1/4개 채썰기 → 냉장
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">   ※ 전분 입히기는 당일에 (미리 하면 눅눅)</t>
-          </r>
-        </is>
-      </c>
-      <c r="B5" s="184" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <b val="1"/>
-              <color rgb="001F3864"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">★ 식사 50분 전 시작
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t>
+   ※ 아이 2명분 300g (어른은 다른 반찬으로 대체)
+※ 월요일 주문분 냉동 대구는 화요일 아침 도착하면
+  바로 냉장실(키친타월 깔고 덮어서)로 → 저녁까지 해동
+  ※ 급하면 밀폐해 찬물 해동(30분마다 물 교체), 실온·온수 X
+1. 소스 재료 계량해 한 통에:
+   육수(또는 물) 100ml + 케첩 1.5T + 설탕 2t
+   + 식초 1T + 소금 한 꼬집 + 간장 1/2t (색 밝게, 추정 비율)
+2. 당근 1/4개 · 양파 1/4개 · 오이 1/4개 채썰기 → 냉장
+   ※ 전분 입히기는 당일에 (미리 하면 눅눅)
 </t>
           </r>
           <r>
@@ -1780,7 +1723,63 @@
               <color rgb="001F3864"/>
               <sz val="12"/>
             </rPr>
-            <t xml:space="preserve">[양지 미역국 — 맨 먼저]
+            <t xml:space="preserve">[양지 미역국 — 🧊냉동OK · 수요일 아침 국밥용 포함]
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">3. 양지 200g 한입크기 → 끓는 물에 데쳐 핏물·기름 빼기 → 냉장
+4. 염장미역 1줌 반 → 물에 담가 짠기 빼고 불려 꼭 짜서
+   한입 크기로 → 냉장
+5. 만능육수 2L 만들어 식혀 냉장
+   (물 2L + 국물멸치 25마리 마른팬 30초 + 다시마
+    + 건새우 1줌 + 마른표고 2개 + 무 한토막)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <b val="1"/>
+              <color rgb="001F3864"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">[잔멸치볶음 — 칼슘]
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">6. 잔멸치 1컵 체에 쳐 가루 털고 마른팬에 살짝 볶기
+   / 아몬드 슬라이스 준비
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <b val="1"/>
+              <color rgb="001F3864"/>
+              <sz val="12"/>
+            </rPr>
+            <t>[키즈김치] 어린이김치 통 준비</t>
+          </r>
+        </is>
+      </c>
+      <c r="B3" s="188" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Malgun Gothic"/>
+              <b val="1"/>
+              <color rgb="001F3864"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">★ 식사 50분 전 시작
+[양지 미역국 — 맨 먼저]
 </t>
           </r>
           <r>
@@ -1789,54 +1788,11 @@
               <sz val="12"/>
             </rPr>
             <t xml:space="preserve">1. 냄비에 데친 양지 + 미역 + 국간장 1T → 1분 볶기
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">   (감칠맛 베이스) ※ 참기름은 향만 몇 방울
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">2. 육수 2L 붓고 중불 20분 → 뜨는 기름 걷기
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">3. 간: 국간장 1.5T + 액젓 1t + 다진마늘 1T → 소금
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">   ※ 기름 뺐다고 밍밍하면 실패! 맛보고 간 확실히
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">4. ★ 아침용 1/3 덜어 식혀 냉장 (수요일 아침 국밥)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t>
+   (감칠맛 베이스) ※ 참기름은 향만 몇 방울
+2. 육수 2L 붓고 중불 20분 → 뜨는 기름 걷기
+3. 간: 국간장 1.5T + 액젓 1t + 다진마늘 1T → 소금
+   ※ 기름 뺐다고 밍밍하면 실패! 맛보고 간 확실히
+4. ★ 아침용 1/3 덜어 식혀 냉장 (수요일 아침 국밥)
 </t>
           </r>
           <r>
@@ -1855,134 +1811,9 @@
               <sz val="12"/>
             </rPr>
             <t xml:space="preserve">5. 기름 살짝, 잔멸치 약불 1분 → 간장 1t + 올리고당 1T
+   + 맛술 1t 약불 30초 → 아몬드·통깨
 </t>
           </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">   + 맛술 1t 약불 30초 → 아몬드·통깨</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="286.4" customHeight="1" s="110">
-      <c r="A6" s="185" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <b val="1"/>
-              <color rgb="001F3864"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">[양지 미역국 — 🧊냉동OK · 수요일 아침 국밥용 포함]
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">3. 양지 200g 한입크기 → 끓는 물에 데쳐 핏물·기름 빼기 → 냉장
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">4. 염장미역 1줌 반 → 물에 담가 짠기 빼고 불려 꼭 짜서
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">   한입 크기로 → 냉장
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">5. 만능육수 2L 만들어 식혀 냉장
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">   (물 2L + 국물멸치 25마리 마른팬 30초 + 다시마
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">    + 건새우 1줌 + 마른표고 2개 + 무 한토막)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <b val="1"/>
-              <color rgb="001F3864"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">[잔멸치볶음 — 칼슘]
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">6. 잔멸치 1컵 체에 쳐 가루 털고 마른팬에 살짝 볶기
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">   / 아몬드 슬라이스 준비
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <b val="1"/>
-              <color rgb="001F3864"/>
-              <sz val="12"/>
-            </rPr>
-            <t>[키즈김치] 어린이김치 통 준비</t>
-          </r>
-        </is>
-      </c>
-      <c r="B6" s="185" t="inlineStr">
-        <is>
           <r>
             <rPr>
               <rFont val="Malgun Gothic"/>
@@ -1999,86 +1830,15 @@
               <sz val="12"/>
             </rPr>
             <t xml:space="preserve">6. 대구 3cm로 썰고 가시 확인 (5세 주의)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">7. ★ 우유 50ml에 10분 담갔다가 물기만 닦기 (비린내 제거)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">8. 소금 1/4t + 후추 + 청주 1/2T → 10분 → 키친타월로 물기 꼼꼼히
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">9. 달걀흰자 1T 버무리고 → 감자전분 약 50g 얇게 입혀 털기
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">10. 170℃ 기름에 1~2번 나눠 2~3분 (떠오를 때까지 건드리지 않기)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">    → 건져 잠깐 식혔다가 → 180℃에 30~60초 한 번 더 (바삭)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">    ※ 한 번에 많이 넣으면 기름 먹음 / 속 하얗게 익었는지 확인
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">11. 소스: 기름 1t에 채소 볶기 → 소스 붓고 끓으면
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">    전분 1/2T + 물 1T로 걸쭉하게 → 맛보고 시면 설탕 조금
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">12. ★ 튀김 위에 소스 끼얹기 (버무리면 눅눅) → 바로 식탁에
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t>
+7. ★ 우유 50ml에 10분 담갔다가 물기만 닦기 (비린내 제거)
+8. 소금 1/4t + 후추 + 청주 1/2T → 10분 → 키친타월로 물기 꼼꼼히
+9. 달걀흰자 1T 버무리고 → 감자전분 약 50g 얇게 입혀 털기
+10. 170℃ 기름에 1~2번 나눠 2~3분 (떠오를 때까지 건드리지 않기)
+    → 건져 잠깐 식혔다가 → 180℃에 30~60초 한 번 더 (바삭)
+    ※ 한 번에 많이 넣으면 기름 먹음 / 속 하얗게 익었는지 확인
+11. 소스: 기름 1t에 채소 볶기 → 소스 붓고 끓으면
+    전분 1/2T + 물 1T로 걸쭉하게 → 맛보고 시면 설탕 조금
+12. ★ 튀김 위에 소스 끼얹기 (버무리면 눅눅) → 바로 식탁에
 </t>
           </r>
           <r>
@@ -2093,33 +1853,38 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="70.55" customHeight="1" s="110">
-      <c r="A8" s="186" t="inlineStr">
+    <row r="4" ht="265" customHeight="1" s="110">
+      <c r="A4" s="204" t="n"/>
+      <c r="B4" s="204" t="n"/>
+    </row>
+    <row r="5" ht="8" customHeight="1" s="110"/>
+    <row r="6" ht="70.55" customHeight="1" s="110">
+      <c r="A6" s="186" t="inlineStr">
         <is>
           <t>수 (10/28)</t>
         </is>
       </c>
-      <c r="B8" s="187" t="inlineStr">
+      <c r="B6" s="187" t="inlineStr">
         <is>
           <t>오야코동 (닭+몽글한 달걀) + 두부 미소장국(칼슘) + 감자채볶음 + 키즈김치 + 배 (간식)
 ※ 호평 메뉴 10주 만·새우 달걀 덮밥 방식 적용</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="22" customHeight="1" s="110">
-      <c r="A9" s="183" t="inlineStr">
+    <row r="7" ht="22" customHeight="1" s="110">
+      <c r="A7" s="183" t="inlineStr">
         <is>
           <t>🌙 전날 밤 준비</t>
         </is>
       </c>
-      <c r="B9" s="183" t="inlineStr">
+      <c r="B7" s="183" t="inlineStr">
         <is>
           <t>🔥 당일 조리</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="373.4" customHeight="1" s="110">
-      <c r="A10" s="188" t="inlineStr">
+    <row r="8" ht="373.4" customHeight="1" s="110">
+      <c r="A8" s="188" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2137,54 +1902,11 @@
               <sz val="12"/>
             </rPr>
             <t xml:space="preserve">1. 닭다리살 500g → 껍질·노란 지방 떼고 1.5cm로 작게
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">   → 청주 1T + 소금 1/3t 밑간 → 냉장
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">2. 양파 1개 채썰기 / 대파 송송 → 냉장
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">3. 덮밥소스 한 통에: 만능육수 250ml + 간장 3T
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">   + 미림 2T + 설탕 1T
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">   (달걀 7개는 당일에 풀기)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t>
+   → 청주 1T + 소금 1/3t 밑간 → 냉장
+2. 양파 1개 채썰기 / 대파 송송 → 냉장
+3. 덮밥소스 한 통에: 만능육수 250ml + 간장 3T
+   + 미림 2T + 설탕 1T
+   (달걀 7개는 당일에 풀기)
 </t>
           </r>
           <r>
@@ -2208,14 +1930,6 @@
           <r>
             <rPr>
               <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
               <b val="1"/>
               <color rgb="001F3864"/>
               <sz val="12"/>
@@ -2234,14 +1948,6 @@
           <r>
             <rPr>
               <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
               <b val="1"/>
               <color rgb="001F3864"/>
               <sz val="12"/>
@@ -2250,7 +1956,7 @@
           </r>
         </is>
       </c>
-      <c r="B10" s="188" t="inlineStr">
+      <c r="B8" s="188" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2260,24 +1966,7 @@
               <sz val="12"/>
             </rPr>
             <t xml:space="preserve">★ 식사 30분 전 시작
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <b val="1"/>
-              <color rgb="001F3864"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">[두부 미소장국 — 먼저]
+[두부 미소장국 — 먼저]
 </t>
           </r>
           <r>
@@ -2286,30 +1975,8 @@
               <sz val="12"/>
             </rPr>
             <t xml:space="preserve">1. 육수 1L 끓이기 → 두부 넣고 3분
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">2. 불 약하게 → 미소된장 2.5T 체에 풀기
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">   ※ 미소는 끓이면 향 날아감, 넣고 바로 불 끄기 → 대파
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t>
+2. 불 약하게 → 미소된장 2.5T 체에 풀기
+   ※ 미소는 끓이면 향 날아감, 넣고 바로 불 끄기 → 대파
 </t>
           </r>
           <r>
@@ -2333,14 +2000,6 @@
           <r>
             <rPr>
               <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
               <b val="1"/>
               <color rgb="001F3864"/>
               <sz val="12"/>
@@ -2354,70 +2013,13 @@
               <sz val="12"/>
             </rPr>
             <t xml:space="preserve">4. 넓은 팬에 덮밥소스 + 양파 → 중불 3분 (양파 투명하게)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">5. 닭 넣고 뚜껑 덮어 중약불 5~6분 → 속까지 익었는지 확인
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">   ※ 닭이 작아서 금방 익음, 오래 끓이면 질겨짐
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">6. ★ 달걀 7개 가볍게 풀어(흰자 덩어리 조금 남게)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">   → 2/3 먼저 둘러 붓고 뚜껑 30초
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">   → 나머지 1/3 붓고 불 끄기 → 뚜껑 덮어 1분 (잔열로 몽글)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">   ※ 아이 것은 흐르지 않게 / 어른 것은 촉촉하게
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">7. 밥 위에 국자로 떠 올리고 소스 조금 → 대파
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t>
+5. 닭 넣고 뚜껑 덮어 중약불 5~6분 → 속까지 익었는지 확인
+   ※ 닭이 작아서 금방 익음, 오래 끓이면 질겨짐
+6. ★ 달걀 7개 가볍게 풀어(흰자 덩어리 조금 남게)
+   → 2/3 먼저 둘러 붓고 뚜껑 30초
+   → 나머지 1/3 붓고 불 끄기 → 뚜껑 덮어 1분 (잔열로 몽글)
+   ※ 아이 것은 흐르지 않게 / 어른 것은 촉촉하게
+7. 밥 위에 국자로 떠 올리고 소스 조금 → 대파
 </t>
           </r>
           <r>
@@ -2432,33 +2034,34 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="70.55" customHeight="1" s="110">
-      <c r="A12" s="189" t="inlineStr">
+    <row r="9" ht="8" customHeight="1" s="110"/>
+    <row r="10" ht="70.55" customHeight="1" s="110">
+      <c r="A10" s="189" t="inlineStr">
         <is>
           <t>금 (10/30)</t>
         </is>
       </c>
-      <c r="B12" s="190" t="inlineStr">
+      <c r="B10" s="190" t="inlineStr">
         <is>
           <t>돼지고기 미트볼 토마토 파스타 + 옥수수 스프 + 키즈김치 + 단감 (간식)
 ※ 이갈이 S등급·신메뉴·치즈주1회(칼슘)</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="22" customHeight="1" s="110">
-      <c r="A13" s="183" t="inlineStr">
+    <row r="11" ht="22" customHeight="1" s="110">
+      <c r="A11" s="183" t="inlineStr">
         <is>
           <t>🌙 전날 밤 준비</t>
         </is>
       </c>
-      <c r="B13" s="183" t="inlineStr">
+      <c r="B11" s="183" t="inlineStr">
         <is>
           <t>🔥 당일 조리</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="408.2" customHeight="1" s="110">
-      <c r="A14" s="184" t="inlineStr">
+    <row r="12" ht="221.5" customHeight="1" s="110">
+      <c r="A12" s="188" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2466,22 +2069,7 @@
               <sz val="12"/>
             </rPr>
             <t xml:space="preserve">※ 돼지 다짐육: 월요일 주문분 → 받자마자 냉동,
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">  목요일 아침 냉장실로 옮겨 해동
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t>
+  목요일 아침 냉장실로 옮겨 해동
 </t>
           </r>
           <r>
@@ -2500,86 +2088,15 @@
               <sz val="12"/>
             </rPr>
             <t xml:space="preserve">   (검증: 만개의레시피·DELISH KITCHEN 등 4곳)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">1. 빵가루 6T + 우유 5T 5분 불리기 + 두부 100g
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">   (면보로 꼭 짜서 으깨기) → 섞기 (촉촉함의 핵심)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">2. 양파 1/2개 다져 전자레인지 1분 → 식히기
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">3. 볼에 돼지 다짐육 500g + ①② + 달걀 1개
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">   + 소금 3/4t + 후추 + 드라이 바질 1/2t + 파마산 3T(선택)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">   → 한 방향으로 점성 생길 때까지만 섞기
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">   ※ 오래 치대면 단단해짐
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">4. 지름 2.5~3cm로 빚어 접시에 한 겹 → 랩 → 냉장 맨 아래 칸
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">   ※ 날고기 반죽은 24시간 내 사용
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t>
+1. 빵가루 6T + 우유 5T 5분 불리기 + 두부 100g
+   (면보로 꼭 짜서 으깨기) → 섞기 (촉촉함의 핵심)
+2. 양파 1/2개 다져 전자레인지 1분 → 식히기
+3. 볼에 돼지 다짐육 500g + ①② + 달걀 1개
+   + 소금 3/4t + 후추 + 드라이 바질 1/2t + 파마산 3T(선택)
+   → 한 방향으로 점성 생길 때까지만 섞기
+   ※ 오래 치대면 단단해짐
+4. 지름 2.5~3cm로 빚어 접시에 한 겹 → 랩 → 냉장 맨 아래 칸
+   ※ 날고기 반죽은 24시간 내 사용
 </t>
           </r>
           <r>
@@ -2603,14 +2120,6 @@
           <r>
             <rPr>
               <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
               <b val="1"/>
               <color rgb="001F3864"/>
               <sz val="12"/>
@@ -2619,7 +2128,7 @@
           </r>
         </is>
       </c>
-      <c r="B14" s="184" t="inlineStr">
+      <c r="B12" s="188" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2629,24 +2138,7 @@
               <sz val="12"/>
             </rPr>
             <t xml:space="preserve">★ 식사 40분 전 시작
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <b val="1"/>
-              <color rgb="001F3864"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">[미트볼 — 굽기] (팬 또는 에어프라이어)
+[미트볼 — 굽기] (팬 또는 에어프라이어)
 </t>
           </r>
           <r>
@@ -2655,62 +2147,12 @@
               <sz val="12"/>
             </rPr>
             <t xml:space="preserve">1. 스텐팬 중불 예열(물방울 테스트) + 기름 2T
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">   → 2번에 나눠 굽기, 처음 1~2분 건드리지 않기
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">   (겉이 익으면 저절로 떨어짐) → 겉만 갈색이면 OK
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">   ※ 에어프라이어: 180℃ 8분 → 뒤집어 3~4분
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">2. 같은 팬에 순한 토마토소스 500g + 토마토 페이스트 1T
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">   + 물 100ml + 설탕 1t → 미트볼 넣고 뚜껑, 약불 15분
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">   (에어프라이어로 구웠으면 5~10분 더 끓이기)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t>
+   → 2번에 나눠 굽기, 처음 1~2분 건드리지 않기
+   (겉이 익으면 저절로 떨어짐) → 겉만 갈색이면 OK
+   ※ 에어프라이어: 180℃ 8분 → 뒤집어 3~4분
+2. 같은 팬에 순한 토마토소스 500g + 토마토 페이스트 1T
+   + 물 100ml + 설탕 1t → 미트볼 넣고 뚜껑, 약불 15분
+   (에어프라이어로 구웠으면 5~10분 더 끓이기)
 </t>
           </r>
           <r>
@@ -2729,38 +2171,9 @@
               <sz val="12"/>
             </rPr>
             <t xml:space="preserve">3. 올리브유 1t에 양파 투명하게 → 콘 + 물 250ml 5분
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">4. 믹서로 곱게 → 아이용은 체에 한 번 거르기
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">5. 냄비에 우유 400ml 넣고 약불로 데우기 (끓어 넘치지 않게)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">   → 소금 1/3t, 필요하면 설탕 한 꼬집
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t>
+4. 믹서로 곱게 → 아이용은 체에 한 번 거르기
+5. 냄비에 우유 400ml 넣고 약불로 데우기 (끓어 넘치지 않게)
+   → 소금 1/3t, 필요하면 설탕 한 꼬집
 </t>
           </r>
           <r>
@@ -2779,46 +2192,12 @@
               <sz val="12"/>
             </rPr>
             <t xml:space="preserve">6. 물 3L + 소금 1.5T, 펜네 400g → 포장 시간보다 1분 덜
+7. 면을 소스 팬에 넣고 모짜렐라 100g과 2~3분 섞기
+   (되직하면 면수 조금)
+8. 남은 모짜렐라 50g 올리고 뚜껑 덮어 녹이기
+   ※ 미트볼 하나 잘라 속 익었는지 확인
 </t>
           </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">7. 면을 소스 팬에 넣고 모짜렐라 100g과 2~3분 섞기
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">   (되직하면 면수 조금)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">8. 남은 모짜렐라 50g 올리고 뚜껑 덮어 녹이기
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">   ※ 미트볼 하나 잘라 속 익었는지 확인</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="25.4" customHeight="1" s="110">
-      <c r="A15" s="185" t="inlineStr"/>
-      <c r="B15" s="185" t="inlineStr">
-        <is>
           <r>
             <rPr>
               <rFont val="Malgun Gothic"/>
@@ -2831,33 +2210,38 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="70.55" customHeight="1" s="110">
-      <c r="A17" s="191" t="inlineStr">
+    <row r="13" ht="221.5" customHeight="1" s="110">
+      <c r="A13" s="204" t="n"/>
+      <c r="B13" s="204" t="n"/>
+    </row>
+    <row r="14" ht="8" customHeight="1" s="110"/>
+    <row r="15" ht="70.55" customHeight="1" s="110">
+      <c r="A15" s="191" t="inlineStr">
         <is>
           <t>아침 (수·토·일)</t>
         </is>
       </c>
-      <c r="B17" s="192" t="inlineStr">
+      <c r="B15" s="192" t="inlineStr">
         <is>
           <t>🌅 아침 (장모님 오시는 주) + 수: 미역국 국밥 + 토: 그릭요거트+그래놀라 + 일: 고구마밥
 ※ 월·화·목·금은 장모님</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="22" customHeight="1" s="110">
-      <c r="A18" s="183" t="inlineStr">
+    <row r="16" ht="22" customHeight="1" s="110">
+      <c r="A16" s="183" t="inlineStr">
         <is>
           <t>🌙 전날 밤 준비</t>
         </is>
       </c>
-      <c r="B18" s="183" t="inlineStr">
+      <c r="B16" s="183" t="inlineStr">
         <is>
           <t>🔥 당일 조리</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="234.2" customHeight="1" s="110">
-      <c r="A19" s="188" t="inlineStr">
+    <row r="17" ht="199.4" customHeight="1" s="110">
+      <c r="A17" s="188" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2880,37 +2264,12 @@
           <r>
             <rPr>
               <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
               <b val="1"/>
               <color rgb="001F3864"/>
               <sz val="12"/>
             </rPr>
             <t xml:space="preserve">[금 밤] 과일 씻어 두기 (토 아침 꺼내기만)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <b val="1"/>
-              <color rgb="001F3864"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">[토 밤] 쌀 씻어 안치고 고구마 1개(지난주 남은 것) 깍둑썰어
+[토 밤] 쌀 씻어 안치고 고구마 1개(지난주 남은 것) 깍둑썰어
 </t>
           </r>
           <r>
@@ -2919,50 +2278,14 @@
               <sz val="12"/>
             </rPr>
             <t xml:space="preserve">         올려 예약취사 (일 아침 시간에 맞춰)
-</t>
+         ※ 고구마 없으면 일요일은 시리얼+우유+과일
+         ※ 날고기·달걀은 예약취사에 넣지 않기
+※ 월·목 밤 "내일 아침 국 있나?" 확인
+   → 없으면 냉동 국팩(🧊) 언 채로 냄비 + 물 100ml</t>
           </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">         ※ 고구마 없으면 일요일은 시리얼+우유+과일
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">         ※ 날고기·달걀은 예약취사에 넣지 않기
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">※ 월·목 밤 "내일 아침 국 있나?" 확인
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">   → 없으면 냉동 국팩(🧊) 언 채로 냄비 + 물 100ml</t>
-          </r>
-        </is>
-      </c>
-      <c r="B19" s="188" t="inlineStr">
+        </is>
+      </c>
+      <c r="B17" s="188" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2980,38 +2303,9 @@
               <sz val="12"/>
             </rPr>
             <t xml:space="preserve">1. 미역국 먹을 만큼 냄비에 → 팔팔 끓으면 찬밥 2분
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">2. 달걀 1~2개 풀어 30초
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">3. 키즈김치 · 김 · 우유 1컵
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">※ 아이 그릇은 국물 반, 건더기·밥 위주
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t>
+2. 달걀 1~2개 풀어 30초
+3. 키즈김치 · 김 · 우유 1컵
+※ 아이 그릇은 국물 반, 건더기·밥 위주
 </t>
           </r>
           <r>
@@ -3035,14 +2329,6 @@
           <r>
             <rPr>
               <rFont val="Malgun Gothic"/>
-              <sz val="12"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Malgun Gothic"/>
               <b val="1"/>
               <color rgb="001F3864"/>
               <sz val="12"/>
@@ -3060,12 +2346,29 @@
         </is>
       </c>
     </row>
+    <row r="18" ht="8" customHeight="1" s="110"/>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
+  <mergeCells count="4">
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="A12:A13"/>
   </mergeCells>
-  <pageMargins left="0.4" right="0.4" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.4" header="0.25" footer="0.2"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="81" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Malgun Gothic,Bold"&amp;11 10월 5주차 식단 (10/27~10/30) · 장모님 오시는 주</oddHeader>
+    <oddFooter/>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <rowBreaks count="3" manualBreakCount="3">
+    <brk id="5" min="0" max="16383" man="1"/>
+    <brk id="9" min="0" max="16383" man="1"/>
+    <brk id="14" min="0" max="16383" man="1"/>
+  </rowBreaks>
 </worksheet>
 </file>
 
@@ -8401,7 +7704,7 @@
     <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
 
